--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>atk_f407</t>
   </si>
@@ -62,19 +62,22 @@
     <t>port.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal.o</t>
+  </si>
+  <si>
+    <t>mc_w.l</t>
+  </si>
+  <si>
+    <t>stdout.o</t>
+  </si>
+  <si>
+    <t>system_stm32f4xx.o</t>
+  </si>
+  <si>
+    <t>led_task.o</t>
+  </si>
+  <si>
     <t>freertos_start.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal.o</t>
-  </si>
-  <si>
-    <t>mc_w.l</t>
-  </si>
-  <si>
-    <t>stdout.o</t>
-  </si>
-  <si>
-    <t>system_stm32f4xx.o</t>
   </si>
   <si>
     <t>delay.o</t>
@@ -329,9 +332,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$67</c:f>
+              <c:f>ram_percent!$A$3:$A$68</c:f>
               <c:strCache>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -375,27 +378,30 @@
                   <c:v>port.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>stm32f4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>mc_w.l</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>stdout.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>system_stm32f4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>led_task.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>stm32f4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>mc_w.l</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>stdout.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>system_stm32f4xx.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -403,74 +409,77 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$67</c:f>
+              <c:f>ram_percent!$B$3:$B$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
-                  <c:v>54.96340179443359</c:v>
+                  <c:v>54.96585845947266</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.94731140136719</c:v>
+                  <c:v>38.94905090332031</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.510867714881897</c:v>
+                  <c:v>1.510935306549072</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.154383420944214</c:v>
+                  <c:v>1.154435038566589</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.144325852394104</c:v>
+                  <c:v>1.144376993179321</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8984746336936951</c:v>
+                  <c:v>0.8985147476196289</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3732469081878662</c:v>
+                  <c:v>0.3732635974884033</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3028440475463867</c:v>
+                  <c:v>0.3028575778007507</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3028440475463867</c:v>
+                  <c:v>0.3028575778007507</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1050455346703529</c:v>
+                  <c:v>0.1050502359867096</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1028105244040489</c:v>
+                  <c:v>0.1028151214122772</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0715203657746315</c:v>
+                  <c:v>0.07152356207370758</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06705034524202347</c:v>
+                  <c:v>0.06705334037542343</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01341006904840469</c:v>
+                  <c:v>0.01341066788882017</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01341006904840469</c:v>
+                  <c:v>0.01005800068378449</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01005755178630352</c:v>
+                  <c:v>0.004470222629606724</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004470222629606724</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004470222629606724</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004470222629606724</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004470222629606724</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.001117505715228617</c:v>
-                </c:pt>
-                <c:pt idx="64">
+                  <c:v>0.004470222629606724</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.001117555657401681</c:v>
+                </c:pt>
+                <c:pt idx="65">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -538,9 +547,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$67</c:f>
+              <c:f>flash_percent!$A$3:$A$68</c:f>
               <c:strCache>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
@@ -644,19 +653,19 @@
                   <c:v>depilogue.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>freertos_start.o</c:v>
+                  <c:v>delay.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>delay.o</c:v>
+                  <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>usbd_ioreq.o</c:v>
+                  <c:v>led.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>led.o</c:v>
+                  <c:v>list.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>list.o</c:v>
+                  <c:v>led_task.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>uldiv.o</c:v>
@@ -671,69 +680,72 @@
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
                 <c:pt idx="43">
+                  <c:v>freertos_start.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>fputc.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -741,203 +753,206 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$67</c:f>
+              <c:f>flash_percent!$B$3:$B$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="66"/>
                 <c:pt idx="0">
-                  <c:v>25.50276184082031</c:v>
+                  <c:v>25.50079917907715</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.686238288879395</c:v>
+                  <c:v>7.685646533966065</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.293651103973389</c:v>
+                  <c:v>7.293089866638184</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.212112426757813</c:v>
+                  <c:v>6.211634159088135</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.249889373779297</c:v>
+                  <c:v>5.249485015869141</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.268421649932861</c:v>
+                  <c:v>4.268093109130859</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.162577152252197</c:v>
+                  <c:v>4.162256717681885</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.502492189407349</c:v>
+                  <c:v>3.502222537994385</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.456305503845215</c:v>
+                  <c:v>3.456039428710938</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.029078483581543</c:v>
+                  <c:v>3.028845310211182</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.40363335609436</c:v>
+                  <c:v>2.403448343276978</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.259299993515015</c:v>
+                  <c:v>2.259125947952271</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.197717666625977</c:v>
+                  <c:v>2.197548389434815</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.120739698410034</c:v>
+                  <c:v>2.120576620101929</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.932144045829773</c:v>
+                  <c:v>1.931995272636414</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.693512678146362</c:v>
+                  <c:v>1.693382382392883</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.591517090797424</c:v>
+                  <c:v>1.591394543647766</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.458730220794678</c:v>
+                  <c:v>1.458617925643921</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.108481049537659</c:v>
+                  <c:v>1.10839569568634</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.016107559204102</c:v>
+                  <c:v>1.016029357910156</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9853164553642273</c:v>
+                  <c:v>0.985240638256073</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8544541597366333</c:v>
+                  <c:v>0.8543883562088013</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8371341228485107</c:v>
+                  <c:v>0.8370696902275085</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8236629962921143</c:v>
+                  <c:v>0.8235995769500732</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6620094776153565</c:v>
+                  <c:v>0.6619585752487183</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6427650451660156</c:v>
+                  <c:v>0.6427155733108521</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6158227920532227</c:v>
+                  <c:v>0.6157754063606262</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.4464715421199799</c:v>
+                  <c:v>0.4464371502399445</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.4387737512588501</c:v>
+                  <c:v>0.4387399554252625</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4291515052318573</c:v>
+                  <c:v>0.4291184842586517</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4272270798683167</c:v>
+                  <c:v>0.4271941781044006</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4041337072849274</c:v>
+                  <c:v>0.4041025936603546</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3925870358943939</c:v>
+                  <c:v>0.3925568163394928</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3579469919204712</c:v>
+                  <c:v>0.357919454574585</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3540981113910675</c:v>
+                  <c:v>0.3386764824390411</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.338702529668808</c:v>
+                  <c:v>0.3348278701305389</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3348536491394043</c:v>
+                  <c:v>0.2924933135509491</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2925158143043518</c:v>
+                  <c:v>0.2847961187362671</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2848180532455444</c:v>
+                  <c:v>0.2001270055770874</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1885957270860672</c:v>
+                  <c:v>0.1885812133550644</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1732001602649689</c:v>
+                  <c:v>0.1731868237257004</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.169351264834404</c:v>
+                  <c:v>0.1693382412195206</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1655023694038391</c:v>
+                  <c:v>0.1654896438121796</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1462579071521759</c:v>
+                  <c:v>0.1616410464048386</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09622231125831604</c:v>
+                  <c:v>0.1462466567754746</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.09237341582775116</c:v>
+                  <c:v>0.0962149053812027</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.09237341582775116</c:v>
+                  <c:v>0.09236630797386169</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.09237341582775116</c:v>
+                  <c:v>0.09236630797386169</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.084675632417202</c:v>
+                  <c:v>0.09236630797386169</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.06928006559610367</c:v>
+                  <c:v>0.08466912060976028</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.06928006559610367</c:v>
+                  <c:v>0.06927473098039627</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.06928006559610367</c:v>
+                  <c:v>0.06927473098039627</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.06928006559610367</c:v>
+                  <c:v>0.06927473098039627</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.06158227846026421</c:v>
+                  <c:v>0.06927473098039627</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.05773338675498962</c:v>
+                  <c:v>0.06157753989100456</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.05773338675498962</c:v>
+                  <c:v>0.05772894248366356</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.05003560334444046</c:v>
+                  <c:v>0.05772894248366356</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.03848892450332642</c:v>
+                  <c:v>0.05003175139427185</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.03464003279805183</c:v>
+                  <c:v>0.03848596289753914</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.01539556961506605</c:v>
+                  <c:v>0.03463736549019814</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.01539556961506605</c:v>
+                  <c:v>0.01539438497275114</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.007697784807533026</c:v>
+                  <c:v>0.01539438497275114</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.007697784807533026</c:v>
+                  <c:v>0.00769719248637557</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.007697784807533026</c:v>
+                  <c:v>0.00769719248637557</c:v>
                 </c:pt>
                 <c:pt idx="64">
+                  <c:v>0.00769719248637557</c:v>
+                </c:pt>
+                <c:pt idx="65">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1042,8 +1057,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H67" totalsRowCount="1">
-  <autoFilter ref="A2:H66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H68" totalsRowCount="1">
+  <autoFilter ref="A2:H67"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1059,8 +1074,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H67" totalsRowCount="1">
-  <autoFilter ref="A2:H66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H68" totalsRowCount="1">
+  <autoFilter ref="A2:H67"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1360,7 +1375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1373,28 +1388,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1402,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>54.96340179443359</v>
+        <v>54.96585845947266</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -1428,7 +1443,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>38.94731140136719</v>
+        <v>38.94905090332031</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -1454,7 +1469,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.510867714881897</v>
+        <v>1.510935306549072</v>
       </c>
       <c r="C5" s="1">
         <v>1352</v>
@@ -1480,7 +1495,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.154383420944214</v>
+        <v>1.154435038566589</v>
       </c>
       <c r="C6" s="1">
         <v>1033</v>
@@ -1506,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.144325852394104</v>
+        <v>1.144376993179321</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1532,7 +1547,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.8984746336936951</v>
+        <v>0.8985147476196289</v>
       </c>
       <c r="C8" s="1">
         <v>804</v>
@@ -1558,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.3732469081878662</v>
+        <v>0.3732635974884033</v>
       </c>
       <c r="C9" s="1">
         <v>334</v>
@@ -1584,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3028440475463867</v>
+        <v>0.3028575778007507</v>
       </c>
       <c r="C10" s="1">
         <v>271</v>
@@ -1610,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3028440475463867</v>
+        <v>0.3028575778007507</v>
       </c>
       <c r="C11" s="1">
         <v>271</v>
@@ -1636,7 +1651,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1050455346703529</v>
+        <v>0.1050502359867096</v>
       </c>
       <c r="C12" s="1">
         <v>94</v>
@@ -1662,7 +1677,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1028105244040489</v>
+        <v>0.1028151214122772</v>
       </c>
       <c r="C13" s="1">
         <v>92</v>
@@ -1688,7 +1703,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0715203657746315</v>
+        <v>0.07152356207370758</v>
       </c>
       <c r="C14" s="1">
         <v>64</v>
@@ -1714,7 +1729,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06705034524202347</v>
+        <v>0.06705334037542343</v>
       </c>
       <c r="C15" s="1">
         <v>60</v>
@@ -1740,7 +1755,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01341006904840469</v>
+        <v>0.01341066788882017</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
@@ -1766,22 +1781,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01341006904840469</v>
+        <v>0.01005800068378449</v>
       </c>
       <c r="C17" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="E17" s="1">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1792,22 +1807,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01005755178630352</v>
+        <v>0.004470222629606724</v>
       </c>
       <c r="C18" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>223</v>
+        <v>2728</v>
       </c>
       <c r="E18" s="1">
-        <v>214</v>
+        <v>2724</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1818,16 +1833,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004470222629606724</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>2728</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1">
-        <v>2724</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1844,19 +1859,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004470222629606724</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1">
         <v>4</v>
@@ -1870,19 +1885,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004470222629606724</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="E21" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
@@ -1896,16 +1911,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004470222629606724</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1922,56 +1937,82 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.001117505715228617</v>
+        <v>0.004470222629606724</v>
       </c>
       <c r="C23" s="1">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1">
+        <v>176</v>
+      </c>
+      <c r="E23" s="1">
+        <v>172</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.001117555657401681</v>
+      </c>
+      <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>2163</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E24" s="1">
         <v>2162</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
         <v>1</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67">
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E67">
+      <c r="E68">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F67">
+      <c r="F68">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G67">
+      <c r="G68">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H67">
+      <c r="H68">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1987,7 +2028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2000,28 +2041,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2029,7 +2070,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>25.50276184082031</v>
+        <v>25.50079917907715</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2055,7 +2096,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>7.686238288879395</v>
+        <v>7.685646533966065</v>
       </c>
       <c r="C4" s="1">
         <v>3994</v>
@@ -2078,10 +2119,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>7.293651103973389</v>
+        <v>7.293089866638184</v>
       </c>
       <c r="C5" s="1">
         <v>3790</v>
@@ -2104,10 +2145,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>6.212112426757813</v>
+        <v>6.211634159088135</v>
       </c>
       <c r="C6" s="1">
         <v>3228</v>
@@ -2130,10 +2171,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>5.249889373779297</v>
+        <v>5.249485015869141</v>
       </c>
       <c r="C7" s="1">
         <v>2728</v>
@@ -2156,10 +2197,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
-        <v>4.268421649932861</v>
+        <v>4.268093109130859</v>
       </c>
       <c r="C8" s="1">
         <v>2218</v>
@@ -2182,10 +2223,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
-        <v>4.162577152252197</v>
+        <v>4.162256717681885</v>
       </c>
       <c r="C9" s="1">
         <v>2163</v>
@@ -2208,10 +2249,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>3.502492189407349</v>
+        <v>3.502222537994385</v>
       </c>
       <c r="C10" s="1">
         <v>1820</v>
@@ -2234,10 +2275,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>3.456305503845215</v>
+        <v>3.456039428710938</v>
       </c>
       <c r="C11" s="1">
         <v>1796</v>
@@ -2263,7 +2304,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>3.029078483581543</v>
+        <v>3.028845310211182</v>
       </c>
       <c r="C12" s="1">
         <v>1574</v>
@@ -2289,7 +2330,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>2.40363335609436</v>
+        <v>2.403448343276978</v>
       </c>
       <c r="C13" s="1">
         <v>1249</v>
@@ -2315,7 +2356,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>2.259299993515015</v>
+        <v>2.259125947952271</v>
       </c>
       <c r="C14" s="1">
         <v>1174</v>
@@ -2338,10 +2379,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2">
-        <v>2.197717666625977</v>
+        <v>2.197548389434815</v>
       </c>
       <c r="C15" s="1">
         <v>1142</v>
@@ -2367,7 +2408,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>2.120739698410034</v>
+        <v>2.120576620101929</v>
       </c>
       <c r="C16" s="1">
         <v>1102</v>
@@ -2390,10 +2431,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2">
-        <v>1.932144045829773</v>
+        <v>1.931995272636414</v>
       </c>
       <c r="C17" s="1">
         <v>1004</v>
@@ -2419,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>1.693512678146362</v>
+        <v>1.693382382392883</v>
       </c>
       <c r="C18" s="1">
         <v>880</v>
@@ -2445,7 +2486,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>1.591517090797424</v>
+        <v>1.591394543647766</v>
       </c>
       <c r="C19" s="1">
         <v>827</v>
@@ -2468,10 +2509,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2">
-        <v>1.458730220794678</v>
+        <v>1.458617925643921</v>
       </c>
       <c r="C20" s="1">
         <v>758</v>
@@ -2497,7 +2538,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="2">
-        <v>1.108481049537659</v>
+        <v>1.10839569568634</v>
       </c>
       <c r="C21" s="1">
         <v>576</v>
@@ -2520,10 +2561,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="2">
-        <v>1.016107559204102</v>
+        <v>1.016029357910156</v>
       </c>
       <c r="C22" s="1">
         <v>528</v>
@@ -2549,7 +2590,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9853164553642273</v>
+        <v>0.985240638256073</v>
       </c>
       <c r="C23" s="1">
         <v>512</v>
@@ -2575,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8544541597366333</v>
+        <v>0.8543883562088013</v>
       </c>
       <c r="C24" s="1">
         <v>444</v>
@@ -2601,7 +2642,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8371341228485107</v>
+        <v>0.8370696902275085</v>
       </c>
       <c r="C25" s="1">
         <v>435</v>
@@ -2627,7 +2668,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8236629962921143</v>
+        <v>0.8235995769500732</v>
       </c>
       <c r="C26" s="1">
         <v>428</v>
@@ -2650,10 +2691,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6620094776153565</v>
+        <v>0.6619585752487183</v>
       </c>
       <c r="C27" s="1">
         <v>344</v>
@@ -2676,10 +2717,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6427650451660156</v>
+        <v>0.6427155733108521</v>
       </c>
       <c r="C28" s="1">
         <v>334</v>
@@ -2705,7 +2746,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6158227920532227</v>
+        <v>0.6157754063606262</v>
       </c>
       <c r="C29" s="1">
         <v>320</v>
@@ -2728,10 +2769,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2">
-        <v>0.4464715421199799</v>
+        <v>0.4464371502399445</v>
       </c>
       <c r="C30" s="1">
         <v>232</v>
@@ -2754,10 +2795,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2">
-        <v>0.4387737512588501</v>
+        <v>0.4387399554252625</v>
       </c>
       <c r="C31" s="1">
         <v>228</v>
@@ -2780,10 +2821,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4291515052318573</v>
+        <v>0.4291184842586517</v>
       </c>
       <c r="C32" s="1">
         <v>223</v>
@@ -2806,10 +2847,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4272270798683167</v>
+        <v>0.4271941781044006</v>
       </c>
       <c r="C33" s="1">
         <v>222</v>
@@ -2832,10 +2873,10 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4041337072849274</v>
+        <v>0.4041025936603546</v>
       </c>
       <c r="C34" s="1">
         <v>210</v>
@@ -2858,10 +2899,10 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3925870358943939</v>
+        <v>0.3925568163394928</v>
       </c>
       <c r="C35" s="1">
         <v>204</v>
@@ -2884,10 +2925,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3579469919204712</v>
+        <v>0.357919454574585</v>
       </c>
       <c r="C36" s="1">
         <v>186</v>
@@ -2910,16 +2951,16 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3540981113910675</v>
+        <v>0.3386764824390411</v>
       </c>
       <c r="C37" s="1">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D37" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E37" s="1">
         <v>172</v>
@@ -2928,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -2936,25 +2977,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0.338702529668808</v>
+        <v>0.3348278701305389</v>
       </c>
       <c r="C38" s="1">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D38" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -2962,19 +3003,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3348536491394043</v>
+        <v>0.2924933135509491</v>
       </c>
       <c r="C39" s="1">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2988,19 +3029,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2925158143043518</v>
+        <v>0.2847961187362671</v>
       </c>
       <c r="C40" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3014,25 +3055,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2848180532455444</v>
+        <v>0.2001270055770874</v>
       </c>
       <c r="C41" s="1">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3040,10 +3081,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1885957270860672</v>
+        <v>0.1885812133550644</v>
       </c>
       <c r="C42" s="1">
         <v>98</v>
@@ -3066,10 +3107,10 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1732001602649689</v>
+        <v>0.1731868237257004</v>
       </c>
       <c r="C43" s="1">
         <v>90</v>
@@ -3092,10 +3133,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>0.169351264834404</v>
+        <v>0.1693382412195206</v>
       </c>
       <c r="C44" s="1">
         <v>88</v>
@@ -3118,10 +3159,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1655023694038391</v>
+        <v>0.1654896438121796</v>
       </c>
       <c r="C45" s="1">
         <v>86</v>
@@ -3144,25 +3185,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B46" s="2">
-        <v>0.1462579071521759</v>
+        <v>0.1616410464048386</v>
       </c>
       <c r="C46" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3173,16 +3214,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09622231125831604</v>
+        <v>0.1462466567754746</v>
       </c>
       <c r="C47" s="1">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3199,16 +3240,16 @@
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.09237341582775116</v>
+        <v>0.0962149053812027</v>
       </c>
       <c r="C48" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3225,7 +3266,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.09237341582775116</v>
+        <v>0.09236630797386169</v>
       </c>
       <c r="C49" s="1">
         <v>48</v>
@@ -3248,25 +3289,25 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.09237341582775116</v>
+        <v>0.09236630797386169</v>
       </c>
       <c r="C50" s="1">
         <v>48</v>
       </c>
       <c r="D50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F50" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -3274,25 +3315,25 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B51" s="2">
-        <v>0.084675632417202</v>
+        <v>0.09236630797386169</v>
       </c>
       <c r="C51" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E51" s="1">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -3303,16 +3344,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.06928006559610367</v>
+        <v>0.08466912060976028</v>
       </c>
       <c r="C52" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3329,7 +3370,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.06928006559610367</v>
+        <v>0.06927473098039627</v>
       </c>
       <c r="C53" s="1">
         <v>36</v>
@@ -3355,7 +3396,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.06928006559610367</v>
+        <v>0.06927473098039627</v>
       </c>
       <c r="C54" s="1">
         <v>36</v>
@@ -3381,7 +3422,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.06928006559610367</v>
+        <v>0.06927473098039627</v>
       </c>
       <c r="C55" s="1">
         <v>36</v>
@@ -3407,16 +3448,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.06158227846026421</v>
+        <v>0.06927473098039627</v>
       </c>
       <c r="C56" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3433,16 +3474,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.05773338675498962</v>
+        <v>0.06157753989100456</v>
       </c>
       <c r="C57" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3459,7 +3500,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.05773338675498962</v>
+        <v>0.05772894248366356</v>
       </c>
       <c r="C58" s="1">
         <v>30</v>
@@ -3485,16 +3526,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.05003560334444046</v>
+        <v>0.05772894248366356</v>
       </c>
       <c r="C59" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3511,16 +3552,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.03848892450332642</v>
+        <v>0.05003175139427185</v>
       </c>
       <c r="C60" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3537,16 +3578,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>0.03464003279805183</v>
+        <v>0.03848596289753914</v>
       </c>
       <c r="C61" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3563,16 +3604,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="2">
-        <v>0.01539556961506605</v>
+        <v>0.03463736549019814</v>
       </c>
       <c r="C62" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3589,7 +3630,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2">
-        <v>0.01539556961506605</v>
+        <v>0.01539438497275114</v>
       </c>
       <c r="C63" s="1">
         <v>8</v>
@@ -3612,25 +3653,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2">
-        <v>0.007697784807533026</v>
+        <v>0.01539438497275114</v>
       </c>
       <c r="C64" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -3638,25 +3679,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="B65" s="2">
-        <v>0.007697784807533026</v>
+        <v>0.00769719248637557</v>
       </c>
       <c r="C65" s="1">
         <v>4</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
         <v>4</v>
-      </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3667,7 +3708,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.007697784807533026</v>
+        <v>0.00769719248637557</v>
       </c>
       <c r="C66" s="1">
         <v>4</v>
@@ -3689,34 +3730,60 @@
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.00769719248637557</v>
+      </c>
+      <c r="C67" s="1">
+        <v>4</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E67">
+      <c r="E68">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F67">
+      <c r="F68">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G67">
+      <c r="G68">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H67">
+      <c r="H68">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
   <si>
     <t>atk_f407</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>led_task.o</t>
+  </si>
+  <si>
+    <t>key_task.o</t>
   </si>
   <si>
     <t>freertos_start.o</t>
@@ -332,9 +335,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$68</c:f>
+              <c:f>ram_percent!$A$3:$A$69</c:f>
               <c:strCache>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -393,15 +396,18 @@
                   <c:v>led_task.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>key_task.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -409,77 +415,80 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$68</c:f>
+              <c:f>ram_percent!$B$3:$B$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
-                  <c:v>54.96585845947266</c:v>
+                  <c:v>54.96340179443359</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.94905090332031</c:v>
+                  <c:v>38.94731140136719</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.510935306549072</c:v>
+                  <c:v>1.510867714881897</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.154435038566589</c:v>
+                  <c:v>1.154383420944214</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.144376993179321</c:v>
+                  <c:v>1.144325852394104</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8985147476196289</c:v>
+                  <c:v>0.8984746336936951</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3732635974884033</c:v>
+                  <c:v>0.3732469081878662</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3028575778007507</c:v>
+                  <c:v>0.3028440475463867</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3028575778007507</c:v>
+                  <c:v>0.3028440475463867</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1050502359867096</c:v>
+                  <c:v>0.1050455346703529</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1028151214122772</c:v>
+                  <c:v>0.1028105244040489</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07152356207370758</c:v>
+                  <c:v>0.0715203657746315</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06705334037542343</c:v>
+                  <c:v>0.06705034524202347</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01341066788882017</c:v>
+                  <c:v>0.01341006904840469</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01005800068378449</c:v>
+                  <c:v>0.01005755178630352</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.004470222629606724</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.004470222629606724</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.004470222629606724</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004470222629606724</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004470222629606724</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.004470222629606724</c:v>
+                  <c:v>0.004470022860914469</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.001117555657401681</c:v>
-                </c:pt>
-                <c:pt idx="65">
+                  <c:v>0.004470022860914469</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.001117505715228617</c:v>
+                </c:pt>
+                <c:pt idx="66">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -547,9 +556,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$68</c:f>
+              <c:f>flash_percent!$A$3:$A$69</c:f>
               <c:strCache>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
@@ -677,75 +686,78 @@
                   <c:v>stm32f4xx_hal_sram.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>freertos_start.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>__dczerorl2.o</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>freertos_start.o</c:v>
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="45">
+                  <c:v>key_task.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>fputc.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -753,206 +765,209 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$68</c:f>
+              <c:f>flash_percent!$B$3:$B$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="66"/>
+                <c:ptCount val="67"/>
                 <c:pt idx="0">
-                  <c:v>25.50079917907715</c:v>
+                  <c:v>25.47041130065918</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.685646533966065</c:v>
+                  <c:v>7.676487922668457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.293089866638184</c:v>
+                  <c:v>7.284399032592773</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.211634159088135</c:v>
+                  <c:v>6.204232215881348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.249485015869141</c:v>
+                  <c:v>5.243229866027832</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.268093109130859</c:v>
+                  <c:v>4.263007164001465</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.162256717681885</c:v>
+                  <c:v>4.157296657562256</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.502222537994385</c:v>
+                  <c:v>3.498049259185791</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.456039428710938</c:v>
+                  <c:v>3.451920986175537</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.028845310211182</c:v>
+                  <c:v>3.025235891342163</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.403448343276978</c:v>
+                  <c:v>2.400584220886231</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.259125947952271</c:v>
+                  <c:v>2.256433963775635</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.197548389434815</c:v>
+                  <c:v>2.194929838180542</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.120576620101929</c:v>
+                  <c:v>2.118049621582031</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.931995272636414</c:v>
+                  <c:v>1.929693102836609</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.693382382392883</c:v>
+                  <c:v>1.691364407539368</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.591394543647766</c:v>
+                  <c:v>1.589498162269592</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.458617925643921</c:v>
+                  <c:v>1.456879854202271</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.10839569568634</c:v>
+                  <c:v>1.107074856758118</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.016029357910156</c:v>
+                  <c:v>1.014818668365479</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.985240638256073</c:v>
+                  <c:v>0.9840666055679321</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8543883562088013</c:v>
+                  <c:v>0.8533702492713928</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8370696902275085</c:v>
+                  <c:v>0.8360722064971924</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8235995769500732</c:v>
+                  <c:v>0.8226181268692017</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6619585752487183</c:v>
+                  <c:v>0.661169707775116</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6427155733108521</c:v>
+                  <c:v>0.6419496536254883</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6157754063606262</c:v>
+                  <c:v>0.6150416135787964</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.4464371502399445</c:v>
+                  <c:v>0.4459051787853241</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.4387399554252625</c:v>
+                  <c:v>0.4382171332836151</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4291184842586517</c:v>
+                  <c:v>0.4286071360111237</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4271941781044006</c:v>
+                  <c:v>0.4266851246356964</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4041025936603546</c:v>
+                  <c:v>0.4036210477352142</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3925568163394928</c:v>
+                  <c:v>0.3920890390872955</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.357919454574585</c:v>
+                  <c:v>0.3574929237365723</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3386764824390411</c:v>
+                  <c:v>0.338272899389267</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3348278701305389</c:v>
+                  <c:v>0.3344288766384125</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.2924933135509491</c:v>
+                  <c:v>0.292144775390625</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2847961187362671</c:v>
+                  <c:v>0.2844567596912384</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2001270055770874</c:v>
+                  <c:v>0.1998885273933411</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1885812133550644</c:v>
+                  <c:v>0.1883564889431</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1731868237257004</c:v>
+                  <c:v>0.1729804575443268</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1693382412195206</c:v>
+                  <c:v>0.1691364496946335</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1654896438121796</c:v>
+                  <c:v>0.1691364496946335</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1616410464048386</c:v>
+                  <c:v>0.165292426943779</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.1462466567754746</c:v>
+                  <c:v>0.1460723876953125</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.0962149053812027</c:v>
+                  <c:v>0.111476294696331</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.09236630797386169</c:v>
+                  <c:v>0.09610024839639664</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.09236630797386169</c:v>
+                  <c:v>0.09225624054670334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.09236630797386169</c:v>
+                  <c:v>0.09225624054670334</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.08466912060976028</c:v>
+                  <c:v>0.09225624054670334</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.06927473098039627</c:v>
+                  <c:v>0.08456822484731674</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.06927473098039627</c:v>
+                  <c:v>0.06919217854738236</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.06927473098039627</c:v>
+                  <c:v>0.06919217854738236</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.06927473098039627</c:v>
+                  <c:v>0.06919217854738236</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06157753989100456</c:v>
+                  <c:v>0.06919217854738236</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.05772894248366356</c:v>
+                  <c:v>0.06150416284799576</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.05772894248366356</c:v>
+                  <c:v>0.05766015127301216</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.05003175139427185</c:v>
+                  <c:v>0.05766015127301216</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.03848596289753914</c:v>
+                  <c:v>0.04997213184833527</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.03463736549019814</c:v>
+                  <c:v>0.03844010084867477</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.01539438497275114</c:v>
+                  <c:v>0.03459608927369118</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.01539438497275114</c:v>
+                  <c:v>0.01537604071199894</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.00769719248637557</c:v>
+                  <c:v>0.01537604071199894</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.00769719248637557</c:v>
+                  <c:v>0.00768802035599947</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.00769719248637557</c:v>
+                  <c:v>0.00768802035599947</c:v>
                 </c:pt>
                 <c:pt idx="65">
+                  <c:v>0.00768802035599947</c:v>
+                </c:pt>
+                <c:pt idx="66">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1057,8 +1072,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H68" totalsRowCount="1">
-  <autoFilter ref="A2:H67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H69" totalsRowCount="1">
+  <autoFilter ref="A2:H68"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1074,8 +1089,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H68" totalsRowCount="1">
-  <autoFilter ref="A2:H67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H69" totalsRowCount="1">
+  <autoFilter ref="A2:H68"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1375,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1388,28 +1403,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1417,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>54.96585845947266</v>
+        <v>54.96340179443359</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -1443,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>38.94905090332031</v>
+        <v>38.94731140136719</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -1469,7 +1484,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.510935306549072</v>
+        <v>1.510867714881897</v>
       </c>
       <c r="C5" s="1">
         <v>1352</v>
@@ -1495,7 +1510,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.154435038566589</v>
+        <v>1.154383420944214</v>
       </c>
       <c r="C6" s="1">
         <v>1033</v>
@@ -1521,7 +1536,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.144376993179321</v>
+        <v>1.144325852394104</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1547,7 +1562,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.8985147476196289</v>
+        <v>0.8984746336936951</v>
       </c>
       <c r="C8" s="1">
         <v>804</v>
@@ -1573,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.3732635974884033</v>
+        <v>0.3732469081878662</v>
       </c>
       <c r="C9" s="1">
         <v>334</v>
@@ -1599,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3028575778007507</v>
+        <v>0.3028440475463867</v>
       </c>
       <c r="C10" s="1">
         <v>271</v>
@@ -1625,7 +1640,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3028575778007507</v>
+        <v>0.3028440475463867</v>
       </c>
       <c r="C11" s="1">
         <v>271</v>
@@ -1651,7 +1666,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1050502359867096</v>
+        <v>0.1050455346703529</v>
       </c>
       <c r="C12" s="1">
         <v>94</v>
@@ -1677,7 +1692,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1028151214122772</v>
+        <v>0.1028105244040489</v>
       </c>
       <c r="C13" s="1">
         <v>92</v>
@@ -1703,7 +1718,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.07152356207370758</v>
+        <v>0.0715203657746315</v>
       </c>
       <c r="C14" s="1">
         <v>64</v>
@@ -1729,7 +1744,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06705334037542343</v>
+        <v>0.06705034524202347</v>
       </c>
       <c r="C15" s="1">
         <v>60</v>
@@ -1755,7 +1770,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01341066788882017</v>
+        <v>0.01341006904840469</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
@@ -1781,7 +1796,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01005800068378449</v>
+        <v>0.01005755178630352</v>
       </c>
       <c r="C17" s="1">
         <v>9</v>
@@ -1807,7 +1822,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.004470222629606724</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1833,7 +1848,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004470222629606724</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1859,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.004470222629606724</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
@@ -1885,7 +1900,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004470222629606724</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -1911,16 +1926,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004470222629606724</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E22" s="1">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1937,16 +1952,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.004470222629606724</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1963,56 +1978,82 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.001117555657401681</v>
+        <v>0.004470022860914469</v>
       </c>
       <c r="C24" s="1">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1">
+        <v>176</v>
+      </c>
+      <c r="E24" s="1">
+        <v>172</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.001117505715228617</v>
+      </c>
+      <c r="C25" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>2163</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E25" s="1">
         <v>2162</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
         <v>1</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68">
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C68">
+      <c r="C69">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D68">
+      <c r="D69">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E68">
+      <c r="E69">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F68">
+      <c r="F69">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G68">
+      <c r="G69">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H68">
+      <c r="H69">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2028,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2041,28 +2082,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s">
         <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2070,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>25.50079917907715</v>
+        <v>25.47041130065918</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2096,7 +2137,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>7.685646533966065</v>
+        <v>7.676487922668457</v>
       </c>
       <c r="C4" s="1">
         <v>3994</v>
@@ -2119,10 +2160,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2">
-        <v>7.293089866638184</v>
+        <v>7.284399032592773</v>
       </c>
       <c r="C5" s="1">
         <v>3790</v>
@@ -2145,10 +2186,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2">
-        <v>6.211634159088135</v>
+        <v>6.204232215881348</v>
       </c>
       <c r="C6" s="1">
         <v>3228</v>
@@ -2174,7 +2215,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>5.249485015869141</v>
+        <v>5.243229866027832</v>
       </c>
       <c r="C7" s="1">
         <v>2728</v>
@@ -2197,10 +2238,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>4.268093109130859</v>
+        <v>4.263007164001465</v>
       </c>
       <c r="C8" s="1">
         <v>2218</v>
@@ -2223,10 +2264,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2">
-        <v>4.162256717681885</v>
+        <v>4.157296657562256</v>
       </c>
       <c r="C9" s="1">
         <v>2163</v>
@@ -2249,10 +2290,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
-        <v>3.502222537994385</v>
+        <v>3.498049259185791</v>
       </c>
       <c r="C10" s="1">
         <v>1820</v>
@@ -2275,10 +2316,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
-        <v>3.456039428710938</v>
+        <v>3.451920986175537</v>
       </c>
       <c r="C11" s="1">
         <v>1796</v>
@@ -2304,7 +2345,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>3.028845310211182</v>
+        <v>3.025235891342163</v>
       </c>
       <c r="C12" s="1">
         <v>1574</v>
@@ -2330,7 +2371,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>2.403448343276978</v>
+        <v>2.400584220886231</v>
       </c>
       <c r="C13" s="1">
         <v>1249</v>
@@ -2356,7 +2397,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>2.259125947952271</v>
+        <v>2.256433963775635</v>
       </c>
       <c r="C14" s="1">
         <v>1174</v>
@@ -2379,10 +2420,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2">
-        <v>2.197548389434815</v>
+        <v>2.194929838180542</v>
       </c>
       <c r="C15" s="1">
         <v>1142</v>
@@ -2408,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>2.120576620101929</v>
+        <v>2.118049621582031</v>
       </c>
       <c r="C16" s="1">
         <v>1102</v>
@@ -2431,10 +2472,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2">
-        <v>1.931995272636414</v>
+        <v>1.929693102836609</v>
       </c>
       <c r="C17" s="1">
         <v>1004</v>
@@ -2460,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>1.693382382392883</v>
+        <v>1.691364407539368</v>
       </c>
       <c r="C18" s="1">
         <v>880</v>
@@ -2486,7 +2527,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>1.591394543647766</v>
+        <v>1.589498162269592</v>
       </c>
       <c r="C19" s="1">
         <v>827</v>
@@ -2509,10 +2550,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2">
-        <v>1.458617925643921</v>
+        <v>1.456879854202271</v>
       </c>
       <c r="C20" s="1">
         <v>758</v>
@@ -2538,7 +2579,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="2">
-        <v>1.10839569568634</v>
+        <v>1.107074856758118</v>
       </c>
       <c r="C21" s="1">
         <v>576</v>
@@ -2561,10 +2602,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2">
-        <v>1.016029357910156</v>
+        <v>1.014818668365479</v>
       </c>
       <c r="C22" s="1">
         <v>528</v>
@@ -2590,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>0.985240638256073</v>
+        <v>0.9840666055679321</v>
       </c>
       <c r="C23" s="1">
         <v>512</v>
@@ -2616,7 +2657,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8543883562088013</v>
+        <v>0.8533702492713928</v>
       </c>
       <c r="C24" s="1">
         <v>444</v>
@@ -2642,7 +2683,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8370696902275085</v>
+        <v>0.8360722064971924</v>
       </c>
       <c r="C25" s="1">
         <v>435</v>
@@ -2668,7 +2709,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8235995769500732</v>
+        <v>0.8226181268692017</v>
       </c>
       <c r="C26" s="1">
         <v>428</v>
@@ -2691,10 +2732,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6619585752487183</v>
+        <v>0.661169707775116</v>
       </c>
       <c r="C27" s="1">
         <v>344</v>
@@ -2717,10 +2758,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6427155733108521</v>
+        <v>0.6419496536254883</v>
       </c>
       <c r="C28" s="1">
         <v>334</v>
@@ -2746,7 +2787,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6157754063606262</v>
+        <v>0.6150416135787964</v>
       </c>
       <c r="C29" s="1">
         <v>320</v>
@@ -2769,10 +2810,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>0.4464371502399445</v>
+        <v>0.4459051787853241</v>
       </c>
       <c r="C30" s="1">
         <v>232</v>
@@ -2795,10 +2836,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2">
-        <v>0.4387399554252625</v>
+        <v>0.4382171332836151</v>
       </c>
       <c r="C31" s="1">
         <v>228</v>
@@ -2824,7 +2865,7 @@
         <v>15</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4291184842586517</v>
+        <v>0.4286071360111237</v>
       </c>
       <c r="C32" s="1">
         <v>223</v>
@@ -2847,10 +2888,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4271941781044006</v>
+        <v>0.4266851246356964</v>
       </c>
       <c r="C33" s="1">
         <v>222</v>
@@ -2873,10 +2914,10 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4041025936603546</v>
+        <v>0.4036210477352142</v>
       </c>
       <c r="C34" s="1">
         <v>210</v>
@@ -2899,10 +2940,10 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3925568163394928</v>
+        <v>0.3920890390872955</v>
       </c>
       <c r="C35" s="1">
         <v>204</v>
@@ -2925,10 +2966,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2">
-        <v>0.357919454574585</v>
+        <v>0.3574929237365723</v>
       </c>
       <c r="C36" s="1">
         <v>186</v>
@@ -2951,10 +2992,10 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3386764824390411</v>
+        <v>0.338272899389267</v>
       </c>
       <c r="C37" s="1">
         <v>176</v>
@@ -2977,10 +3018,10 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3348278701305389</v>
+        <v>0.3344288766384125</v>
       </c>
       <c r="C38" s="1">
         <v>174</v>
@@ -3003,10 +3044,10 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.2924933135509491</v>
+        <v>0.292144775390625</v>
       </c>
       <c r="C39" s="1">
         <v>152</v>
@@ -3029,10 +3070,10 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2847961187362671</v>
+        <v>0.2844567596912384</v>
       </c>
       <c r="C40" s="1">
         <v>148</v>
@@ -3058,7 +3099,7 @@
         <v>19</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2001270055770874</v>
+        <v>0.1998885273933411</v>
       </c>
       <c r="C41" s="1">
         <v>104</v>
@@ -3081,10 +3122,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1885812133550644</v>
+        <v>0.1883564889431</v>
       </c>
       <c r="C42" s="1">
         <v>98</v>
@@ -3107,10 +3148,10 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1731868237257004</v>
+        <v>0.1729804575443268</v>
       </c>
       <c r="C43" s="1">
         <v>90</v>
@@ -3133,10 +3174,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1693382412195206</v>
+        <v>0.1691364496946335</v>
       </c>
       <c r="C44" s="1">
         <v>88</v>
@@ -3159,25 +3200,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1654896438121796</v>
+        <v>0.1691364496946335</v>
       </c>
       <c r="C45" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3185,25 +3226,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.1616410464048386</v>
+        <v>0.165292426943779</v>
       </c>
       <c r="C46" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3211,10 +3252,10 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.1462466567754746</v>
+        <v>0.1460723876953125</v>
       </c>
       <c r="C47" s="1">
         <v>76</v>
@@ -3237,25 +3278,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B48" s="2">
-        <v>0.0962149053812027</v>
+        <v>0.111476294696331</v>
       </c>
       <c r="C48" s="1">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -3266,16 +3307,16 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.09236630797386169</v>
+        <v>0.09610024839639664</v>
       </c>
       <c r="C49" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3292,7 +3333,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.09236630797386169</v>
+        <v>0.09225624054670334</v>
       </c>
       <c r="C50" s="1">
         <v>48</v>
@@ -3315,25 +3356,25 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.09236630797386169</v>
+        <v>0.09225624054670334</v>
       </c>
       <c r="C51" s="1">
         <v>48</v>
       </c>
       <c r="D51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -3341,25 +3382,25 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="B52" s="2">
-        <v>0.08466912060976028</v>
+        <v>0.09225624054670334</v>
       </c>
       <c r="C52" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E52" s="1">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -3370,16 +3411,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.06927473098039627</v>
+        <v>0.08456822484731674</v>
       </c>
       <c r="C53" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3396,7 +3437,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.06927473098039627</v>
+        <v>0.06919217854738236</v>
       </c>
       <c r="C54" s="1">
         <v>36</v>
@@ -3422,7 +3463,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.06927473098039627</v>
+        <v>0.06919217854738236</v>
       </c>
       <c r="C55" s="1">
         <v>36</v>
@@ -3448,7 +3489,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.06927473098039627</v>
+        <v>0.06919217854738236</v>
       </c>
       <c r="C56" s="1">
         <v>36</v>
@@ -3474,16 +3515,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06157753989100456</v>
+        <v>0.06919217854738236</v>
       </c>
       <c r="C57" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3500,16 +3541,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.05772894248366356</v>
+        <v>0.06150416284799576</v>
       </c>
       <c r="C58" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3526,7 +3567,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.05772894248366356</v>
+        <v>0.05766015127301216</v>
       </c>
       <c r="C59" s="1">
         <v>30</v>
@@ -3552,16 +3593,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.05003175139427185</v>
+        <v>0.05766015127301216</v>
       </c>
       <c r="C60" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3578,16 +3619,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>0.03848596289753914</v>
+        <v>0.04997213184833527</v>
       </c>
       <c r="C61" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3604,16 +3645,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="2">
-        <v>0.03463736549019814</v>
+        <v>0.03844010084867477</v>
       </c>
       <c r="C62" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3630,16 +3671,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="2">
-        <v>0.01539438497275114</v>
+        <v>0.03459608927369118</v>
       </c>
       <c r="C63" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3656,7 +3697,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2">
-        <v>0.01539438497275114</v>
+        <v>0.01537604071199894</v>
       </c>
       <c r="C64" s="1">
         <v>8</v>
@@ -3679,25 +3720,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2">
-        <v>0.00769719248637557</v>
+        <v>0.01537604071199894</v>
       </c>
       <c r="C65" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D65" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3705,25 +3746,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B66" s="2">
-        <v>0.00769719248637557</v>
+        <v>0.00768802035599947</v>
       </c>
       <c r="C66" s="1">
         <v>4</v>
       </c>
       <c r="D66" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
         <v>4</v>
-      </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -3734,7 +3775,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.00769719248637557</v>
+        <v>0.00768802035599947</v>
       </c>
       <c r="C67" s="1">
         <v>4</v>
@@ -3756,34 +3797,60 @@
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.00768802035599947</v>
+      </c>
+      <c r="C68" s="1">
+        <v>4</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>4</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C68">
+      <c r="C69">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D68">
+      <c r="D69">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E68">
+      <c r="E69">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F68">
+      <c r="F69">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G68">
+      <c r="G69">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H68">
+      <c r="H69">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="156">
   <si>
     <t>atk_f407</t>
   </si>
@@ -26,9 +26,6 @@
     <t>malloc.o</t>
   </si>
   <si>
-    <t>usbd_cdc_interface.o</t>
-  </si>
-  <si>
     <t>usbd_conf.o</t>
   </si>
   <si>
@@ -38,21 +35,24 @@
     <t>tasks.o</t>
   </si>
   <si>
-    <t>usbd_desc.o</t>
-  </si>
-  <si>
-    <t>usbd_cdc.o</t>
-  </si>
-  <si>
     <t>usart.o</t>
   </si>
   <si>
+    <t>ai_lib.o</t>
+  </si>
+  <si>
+    <t>c_w.l</t>
+  </si>
+  <si>
+    <t>libspace.o</t>
+  </si>
+  <si>
+    <t>dma.o</t>
+  </si>
+  <si>
     <t>lcd.o</t>
   </si>
   <si>
-    <t>can.o</t>
-  </si>
-  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -65,12 +65,6 @@
     <t>stm32f4xx_hal.o</t>
   </si>
   <si>
-    <t>mc_w.l</t>
-  </si>
-  <si>
-    <t>stdout.o</t>
-  </si>
-  <si>
     <t>system_stm32f4xx.o</t>
   </si>
   <si>
@@ -86,136 +80,379 @@
     <t>delay.o</t>
   </si>
   <si>
+    <t>ai_task.o</t>
+  </si>
+  <si>
     <t>usbd_ctlreq.o</t>
   </si>
   <si>
+    <t>fz_wm.l</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_pcd.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_ll_usb.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_pcd.o</t>
-  </si>
-  <si>
-    <t>printfa.o</t>
+    <t>stm32f4xx_hal_uart.o</t>
+  </si>
+  <si>
+    <t>output_array.o</t>
+  </si>
+  <si>
+    <t>btod.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_rcc.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_uart.o</t>
-  </si>
-  <si>
-    <t>mf_w.l</t>
+    <t>m_wm.l</t>
+  </si>
+  <si>
+    <t>_printf_fp_dec.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_dma.o</t>
+  </si>
+  <si>
+    <t>exp.o</t>
   </si>
   <si>
     <t>usbd_core.o</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_can.o</t>
+    <t>daddsub_clz.o</t>
+  </si>
+  <si>
+    <t>_printf_fp_hex.o</t>
+  </si>
+  <si>
+    <t>ddiv.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_gpio.o</t>
   </si>
   <si>
+    <t>__printf_flags_ss_wp.o</t>
+  </si>
+  <si>
+    <t>bigflt0.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_cortex.o</t>
   </si>
   <si>
-    <t>dadd.o</t>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>lc_ctype_c.o</t>
+  </si>
+  <si>
+    <t>poly.o</t>
+  </si>
+  <si>
+    <t>lludivv7m.o</t>
   </si>
   <si>
     <t>stm32f4xx_ll_fsmc.o</t>
   </si>
   <si>
-    <t>dmul.o</t>
-  </si>
-  <si>
-    <t>ddiv.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_dma.o</t>
-  </si>
-  <si>
     <t>sys.o</t>
   </si>
   <si>
-    <t>depilogue.o</t>
+    <t>_printf_wctomb.o</t>
+  </si>
+  <si>
+    <t>_printf_hex_int_ll_ptr.o</t>
+  </si>
+  <si>
+    <t>_printf_intcommon.o</t>
+  </si>
+  <si>
+    <t>dnaninf.o</t>
+  </si>
+  <si>
+    <t>led.o</t>
+  </si>
+  <si>
+    <t>list.o</t>
+  </si>
+  <si>
+    <t>fnaninf.o</t>
+  </si>
+  <si>
+    <t>rt_memcpy_v6.o</t>
+  </si>
+  <si>
+    <t>lludiv10.o</t>
   </si>
   <si>
     <t>usbd_ioreq.o</t>
   </si>
   <si>
-    <t>led.o</t>
-  </si>
-  <si>
-    <t>list.o</t>
-  </si>
-  <si>
-    <t>uldiv.o</t>
+    <t>strcmpv7m.o</t>
+  </si>
+  <si>
+    <t>_printf_fp_infnan.o</t>
+  </si>
+  <si>
+    <t>_printf_longlong_dec.o</t>
+  </si>
+  <si>
+    <t>dleqf.o</t>
+  </si>
+  <si>
+    <t>_printf_dec.o</t>
+  </si>
+  <si>
+    <t>_printf_oct_int_ll.o</t>
+  </si>
+  <si>
+    <t>drleqf.o</t>
+  </si>
+  <si>
+    <t>rt_memcpy_w.o</t>
+  </si>
+  <si>
+    <t>d2f.o</t>
+  </si>
+  <si>
+    <t>dfix.o</t>
+  </si>
+  <si>
+    <t>dfixu.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_sram.o</t>
+  </si>
+  <si>
+    <t>f2d.o</t>
+  </si>
+  <si>
+    <t>dunder.o</t>
+  </si>
+  <si>
+    <t>dflt_clz.o</t>
+  </si>
+  <si>
+    <t>_printf_str.o</t>
+  </si>
+  <si>
+    <t>rt_memclr_w.o</t>
+  </si>
+  <si>
+    <t>_printf_pad.o</t>
+  </si>
+  <si>
+    <t>sys_stackheap_outer.o</t>
+  </si>
+  <si>
+    <t>lc_numeric_c.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
+  </si>
+  <si>
+    <t>rt_memclr.o</t>
+  </si>
+  <si>
+    <t>_wcrtomb.o</t>
+  </si>
+  <si>
+    <t>vsnprintf.o</t>
+  </si>
+  <si>
+    <t>__scatter.o</t>
+  </si>
+  <si>
+    <t>fpclassify.o</t>
+  </si>
+  <si>
+    <t>_printf_char_common.o</t>
+  </si>
+  <si>
+    <t>_printf_wchar.o</t>
+  </si>
+  <si>
+    <t>_printf_char.o</t>
+  </si>
+  <si>
+    <t>_printf_charcount.o</t>
+  </si>
+  <si>
+    <t>_printf_truncate.o</t>
+  </si>
+  <si>
+    <t>_printf_char_file.o</t>
+  </si>
+  <si>
+    <t>libinit2.o</t>
+  </si>
+  <si>
+    <t>__scatter_zi.o</t>
+  </si>
+  <si>
+    <t>__scatter_copy.o</t>
+  </si>
+  <si>
+    <t>dcmpi.o</t>
+  </si>
+  <si>
+    <t>__2printf.o</t>
+  </si>
+  <si>
+    <t>_rserrno.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_it.o</t>
+  </si>
+  <si>
+    <t>exit.o</t>
+  </si>
+  <si>
+    <t>rt_ctype_table.o</t>
+  </si>
+  <si>
+    <t>aeabi_memset.o</t>
+  </si>
+  <si>
+    <t>_snputc.o</t>
+  </si>
+  <si>
+    <t>__printf_wp.o</t>
+  </si>
+  <si>
+    <t>dretinf.o</t>
+  </si>
+  <si>
+    <t>__rtentry2.o</t>
+  </si>
+  <si>
+    <t>fretinf.o</t>
+  </si>
+  <si>
+    <t>fpinit.o</t>
+  </si>
+  <si>
+    <t>rtexit2.o</t>
+  </si>
+  <si>
+    <t>_sputc.o</t>
+  </si>
+  <si>
+    <t>_printf_ll.o</t>
+  </si>
+  <si>
+    <t>_printf_l.o</t>
+  </si>
+  <si>
+    <t>rt_locale_intlibspace.o</t>
+  </si>
+  <si>
+    <t>rt_errno_addr_intlibspace.o</t>
+  </si>
+  <si>
+    <t>ferror.o</t>
+  </si>
+  <si>
+    <t>__main.o</t>
+  </si>
+  <si>
+    <t>heapauxi.o</t>
+  </si>
+  <si>
+    <t>_printf_x.o</t>
+  </si>
+  <si>
+    <t>_printf_u.o</t>
+  </si>
+  <si>
+    <t>_printf_s.o</t>
+  </si>
+  <si>
+    <t>_printf_p.o</t>
+  </si>
+  <si>
+    <t>_printf_o.o</t>
+  </si>
+  <si>
+    <t>_printf_n.o</t>
+  </si>
+  <si>
+    <t>_printf_ls.o</t>
+  </si>
+  <si>
+    <t>_printf_llx.o</t>
+  </si>
+  <si>
+    <t>_printf_llu.o</t>
+  </si>
+  <si>
+    <t>_printf_llo.o</t>
+  </si>
+  <si>
+    <t>_printf_lli.o</t>
+  </si>
+  <si>
+    <t>_printf_lld.o</t>
+  </si>
+  <si>
+    <t>_printf_lc.o</t>
+  </si>
+  <si>
+    <t>_printf_i.o</t>
+  </si>
+  <si>
+    <t>_printf_g.o</t>
+  </si>
+  <si>
+    <t>_printf_f.o</t>
+  </si>
+  <si>
+    <t>_printf_e.o</t>
+  </si>
+  <si>
+    <t>_printf_d.o</t>
+  </si>
+  <si>
+    <t>_printf_c.o</t>
+  </si>
+  <si>
+    <t>_printf_a.o</t>
+  </si>
+  <si>
+    <t>__rtentry4.o</t>
+  </si>
+  <si>
+    <t>printf2.o</t>
+  </si>
+  <si>
+    <t>printf1.o</t>
+  </si>
+  <si>
+    <t>_printf_percent_end.o</t>
+  </si>
+  <si>
+    <t>use_no_semi_2.o</t>
+  </si>
+  <si>
+    <t>use_no_semi.o</t>
+  </si>
+  <si>
+    <t>rtexit.o</t>
+  </si>
+  <si>
+    <t>libshutdown2.o</t>
+  </si>
+  <si>
+    <t>libshutdown.o</t>
+  </si>
+  <si>
+    <t>libinit.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_pcd_ex.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_sram.o</t>
-  </si>
-  <si>
-    <t>__dczerorl2.o</t>
-  </si>
-  <si>
-    <t>main.o</t>
-  </si>
-  <si>
-    <t>dfixui.o</t>
-  </si>
-  <si>
-    <t>dfixul.o</t>
-  </si>
-  <si>
-    <t>cdrcmple.o</t>
-  </si>
-  <si>
-    <t>uidiv.o</t>
-  </si>
-  <si>
-    <t>memseta.o</t>
-  </si>
-  <si>
-    <t>memcpya.o</t>
-  </si>
-  <si>
-    <t>llsshr.o</t>
-  </si>
-  <si>
-    <t>init.o</t>
-  </si>
-  <si>
-    <t>llushr.o</t>
-  </si>
-  <si>
-    <t>llshl.o</t>
-  </si>
-  <si>
-    <t>handlers.o</t>
-  </si>
-  <si>
-    <t>dfltui.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_it.o</t>
-  </si>
-  <si>
-    <t>fputc.o</t>
-  </si>
-  <si>
-    <t>entry9a.o</t>
-  </si>
-  <si>
-    <t>entry2.o</t>
-  </si>
-  <si>
-    <t>entry5.o</t>
-  </si>
-  <si>
-    <t>entry12b.o</t>
   </si>
   <si>
     <t>File_name</t>
@@ -335,9 +572,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$69</c:f>
+              <c:f>ram_percent!$A$3:$A$148</c:f>
               <c:strCache>
-                <c:ptCount val="67"/>
+                <c:ptCount val="146"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -345,31 +582,31 @@
                   <c:v>malloc.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>usbd_cdc_interface.o</c:v>
+                  <c:v>usbd_conf.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>usbd_conf.o</c:v>
+                  <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>startup_stm32f407xx.o</c:v>
+                  <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>tasks.o</c:v>
+                  <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>usbd_desc.o</c:v>
+                  <c:v>ai_lib.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>usbd_cdc.o</c:v>
+                  <c:v>c_w.l</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>usart.o</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>lcd.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>can.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>queue.o</c:v>
@@ -384,30 +621,27 @@
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>mc_w.l</c:v>
+                  <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>stdout.o</c:v>
+                  <c:v>led_task.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>system_stm32f4xx.o</c:v>
+                  <c:v>key_task.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>led_task.o</c:v>
+                  <c:v>freertos_start.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>key_task.o</c:v>
+                  <c:v>delay.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>freertos_start.o</c:v>
+                  <c:v>ai_task.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>delay.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="145">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -415,80 +649,77 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$69</c:f>
+              <c:f>ram_percent!$B$3:$B$148</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="146"/>
                 <c:pt idx="0">
-                  <c:v>54.96340179443359</c:v>
+                  <c:v>55.90615463256836</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.94731140136719</c:v>
+                  <c:v>39.61534881591797</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.510867714881897</c:v>
+                  <c:v>1.17418384552002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.154383420944214</c:v>
+                  <c:v>1.16395378112793</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.144325852394104</c:v>
+                  <c:v>0.9138855934143066</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8984746336936951</c:v>
+                  <c:v>0.3125852644443512</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3732469081878662</c:v>
+                  <c:v>0.2864417433738709</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3028440475463867</c:v>
+                  <c:v>0.1091206669807434</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3028440475463867</c:v>
+                  <c:v>0.1091206669807434</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1050455346703529</c:v>
+                  <c:v>0.1091206669807434</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1028105244040489</c:v>
+                  <c:v>0.1068473234772682</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0715203657746315</c:v>
+                  <c:v>0.07274711132049561</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06705034524202347</c:v>
+                  <c:v>0.06820041686296463</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01341006904840469</c:v>
+                  <c:v>0.01364008337259293</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01005755178630352</c:v>
+                  <c:v>0.0102300625294447</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004546694457530975</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004546694457530975</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004546694457530975</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004546694457530975</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004546694457530975</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.004470022860914469</c:v>
+                  <c:v>0.004546694457530975</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.004470022860914469</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.001117505715228617</c:v>
-                </c:pt>
-                <c:pt idx="66">
+                  <c:v>0.001136673614382744</c:v>
+                </c:pt>
+                <c:pt idx="145">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -556,208 +787,445 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$69</c:f>
+              <c:f>flash_percent!$A$3:$A$148</c:f>
               <c:strCache>
-                <c:ptCount val="67"/>
+                <c:ptCount val="146"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>c_w.l</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>fz_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>stm32f4xx_hal_pcd.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>stm32f4xx_ll_usb.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>stm32f4xx_hal_pcd.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>mc_w.l</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>printfa.o</c:v>
-                </c:pt>
                 <c:pt idx="6">
+                  <c:v>stm32f4xx_hal_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>output_array.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
+                  <c:v>btod.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>stm32f4xx_hal_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>usbd_cdc.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
+                  <c:v>m_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>mf_w.l</c:v>
-                </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
+                  <c:v>_printf_fp_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>stm32f4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>exp.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>usbd_core.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
+                  <c:v>daddsub_clz.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>_printf_fp_hex.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>ai_lib.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>ddiv.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>stm32f4xx_hal_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>stm32f4xx_hal_can.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="27">
+                  <c:v>startup_stm32f407xx.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>malloc.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>stm32f4xx_hal_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>usbd_desc.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>startup_stm32f407xx.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>usbd_cdc_interface.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="29">
+                  <c:v>__printf_flags_ss_wp.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>ai_task.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>bigflt0.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>dadd.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>can.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="33">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>lc_ctype_c.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>poly.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>lludivv7m.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>stm32f4xx_ll_fsmc.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="38">
+                  <c:v>sys.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>_printf_wctomb.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>_printf_hex_int_ll_ptr.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
-                  <c:v>ddiv.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>stm32f4xx_hal_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>sys.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>depilogue.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="42">
+                  <c:v>_printf_intcommon.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="44">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>dnaninf.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>led.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>list.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>fnaninf.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>rt_memcpy_v6.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>lludiv10.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>led.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>list.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="52">
+                  <c:v>strcmpv7m.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>_printf_fp_infnan.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>_printf_longlong_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>dleqf.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>_printf_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>_printf_oct_int_ll.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>drleqf.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
-                  <c:v>uldiv.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="60">
+                  <c:v>rt_memcpy_w.o</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>d2f.o</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>dfix.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>freertos_start.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>dfixu.o</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>stm32f4xx_hal_sram.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>f2d.o</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>dunder.o</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>dflt_clz.o</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>_printf_str.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>rt_memclr_w.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>_printf_pad.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>sys_stackheap_outer.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>lc_numeric_c.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>rt_memclr.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>_wcrtomb.o</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>key_task.o</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>vsnprintf.o</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>__scatter.o</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>fpclassify.o</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>_printf_char_common.o</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>system_stm32f4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>_printf_wchar.o</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>_printf_char.o</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>_printf_charcount.o</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>_printf_truncate.o</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>_printf_char_file.o</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>libinit2.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>__scatter_zi.o</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>__scatter_copy.o</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>dcmpi.o</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>__2printf.o</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>_rserrno.o</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>stm32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>exit.o</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>rt_ctype_table.o</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>aeabi_memset.o</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>_snputc.o</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>__printf_wp.o</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>dretinf.o</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>__rtentry2.o</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>fretinf.o</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>fpinit.o</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>rtexit2.o</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>_sputc.o</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>_printf_ll.o</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>_printf_l.o</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>rt_locale_intlibspace.o</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>rt_errno_addr_intlibspace.o</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>libspace.o</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>ferror.o</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>__main.o</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>heapauxi.o</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>_printf_x.o</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>_printf_u.o</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>_printf_s.o</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>_printf_p.o</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>_printf_o.o</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>_printf_n.o</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>_printf_ls.o</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>_printf_llx.o</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>_printf_llu.o</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>_printf_llo.o</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>_printf_lli.o</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>_printf_lld.o</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>_printf_lc.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>_printf_i.o</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>_printf_g.o</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>_printf_f.o</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>_printf_e.o</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>_printf_d.o</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>_printf_c.o</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>_printf_a.o</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>__rtentry4.o</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>printf2.o</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>printf1.o</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>_printf_percent_end.o</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>use_no_semi_2.o</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>use_no_semi.o</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>rtexit.o</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>libshutdown2.o</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>libshutdown.o</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>libinit.o</c:v>
+                </c:pt>
+                <c:pt idx="144">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
-                  <c:v>stm32f4xx_hal_sram.o</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>freertos_start.o</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>__dczerorl2.o</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>key_task.o</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>dfixui.o</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>dfixul.o</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>cdrcmple.o</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>system_stm32f4xx.o</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>uidiv.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>memseta.o</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>memcpya.o</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>llsshr.o</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>init.o</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>llushr.o</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>llshl.o</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>handlers.o</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>dfltui.o</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>stm32f4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>fputc.o</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>entry9a.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>entry2.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>stdout.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>entry12b.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="145">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -765,209 +1233,446 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$69</c:f>
+              <c:f>flash_percent!$B$3:$B$148</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="67"/>
+                <c:ptCount val="146"/>
                 <c:pt idx="0">
-                  <c:v>25.47041130065918</c:v>
+                  <c:v>19.53535079956055</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.676487922668457</c:v>
+                  <c:v>11.79757022857666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.284399032592773</c:v>
+                  <c:v>5.887729167938232</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.204232215881348</c:v>
+                  <c:v>4.266171455383301</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.243229866027832</c:v>
+                  <c:v>3.933014869689941</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.263007164001465</c:v>
+                  <c:v>3.764962673187256</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.157296657562256</c:v>
+                  <c:v>3.278495311737061</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.498049259185791</c:v>
+                  <c:v>3.225425958633423</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.451920986175537</c:v>
+                  <c:v>3.032313108444214</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.025235891342163</c:v>
+                  <c:v>2.853941917419434</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.400584220886231</c:v>
+                  <c:v>2.682941198348999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.256433963775635</c:v>
+                  <c:v>2.32030200958252</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.194929838180542</c:v>
+                  <c:v>1.951766014099121</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.118049621582031</c:v>
+                  <c:v>1.730644464492798</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.929693102836609</c:v>
+                  <c:v>1.624506115913391</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.691364407539368</c:v>
+                  <c:v>1.553747296333313</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.589498162269592</c:v>
+                  <c:v>1.441712379455566</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.456879854202271</c:v>
+                  <c:v>1.391591429710388</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.107074856758118</c:v>
+                  <c:v>1.30903947353363</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.014818668365479</c:v>
+                  <c:v>1.297246336936951</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9840666055679321</c:v>
+                  <c:v>1.217642545700073</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8533702492713928</c:v>
+                  <c:v>1.182263135910034</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8360722064971924</c:v>
+                  <c:v>1.155728578567505</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8226181268692017</c:v>
+                  <c:v>1.048116087913513</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.661169707775116</c:v>
+                  <c:v>1.01421070098877</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6419496536254883</c:v>
+                  <c:v>0.7783477902412415</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6150416135787964</c:v>
+                  <c:v>0.7503390312194824</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.4459051787853241</c:v>
+                  <c:v>0.6898991465568543</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.4382171332836151</c:v>
+                  <c:v>0.6368299722671509</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4286071360111237</c:v>
+                  <c:v>0.6029247045516968</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4266851246356964</c:v>
+                  <c:v>0.566071093082428</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4036210477352142</c:v>
+                  <c:v>0.5542779564857483</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3920890390872955</c:v>
+                  <c:v>0.5071053504943848</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3574929237365723</c:v>
+                  <c:v>0.5012087821960449</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.338272899389267</c:v>
+                  <c:v>0.4658293426036835</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3344288766384125</c:v>
+                  <c:v>0.365587592124939</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.292144775390625</c:v>
+                  <c:v>0.3508461713790894</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2844567596912384</c:v>
+                  <c:v>0.3420012891292572</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1998885273933411</c:v>
+                  <c:v>0.3007252812385559</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1883564889431</c:v>
+                  <c:v>0.2889321446418762</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1729804575443268</c:v>
+                  <c:v>0.2771389782428742</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1691364496946335</c:v>
+                  <c:v>0.2697682678699493</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1691364496946335</c:v>
+                  <c:v>0.2623975574970245</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.165292426943779</c:v>
+                  <c:v>0.2594492733478546</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.1460723876953125</c:v>
+                  <c:v>0.2476561069488525</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.111476294696331</c:v>
+                  <c:v>0.2299663871526718</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.09610024839639664</c:v>
+                  <c:v>0.224069818854332</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.09225624054670334</c:v>
+                  <c:v>0.2181732356548309</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.09225624054670334</c:v>
+                  <c:v>0.2063800990581513</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.09225624054670334</c:v>
+                  <c:v>0.2034318000078201</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.08456822484731674</c:v>
+                  <c:v>0.2034318000078201</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.06919217854738236</c:v>
+                  <c:v>0.1975352317094803</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.06919217854738236</c:v>
+                  <c:v>0.1886903643608093</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.06919217854738236</c:v>
+                  <c:v>0.1886903643608093</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06919217854738236</c:v>
+                  <c:v>0.1827937960624695</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.06150416284799576</c:v>
+                  <c:v>0.1768972277641296</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.05766015127301216</c:v>
+                  <c:v>0.1768972277641296</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.05766015127301216</c:v>
+                  <c:v>0.1651040762662888</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.04997213184833527</c:v>
+                  <c:v>0.1592074930667877</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.03844010084867477</c:v>
+                  <c:v>0.1533109247684479</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.03459608927369118</c:v>
+                  <c:v>0.147414356470108</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.01537604071199894</c:v>
+                  <c:v>0.1444660723209381</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.01537604071199894</c:v>
+                  <c:v>0.1385694891214371</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.00768802035599947</c:v>
+                  <c:v>0.1356212049722672</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.00768802035599947</c:v>
+                  <c:v>0.1326729208230972</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.00768802035599947</c:v>
+                  <c:v>0.1297246366739273</c:v>
                 </c:pt>
                 <c:pt idx="66">
+                  <c:v>0.1267763376235962</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.1238280534744263</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.1238280534744263</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.1208797693252564</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.1149831935763359</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.1149831935763359</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.1090866178274155</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.1061383336782455</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.1061383336782455</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.1002417579293251</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.09434518218040466</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.0855003222823143</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.07665546238422394</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.07665546238422394</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.0707588866353035</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.0707588866353035</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.0707588866353035</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.06486231833696365</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.06486231833696365</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.05896574258804321</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.05306916683912277</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.05306916683912277</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.05012087896466255</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.04127601906657219</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.03832773119211197</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.03537944331765175</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.03537944331765175</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.03243115916848183</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.02948287129402161</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.02653458341956139</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.02358629554510117</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.02358629554510117</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.02358629554510117</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.0206380095332861</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.01768972165882587</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.01768972165882587</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.0147414356470108</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.0147414356470108</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.0147414356470108</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.0147414356470108</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.0147414356470108</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.0147414356470108</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.01179314777255058</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.01179314777255058</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.01179314777255058</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.01179314777255058</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.01179314777255058</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.008844860829412937</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.005896573886275291</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.005896573886275291</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.005896573886275291</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.002948286943137646</c:v>
+                </c:pt>
+                <c:pt idx="145">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1072,8 +1777,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H69" totalsRowCount="1">
-  <autoFilter ref="A2:H68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H148" totalsRowCount="1">
+  <autoFilter ref="A2:H147"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1089,8 +1794,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H69" totalsRowCount="1">
-  <autoFilter ref="A2:H68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H148" totalsRowCount="1">
+  <autoFilter ref="A2:H147"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1390,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1403,28 +2108,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1432,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>54.96340179443359</v>
+        <v>55.90615463256836</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -1458,16 +2163,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>38.94731140136719</v>
+        <v>39.61534881591797</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
       </c>
       <c r="D4" s="1">
-        <v>576</v>
+        <v>432</v>
       </c>
       <c r="E4" s="1">
-        <v>504</v>
+        <v>360</v>
       </c>
       <c r="F4" s="1">
         <v>36</v>
@@ -1484,25 +2189,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.510867714881897</v>
+        <v>1.17418384552002</v>
       </c>
       <c r="C5" s="1">
-        <v>1352</v>
+        <v>1033</v>
       </c>
       <c r="D5" s="1">
-        <v>428</v>
+        <v>509</v>
       </c>
       <c r="E5" s="1">
-        <v>396</v>
+        <v>508</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>1320</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1510,25 +2215,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.154383420944214</v>
+        <v>1.16395378112793</v>
       </c>
       <c r="C6" s="1">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="D6" s="1">
-        <v>827</v>
+        <v>468</v>
       </c>
       <c r="E6" s="1">
-        <v>826</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>1032</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1536,25 +2241,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.144325852394104</v>
+        <v>0.9138855934143066</v>
       </c>
       <c r="C7" s="1">
-        <v>1024</v>
+        <v>804</v>
       </c>
       <c r="D7" s="1">
-        <v>444</v>
+        <v>3994</v>
       </c>
       <c r="E7" s="1">
-        <v>52</v>
+        <v>3930</v>
       </c>
       <c r="F7" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H7" s="1">
-        <v>1024</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1562,25 +2267,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.8984746336936951</v>
+        <v>0.3125852644443512</v>
       </c>
       <c r="C8" s="1">
-        <v>804</v>
+        <v>275</v>
       </c>
       <c r="D8" s="1">
-        <v>3994</v>
+        <v>711</v>
       </c>
       <c r="E8" s="1">
-        <v>3930</v>
+        <v>704</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="H8" s="1">
-        <v>740</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1588,25 +2293,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.3732469081878662</v>
+        <v>0.2864417433738709</v>
       </c>
       <c r="C9" s="1">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="D9" s="1">
-        <v>512</v>
+        <v>784</v>
       </c>
       <c r="E9" s="1">
-        <v>434</v>
+        <v>712</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G9" s="1">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1614,25 +2319,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3028440475463867</v>
+        <v>0.1091206669807434</v>
       </c>
       <c r="C10" s="1">
-        <v>271</v>
+        <v>96</v>
       </c>
       <c r="D10" s="1">
-        <v>1249</v>
+        <v>8003</v>
       </c>
       <c r="E10" s="1">
-        <v>978</v>
+        <v>7452</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G10" s="1">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1640,25 +2345,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3028440475463867</v>
+        <v>0.1091206669807434</v>
       </c>
       <c r="C11" s="1">
-        <v>271</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1">
-        <v>435</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>432</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>268</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1666,16 +2371,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1050455346703529</v>
+        <v>0.1091206669807434</v>
       </c>
       <c r="C12" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1">
-        <v>13252</v>
+        <v>168</v>
       </c>
       <c r="E12" s="1">
-        <v>13252</v>
+        <v>168</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1684,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1692,16 +2397,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1028105244040489</v>
+        <v>0.1068473234772682</v>
       </c>
       <c r="C13" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1">
-        <v>320</v>
+        <v>13252</v>
       </c>
       <c r="E13" s="1">
-        <v>320</v>
+        <v>13252</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1710,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1718,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0715203657746315</v>
+        <v>0.07274711132049561</v>
       </c>
       <c r="C14" s="1">
         <v>64</v>
@@ -1744,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06705034524202347</v>
+        <v>0.06820041686296463</v>
       </c>
       <c r="C15" s="1">
         <v>60</v>
@@ -1770,7 +2475,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01341006904840469</v>
+        <v>0.01364008337259293</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
@@ -1796,16 +2501,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01005755178630352</v>
+        <v>0.0102300625294447</v>
       </c>
       <c r="C17" s="1">
         <v>9</v>
       </c>
       <c r="D17" s="1">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="E17" s="1">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1822,19 +2527,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004546694457530975</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>2728</v>
+        <v>48</v>
       </c>
       <c r="E18" s="1">
-        <v>2724</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G18" s="1">
         <v>4</v>
@@ -1848,16 +2553,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004546694457530975</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1874,19 +2579,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004546694457530975</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E20" s="1">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>4</v>
@@ -1900,16 +2605,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004546694457530975</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E21" s="1">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1926,16 +2631,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004546694457530975</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="E22" s="1">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1952,19 +2657,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.004546694457530975</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>88</v>
+        <v>384</v>
       </c>
       <c r="E23" s="1">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1">
         <v>4</v>
@@ -1978,82 +2683,56 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.004470022860914469</v>
+        <v>0.001136673614382744</v>
       </c>
       <c r="C24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" s="1">
-        <v>176</v>
+        <v>2057</v>
       </c>
       <c r="E24" s="1">
-        <v>172</v>
+        <v>2056</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2">
-        <v>0.001117505715228617</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2163</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2162</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69">
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+      <c r="B148">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C69">
+      <c r="C148">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D69">
+      <c r="D148">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E69">
+      <c r="E148">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F69">
+      <c r="F148">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G69">
+      <c r="G148">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H69">
+      <c r="H148">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2069,7 +2748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2082,36 +2761,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
-        <v>25.47041130065918</v>
+        <v>19.53535079956055</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2134,71 +2813,71 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>7.676487922668457</v>
+        <v>11.79757022857666</v>
       </c>
       <c r="C4" s="1">
-        <v>3994</v>
+        <v>8003</v>
       </c>
       <c r="D4" s="1">
-        <v>804</v>
+        <v>96</v>
       </c>
       <c r="E4" s="1">
-        <v>3930</v>
+        <v>7452</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G4" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>740</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>7.284399032592773</v>
+        <v>5.887729167938232</v>
       </c>
       <c r="C5" s="1">
-        <v>3790</v>
+        <v>3994</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="E5" s="1">
-        <v>3790</v>
+        <v>3930</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
-        <v>6.204232215881348</v>
+        <v>4.266171455383301</v>
       </c>
       <c r="C6" s="1">
-        <v>3228</v>
+        <v>2894</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>3228</v>
+        <v>2894</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2212,25 +2891,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
-        <v>5.243229866027832</v>
+        <v>3.933014869689941</v>
       </c>
       <c r="C7" s="1">
-        <v>2728</v>
+        <v>2668</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>2724</v>
+        <v>2668</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -2238,19 +2917,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
-        <v>4.263007164001465</v>
+        <v>3.764962673187256</v>
       </c>
       <c r="C8" s="1">
-        <v>2218</v>
+        <v>2554</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2218</v>
+        <v>2554</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2264,25 +2943,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>4.157296657562256</v>
+        <v>3.278495311737061</v>
       </c>
       <c r="C9" s="1">
-        <v>2163</v>
+        <v>2224</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>2162</v>
+        <v>2224</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2293,19 +2972,19 @@
         <v>27</v>
       </c>
       <c r="B10" s="2">
-        <v>3.498049259185791</v>
+        <v>3.225425958633423</v>
       </c>
       <c r="C10" s="1">
-        <v>1820</v>
+        <v>2188</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>1820</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>2188</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2316,25 +2995,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2">
-        <v>3.451920986175537</v>
+        <v>3.032313108444214</v>
       </c>
       <c r="C11" s="1">
-        <v>1796</v>
+        <v>2057</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>1796</v>
+        <v>2056</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -2342,19 +3021,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>3.025235891342163</v>
+        <v>2.853941917419434</v>
       </c>
       <c r="C12" s="1">
-        <v>1574</v>
+        <v>1936</v>
       </c>
       <c r="D12" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1574</v>
+        <v>1936</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2363,30 +3042,30 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>2.400584220886231</v>
+        <v>2.682941198348999</v>
       </c>
       <c r="C13" s="1">
-        <v>1249</v>
+        <v>1820</v>
       </c>
       <c r="D13" s="1">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>978</v>
+        <v>1820</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -2394,48 +3073,48 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2.256433963775635</v>
+        <v>2.32030200958252</v>
       </c>
       <c r="C14" s="1">
-        <v>1174</v>
+        <v>1574</v>
       </c>
       <c r="D14" s="1">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1">
-        <v>1162</v>
+        <v>1574</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2">
-        <v>2.194929838180542</v>
+        <v>1.951766014099121</v>
       </c>
       <c r="C15" s="1">
-        <v>1142</v>
+        <v>1324</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1142</v>
+        <v>1236</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -2446,126 +3125,126 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>2.118049621582031</v>
+        <v>1.730644464492798</v>
       </c>
       <c r="C16" s="1">
-        <v>1102</v>
+        <v>1174</v>
       </c>
       <c r="D16" s="1">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1">
-        <v>1082</v>
+        <v>1162</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>1.929693102836609</v>
+        <v>1.624506115913391</v>
       </c>
       <c r="C17" s="1">
-        <v>1004</v>
+        <v>1102</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1">
-        <v>1004</v>
+        <v>1082</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2">
-        <v>1.691364407539368</v>
+        <v>1.553747296333313</v>
       </c>
       <c r="C18" s="1">
-        <v>880</v>
+        <v>1054</v>
       </c>
       <c r="D18" s="1">
-        <v>49184</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>848</v>
+        <v>1054</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2">
-        <v>1.589498162269592</v>
+        <v>1.441712379455566</v>
       </c>
       <c r="C19" s="1">
-        <v>827</v>
+        <v>978</v>
       </c>
       <c r="D19" s="1">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>826</v>
+        <v>970</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>1032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2">
-        <v>1.456879854202271</v>
+        <v>1.391591429710388</v>
       </c>
       <c r="C20" s="1">
-        <v>758</v>
+        <v>944</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>758</v>
+        <v>856</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -2576,175 +3255,175 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2">
-        <v>1.107074856758118</v>
+        <v>1.30903947353363</v>
       </c>
       <c r="C21" s="1">
-        <v>576</v>
+        <v>888</v>
       </c>
       <c r="D21" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>504</v>
+        <v>888</v>
       </c>
       <c r="F21" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1.297246336936951</v>
+      </c>
+      <c r="C22" s="1">
+        <v>880</v>
+      </c>
+      <c r="D22" s="1">
+        <v>49184</v>
+      </c>
+      <c r="E22" s="1">
+        <v>848</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
         <v>32</v>
       </c>
-      <c r="B22" s="2">
-        <v>1.014818668365479</v>
-      </c>
-      <c r="C22" s="1">
-        <v>528</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1">
-        <v>528</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9840666055679321</v>
+        <v>1.217642545700073</v>
       </c>
       <c r="C23" s="1">
-        <v>512</v>
+        <v>826</v>
       </c>
       <c r="D23" s="1">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>434</v>
+        <v>826</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8533702492713928</v>
+        <v>1.182263135910034</v>
       </c>
       <c r="C24" s="1">
-        <v>444</v>
+        <v>802</v>
       </c>
       <c r="D24" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>52</v>
+        <v>764</v>
       </c>
       <c r="F24" s="1">
-        <v>392</v>
+        <v>38</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8360722064971924</v>
+        <v>1.155728578567505</v>
       </c>
       <c r="C25" s="1">
-        <v>435</v>
+        <v>784</v>
       </c>
       <c r="D25" s="1">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="E25" s="1">
-        <v>432</v>
+        <v>712</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G25" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8226181268692017</v>
+        <v>1.048116087913513</v>
       </c>
       <c r="C26" s="1">
-        <v>428</v>
+        <v>711</v>
       </c>
       <c r="D26" s="1">
-        <v>1352</v>
+        <v>275</v>
       </c>
       <c r="E26" s="1">
-        <v>396</v>
+        <v>704</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H26" s="1">
-        <v>1320</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2">
-        <v>0.661169707775116</v>
+        <v>1.01421070098877</v>
       </c>
       <c r="C27" s="1">
-        <v>344</v>
+        <v>688</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>344</v>
+        <v>688</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2758,19 +3437,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6419496536254883</v>
+        <v>0.7783477902412415</v>
       </c>
       <c r="C28" s="1">
-        <v>334</v>
+        <v>528</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>334</v>
+        <v>528</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2784,103 +3463,103 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6150416135787964</v>
+        <v>0.7503390312194824</v>
       </c>
       <c r="C29" s="1">
-        <v>320</v>
+        <v>509</v>
       </c>
       <c r="D29" s="1">
-        <v>92</v>
+        <v>1033</v>
       </c>
       <c r="E29" s="1">
-        <v>320</v>
+        <v>508</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="1">
-        <v>92</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>0.4459051787853241</v>
+        <v>0.6898991465568543</v>
       </c>
       <c r="C30" s="1">
-        <v>232</v>
+        <v>468</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E30" s="1">
-        <v>232</v>
+        <v>76</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.6368299722671509</v>
+      </c>
+      <c r="C31" s="1">
+        <v>432</v>
+      </c>
+      <c r="D31" s="1">
+        <v>34852</v>
+      </c>
+      <c r="E31" s="1">
+        <v>360</v>
+      </c>
+      <c r="F31" s="1">
         <v>36</v>
       </c>
-      <c r="B31" s="2">
-        <v>0.4382171332836151</v>
-      </c>
-      <c r="C31" s="1">
-        <v>228</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>228</v>
-      </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4286071360111237</v>
+        <v>0.6029247045516968</v>
       </c>
       <c r="C32" s="1">
-        <v>223</v>
+        <v>409</v>
       </c>
       <c r="D32" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>214</v>
+        <v>392</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2888,25 +3567,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4266851246356964</v>
+        <v>0.566071093082428</v>
       </c>
       <c r="C33" s="1">
-        <v>222</v>
+        <v>384</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>222</v>
+        <v>332</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2914,22 +3593,22 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4036210477352142</v>
+        <v>0.5542779564857483</v>
       </c>
       <c r="C34" s="1">
-        <v>210</v>
+        <v>376</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -2940,19 +3619,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3920890390872955</v>
+        <v>0.5071053504943848</v>
       </c>
       <c r="C35" s="1">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2966,19 +3645,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3574929237365723</v>
+        <v>0.5012087821960449</v>
       </c>
       <c r="C36" s="1">
-        <v>186</v>
+        <v>340</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>186</v>
+        <v>340</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2992,25 +3671,25 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2">
-        <v>0.338272899389267</v>
+        <v>0.4658293426036835</v>
       </c>
       <c r="C37" s="1">
-        <v>176</v>
+        <v>316</v>
       </c>
       <c r="D37" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G37" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -3018,19 +3697,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3344288766384125</v>
+        <v>0.365587592124939</v>
       </c>
       <c r="C38" s="1">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -3044,19 +3723,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2">
-        <v>0.292144775390625</v>
+        <v>0.3508461713790894</v>
       </c>
       <c r="C39" s="1">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -3070,19 +3749,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2844567596912384</v>
+        <v>0.3420012891292572</v>
       </c>
       <c r="C40" s="1">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3096,25 +3775,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1998885273933411</v>
+        <v>0.3007252812385559</v>
       </c>
       <c r="C41" s="1">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="D41" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3122,22 +3801,22 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1883564889431</v>
+        <v>0.2889321446418762</v>
       </c>
       <c r="C42" s="1">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -3148,22 +3827,22 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1729804575443268</v>
+        <v>0.2771389782428742</v>
       </c>
       <c r="C43" s="1">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -3174,25 +3853,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1691364496946335</v>
+        <v>0.2697682678699493</v>
       </c>
       <c r="C44" s="1">
-        <v>88</v>
+        <v>183</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E44" s="1">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3200,25 +3879,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1691364496946335</v>
+        <v>0.2623975574970245</v>
       </c>
       <c r="C45" s="1">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="D45" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3226,25 +3905,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B46" s="2">
-        <v>0.165292426943779</v>
+        <v>0.2594492733478546</v>
       </c>
       <c r="C46" s="1">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3252,19 +3931,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B47" s="2">
-        <v>0.1460723876953125</v>
+        <v>0.2476561069488525</v>
       </c>
       <c r="C47" s="1">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E47" s="1">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3273,30 +3952,30 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B48" s="2">
-        <v>0.111476294696331</v>
+        <v>0.2299663871526718</v>
       </c>
       <c r="C48" s="1">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="D48" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -3304,19 +3983,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B49" s="2">
-        <v>0.09610024839639664</v>
+        <v>0.224069818854332</v>
       </c>
       <c r="C49" s="1">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3330,19 +4009,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B50" s="2">
-        <v>0.09225624054670334</v>
+        <v>0.2181732356548309</v>
       </c>
       <c r="C50" s="1">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3356,19 +4035,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B51" s="2">
-        <v>0.09225624054670334</v>
+        <v>0.2063800990581513</v>
       </c>
       <c r="C51" s="1">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3382,25 +4061,25 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B52" s="2">
-        <v>0.09225624054670334</v>
+        <v>0.2034318000078201</v>
       </c>
       <c r="C52" s="1">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="D52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="F52" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -3408,19 +4087,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B53" s="2">
-        <v>0.08456822484731674</v>
+        <v>0.2034318000078201</v>
       </c>
       <c r="C53" s="1">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3434,19 +4113,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B54" s="2">
-        <v>0.06919217854738236</v>
+        <v>0.1975352317094803</v>
       </c>
       <c r="C54" s="1">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3460,19 +4139,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B55" s="2">
-        <v>0.06919217854738236</v>
+        <v>0.1886903643608093</v>
       </c>
       <c r="C55" s="1">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3486,19 +4165,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B56" s="2">
-        <v>0.06919217854738236</v>
+        <v>0.1886903643608093</v>
       </c>
       <c r="C56" s="1">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3512,19 +4191,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06919217854738236</v>
+        <v>0.1827937960624695</v>
       </c>
       <c r="C57" s="1">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3538,19 +4217,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B58" s="2">
-        <v>0.06150416284799576</v>
+        <v>0.1768972277641296</v>
       </c>
       <c r="C58" s="1">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3564,19 +4243,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B59" s="2">
-        <v>0.05766015127301216</v>
+        <v>0.1768972277641296</v>
       </c>
       <c r="C59" s="1">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3590,19 +4269,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B60" s="2">
-        <v>0.05766015127301216</v>
+        <v>0.1651040762662888</v>
       </c>
       <c r="C60" s="1">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3616,19 +4295,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B61" s="2">
-        <v>0.04997213184833527</v>
+        <v>0.1592074930667877</v>
       </c>
       <c r="C61" s="1">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3642,25 +4321,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B62" s="2">
-        <v>0.03844010084867477</v>
+        <v>0.1533109247684479</v>
       </c>
       <c r="C62" s="1">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="D62" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E62" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -3668,19 +4347,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2">
-        <v>0.03459608927369118</v>
+        <v>0.147414356470108</v>
       </c>
       <c r="C63" s="1">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3694,19 +4373,19 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2">
-        <v>0.01537604071199894</v>
+        <v>0.1444660723209381</v>
       </c>
       <c r="C64" s="1">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3720,19 +4399,19 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B65" s="2">
-        <v>0.01537604071199894</v>
+        <v>0.1385694891214371</v>
       </c>
       <c r="C65" s="1">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3746,19 +4425,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B66" s="2">
-        <v>0.00768802035599947</v>
+        <v>0.1356212049722672</v>
       </c>
       <c r="C66" s="1">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
       </c>
       <c r="E66" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3772,19 +4451,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B67" s="2">
-        <v>0.00768802035599947</v>
+        <v>0.1326729208230972</v>
       </c>
       <c r="C67" s="1">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3798,59 +4477,2113 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B68" s="2">
-        <v>0.00768802035599947</v>
+        <v>0.1297246366739273</v>
       </c>
       <c r="C68" s="1">
+        <v>88</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>88</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.1267763376235962</v>
+      </c>
+      <c r="C69" s="1">
+        <v>86</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>86</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.1238280534744263</v>
+      </c>
+      <c r="C70" s="1">
+        <v>84</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>84</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.1238280534744263</v>
+      </c>
+      <c r="C71" s="1">
+        <v>84</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>84</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.1208797693252564</v>
+      </c>
+      <c r="C72" s="1">
+        <v>82</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>82</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.1149831935763359</v>
+      </c>
+      <c r="C73" s="1">
+        <v>78</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>78</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.1149831935763359</v>
+      </c>
+      <c r="C74" s="1">
+        <v>78</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>78</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.1090866178274155</v>
+      </c>
+      <c r="C75" s="1">
+        <v>74</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>74</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.1061383336782455</v>
+      </c>
+      <c r="C76" s="1">
+        <v>72</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>44</v>
+      </c>
+      <c r="F76" s="1">
+        <v>28</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.1061383336782455</v>
+      </c>
+      <c r="C77" s="1">
+        <v>72</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>72</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.1002417579293251</v>
+      </c>
+      <c r="C78" s="1">
+        <v>68</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>68</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2">
+        <v>0.09434518218040466</v>
+      </c>
+      <c r="C79" s="1">
+        <v>64</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>64</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" s="2">
+        <v>0.0855003222823143</v>
+      </c>
+      <c r="C80" s="1">
+        <v>58</v>
+      </c>
+      <c r="D80" s="1">
         <v>4</v>
       </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
+      <c r="E80" s="1">
+        <v>54</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
         <v>4</v>
       </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69">
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="2">
+        <v>0.07665546238422394</v>
+      </c>
+      <c r="C81" s="1">
+        <v>52</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>52</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="2">
+        <v>0.07665546238422394</v>
+      </c>
+      <c r="C82" s="1">
+        <v>52</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1">
+        <v>52</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="2">
+        <v>0.0707588866353035</v>
+      </c>
+      <c r="C83" s="1">
+        <v>48</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <v>48</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="2">
+        <v>0.0707588866353035</v>
+      </c>
+      <c r="C84" s="1">
+        <v>48</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1">
+        <v>48</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" s="2">
+        <v>0.0707588866353035</v>
+      </c>
+      <c r="C85" s="1">
+        <v>48</v>
+      </c>
+      <c r="D85" s="1">
+        <v>4</v>
+      </c>
+      <c r="E85" s="1">
+        <v>20</v>
+      </c>
+      <c r="F85" s="1">
+        <v>24</v>
+      </c>
+      <c r="G85" s="1">
+        <v>4</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>0.06486231833696365</v>
+      </c>
+      <c r="C86" s="1">
+        <v>44</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <v>44</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>0.06486231833696365</v>
+      </c>
+      <c r="C87" s="1">
+        <v>44</v>
+      </c>
+      <c r="D87" s="1">
+        <v>0</v>
+      </c>
+      <c r="E87" s="1">
+        <v>44</v>
+      </c>
+      <c r="F87" s="1">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>0.05896574258804321</v>
+      </c>
+      <c r="C88" s="1">
+        <v>40</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1">
+        <v>40</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2">
+        <v>0.05306916683912277</v>
+      </c>
+      <c r="C89" s="1">
+        <v>36</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0</v>
+      </c>
+      <c r="E89" s="1">
+        <v>36</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2">
+        <v>0.05306916683912277</v>
+      </c>
+      <c r="C90" s="1">
+        <v>36</v>
+      </c>
+      <c r="D90" s="1">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1">
+        <v>36</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2">
+        <v>0.05012087896466255</v>
+      </c>
+      <c r="C91" s="1">
+        <v>34</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0</v>
+      </c>
+      <c r="E91" s="1">
+        <v>34</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2">
+        <v>0.04127601906657219</v>
+      </c>
+      <c r="C92" s="1">
+        <v>28</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1">
+        <v>28</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2">
+        <v>0.03832773119211197</v>
+      </c>
+      <c r="C93" s="1">
+        <v>26</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0</v>
+      </c>
+      <c r="E93" s="1">
+        <v>26</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2">
+        <v>0.03537944331765175</v>
+      </c>
+      <c r="C94" s="1">
+        <v>24</v>
+      </c>
+      <c r="D94" s="1">
+        <v>0</v>
+      </c>
+      <c r="E94" s="1">
+        <v>24</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2">
+        <v>0.03537944331765175</v>
+      </c>
+      <c r="C95" s="1">
+        <v>24</v>
+      </c>
+      <c r="D95" s="1">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1">
+        <v>24</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2">
+        <v>0.03243115916848183</v>
+      </c>
+      <c r="C96" s="1">
+        <v>22</v>
+      </c>
+      <c r="D96" s="1">
+        <v>0</v>
+      </c>
+      <c r="E96" s="1">
+        <v>22</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2">
+        <v>0.02948287129402161</v>
+      </c>
+      <c r="C97" s="1">
+        <v>20</v>
+      </c>
+      <c r="D97" s="1">
+        <v>0</v>
+      </c>
+      <c r="E97" s="1">
+        <v>20</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2">
+        <v>0.02653458341956139</v>
+      </c>
+      <c r="C98" s="1">
+        <v>18</v>
+      </c>
+      <c r="D98" s="1">
+        <v>0</v>
+      </c>
+      <c r="E98" s="1">
+        <v>18</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2">
+        <v>0.02358629554510117</v>
+      </c>
+      <c r="C99" s="1">
+        <v>16</v>
+      </c>
+      <c r="D99" s="1">
+        <v>0</v>
+      </c>
+      <c r="E99" s="1">
+        <v>16</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2">
+        <v>0.02358629554510117</v>
+      </c>
+      <c r="C100" s="1">
+        <v>16</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0</v>
+      </c>
+      <c r="E100" s="1">
+        <v>16</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2">
+        <v>0.02358629554510117</v>
+      </c>
+      <c r="C101" s="1">
+        <v>16</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1">
+        <v>16</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0.0206380095332861</v>
+      </c>
+      <c r="C102" s="1">
+        <v>14</v>
+      </c>
+      <c r="D102" s="1">
+        <v>0</v>
+      </c>
+      <c r="E102" s="1">
+        <v>14</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0.01768972165882587</v>
+      </c>
+      <c r="C103" s="1">
+        <v>12</v>
+      </c>
+      <c r="D103" s="1">
+        <v>0</v>
+      </c>
+      <c r="E103" s="1">
+        <v>12</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0.01768972165882587</v>
+      </c>
+      <c r="C104" s="1">
+        <v>12</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1">
+        <v>12</v>
+      </c>
+      <c r="F104" s="1">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2">
+        <v>0.0147414356470108</v>
+      </c>
+      <c r="C105" s="1">
+        <v>10</v>
+      </c>
+      <c r="D105" s="1">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1">
+        <v>10</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0.0147414356470108</v>
+      </c>
+      <c r="C106" s="1">
+        <v>10</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="1">
+        <v>10</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2">
+        <v>0.0147414356470108</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10</v>
+      </c>
+      <c r="D107" s="1">
+        <v>0</v>
+      </c>
+      <c r="E107" s="1">
+        <v>10</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2">
+        <v>0.0147414356470108</v>
+      </c>
+      <c r="C108" s="1">
+        <v>10</v>
+      </c>
+      <c r="D108" s="1">
+        <v>0</v>
+      </c>
+      <c r="E108" s="1">
+        <v>10</v>
+      </c>
+      <c r="F108" s="1">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2">
+        <v>0.0147414356470108</v>
+      </c>
+      <c r="C109" s="1">
+        <v>10</v>
+      </c>
+      <c r="D109" s="1">
+        <v>0</v>
+      </c>
+      <c r="E109" s="1">
+        <v>10</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2">
+        <v>0.0147414356470108</v>
+      </c>
+      <c r="C110" s="1">
+        <v>10</v>
+      </c>
+      <c r="D110" s="1">
+        <v>0</v>
+      </c>
+      <c r="E110" s="1">
+        <v>10</v>
+      </c>
+      <c r="F110" s="1">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2">
+        <v>0.01179314777255058</v>
+      </c>
+      <c r="C111" s="1">
+        <v>8</v>
+      </c>
+      <c r="D111" s="1">
+        <v>0</v>
+      </c>
+      <c r="E111" s="1">
+        <v>8</v>
+      </c>
+      <c r="F111" s="1">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2">
+        <v>0.01179314777255058</v>
+      </c>
+      <c r="C112" s="1">
+        <v>8</v>
+      </c>
+      <c r="D112" s="1">
+        <v>0</v>
+      </c>
+      <c r="E112" s="1">
+        <v>8</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" s="2">
+        <v>0.01179314777255058</v>
+      </c>
+      <c r="C113" s="1">
+        <v>8</v>
+      </c>
+      <c r="D113" s="1">
+        <v>96</v>
+      </c>
+      <c r="E113" s="1">
+        <v>8</v>
+      </c>
+      <c r="F113" s="1">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2">
+        <v>0.01179314777255058</v>
+      </c>
+      <c r="C114" s="1">
+        <v>8</v>
+      </c>
+      <c r="D114" s="1">
+        <v>0</v>
+      </c>
+      <c r="E114" s="1">
+        <v>8</v>
+      </c>
+      <c r="F114" s="1">
+        <v>0</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2">
+        <v>0.01179314777255058</v>
+      </c>
+      <c r="C115" s="1">
+        <v>8</v>
+      </c>
+      <c r="D115" s="1">
+        <v>0</v>
+      </c>
+      <c r="E115" s="1">
+        <v>8</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C116" s="1">
+        <v>6</v>
+      </c>
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>6</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C117" s="1">
+        <v>6</v>
+      </c>
+      <c r="D117" s="1">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1">
+        <v>6</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C118" s="1">
+        <v>6</v>
+      </c>
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>6</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C119" s="1">
+        <v>6</v>
+      </c>
+      <c r="D119" s="1">
+        <v>0</v>
+      </c>
+      <c r="E119" s="1">
+        <v>6</v>
+      </c>
+      <c r="F119" s="1">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C120" s="1">
+        <v>6</v>
+      </c>
+      <c r="D120" s="1">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1">
+        <v>6</v>
+      </c>
+      <c r="F120" s="1">
+        <v>0</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C121" s="1">
+        <v>6</v>
+      </c>
+      <c r="D121" s="1">
+        <v>0</v>
+      </c>
+      <c r="E121" s="1">
+        <v>6</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C122" s="1">
+        <v>6</v>
+      </c>
+      <c r="D122" s="1">
+        <v>0</v>
+      </c>
+      <c r="E122" s="1">
+        <v>6</v>
+      </c>
+      <c r="F122" s="1">
+        <v>0</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C123" s="1">
+        <v>6</v>
+      </c>
+      <c r="D123" s="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1">
+        <v>6</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C124" s="1">
+        <v>6</v>
+      </c>
+      <c r="D124" s="1">
+        <v>0</v>
+      </c>
+      <c r="E124" s="1">
+        <v>6</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C125" s="1">
+        <v>6</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0</v>
+      </c>
+      <c r="E125" s="1">
+        <v>6</v>
+      </c>
+      <c r="F125" s="1">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C126" s="1">
+        <v>6</v>
+      </c>
+      <c r="D126" s="1">
+        <v>0</v>
+      </c>
+      <c r="E126" s="1">
+        <v>6</v>
+      </c>
+      <c r="F126" s="1">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C127" s="1">
+        <v>6</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0</v>
+      </c>
+      <c r="E127" s="1">
+        <v>6</v>
+      </c>
+      <c r="F127" s="1">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C128" s="1">
+        <v>6</v>
+      </c>
+      <c r="D128" s="1">
+        <v>0</v>
+      </c>
+      <c r="E128" s="1">
+        <v>6</v>
+      </c>
+      <c r="F128" s="1">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C129" s="1">
+        <v>6</v>
+      </c>
+      <c r="D129" s="1">
+        <v>0</v>
+      </c>
+      <c r="E129" s="1">
+        <v>6</v>
+      </c>
+      <c r="F129" s="1">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C130" s="1">
+        <v>6</v>
+      </c>
+      <c r="D130" s="1">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1">
+        <v>6</v>
+      </c>
+      <c r="F130" s="1">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C131" s="1">
+        <v>6</v>
+      </c>
+      <c r="D131" s="1">
+        <v>0</v>
+      </c>
+      <c r="E131" s="1">
+        <v>6</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C132" s="1">
+        <v>6</v>
+      </c>
+      <c r="D132" s="1">
+        <v>0</v>
+      </c>
+      <c r="E132" s="1">
+        <v>6</v>
+      </c>
+      <c r="F132" s="1">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C133" s="1">
+        <v>6</v>
+      </c>
+      <c r="D133" s="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1">
+        <v>6</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C134" s="1">
+        <v>6</v>
+      </c>
+      <c r="D134" s="1">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1">
+        <v>6</v>
+      </c>
+      <c r="F134" s="1">
+        <v>0</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C135" s="1">
+        <v>6</v>
+      </c>
+      <c r="D135" s="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1">
+        <v>6</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C136" s="1">
+        <v>6</v>
+      </c>
+      <c r="D136" s="1">
+        <v>0</v>
+      </c>
+      <c r="E136" s="1">
+        <v>6</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2">
+        <v>0.008844860829412937</v>
+      </c>
+      <c r="C137" s="1">
+        <v>6</v>
+      </c>
+      <c r="D137" s="1">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1">
+        <v>6</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.005896573886275291</v>
+      </c>
+      <c r="C138" s="1">
+        <v>4</v>
+      </c>
+      <c r="D138" s="1">
+        <v>0</v>
+      </c>
+      <c r="E138" s="1">
+        <v>4</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2">
+        <v>0.005896573886275291</v>
+      </c>
+      <c r="C139" s="1">
+        <v>4</v>
+      </c>
+      <c r="D139" s="1">
+        <v>0</v>
+      </c>
+      <c r="E139" s="1">
+        <v>4</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.005896573886275291</v>
+      </c>
+      <c r="C140" s="1">
+        <v>4</v>
+      </c>
+      <c r="D140" s="1">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1">
+        <v>4</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C141" s="1">
+        <v>2</v>
+      </c>
+      <c r="D141" s="1">
+        <v>0</v>
+      </c>
+      <c r="E141" s="1">
+        <v>2</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C142" s="1">
+        <v>2</v>
+      </c>
+      <c r="D142" s="1">
+        <v>0</v>
+      </c>
+      <c r="E142" s="1">
+        <v>2</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C143" s="1">
+        <v>2</v>
+      </c>
+      <c r="D143" s="1">
+        <v>0</v>
+      </c>
+      <c r="E143" s="1">
+        <v>2</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C144" s="1">
+        <v>2</v>
+      </c>
+      <c r="D144" s="1">
+        <v>0</v>
+      </c>
+      <c r="E144" s="1">
+        <v>2</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C145" s="1">
+        <v>2</v>
+      </c>
+      <c r="D145" s="1">
+        <v>0</v>
+      </c>
+      <c r="E145" s="1">
+        <v>2</v>
+      </c>
+      <c r="F145" s="1">
+        <v>0</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C146" s="1">
+        <v>2</v>
+      </c>
+      <c r="D146" s="1">
+        <v>0</v>
+      </c>
+      <c r="E146" s="1">
+        <v>2</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2">
+        <v>0.002948286943137646</v>
+      </c>
+      <c r="C147" s="1">
+        <v>2</v>
+      </c>
+      <c r="D147" s="1">
+        <v>0</v>
+      </c>
+      <c r="E147" s="1">
+        <v>2</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+      <c r="B148">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C69">
+      <c r="C148">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D69">
+      <c r="D148">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E69">
+      <c r="E148">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F69">
+      <c r="F148">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G69">
+      <c r="G148">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H69">
+      <c r="H148">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
   <si>
     <t>atk_f407</t>
   </si>
@@ -38,9 +38,6 @@
     <t>usart.o</t>
   </si>
   <si>
-    <t>ai_lib.o</t>
-  </si>
-  <si>
     <t>c_w.l</t>
   </si>
   <si>
@@ -53,6 +50,9 @@
     <t>lcd.o</t>
   </si>
   <si>
+    <t>can.o</t>
+  </si>
+  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -86,201 +86,168 @@
     <t>usbd_ctlreq.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_pcd.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_ll_usb.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_uart.o</t>
+  </si>
+  <si>
+    <t>btod.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_rcc.o</t>
+  </si>
+  <si>
+    <t>_printf_fp_dec.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_dma.o</t>
+  </si>
+  <si>
+    <t>usbd_core.o</t>
+  </si>
+  <si>
+    <t>_printf_fp_hex.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_can.o</t>
+  </si>
+  <si>
     <t>fz_wm.l</t>
   </si>
   <si>
-    <t>stm32f4xx_hal_pcd.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_ll_usb.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_uart.o</t>
-  </si>
-  <si>
-    <t>output_array.o</t>
-  </si>
-  <si>
-    <t>btod.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_rcc.o</t>
+    <t>stm32f4xx_hal_gpio.o</t>
+  </si>
+  <si>
+    <t>__printf_flags_ss_wp.o</t>
+  </si>
+  <si>
+    <t>bigflt0.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_cortex.o</t>
+  </si>
+  <si>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>lc_ctype_c.o</t>
+  </si>
+  <si>
+    <t>lludivv7m.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_ll_fsmc.o</t>
+  </si>
+  <si>
+    <t>sys.o</t>
+  </si>
+  <si>
+    <t>_printf_wctomb.o</t>
+  </si>
+  <si>
+    <t>_printf_hex_int_ll_ptr.o</t>
+  </si>
+  <si>
+    <t>_printf_intcommon.o</t>
+  </si>
+  <si>
+    <t>dnaninf.o</t>
+  </si>
+  <si>
+    <t>led.o</t>
+  </si>
+  <si>
+    <t>list.o</t>
+  </si>
+  <si>
+    <t>rt_memcpy_v6.o</t>
+  </si>
+  <si>
+    <t>lludiv10.o</t>
+  </si>
+  <si>
+    <t>usbd_ioreq.o</t>
+  </si>
+  <si>
+    <t>strcmpv7m.o</t>
+  </si>
+  <si>
+    <t>_printf_fp_infnan.o</t>
+  </si>
+  <si>
+    <t>_printf_longlong_dec.o</t>
+  </si>
+  <si>
+    <t>_printf_dec.o</t>
+  </si>
+  <si>
+    <t>_printf_oct_int_ll.o</t>
+  </si>
+  <si>
+    <t>rt_memcpy_w.o</t>
+  </si>
+  <si>
+    <t>dfixu.o</t>
+  </si>
+  <si>
+    <t>stm32f4xx_hal_sram.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
+  </si>
+  <si>
+    <t>_printf_str.o</t>
+  </si>
+  <si>
+    <t>rt_memclr_w.o</t>
+  </si>
+  <si>
+    <t>_printf_pad.o</t>
+  </si>
+  <si>
+    <t>sys_stackheap_outer.o</t>
+  </si>
+  <si>
+    <t>lc_numeric_c.o</t>
+  </si>
+  <si>
+    <t>rt_memclr.o</t>
+  </si>
+  <si>
+    <t>_wcrtomb.o</t>
+  </si>
+  <si>
+    <t>vsnprintf.o</t>
+  </si>
+  <si>
+    <t>__scatter.o</t>
   </si>
   <si>
     <t>m_wm.l</t>
   </si>
   <si>
-    <t>_printf_fp_dec.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_dma.o</t>
-  </si>
-  <si>
-    <t>exp.o</t>
-  </si>
-  <si>
-    <t>usbd_core.o</t>
-  </si>
-  <si>
-    <t>daddsub_clz.o</t>
-  </si>
-  <si>
-    <t>_printf_fp_hex.o</t>
-  </si>
-  <si>
-    <t>ddiv.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_gpio.o</t>
-  </si>
-  <si>
-    <t>__printf_flags_ss_wp.o</t>
-  </si>
-  <si>
-    <t>bigflt0.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_cortex.o</t>
-  </si>
-  <si>
-    <t>dmul.o</t>
-  </si>
-  <si>
-    <t>lc_ctype_c.o</t>
-  </si>
-  <si>
-    <t>poly.o</t>
-  </si>
-  <si>
-    <t>lludivv7m.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_ll_fsmc.o</t>
-  </si>
-  <si>
-    <t>sys.o</t>
-  </si>
-  <si>
-    <t>_printf_wctomb.o</t>
-  </si>
-  <si>
-    <t>_printf_hex_int_ll_ptr.o</t>
-  </si>
-  <si>
-    <t>_printf_intcommon.o</t>
-  </si>
-  <si>
-    <t>dnaninf.o</t>
-  </si>
-  <si>
-    <t>led.o</t>
-  </si>
-  <si>
-    <t>list.o</t>
-  </si>
-  <si>
-    <t>fnaninf.o</t>
-  </si>
-  <si>
-    <t>rt_memcpy_v6.o</t>
-  </si>
-  <si>
-    <t>lludiv10.o</t>
-  </si>
-  <si>
-    <t>usbd_ioreq.o</t>
-  </si>
-  <si>
-    <t>strcmpv7m.o</t>
-  </si>
-  <si>
-    <t>_printf_fp_infnan.o</t>
-  </si>
-  <si>
-    <t>_printf_longlong_dec.o</t>
-  </si>
-  <si>
-    <t>dleqf.o</t>
-  </si>
-  <si>
-    <t>_printf_dec.o</t>
-  </si>
-  <si>
-    <t>_printf_oct_int_ll.o</t>
-  </si>
-  <si>
-    <t>drleqf.o</t>
-  </si>
-  <si>
-    <t>rt_memcpy_w.o</t>
-  </si>
-  <si>
-    <t>d2f.o</t>
-  </si>
-  <si>
-    <t>dfix.o</t>
-  </si>
-  <si>
-    <t>dfixu.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_sram.o</t>
-  </si>
-  <si>
-    <t>f2d.o</t>
-  </si>
-  <si>
-    <t>dunder.o</t>
+    <t>fpclassify.o</t>
+  </si>
+  <si>
+    <t>_printf_char_common.o</t>
+  </si>
+  <si>
+    <t>_printf_wchar.o</t>
+  </si>
+  <si>
+    <t>_printf_char.o</t>
+  </si>
+  <si>
+    <t>_printf_charcount.o</t>
   </si>
   <si>
     <t>dflt_clz.o</t>
   </si>
   <si>
-    <t>_printf_str.o</t>
-  </si>
-  <si>
-    <t>rt_memclr_w.o</t>
-  </si>
-  <si>
-    <t>_printf_pad.o</t>
-  </si>
-  <si>
-    <t>sys_stackheap_outer.o</t>
-  </si>
-  <si>
-    <t>lc_numeric_c.o</t>
-  </si>
-  <si>
-    <t>main.o</t>
-  </si>
-  <si>
-    <t>rt_memclr.o</t>
-  </si>
-  <si>
-    <t>_wcrtomb.o</t>
-  </si>
-  <si>
-    <t>vsnprintf.o</t>
-  </si>
-  <si>
-    <t>__scatter.o</t>
-  </si>
-  <si>
-    <t>fpclassify.o</t>
-  </si>
-  <si>
-    <t>_printf_char_common.o</t>
-  </si>
-  <si>
-    <t>_printf_wchar.o</t>
-  </si>
-  <si>
-    <t>_printf_char.o</t>
-  </si>
-  <si>
-    <t>_printf_charcount.o</t>
-  </si>
-  <si>
     <t>_printf_truncate.o</t>
   </si>
   <si>
@@ -296,15 +263,9 @@
     <t>__scatter_copy.o</t>
   </si>
   <si>
-    <t>dcmpi.o</t>
-  </si>
-  <si>
     <t>__2printf.o</t>
   </si>
   <si>
-    <t>_rserrno.o</t>
-  </si>
-  <si>
     <t>stm32f4xx_it.o</t>
   </si>
   <si>
@@ -329,9 +290,6 @@
     <t>__rtentry2.o</t>
   </si>
   <si>
-    <t>fretinf.o</t>
-  </si>
-  <si>
     <t>fpinit.o</t>
   </si>
   <si>
@@ -348,9 +306,6 @@
   </si>
   <si>
     <t>rt_locale_intlibspace.o</t>
-  </si>
-  <si>
-    <t>rt_errno_addr_intlibspace.o</t>
   </si>
   <si>
     <t>ferror.o</t>
@@ -572,9 +527,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$148</c:f>
+              <c:f>ram_percent!$A$3:$A$133</c:f>
               <c:strCache>
-                <c:ptCount val="146"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -594,19 +549,19 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>ai_lib.o</c:v>
+                  <c:v>c_w.l</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>c_w.l</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>libspace.o</c:v>
+                  <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>dma.o</c:v>
+                  <c:v>lcd.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>lcd.o</c:v>
+                  <c:v>can.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>queue.o</c:v>
@@ -641,7 +596,7 @@
                 <c:pt idx="21">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="130">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -649,77 +604,77 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$148</c:f>
+              <c:f>ram_percent!$B$3:$B$133</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="146"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
-                  <c:v>55.90615463256836</c:v>
+                  <c:v>56.00801849365234</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.61534881591797</c:v>
+                  <c:v>39.68752670288086</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.17418384552002</c:v>
+                  <c:v>1.176323175430298</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.16395378112793</c:v>
+                  <c:v>1.166074514389038</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9138855934143066</c:v>
+                  <c:v>0.915550708770752</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3125852644443512</c:v>
+                  <c:v>0.3131547868251801</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2864417433738709</c:v>
+                  <c:v>0.1093194857239723</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1091206669807434</c:v>
+                  <c:v>0.1093194857239723</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1091206669807434</c:v>
+                  <c:v>0.1093194857239723</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1091206669807434</c:v>
+                  <c:v>0.1070419996976852</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1068473234772682</c:v>
+                  <c:v>0.1047645062208176</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07274711132049561</c:v>
+                  <c:v>0.07287965714931488</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06820041686296463</c:v>
+                  <c:v>0.06832467764616013</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01364008337259293</c:v>
+                  <c:v>0.01366493571549654</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0102300625294447</c:v>
+                  <c:v>0.01024870201945305</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.004546694457530975</c:v>
+                  <c:v>0.00455497857183218</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.004546694457530975</c:v>
+                  <c:v>0.00455497857183218</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.004546694457530975</c:v>
+                  <c:v>0.00455497857183218</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004546694457530975</c:v>
+                  <c:v>0.00455497857183218</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004546694457530975</c:v>
+                  <c:v>0.00455497857183218</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.004546694457530975</c:v>
+                  <c:v>0.00455497857183218</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.001136673614382744</c:v>
-                </c:pt>
-                <c:pt idx="145">
+                  <c:v>0.001138744642958045</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -787,9 +742,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$148</c:f>
+              <c:f>flash_percent!$A$3:$A$133</c:f>
               <c:strCache>
-                <c:ptCount val="146"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
@@ -800,432 +755,387 @@
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>stm32f4xx_hal_pcd.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>stm32f4xx_ll_usb.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>stm32f4xx_hal_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>usbd_ctlreq.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>btod.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>stm32f4xx_hal_rcc.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>queue.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>port.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>timers.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>_printf_fp_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>stm32f4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>usbd_core.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>heap_4.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>_printf_fp_hex.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>stm32f4xx_hal_can.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>fz_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>stm32f4xx_hal_pcd.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>stm32f4xx_ll_usb.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>stm32f4xx_hal_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>output_array.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>usbd_ctlreq.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>btod.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>stm32f4xx_hal_rcc.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>queue.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
+                  <c:v>stm32f4xx_hal_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>usbd_conf.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>startup_stm32f407xx.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>__printf_flags_ss_wp.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>bigflt0.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>stm32f4xx_hal_cortex.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>can.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>lc_ctype_c.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>lludivv7m.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>malloc.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>sys.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>_printf_wctomb.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>_printf_hex_int_ll_ptr.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>stm32f4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>_printf_intcommon.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>delay.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>dnaninf.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>led.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>list.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>rt_memcpy_v6.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>lludiv10.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>usbd_ioreq.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>strcmpv7m.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>_printf_fp_infnan.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>_printf_longlong_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>_printf_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>_printf_oct_int_ll.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>ai_task.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>led_task.o</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>rt_memcpy_w.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>freertos_start.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>dfixu.o</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>stm32f4xx_hal_sram.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>_printf_str.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>rt_memclr_w.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>_printf_pad.o</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>sys_stackheap_outer.o</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>lc_numeric_c.o</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>rt_memclr.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>_wcrtomb.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>key_task.o</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>vsnprintf.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>__scatter.o</c:v>
+                </c:pt>
+                <c:pt idx="67">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>timers.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>_printf_fp_dec.o</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>stm32f4xx_hal_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>exp.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>usbd_core.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>daddsub_clz.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>_printf_fp_hex.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>ai_lib.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>ddiv.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>stm32f4xx_hal_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>usbd_conf.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>startup_stm32f407xx.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>malloc.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>__printf_flags_ss_wp.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>ai_task.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>bigflt0.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>stm32f4xx_hal_cortex.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>lc_ctype_c.o</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>poly.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>lludivv7m.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>sys.o</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>_printf_wctomb.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>_printf_hex_int_ll_ptr.o</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>stm32f4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>_printf_intcommon.o</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>delay.o</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>dma.o</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>dnaninf.o</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>led.o</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>list.o</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>fnaninf.o</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>rt_memcpy_v6.o</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>lludiv10.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>usbd_ioreq.o</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>strcmpv7m.o</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>_printf_fp_infnan.o</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>_printf_longlong_dec.o</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>dleqf.o</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>_printf_dec.o</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>_printf_oct_int_ll.o</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>drleqf.o</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>led_task.o</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>rt_memcpy_w.o</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>d2f.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>dfix.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>freertos_start.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>dfixu.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>stm32f4xx_hal_sram.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>f2d.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>dunder.o</c:v>
-                </c:pt>
                 <c:pt idx="68">
+                  <c:v>fpclassify.o</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>_printf_char_common.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>system_stm32f4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>_printf_wchar.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>_printf_char.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>_printf_charcount.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>dflt_clz.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
-                  <c:v>_printf_str.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>rt_memclr_w.o</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>_printf_pad.o</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>sys_stackheap_outer.o</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>lc_numeric_c.o</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>main.o</c:v>
-                </c:pt>
                 <c:pt idx="75">
-                  <c:v>rt_memclr.o</c:v>
+                  <c:v>_printf_truncate.o</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>_wcrtomb.o</c:v>
+                  <c:v>_printf_char_file.o</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>key_task.o</c:v>
+                  <c:v>libinit2.o</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>vsnprintf.o</c:v>
+                  <c:v>__scatter_zi.o</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>__scatter.o</c:v>
+                  <c:v>__scatter_copy.o</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>fpclassify.o</c:v>
+                  <c:v>__2printf.o</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>_printf_char_common.o</c:v>
+                  <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>system_stm32f4xx.o</c:v>
+                  <c:v>exit.o</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>_printf_wchar.o</c:v>
+                  <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>_printf_char.o</c:v>
+                  <c:v>aeabi_memset.o</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>_printf_charcount.o</c:v>
+                  <c:v>_snputc.o</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>_printf_truncate.o</c:v>
+                  <c:v>__printf_wp.o</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>_printf_char_file.o</c:v>
+                  <c:v>dretinf.o</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>libinit2.o</c:v>
+                  <c:v>__rtentry2.o</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>__scatter_zi.o</c:v>
+                  <c:v>fpinit.o</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>__scatter_copy.o</c:v>
+                  <c:v>rtexit2.o</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>dcmpi.o</c:v>
+                  <c:v>_sputc.o</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>__2printf.o</c:v>
+                  <c:v>_printf_ll.o</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>_rserrno.o</c:v>
+                  <c:v>_printf_l.o</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>stm32f4xx_it.o</c:v>
+                  <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>exit.o</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>rt_ctype_table.o</c:v>
+                  <c:v>ferror.o</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>aeabi_memset.o</c:v>
+                  <c:v>__main.o</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>_snputc.o</c:v>
+                  <c:v>heapauxi.o</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>__printf_wp.o</c:v>
+                  <c:v>_printf_x.o</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>dretinf.o</c:v>
+                  <c:v>_printf_u.o</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>__rtentry2.o</c:v>
+                  <c:v>_printf_s.o</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>fretinf.o</c:v>
+                  <c:v>_printf_p.o</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>fpinit.o</c:v>
+                  <c:v>_printf_o.o</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>rtexit2.o</c:v>
+                  <c:v>_printf_n.o</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>_sputc.o</c:v>
+                  <c:v>_printf_ls.o</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>_printf_ll.o</c:v>
+                  <c:v>_printf_llx.o</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>_printf_l.o</c:v>
+                  <c:v>_printf_llu.o</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>rt_locale_intlibspace.o</c:v>
+                  <c:v>_printf_llo.o</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>rt_errno_addr_intlibspace.o</c:v>
+                  <c:v>_printf_lli.o</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>libspace.o</c:v>
+                  <c:v>_printf_lld.o</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>ferror.o</c:v>
+                  <c:v>_printf_lc.o</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>__main.o</c:v>
+                  <c:v>_printf_i.o</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>heapauxi.o</c:v>
+                  <c:v>_printf_g.o</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>_printf_x.o</c:v>
+                  <c:v>_printf_f.o</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>_printf_u.o</c:v>
+                  <c:v>_printf_e.o</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>_printf_s.o</c:v>
+                  <c:v>_printf_d.o</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>_printf_p.o</c:v>
+                  <c:v>_printf_c.o</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>_printf_o.o</c:v>
+                  <c:v>_printf_a.o</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>_printf_n.o</c:v>
+                  <c:v>__rtentry4.o</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>_printf_ls.o</c:v>
+                  <c:v>printf2.o</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>_printf_llx.o</c:v>
+                  <c:v>printf1.o</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>_printf_llu.o</c:v>
+                  <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>_printf_llo.o</c:v>
+                  <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>_printf_lli.o</c:v>
+                  <c:v>use_no_semi.o</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>_printf_lld.o</c:v>
+                  <c:v>rtexit.o</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>_printf_lc.o</c:v>
+                  <c:v>libshutdown2.o</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>_printf_i.o</c:v>
+                  <c:v>libshutdown.o</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>_printf_g.o</c:v>
+                  <c:v>libinit.o</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>_printf_f.o</c:v>
+                  <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>_printf_e.o</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>_printf_d.o</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>_printf_c.o</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>_printf_a.o</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>__rtentry4.o</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>printf2.o</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>printf1.o</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>_printf_percent_end.o</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>use_no_semi_2.o</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>use_no_semi.o</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>rtexit.o</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>libshutdown2.o</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>libshutdown.o</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>libinit.o</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="145">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1233,446 +1143,401 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$148</c:f>
+              <c:f>flash_percent!$B$3:$B$133</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="146"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
-                  <c:v>19.53535079956055</c:v>
+                  <c:v>22.69877624511719</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.79757022857666</c:v>
+                  <c:v>13.65660667419434</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.887729167938232</c:v>
+                  <c:v>6.841149806976318</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.266171455383301</c:v>
+                  <c:v>4.569901466369629</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.933014869689941</c:v>
+                  <c:v>4.374636173248291</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.764962673187256</c:v>
+                  <c:v>3.809393405914307</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.278495311737061</c:v>
+                  <c:v>3.523346185684204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.225425958633423</c:v>
+                  <c:v>3.31609058380127</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.032313108444214</c:v>
+                  <c:v>3.117399215698242</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.853941917419434</c:v>
+                  <c:v>2.696036338806152</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.682941198348999</c:v>
+                  <c:v>2.010893821716309</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.32030200958252</c:v>
+                  <c:v>1.887568116188049</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.951766014099121</c:v>
+                  <c:v>1.80535101890564</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.730644464492798</c:v>
+                  <c:v>1.675173878669739</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.624506115913391</c:v>
+                  <c:v>1.521016716957092</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.553747296333313</c:v>
+                  <c:v>1.507313847541809</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.441712379455566</c:v>
+                  <c:v>1.373711109161377</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.391591429710388</c:v>
+                  <c:v>1.298345327377319</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.30903947353363</c:v>
+                  <c:v>1.217841148376465</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.297246336936951</c:v>
+                  <c:v>1.120208263397217</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.217642545700073</c:v>
+                  <c:v>0.9043883681297302</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.182263135910034</c:v>
+                  <c:v>0.8718440532684326</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.155728578567505</c:v>
+                  <c:v>0.801616907119751</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.048116087913513</c:v>
+                  <c:v>0.7005583643913269</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.01421070098877</c:v>
+                  <c:v>0.6440341472625732</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7783477902412415</c:v>
+                  <c:v>0.5892227292060852</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.7503390312194824</c:v>
+                  <c:v>0.5823712944984436</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6898991465568543</c:v>
+                  <c:v>0.5481141209602356</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.6368299722671509</c:v>
+                  <c:v>0.5412627458572388</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.6029247045516968</c:v>
+                  <c:v>0.4076598882675171</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.566071093082428</c:v>
+                  <c:v>0.3973827660083771</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.5542779564857483</c:v>
+                  <c:v>0.3836798965930939</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.5071053504943848</c:v>
+                  <c:v>0.3494227528572083</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.5012087821960449</c:v>
+                  <c:v>0.3357199132442474</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4658293426036835</c:v>
+                  <c:v>0.3220170736312866</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.365587592124939</c:v>
+                  <c:v>0.3134527802467346</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3508461713790894</c:v>
+                  <c:v>0.3048884868621826</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3420012891292572</c:v>
+                  <c:v>0.3014627695083618</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3007252812385559</c:v>
+                  <c:v>0.287759929895401</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2889321446418762</c:v>
+                  <c:v>0.2672056555747986</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2771389782428742</c:v>
+                  <c:v>0.260354220867157</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2697682678699493</c:v>
+                  <c:v>0.2535027861595154</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2623975574970245</c:v>
+                  <c:v>0.2363742291927338</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2594492733478546</c:v>
+                  <c:v>0.2363742291927338</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2476561069488525</c:v>
+                  <c:v>0.2295227944850922</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2299663871526718</c:v>
+                  <c:v>0.219245657324791</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.224069818854332</c:v>
+                  <c:v>0.219245657324791</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2181732356548309</c:v>
+                  <c:v>0.2123942375183106</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2063800990581513</c:v>
+                  <c:v>0.205542802810669</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2034318000078201</c:v>
+                  <c:v>0.1918399482965469</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.2034318000078201</c:v>
+                  <c:v>0.1849885284900665</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1975352317094803</c:v>
+                  <c:v>0.1781370937824249</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1886903643608093</c:v>
+                  <c:v>0.1712856739759445</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1886903643608093</c:v>
+                  <c:v>0.1575828194618225</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1827937960624695</c:v>
+                  <c:v>0.1541571021080017</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1768972277641296</c:v>
+                  <c:v>0.1507313847541809</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1768972277641296</c:v>
+                  <c:v>0.1507313847541809</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1651040762662888</c:v>
+                  <c:v>0.1404542475938797</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1592074930667877</c:v>
+                  <c:v>0.1336028277873993</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1533109247684479</c:v>
+                  <c:v>0.1336028277873993</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.147414356470108</c:v>
+                  <c:v>0.1267513930797577</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1444660723209381</c:v>
+                  <c:v>0.1233256831765175</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1385694891214371</c:v>
+                  <c:v>0.1164742559194565</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1356212049722672</c:v>
+                  <c:v>0.1096228286623955</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1326729208230972</c:v>
+                  <c:v>0.09934569150209427</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.1297246366739273</c:v>
+                  <c:v>0.08906854689121246</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.1267763376235962</c:v>
+                  <c:v>0.08906854689121246</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.1238280534744263</c:v>
+                  <c:v>0.08221711963415146</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.1238280534744263</c:v>
+                  <c:v>0.08221711963415146</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.1208797693252564</c:v>
+                  <c:v>0.08221711963415146</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.1149831935763359</c:v>
+                  <c:v>0.08221711963415146</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.1149831935763359</c:v>
+                  <c:v>0.07536569237709045</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.1090866178274155</c:v>
+                  <c:v>0.07536569237709045</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.1061383336782455</c:v>
+                  <c:v>0.06851426512002945</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.1061383336782455</c:v>
+                  <c:v>0.06508855521678925</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.1002417579293251</c:v>
+                  <c:v>0.06166284158825874</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.09434518218040466</c:v>
+                  <c:v>0.06166284158825874</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.0855003222823143</c:v>
+                  <c:v>0.05823712795972824</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.07665546238422394</c:v>
+                  <c:v>0.04795998707413673</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.07665546238422394</c:v>
+                  <c:v>0.04453427344560623</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.0707588866353035</c:v>
+                  <c:v>0.04110855981707573</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.0707588866353035</c:v>
+                  <c:v>0.03425713256001473</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.0707588866353035</c:v>
+                  <c:v>0.03083142079412937</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.06486231833696365</c:v>
+                  <c:v>0.02740570716559887</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.06486231833696365</c:v>
+                  <c:v>0.02740570716559887</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.05896574258804321</c:v>
+                  <c:v>0.02740570716559887</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.05306916683912277</c:v>
+                  <c:v>0.02397999353706837</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.05306916683912277</c:v>
+                  <c:v>0.02055427990853787</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.05012087896466255</c:v>
+                  <c:v>0.02055427990853787</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.04127601906657219</c:v>
+                  <c:v>0.01712856628000736</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.03832773119211197</c:v>
+                  <c:v>0.01712856628000736</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.03537944331765175</c:v>
+                  <c:v>0.01712856628000736</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.03537944331765175</c:v>
+                  <c:v>0.01712856628000736</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.03243115916848183</c:v>
+                  <c:v>0.01712856628000736</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.02948287129402161</c:v>
+                  <c:v>0.01370285358279944</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.02653458341956139</c:v>
+                  <c:v>0.01370285358279944</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.02358629554510117</c:v>
+                  <c:v>0.01370285358279944</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.02358629554510117</c:v>
+                  <c:v>0.01370285358279944</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.02358629554510117</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.0206380095332861</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01768972165882587</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01768972165882587</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.0147414356470108</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.0147414356470108</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.0147414356470108</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.0147414356470108</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.0147414356470108</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.0147414356470108</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.01179314777255058</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.01179314777255058</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.01179314777255058</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.01179314777255058</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.01179314777255058</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.01027713995426893</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.006851426791399717</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.006851426791399717</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.006851426791399717</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.008844860829412937</c:v>
+                  <c:v>0.003425713395699859</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.008844860829412937</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>0.008844860829412937</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>0.008844860829412937</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>0.008844860829412937</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>0.008844860829412937</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>0.005896573886275291</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>0.005896573886275291</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>0.005896573886275291</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>0.002948286943137646</c:v>
-                </c:pt>
-                <c:pt idx="145">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1777,8 +1642,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H148" totalsRowCount="1">
-  <autoFilter ref="A2:H147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H133" totalsRowCount="1">
+  <autoFilter ref="A2:H132"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1794,8 +1659,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H148" totalsRowCount="1">
-  <autoFilter ref="A2:H147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H133" totalsRowCount="1">
+  <autoFilter ref="A2:H132"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2095,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2108,28 +1973,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2137,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>55.90615463256836</v>
+        <v>56.00801849365234</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2163,16 +2028,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>39.61534881591797</v>
+        <v>39.68752670288086</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
       </c>
       <c r="D4" s="1">
-        <v>432</v>
+        <v>224</v>
       </c>
       <c r="E4" s="1">
-        <v>360</v>
+        <v>152</v>
       </c>
       <c r="F4" s="1">
         <v>36</v>
@@ -2189,7 +2054,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.17418384552002</v>
+        <v>1.176323175430298</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -2215,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.16395378112793</v>
+        <v>1.166074514389038</v>
       </c>
       <c r="C6" s="1">
         <v>1024</v>
@@ -2241,7 +2106,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.9138855934143066</v>
+        <v>0.915550708770752</v>
       </c>
       <c r="C7" s="1">
         <v>804</v>
@@ -2267,7 +2132,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3125852644443512</v>
+        <v>0.3131547868251801</v>
       </c>
       <c r="C8" s="1">
         <v>275</v>
@@ -2293,25 +2158,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2864417433738709</v>
+        <v>0.1093194857239723</v>
       </c>
       <c r="C9" s="1">
-        <v>252</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1">
-        <v>784</v>
+        <v>7973</v>
       </c>
       <c r="E9" s="1">
-        <v>712</v>
+        <v>7422</v>
       </c>
       <c r="F9" s="1">
-        <v>72</v>
+        <v>551</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>252</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2319,19 +2184,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1091206669807434</v>
+        <v>0.1093194857239723</v>
       </c>
       <c r="C10" s="1">
         <v>96</v>
       </c>
       <c r="D10" s="1">
-        <v>8003</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>7452</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2345,16 +2210,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1091206669807434</v>
+        <v>0.1093194857239723</v>
       </c>
       <c r="C11" s="1">
         <v>96</v>
       </c>
       <c r="D11" s="1">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="E11" s="1">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2371,16 +2236,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1091206669807434</v>
+        <v>0.1070419996976852</v>
       </c>
       <c r="C12" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1">
-        <v>168</v>
+        <v>13252</v>
       </c>
       <c r="E12" s="1">
-        <v>168</v>
+        <v>13252</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2389,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2397,16 +2262,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1068473234772682</v>
+        <v>0.1047645062208176</v>
       </c>
       <c r="C13" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1">
-        <v>13252</v>
+        <v>320</v>
       </c>
       <c r="E13" s="1">
-        <v>13252</v>
+        <v>320</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2415,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2423,7 +2288,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.07274711132049561</v>
+        <v>0.07287965714931488</v>
       </c>
       <c r="C14" s="1">
         <v>64</v>
@@ -2449,7 +2314,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06820041686296463</v>
+        <v>0.06832467764616013</v>
       </c>
       <c r="C15" s="1">
         <v>60</v>
@@ -2475,7 +2340,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01364008337259293</v>
+        <v>0.01366493571549654</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
@@ -2501,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0102300625294447</v>
+        <v>0.01024870201945305</v>
       </c>
       <c r="C17" s="1">
         <v>9</v>
@@ -2527,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.004546694457530975</v>
+        <v>0.00455497857183218</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -2553,7 +2418,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004546694457530975</v>
+        <v>0.00455497857183218</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -2579,7 +2444,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.004546694457530975</v>
+        <v>0.00455497857183218</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
@@ -2605,7 +2470,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004546694457530975</v>
+        <v>0.00455497857183218</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -2631,7 +2496,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004546694457530975</v>
+        <v>0.00455497857183218</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
@@ -2657,19 +2522,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.004546694457530975</v>
+        <v>0.00455497857183218</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>384</v>
+        <v>108</v>
       </c>
       <c r="E23" s="1">
-        <v>332</v>
+        <v>104</v>
       </c>
       <c r="F23" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
         <v>4</v>
@@ -2683,7 +2548,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.001136673614382744</v>
+        <v>0.001138744642958045</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -2704,35 +2569,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
-      <c r="A148" t="s">
-        <v>147</v>
-      </c>
-      <c r="B148">
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C148">
+      <c r="C133">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D148">
+      <c r="D133">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E148">
+      <c r="E133">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F148">
+      <c r="F133">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G148">
+      <c r="G133">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H148">
+      <c r="H133">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2748,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2761,36 +2626,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>19.53535079956055</v>
+        <v>22.69877624511719</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2813,19 +2678,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>11.79757022857666</v>
+        <v>13.65660667419434</v>
       </c>
       <c r="C4" s="1">
-        <v>8003</v>
+        <v>7973</v>
       </c>
       <c r="D4" s="1">
         <v>96</v>
       </c>
       <c r="E4" s="1">
-        <v>7452</v>
+        <v>7422</v>
       </c>
       <c r="F4" s="1">
         <v>551</v>
@@ -2842,7 +2707,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>5.887729167938232</v>
+        <v>6.841149806976318</v>
       </c>
       <c r="C5" s="1">
         <v>3994</v>
@@ -2868,16 +2733,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="2">
-        <v>4.266171455383301</v>
+        <v>4.569901466369629</v>
       </c>
       <c r="C6" s="1">
-        <v>2894</v>
+        <v>2668</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2894</v>
+        <v>2668</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2894,16 +2759,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="2">
-        <v>3.933014869689941</v>
+        <v>4.374636173248291</v>
       </c>
       <c r="C7" s="1">
-        <v>2668</v>
+        <v>2554</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>2668</v>
+        <v>2554</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2920,16 +2785,16 @@
         <v>25</v>
       </c>
       <c r="B8" s="2">
-        <v>3.764962673187256</v>
+        <v>3.809393405914307</v>
       </c>
       <c r="C8" s="1">
-        <v>2554</v>
+        <v>2224</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2554</v>
+        <v>2224</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2943,25 +2808,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
-        <v>3.278495311737061</v>
+        <v>3.523346185684204</v>
       </c>
       <c r="C9" s="1">
-        <v>2224</v>
+        <v>2057</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>2224</v>
+        <v>2056</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2969,22 +2834,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>3.225425958633423</v>
+        <v>3.31609058380127</v>
       </c>
       <c r="C10" s="1">
-        <v>2188</v>
+        <v>1936</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>1936</v>
       </c>
       <c r="F10" s="1">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2995,25 +2860,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>3.032313108444214</v>
+        <v>3.117399215698242</v>
       </c>
       <c r="C11" s="1">
-        <v>2057</v>
+        <v>1820</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>2056</v>
+        <v>1820</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -3021,19 +2886,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>2.853941917419434</v>
+        <v>2.696036338806152</v>
       </c>
       <c r="C12" s="1">
-        <v>1936</v>
+        <v>1574</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1">
-        <v>1936</v>
+        <v>1574</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -3042,30 +2907,30 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>2.682941198348999</v>
+        <v>2.010893821716309</v>
       </c>
       <c r="C13" s="1">
-        <v>1820</v>
+        <v>1174</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1">
-        <v>1820</v>
+        <v>1162</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -3073,48 +2938,48 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>2.32030200958252</v>
+        <v>1.887568116188049</v>
       </c>
       <c r="C14" s="1">
-        <v>1574</v>
+        <v>1102</v>
       </c>
       <c r="D14" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1">
-        <v>1574</v>
+        <v>1082</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H14" s="1">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2">
-        <v>1.951766014099121</v>
+        <v>1.80535101890564</v>
       </c>
       <c r="C15" s="1">
-        <v>1324</v>
+        <v>1054</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1236</v>
+        <v>1054</v>
       </c>
       <c r="F15" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -3125,25 +2990,25 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2">
-        <v>1.730644464492798</v>
+        <v>1.675173878669739</v>
       </c>
       <c r="C16" s="1">
-        <v>1174</v>
+        <v>978</v>
       </c>
       <c r="D16" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>1162</v>
+        <v>970</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -3151,74 +3016,74 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2">
-        <v>1.624506115913391</v>
+        <v>1.521016716957092</v>
       </c>
       <c r="C17" s="1">
-        <v>1102</v>
+        <v>888</v>
       </c>
       <c r="D17" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>1082</v>
+        <v>888</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>1.553747296333313</v>
+        <v>1.507313847541809</v>
       </c>
       <c r="C18" s="1">
-        <v>1054</v>
+        <v>880</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>49184</v>
       </c>
       <c r="E18" s="1">
-        <v>1054</v>
+        <v>848</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2">
-        <v>1.441712379455566</v>
+        <v>1.373711109161377</v>
       </c>
       <c r="C19" s="1">
-        <v>978</v>
+        <v>802</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>970</v>
+        <v>764</v>
       </c>
       <c r="F19" s="1">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3229,22 +3094,22 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2">
-        <v>1.391591429710388</v>
+        <v>1.298345327377319</v>
       </c>
       <c r="C20" s="1">
-        <v>944</v>
+        <v>758</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>856</v>
+        <v>758</v>
       </c>
       <c r="F20" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -3255,71 +3120,71 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B21" s="2">
-        <v>1.30903947353363</v>
+        <v>1.217841148376465</v>
       </c>
       <c r="C21" s="1">
-        <v>888</v>
+        <v>711</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="E21" s="1">
-        <v>888</v>
+        <v>704</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2">
-        <v>1.297246336936951</v>
+        <v>1.120208263397217</v>
       </c>
       <c r="C22" s="1">
-        <v>880</v>
+        <v>654</v>
       </c>
       <c r="D22" s="1">
-        <v>49184</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>848</v>
+        <v>654</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2">
-        <v>1.217642545700073</v>
+        <v>0.9043883681297302</v>
       </c>
       <c r="C23" s="1">
-        <v>826</v>
+        <v>528</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>826</v>
+        <v>528</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -3333,100 +3198,100 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B24" s="2">
-        <v>1.182263135910034</v>
+        <v>0.8718440532684326</v>
       </c>
       <c r="C24" s="1">
-        <v>802</v>
+        <v>509</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="E24" s="1">
-        <v>764</v>
+        <v>508</v>
       </c>
       <c r="F24" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>1.155728578567505</v>
+        <v>0.801616907119751</v>
       </c>
       <c r="C25" s="1">
-        <v>784</v>
+        <v>468</v>
       </c>
       <c r="D25" s="1">
-        <v>252</v>
+        <v>1024</v>
       </c>
       <c r="E25" s="1">
-        <v>712</v>
+        <v>76</v>
       </c>
       <c r="F25" s="1">
-        <v>72</v>
+        <v>392</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>252</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2">
-        <v>1.048116087913513</v>
+        <v>0.7005583643913269</v>
       </c>
       <c r="C26" s="1">
-        <v>711</v>
+        <v>409</v>
       </c>
       <c r="D26" s="1">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>704</v>
+        <v>392</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G26" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2">
-        <v>1.01421070098877</v>
+        <v>0.6440341472625732</v>
       </c>
       <c r="C27" s="1">
-        <v>688</v>
+        <v>376</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>688</v>
+        <v>228</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -3437,19 +3302,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7783477902412415</v>
+        <v>0.5892227292060852</v>
       </c>
       <c r="C28" s="1">
-        <v>528</v>
+        <v>344</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>528</v>
+        <v>344</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -3463,100 +3328,100 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>0.7503390312194824</v>
+        <v>0.5823712944984436</v>
       </c>
       <c r="C29" s="1">
-        <v>509</v>
+        <v>340</v>
       </c>
       <c r="D29" s="1">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>508</v>
+        <v>340</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>1032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6898991465568543</v>
+        <v>0.5481141209602356</v>
       </c>
       <c r="C30" s="1">
-        <v>468</v>
+        <v>320</v>
       </c>
       <c r="D30" s="1">
-        <v>1024</v>
+        <v>92</v>
       </c>
       <c r="E30" s="1">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="F30" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>1024</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2">
-        <v>0.6368299722671509</v>
+        <v>0.5412627458572388</v>
       </c>
       <c r="C31" s="1">
-        <v>432</v>
+        <v>316</v>
       </c>
       <c r="D31" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>360</v>
+        <v>44</v>
       </c>
       <c r="F31" s="1">
-        <v>36</v>
+        <v>272</v>
       </c>
       <c r="G31" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2">
-        <v>0.6029247045516968</v>
+        <v>0.4076598882675171</v>
       </c>
       <c r="C32" s="1">
-        <v>409</v>
+        <v>238</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>392</v>
+        <v>238</v>
       </c>
       <c r="F32" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -3567,25 +3432,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B33" s="2">
-        <v>0.566071093082428</v>
+        <v>0.3973827660083771</v>
       </c>
       <c r="C33" s="1">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>332</v>
+        <v>232</v>
       </c>
       <c r="F33" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -3593,45 +3458,45 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B34" s="2">
-        <v>0.5542779564857483</v>
+        <v>0.3836798965930939</v>
       </c>
       <c r="C34" s="1">
-        <v>376</v>
+        <v>224</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>34852</v>
       </c>
       <c r="E34" s="1">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="F34" s="1">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2">
-        <v>0.5071053504943848</v>
+        <v>0.3494227528572083</v>
       </c>
       <c r="C35" s="1">
-        <v>344</v>
+        <v>204</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>344</v>
+        <v>204</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -3645,22 +3510,22 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2">
-        <v>0.5012087821960449</v>
+        <v>0.3357199132442474</v>
       </c>
       <c r="C36" s="1">
-        <v>340</v>
+        <v>196</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>340</v>
+        <v>188</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -3671,22 +3536,22 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4658293426036835</v>
+        <v>0.3220170736312866</v>
       </c>
       <c r="C37" s="1">
-        <v>316</v>
+        <v>188</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="F37" s="1">
-        <v>272</v>
+        <v>40</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -3697,25 +3562,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B38" s="2">
-        <v>0.365587592124939</v>
+        <v>0.3134527802467346</v>
       </c>
       <c r="C38" s="1">
-        <v>248</v>
+        <v>183</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1">
-        <v>248</v>
+        <v>174</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -3726,16 +3591,16 @@
         <v>45</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3508461713790894</v>
+        <v>0.3048884868621826</v>
       </c>
       <c r="C39" s="1">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -3749,25 +3614,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3420012891292572</v>
+        <v>0.3014627695083618</v>
       </c>
       <c r="C40" s="1">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E40" s="1">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -3775,19 +3640,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3007252812385559</v>
+        <v>0.287759929895401</v>
       </c>
       <c r="C41" s="1">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E41" s="1">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3796,27 +3661,27 @@
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2889321446418762</v>
+        <v>0.2672056555747986</v>
       </c>
       <c r="C42" s="1">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="F42" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -3827,22 +3692,22 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2771389782428742</v>
+        <v>0.260354220867157</v>
       </c>
       <c r="C43" s="1">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F43" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -3853,25 +3718,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2697682678699493</v>
+        <v>0.2535027861595154</v>
       </c>
       <c r="C44" s="1">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="D44" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3879,19 +3744,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2623975574970245</v>
+        <v>0.2363742291927338</v>
       </c>
       <c r="C45" s="1">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3905,25 +3770,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2594492733478546</v>
+        <v>0.2363742291927338</v>
       </c>
       <c r="C46" s="1">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3931,19 +3796,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2476561069488525</v>
+        <v>0.2295227944850922</v>
       </c>
       <c r="C47" s="1">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D47" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3952,24 +3817,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2299663871526718</v>
+        <v>0.219245657324791</v>
       </c>
       <c r="C48" s="1">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3983,19 +3848,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B49" s="2">
-        <v>0.224069818854332</v>
+        <v>0.219245657324791</v>
       </c>
       <c r="C49" s="1">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -4009,19 +3874,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2181732356548309</v>
+        <v>0.2123942375183106</v>
       </c>
       <c r="C50" s="1">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -4035,19 +3900,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2063800990581513</v>
+        <v>0.205542802810669</v>
       </c>
       <c r="C51" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -4061,19 +3926,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2034318000078201</v>
+        <v>0.1918399482965469</v>
       </c>
       <c r="C52" s="1">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -4087,25 +3952,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B53" s="2">
-        <v>0.2034318000078201</v>
+        <v>0.1849885284900665</v>
       </c>
       <c r="C53" s="1">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -4113,25 +3978,25 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1975352317094803</v>
+        <v>0.1781370937824249</v>
       </c>
       <c r="C54" s="1">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -4139,19 +4004,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1886903643608093</v>
+        <v>0.1712856739759445</v>
       </c>
       <c r="C55" s="1">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -4165,25 +4030,25 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1886903643608093</v>
+        <v>0.1575828194618225</v>
       </c>
       <c r="C56" s="1">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E56" s="1">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -4191,19 +4056,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1827937960624695</v>
+        <v>0.1541571021080017</v>
       </c>
       <c r="C57" s="1">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4217,19 +4082,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1768972277641296</v>
+        <v>0.1507313847541809</v>
       </c>
       <c r="C58" s="1">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -4243,19 +4108,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1768972277641296</v>
+        <v>0.1507313847541809</v>
       </c>
       <c r="C59" s="1">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -4269,19 +4134,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1651040762662888</v>
+        <v>0.1404542475938797</v>
       </c>
       <c r="C60" s="1">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -4295,19 +4160,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1592074930667877</v>
+        <v>0.1336028277873993</v>
       </c>
       <c r="C61" s="1">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4321,25 +4186,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1533109247684479</v>
+        <v>0.1336028277873993</v>
       </c>
       <c r="C62" s="1">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D62" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -4347,19 +4212,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2">
-        <v>0.147414356470108</v>
+        <v>0.1267513930797577</v>
       </c>
       <c r="C63" s="1">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -4373,22 +4238,22 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1444660723209381</v>
+        <v>0.1233256831765175</v>
       </c>
       <c r="C64" s="1">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="F64" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -4399,19 +4264,19 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1385694891214371</v>
+        <v>0.1164742559194565</v>
       </c>
       <c r="C65" s="1">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -4425,25 +4290,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1356212049722672</v>
+        <v>0.1096228286623955</v>
       </c>
       <c r="C66" s="1">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D66" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -4451,25 +4316,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1326729208230972</v>
+        <v>0.09934569150209427</v>
       </c>
       <c r="C67" s="1">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E67" s="1">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -4477,19 +4342,19 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.1297246366739273</v>
+        <v>0.08906854689121246</v>
       </c>
       <c r="C68" s="1">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -4503,19 +4368,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.1267763376235962</v>
+        <v>0.08906854689121246</v>
       </c>
       <c r="C69" s="1">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -4529,19 +4394,19 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.1238280534744263</v>
+        <v>0.08221711963415146</v>
       </c>
       <c r="C70" s="1">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4555,19 +4420,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.1238280534744263</v>
+        <v>0.08221711963415146</v>
       </c>
       <c r="C71" s="1">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4581,19 +4446,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.1208797693252564</v>
+        <v>0.08221711963415146</v>
       </c>
       <c r="C72" s="1">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -4607,25 +4472,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="B73" s="2">
-        <v>0.1149831935763359</v>
+        <v>0.08221711963415146</v>
       </c>
       <c r="C73" s="1">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4633,19 +4498,19 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.1149831935763359</v>
+        <v>0.07536569237709045</v>
       </c>
       <c r="C74" s="1">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4659,19 +4524,19 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.1090866178274155</v>
+        <v>0.07536569237709045</v>
       </c>
       <c r="C75" s="1">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4685,22 +4550,22 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.1061383336782455</v>
+        <v>0.06851426512002945</v>
       </c>
       <c r="C76" s="1">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F76" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -4711,19 +4576,19 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.1061383336782455</v>
+        <v>0.06508855521678925</v>
       </c>
       <c r="C77" s="1">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4737,19 +4602,19 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2">
-        <v>0.1002417579293251</v>
+        <v>0.06166284158825874</v>
       </c>
       <c r="C78" s="1">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4763,19 +4628,19 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2">
-        <v>0.09434518218040466</v>
+        <v>0.06166284158825874</v>
       </c>
       <c r="C79" s="1">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4789,25 +4654,25 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2">
-        <v>0.0855003222823143</v>
+        <v>0.05823712795972824</v>
       </c>
       <c r="C80" s="1">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D80" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -4815,19 +4680,19 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2">
-        <v>0.07665546238422394</v>
+        <v>0.04795998707413673</v>
       </c>
       <c r="C81" s="1">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4841,19 +4706,19 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>0.07665546238422394</v>
+        <v>0.04453427344560623</v>
       </c>
       <c r="C82" s="1">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4867,19 +4732,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2">
-        <v>0.0707588866353035</v>
+        <v>0.04110855981707573</v>
       </c>
       <c r="C83" s="1">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4893,19 +4758,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2">
-        <v>0.0707588866353035</v>
+        <v>0.03425713256001473</v>
       </c>
       <c r="C84" s="1">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4919,25 +4784,25 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>0.0707588866353035</v>
+        <v>0.03083142079412937</v>
       </c>
       <c r="C85" s="1">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -4948,16 +4813,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.06486231833696365</v>
+        <v>0.02740570716559887</v>
       </c>
       <c r="C86" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4974,16 +4839,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.06486231833696365</v>
+        <v>0.02740570716559887</v>
       </c>
       <c r="C87" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5000,16 +4865,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.05896574258804321</v>
+        <v>0.02740570716559887</v>
       </c>
       <c r="C88" s="1">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -5026,16 +4891,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.05306916683912277</v>
+        <v>0.02397999353706837</v>
       </c>
       <c r="C89" s="1">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5052,16 +4917,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.05306916683912277</v>
+        <v>0.02055427990853787</v>
       </c>
       <c r="C90" s="1">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5078,16 +4943,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.05012087896466255</v>
+        <v>0.02055427990853787</v>
       </c>
       <c r="C91" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5104,16 +4969,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.04127601906657219</v>
+        <v>0.01712856628000736</v>
       </c>
       <c r="C92" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -5130,16 +4995,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.03832773119211197</v>
+        <v>0.01712856628000736</v>
       </c>
       <c r="C93" s="1">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5156,16 +5021,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.03537944331765175</v>
+        <v>0.01712856628000736</v>
       </c>
       <c r="C94" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -5182,16 +5047,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.03537944331765175</v>
+        <v>0.01712856628000736</v>
       </c>
       <c r="C95" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -5208,16 +5073,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.03243115916848183</v>
+        <v>0.01712856628000736</v>
       </c>
       <c r="C96" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5234,16 +5099,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.02948287129402161</v>
+        <v>0.01370285358279944</v>
       </c>
       <c r="C97" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5257,19 +5122,19 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B98" s="2">
-        <v>0.02653458341956139</v>
+        <v>0.01370285358279944</v>
       </c>
       <c r="C98" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D98" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E98" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5278,24 +5143,24 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="2">
-        <v>0.02358629554510117</v>
+        <v>0.01370285358279944</v>
       </c>
       <c r="C99" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5309,19 +5174,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" s="2">
-        <v>0.02358629554510117</v>
+        <v>0.01370285358279944</v>
       </c>
       <c r="C100" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5335,19 +5200,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="2">
-        <v>0.02358629554510117</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C101" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -5361,19 +5226,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.0206380095332861</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C102" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5387,19 +5252,19 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01768972165882587</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C103" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5413,19 +5278,19 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01768972165882587</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C104" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -5439,19 +5304,19 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.0147414356470108</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C105" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -5465,19 +5330,19 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.0147414356470108</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C106" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -5491,19 +5356,19 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.0147414356470108</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C107" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -5517,19 +5382,19 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="2">
-        <v>0.0147414356470108</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C108" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -5543,19 +5408,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="2">
-        <v>0.0147414356470108</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C109" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -5569,19 +5434,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B110" s="2">
-        <v>0.0147414356470108</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C110" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -5595,19 +5460,19 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="2">
-        <v>0.01179314777255058</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C111" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -5621,19 +5486,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="2">
-        <v>0.01179314777255058</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C112" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -5647,19 +5512,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.01179314777255058</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C113" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D113" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -5668,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="H113" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -5676,16 +5541,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.01179314777255058</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C114" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -5702,16 +5567,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.01179314777255058</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C115" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -5728,7 +5593,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5754,7 +5619,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5780,7 +5645,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5806,7 +5671,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5832,7 +5697,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5858,7 +5723,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5884,7 +5749,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.01027713995426893</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5910,16 +5775,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.006851426791399717</v>
       </c>
       <c r="C123" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -5936,16 +5801,16 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.006851426791399717</v>
       </c>
       <c r="C124" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -5962,16 +5827,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.006851426791399717</v>
       </c>
       <c r="C125" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
       </c>
       <c r="E125" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -5988,16 +5853,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C126" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -6014,16 +5879,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C127" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -6040,16 +5905,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C128" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -6066,16 +5931,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C129" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -6092,16 +5957,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C130" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -6118,16 +5983,16 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C131" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -6144,16 +6009,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.008844860829412937</v>
+        <v>0.003425713395699859</v>
       </c>
       <c r="C132" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -6166,424 +6031,34 @@
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B133" s="2">
-        <v>0.008844860829412937</v>
-      </c>
-      <c r="C133" s="1">
-        <v>6</v>
-      </c>
-      <c r="D133" s="1">
-        <v>0</v>
-      </c>
-      <c r="E133" s="1">
-        <v>6</v>
-      </c>
-      <c r="F133" s="1">
-        <v>0</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0</v>
-      </c>
-      <c r="H133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="1" t="s">
+      <c r="A133" t="s">
         <v>132</v>
       </c>
-      <c r="B134" s="2">
-        <v>0.008844860829412937</v>
-      </c>
-      <c r="C134" s="1">
-        <v>6</v>
-      </c>
-      <c r="D134" s="1">
-        <v>0</v>
-      </c>
-      <c r="E134" s="1">
-        <v>6</v>
-      </c>
-      <c r="F134" s="1">
-        <v>0</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0</v>
-      </c>
-      <c r="H134" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B135" s="2">
-        <v>0.008844860829412937</v>
-      </c>
-      <c r="C135" s="1">
-        <v>6</v>
-      </c>
-      <c r="D135" s="1">
-        <v>0</v>
-      </c>
-      <c r="E135" s="1">
-        <v>6</v>
-      </c>
-      <c r="F135" s="1">
-        <v>0</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0</v>
-      </c>
-      <c r="H135" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B136" s="2">
-        <v>0.008844860829412937</v>
-      </c>
-      <c r="C136" s="1">
-        <v>6</v>
-      </c>
-      <c r="D136" s="1">
-        <v>0</v>
-      </c>
-      <c r="E136" s="1">
-        <v>6</v>
-      </c>
-      <c r="F136" s="1">
-        <v>0</v>
-      </c>
-      <c r="G136" s="1">
-        <v>0</v>
-      </c>
-      <c r="H136" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B137" s="2">
-        <v>0.008844860829412937</v>
-      </c>
-      <c r="C137" s="1">
-        <v>6</v>
-      </c>
-      <c r="D137" s="1">
-        <v>0</v>
-      </c>
-      <c r="E137" s="1">
-        <v>6</v>
-      </c>
-      <c r="F137" s="1">
-        <v>0</v>
-      </c>
-      <c r="G137" s="1">
-        <v>0</v>
-      </c>
-      <c r="H137" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B138" s="2">
-        <v>0.005896573886275291</v>
-      </c>
-      <c r="C138" s="1">
-        <v>4</v>
-      </c>
-      <c r="D138" s="1">
-        <v>0</v>
-      </c>
-      <c r="E138" s="1">
-        <v>4</v>
-      </c>
-      <c r="F138" s="1">
-        <v>0</v>
-      </c>
-      <c r="G138" s="1">
-        <v>0</v>
-      </c>
-      <c r="H138" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B139" s="2">
-        <v>0.005896573886275291</v>
-      </c>
-      <c r="C139" s="1">
-        <v>4</v>
-      </c>
-      <c r="D139" s="1">
-        <v>0</v>
-      </c>
-      <c r="E139" s="1">
-        <v>4</v>
-      </c>
-      <c r="F139" s="1">
-        <v>0</v>
-      </c>
-      <c r="G139" s="1">
-        <v>0</v>
-      </c>
-      <c r="H139" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B140" s="2">
-        <v>0.005896573886275291</v>
-      </c>
-      <c r="C140" s="1">
-        <v>4</v>
-      </c>
-      <c r="D140" s="1">
-        <v>0</v>
-      </c>
-      <c r="E140" s="1">
-        <v>4</v>
-      </c>
-      <c r="F140" s="1">
-        <v>0</v>
-      </c>
-      <c r="G140" s="1">
-        <v>0</v>
-      </c>
-      <c r="H140" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B141" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C141" s="1">
-        <v>2</v>
-      </c>
-      <c r="D141" s="1">
-        <v>0</v>
-      </c>
-      <c r="E141" s="1">
-        <v>2</v>
-      </c>
-      <c r="F141" s="1">
-        <v>0</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0</v>
-      </c>
-      <c r="H141" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B142" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C142" s="1">
-        <v>2</v>
-      </c>
-      <c r="D142" s="1">
-        <v>0</v>
-      </c>
-      <c r="E142" s="1">
-        <v>2</v>
-      </c>
-      <c r="F142" s="1">
-        <v>0</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0</v>
-      </c>
-      <c r="H142" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B143" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C143" s="1">
-        <v>2</v>
-      </c>
-      <c r="D143" s="1">
-        <v>0</v>
-      </c>
-      <c r="E143" s="1">
-        <v>2</v>
-      </c>
-      <c r="F143" s="1">
-        <v>0</v>
-      </c>
-      <c r="G143" s="1">
-        <v>0</v>
-      </c>
-      <c r="H143" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B144" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C144" s="1">
-        <v>2</v>
-      </c>
-      <c r="D144" s="1">
-        <v>0</v>
-      </c>
-      <c r="E144" s="1">
-        <v>2</v>
-      </c>
-      <c r="F144" s="1">
-        <v>0</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0</v>
-      </c>
-      <c r="H144" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B145" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C145" s="1">
-        <v>2</v>
-      </c>
-      <c r="D145" s="1">
-        <v>0</v>
-      </c>
-      <c r="E145" s="1">
-        <v>2</v>
-      </c>
-      <c r="F145" s="1">
-        <v>0</v>
-      </c>
-      <c r="G145" s="1">
-        <v>0</v>
-      </c>
-      <c r="H145" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B146" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C146" s="1">
-        <v>2</v>
-      </c>
-      <c r="D146" s="1">
-        <v>0</v>
-      </c>
-      <c r="E146" s="1">
-        <v>2</v>
-      </c>
-      <c r="F146" s="1">
-        <v>0</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0</v>
-      </c>
-      <c r="H146" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B147" s="2">
-        <v>0.002948286943137646</v>
-      </c>
-      <c r="C147" s="1">
-        <v>2</v>
-      </c>
-      <c r="D147" s="1">
-        <v>0</v>
-      </c>
-      <c r="E147" s="1">
-        <v>2</v>
-      </c>
-      <c r="F147" s="1">
-        <v>0</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0</v>
-      </c>
-      <c r="H147" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" t="s">
-        <v>147</v>
-      </c>
-      <c r="B148">
+      <c r="B133">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C148">
+      <c r="C133">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D148">
+      <c r="D133">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E148">
+      <c r="E133">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F148">
+      <c r="F133">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G148">
+      <c r="G133">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H148">
+      <c r="H133">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
   <si>
     <t>atk_f407</t>
   </si>
@@ -65,6 +65,9 @@
     <t>stm32f4xx_hal.o</t>
   </si>
   <si>
+    <t>can_task.o</t>
+  </si>
+  <si>
     <t>system_stm32f4xx.o</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>stm32f4xx_hal_rcc.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_can.o</t>
+  </si>
+  <si>
     <t>_printf_fp_dec.o</t>
   </si>
   <si>
@@ -111,9 +117,6 @@
   </si>
   <si>
     <t>_printf_fp_hex.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_can.o</t>
   </si>
   <si>
     <t>fz_wm.l</t>
@@ -527,9 +530,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$133</c:f>
+              <c:f>ram_percent!$A$3:$A$134</c:f>
               <c:strCache>
-                <c:ptCount val="131"/>
+                <c:ptCount val="132"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -576,27 +579,30 @@
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>can_task.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>key_task.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="131">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -604,77 +610,80 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$133</c:f>
+              <c:f>ram_percent!$B$3:$B$134</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="131"/>
+                <c:ptCount val="132"/>
                 <c:pt idx="0">
-                  <c:v>56.00801849365234</c:v>
+                  <c:v>56.00291442871094</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.68752670288086</c:v>
+                  <c:v>39.68391418457031</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.176323175430298</c:v>
+                  <c:v>1.176216125488281</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.166074514389038</c:v>
+                  <c:v>1.165968298912048</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.915550708770752</c:v>
+                  <c:v>0.9154673218727112</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3131547868251801</c:v>
+                  <c:v>0.313126266002655</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1093194857239723</c:v>
+                  <c:v>0.1093095317482948</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1093194857239723</c:v>
+                  <c:v>0.1093095317482948</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1093194857239723</c:v>
+                  <c:v>0.1093095317482948</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1070419996976852</c:v>
+                  <c:v>0.1070322468876839</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1047645062208176</c:v>
+                  <c:v>0.1047549620270729</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07287965714931488</c:v>
+                  <c:v>0.07287301868200302</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06832467764616013</c:v>
+                  <c:v>0.06831845641136169</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01366493571549654</c:v>
+                  <c:v>0.01366369146853685</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01024870201945305</c:v>
+                  <c:v>0.01024776790291071</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.00455497857183218</c:v>
+                  <c:v>0.009109127335250378</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00455497857183218</c:v>
+                  <c:v>0.004554563667625189</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00455497857183218</c:v>
+                  <c:v>0.004554563667625189</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00455497857183218</c:v>
+                  <c:v>0.004554563667625189</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.00455497857183218</c:v>
+                  <c:v>0.004554563667625189</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.00455497857183218</c:v>
+                  <c:v>0.004554563667625189</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.001138744642958045</c:v>
-                </c:pt>
-                <c:pt idx="130">
+                  <c:v>0.004554563667625189</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.001138640916906297</c:v>
+                </c:pt>
+                <c:pt idx="131">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -742,9 +751,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$133</c:f>
+              <c:f>flash_percent!$A$3:$A$134</c:f>
               <c:strCache>
-                <c:ptCount val="131"/>
+                <c:ptCount val="132"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
@@ -773,31 +782,31 @@
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>stm32f4xx_hal_can.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>_printf_fp_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>usbd_core.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>_printf_fp_hex.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>stm32f4xx_hal_can.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>usart.o</c:v>
@@ -812,330 +821,333 @@
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>can.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>__printf_flags_ss_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>bigflt0.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>can.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>can_task.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>stm32f4xx_ll_fsmc.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>malloc.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>_printf_wctomb.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>_printf_hex_int_ll_ptr.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>dnaninf.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>led.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>strcmpv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>_printf_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>_printf_oct_int_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>dfixu.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>stm32f4xx_hal_sram.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>_printf_str.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>_printf_pad.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>lc_numeric_c.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>rt_memclr.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>_wcrtomb.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>key_task.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>vsnprintf.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>fpclassify.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>_printf_char_common.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>_printf_wchar.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>_printf_char.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>_printf_charcount.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>dflt_clz.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>_printf_truncate.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>_printf_char_file.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>__2printf.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>aeabi_memset.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>_snputc.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>__printf_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>dretinf.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>_sputc.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>_printf_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>_printf_l.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>ferror.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>_printf_x.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="101">
                   <c:v>_printf_u.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="102">
                   <c:v>_printf_s.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="103">
                   <c:v>_printf_p.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="104">
                   <c:v>_printf_o.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="105">
                   <c:v>_printf_n.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="106">
                   <c:v>_printf_ls.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="107">
                   <c:v>_printf_llx.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="108">
                   <c:v>_printf_llu.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="109">
                   <c:v>_printf_llo.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="110">
                   <c:v>_printf_lli.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="111">
                   <c:v>_printf_lld.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="112">
                   <c:v>_printf_lc.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="113">
                   <c:v>_printf_i.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="114">
                   <c:v>_printf_g.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="115">
                   <c:v>_printf_f.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="116">
                   <c:v>_printf_e.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="117">
                   <c:v>_printf_d.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="118">
                   <c:v>_printf_c.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="119">
                   <c:v>_printf_a.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="120">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="121">
                   <c:v>printf2.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="122">
                   <c:v>printf1.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="123">
                   <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="124">
                   <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="125">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="126">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="127">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="128">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="129">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="130">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="131">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1143,401 +1155,404 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$133</c:f>
+              <c:f>flash_percent!$B$3:$B$134</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="131"/>
+                <c:ptCount val="132"/>
                 <c:pt idx="0">
-                  <c:v>22.69877624511719</c:v>
+                  <c:v>22.19765472412109</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.65660667419434</c:v>
+                  <c:v>13.35510921478272</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.841149806976318</c:v>
+                  <c:v>6.690117359161377</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.569901466369629</c:v>
+                  <c:v>4.469011783599854</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.374636173248291</c:v>
+                  <c:v>4.278057098388672</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.809393405914307</c:v>
+                  <c:v>3.725293159484863</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.523346185684204</c:v>
+                  <c:v>3.445561170578003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.31609058380127</c:v>
+                  <c:v>3.242881059646606</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.117399215698242</c:v>
+                  <c:v>3.04857611656189</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.696036338806152</c:v>
+                  <c:v>2.777219533920288</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.010893821716309</c:v>
+                  <c:v>2.636515855789185</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.887568116188049</c:v>
+                  <c:v>1.966499209403992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.80535101890564</c:v>
+                  <c:v>1.845896124839783</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.675173878669739</c:v>
+                  <c:v>1.765494108200073</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.521016716957092</c:v>
+                  <c:v>1.638190984725952</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.507313847541809</c:v>
+                  <c:v>1.487437129020691</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.373711109161377</c:v>
+                  <c:v>1.474036812782288</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.298345327377319</c:v>
+                  <c:v>1.343383550643921</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.217841148376465</c:v>
+                  <c:v>1.190954804420471</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.120208263397217</c:v>
+                  <c:v>1.095477342605591</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9043883681297302</c:v>
+                  <c:v>0.8844221234321594</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8718440532684326</c:v>
+                  <c:v>0.8525963425636292</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.801616907119751</c:v>
+                  <c:v>0.8241205811500549</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7005583643913269</c:v>
+                  <c:v>0.7839195728302002</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6440341472625732</c:v>
+                  <c:v>0.6850921511650085</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5892227292060852</c:v>
+                  <c:v>0.6298157572746277</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5823712944984436</c:v>
+                  <c:v>0.5762144327163696</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5481141209602356</c:v>
+                  <c:v>0.5695142149925232</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5412627458572388</c:v>
+                  <c:v>0.5293132066726685</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4076598882675171</c:v>
+                  <c:v>0.4053601324558258</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.3973827660083771</c:v>
+                  <c:v>0.3986599743366242</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3836798965930939</c:v>
+                  <c:v>0.3886097073554993</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3494227528572083</c:v>
+                  <c:v>0.375209391117096</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3357199132442474</c:v>
+                  <c:v>0.3417085409164429</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3220170736312866</c:v>
+                  <c:v>0.3283081948757172</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3134527802467346</c:v>
+                  <c:v>0.3149078786373138</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3048884868621826</c:v>
+                  <c:v>0.3065326511859894</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3014627695083618</c:v>
+                  <c:v>0.2981574535369873</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.287759929895401</c:v>
+                  <c:v>0.2948073744773865</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2672056555747986</c:v>
+                  <c:v>0.2814070284366608</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.260354220867157</c:v>
+                  <c:v>0.2613065242767334</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2535027861595154</c:v>
+                  <c:v>0.2546063661575317</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2363742291927338</c:v>
+                  <c:v>0.2479061931371689</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2363742291927338</c:v>
+                  <c:v>0.2311557829380035</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2295227944850922</c:v>
+                  <c:v>0.2311557829380035</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.219245657324791</c:v>
+                  <c:v>0.2244556099176407</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.219245657324791</c:v>
+                  <c:v>0.214405357837677</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2123942375183106</c:v>
+                  <c:v>0.214405357837677</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.205542802810669</c:v>
+                  <c:v>0.2077051997184753</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1918399482965469</c:v>
+                  <c:v>0.2010050266981125</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1849885284900665</c:v>
+                  <c:v>0.187604695558548</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1781370937824249</c:v>
+                  <c:v>0.1809045225381851</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1712856739759445</c:v>
+                  <c:v>0.1742043495178223</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1575828194618225</c:v>
+                  <c:v>0.1675041913986206</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1541571021080017</c:v>
+                  <c:v>0.1608040183782578</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1507313847541809</c:v>
+                  <c:v>0.1507537662982941</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1507313847541809</c:v>
+                  <c:v>0.1474036872386932</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1404542475938797</c:v>
+                  <c:v>0.1474036872386932</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1336028277873993</c:v>
+                  <c:v>0.1373534351587296</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1336028277873993</c:v>
+                  <c:v>0.1306532621383667</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1267513930797577</c:v>
+                  <c:v>0.1306532621383667</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1233256831765175</c:v>
+                  <c:v>0.1239530965685844</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1164742559194565</c:v>
+                  <c:v>0.1206030175089836</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1096228286623955</c:v>
+                  <c:v>0.1139028444886208</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.09934569150209427</c:v>
+                  <c:v>0.1072026789188385</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.08906854689121246</c:v>
+                  <c:v>0.09715242683887482</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.08906854689121246</c:v>
+                  <c:v>0.08710217475891113</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.08221711963415146</c:v>
+                  <c:v>0.08710217475891113</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.08221711963415146</c:v>
+                  <c:v>0.08040200918912888</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.08221711963415146</c:v>
+                  <c:v>0.08040200918912888</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.08221711963415146</c:v>
+                  <c:v>0.08040200918912888</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.07536569237709045</c:v>
+                  <c:v>0.08040200918912888</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07536569237709045</c:v>
+                  <c:v>0.07370184361934662</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.06851426512002945</c:v>
+                  <c:v>0.07370184361934662</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.06508855521678925</c:v>
+                  <c:v>0.06700167804956436</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.06166284158825874</c:v>
+                  <c:v>0.06365159153938294</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.06166284158825874</c:v>
+                  <c:v>0.06030150875449181</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.05823712795972824</c:v>
+                  <c:v>0.06030150875449181</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.04795998707413673</c:v>
+                  <c:v>0.05695142224431038</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.04453427344560623</c:v>
+                  <c:v>0.04690117388963699</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.04110855981707573</c:v>
+                  <c:v>0.04355108737945557</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.03425713256001473</c:v>
+                  <c:v>0.04020100459456444</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.03083142079412937</c:v>
+                  <c:v>0.03350083902478218</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.02740570716559887</c:v>
+                  <c:v>0.0301507543772459</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.02740570716559887</c:v>
+                  <c:v>0.02680066972970963</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.02740570716559887</c:v>
+                  <c:v>0.02680066972970963</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.02397999353706837</c:v>
+                  <c:v>0.02680066972970963</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.02055427990853787</c:v>
+                  <c:v>0.0234505869448185</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.02055427990853787</c:v>
+                  <c:v>0.02010050229728222</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.01712856628000736</c:v>
+                  <c:v>0.02010050229728222</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.01712856628000736</c:v>
+                  <c:v>0.01675041951239109</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.01712856628000736</c:v>
+                  <c:v>0.01675041951239109</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.01712856628000736</c:v>
+                  <c:v>0.01675041951239109</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01712856628000736</c:v>
+                  <c:v>0.01675041951239109</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01370285358279944</c:v>
+                  <c:v>0.01675041951239109</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01370285358279944</c:v>
+                  <c:v>0.01340033486485481</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01370285358279944</c:v>
+                  <c:v>0.01340033486485481</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01370285358279944</c:v>
+                  <c:v>0.01340033486485481</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01340033486485481</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.01027713995426893</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.006851426791399717</c:v>
+                  <c:v>0.01005025114864111</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.006851426791399717</c:v>
+                  <c:v>0.006700167432427406</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.006851426791399717</c:v>
+                  <c:v>0.006700167432427406</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.006700167432427406</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.003350083716213703</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.003350083716213703</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.003350083716213703</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.003350083716213703</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.003350083716213703</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.003425713395699859</c:v>
+                  <c:v>0.003350083716213703</c:v>
                 </c:pt>
                 <c:pt idx="130">
+                  <c:v>0.003350083716213703</c:v>
+                </c:pt>
+                <c:pt idx="131">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1642,8 +1657,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H133" totalsRowCount="1">
-  <autoFilter ref="A2:H132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H134" totalsRowCount="1">
+  <autoFilter ref="A2:H133"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1659,8 +1674,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H133" totalsRowCount="1">
-  <autoFilter ref="A2:H132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H134" totalsRowCount="1">
+  <autoFilter ref="A2:H133"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1960,7 +1975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1973,28 +1988,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2002,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>56.00801849365234</v>
+        <v>56.00291442871094</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2028,7 +2043,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>39.68752670288086</v>
+        <v>39.68391418457031</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -2054,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.176323175430298</v>
+        <v>1.176216125488281</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -2080,7 +2095,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.166074514389038</v>
+        <v>1.165968298912048</v>
       </c>
       <c r="C6" s="1">
         <v>1024</v>
@@ -2106,7 +2121,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.915550708770752</v>
+        <v>0.9154673218727112</v>
       </c>
       <c r="C7" s="1">
         <v>804</v>
@@ -2132,7 +2147,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3131547868251801</v>
+        <v>0.313126266002655</v>
       </c>
       <c r="C8" s="1">
         <v>275</v>
@@ -2158,7 +2173,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1093194857239723</v>
+        <v>0.1093095317482948</v>
       </c>
       <c r="C9" s="1">
         <v>96</v>
@@ -2184,7 +2199,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1093194857239723</v>
+        <v>0.1093095317482948</v>
       </c>
       <c r="C10" s="1">
         <v>96</v>
@@ -2210,7 +2225,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1093194857239723</v>
+        <v>0.1093095317482948</v>
       </c>
       <c r="C11" s="1">
         <v>96</v>
@@ -2236,7 +2251,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1070419996976852</v>
+        <v>0.1070322468876839</v>
       </c>
       <c r="C12" s="1">
         <v>94</v>
@@ -2262,16 +2277,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1047645062208176</v>
+        <v>0.1047549620270729</v>
       </c>
       <c r="C13" s="1">
         <v>92</v>
       </c>
       <c r="D13" s="1">
-        <v>320</v>
+        <v>492</v>
       </c>
       <c r="E13" s="1">
-        <v>320</v>
+        <v>492</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2288,7 +2303,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.07287965714931488</v>
+        <v>0.07287301868200302</v>
       </c>
       <c r="C14" s="1">
         <v>64</v>
@@ -2314,7 +2329,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06832467764616013</v>
+        <v>0.06831845641136169</v>
       </c>
       <c r="C15" s="1">
         <v>60</v>
@@ -2340,7 +2355,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01366493571549654</v>
+        <v>0.01366369146853685</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
@@ -2366,7 +2381,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01024870201945305</v>
+        <v>0.01024776790291071</v>
       </c>
       <c r="C17" s="1">
         <v>9</v>
@@ -2392,22 +2407,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.00455497857183218</v>
+        <v>0.009109127335250378</v>
       </c>
       <c r="C18" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>48</v>
+        <v>242</v>
       </c>
       <c r="E18" s="1">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="F18" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -2418,19 +2433,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.00455497857183218</v>
+        <v>0.004554563667625189</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G19" s="1">
         <v>4</v>
@@ -2444,16 +2459,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.00455497857183218</v>
+        <v>0.004554563667625189</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="E20" s="1">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2470,16 +2485,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.00455497857183218</v>
+        <v>0.004554563667625189</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2496,16 +2511,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.00455497857183218</v>
+        <v>0.004554563667625189</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="E22" s="1">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2522,16 +2537,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.00455497857183218</v>
+        <v>0.004554563667625189</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="E23" s="1">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2548,56 +2563,82 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.001138744642958045</v>
+        <v>0.004554563667625189</v>
       </c>
       <c r="C24" s="1">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1">
+        <v>108</v>
+      </c>
+      <c r="E24" s="1">
+        <v>104</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.001138640916906297</v>
+      </c>
+      <c r="C25" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25" s="1">
         <v>2057</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E25" s="1">
         <v>2056</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
         <v>1</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" t="s">
-        <v>132</v>
-      </c>
-      <c r="B133">
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C133">
+      <c r="C134">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D133">
+      <c r="D134">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E133">
+      <c r="E134">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F133">
+      <c r="F134">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G133">
+      <c r="G134">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H133">
+      <c r="H134">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2613,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2626,28 +2667,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" t="s">
         <v>140</v>
-      </c>
-      <c r="C2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2655,7 +2696,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>22.69877624511719</v>
+        <v>22.19765472412109</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2681,7 +2722,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>13.65660667419434</v>
+        <v>13.35510921478272</v>
       </c>
       <c r="C4" s="1">
         <v>7973</v>
@@ -2707,7 +2748,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>6.841149806976318</v>
+        <v>6.690117359161377</v>
       </c>
       <c r="C5" s="1">
         <v>3994</v>
@@ -2730,10 +2771,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>4.569901466369629</v>
+        <v>4.469011783599854</v>
       </c>
       <c r="C6" s="1">
         <v>2668</v>
@@ -2756,10 +2797,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>4.374636173248291</v>
+        <v>4.278057098388672</v>
       </c>
       <c r="C7" s="1">
         <v>2554</v>
@@ -2782,10 +2823,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>3.809393405914307</v>
+        <v>3.725293159484863</v>
       </c>
       <c r="C8" s="1">
         <v>2224</v>
@@ -2808,10 +2849,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2">
-        <v>3.523346185684204</v>
+        <v>3.445561170578003</v>
       </c>
       <c r="C9" s="1">
         <v>2057</v>
@@ -2834,10 +2875,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
-        <v>3.31609058380127</v>
+        <v>3.242881059646606</v>
       </c>
       <c r="C10" s="1">
         <v>1936</v>
@@ -2860,10 +2901,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
-        <v>3.117399215698242</v>
+        <v>3.04857611656189</v>
       </c>
       <c r="C11" s="1">
         <v>1820</v>
@@ -2886,19 +2927,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
-        <v>2.696036338806152</v>
+        <v>2.777219533920288</v>
       </c>
       <c r="C12" s="1">
-        <v>1574</v>
+        <v>1658</v>
       </c>
       <c r="D12" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1574</v>
+        <v>1658</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2907,105 +2948,105 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>2.010893821716309</v>
+        <v>2.636515855789185</v>
       </c>
       <c r="C13" s="1">
-        <v>1174</v>
+        <v>1574</v>
       </c>
       <c r="D13" s="1">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1">
-        <v>1162</v>
+        <v>1574</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>1.887568116188049</v>
+        <v>1.966499209403992</v>
       </c>
       <c r="C14" s="1">
-        <v>1102</v>
+        <v>1174</v>
       </c>
       <c r="D14" s="1">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1">
-        <v>1082</v>
+        <v>1162</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>1.80535101890564</v>
+        <v>1.845896124839783</v>
       </c>
       <c r="C15" s="1">
-        <v>1054</v>
+        <v>1102</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2">
-        <v>1.675173878669739</v>
+        <v>1.765494108200073</v>
       </c>
       <c r="C16" s="1">
-        <v>978</v>
+        <v>1054</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>970</v>
+        <v>1054</v>
       </c>
       <c r="F16" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -3016,22 +3057,22 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2">
-        <v>1.521016716957092</v>
+        <v>1.638190984725952</v>
       </c>
       <c r="C17" s="1">
-        <v>888</v>
+        <v>978</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>888</v>
+        <v>970</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -3042,74 +3083,74 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2">
-        <v>1.507313847541809</v>
+        <v>1.487437129020691</v>
       </c>
       <c r="C18" s="1">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D18" s="1">
-        <v>49184</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>848</v>
+        <v>888</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>1.373711109161377</v>
+        <v>1.474036812782288</v>
       </c>
       <c r="C19" s="1">
-        <v>802</v>
+        <v>880</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>49184</v>
       </c>
       <c r="E19" s="1">
-        <v>764</v>
+        <v>848</v>
       </c>
       <c r="F19" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2">
-        <v>1.298345327377319</v>
+        <v>1.343383550643921</v>
       </c>
       <c r="C20" s="1">
-        <v>758</v>
+        <v>802</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -3123,7 +3164,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="2">
-        <v>1.217841148376465</v>
+        <v>1.190954804420471</v>
       </c>
       <c r="C21" s="1">
         <v>711</v>
@@ -3146,10 +3187,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2">
-        <v>1.120208263397217</v>
+        <v>1.095477342605591</v>
       </c>
       <c r="C22" s="1">
         <v>654</v>
@@ -3172,10 +3213,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9043883681297302</v>
+        <v>0.8844221234321594</v>
       </c>
       <c r="C23" s="1">
         <v>528</v>
@@ -3201,7 +3242,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8718440532684326</v>
+        <v>0.8525963425636292</v>
       </c>
       <c r="C24" s="1">
         <v>509</v>
@@ -3224,54 +3265,54 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B25" s="2">
-        <v>0.801616907119751</v>
+        <v>0.8241205811500549</v>
       </c>
       <c r="C25" s="1">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="D25" s="1">
-        <v>1024</v>
+        <v>92</v>
       </c>
       <c r="E25" s="1">
-        <v>76</v>
+        <v>492</v>
       </c>
       <c r="F25" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>1024</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7005583643913269</v>
+        <v>0.7839195728302002</v>
       </c>
       <c r="C26" s="1">
-        <v>409</v>
+        <v>468</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E26" s="1">
+        <v>76</v>
+      </c>
+      <c r="F26" s="1">
         <v>392</v>
       </c>
-      <c r="F26" s="1">
-        <v>17</v>
-      </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3279,19 +3320,19 @@
         <v>36</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6440341472625732</v>
+        <v>0.6850921511650085</v>
       </c>
       <c r="C27" s="1">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>228</v>
+        <v>392</v>
       </c>
       <c r="F27" s="1">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -3305,19 +3346,19 @@
         <v>37</v>
       </c>
       <c r="B28" s="2">
-        <v>0.5892227292060852</v>
+        <v>0.6298157572746277</v>
       </c>
       <c r="C28" s="1">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -3331,16 +3372,16 @@
         <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5823712944984436</v>
+        <v>0.5762144327163696</v>
       </c>
       <c r="C29" s="1">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -3354,19 +3395,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5481141209602356</v>
+        <v>0.5695142149925232</v>
       </c>
       <c r="C30" s="1">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="D30" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -3375,15 +3416,15 @@
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5412627458572388</v>
+        <v>0.5293132066726685</v>
       </c>
       <c r="C31" s="1">
         <v>316</v>
@@ -3406,25 +3447,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4076598882675171</v>
+        <v>0.4053601324558258</v>
       </c>
       <c r="C32" s="1">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E32" s="1">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -3435,16 +3476,16 @@
         <v>41</v>
       </c>
       <c r="B33" s="2">
-        <v>0.3973827660083771</v>
+        <v>0.3986599743366242</v>
       </c>
       <c r="C33" s="1">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -3458,54 +3499,54 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3836798965930939</v>
+        <v>0.3886097073554993</v>
       </c>
       <c r="C34" s="1">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D34" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="F34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3494227528572083</v>
+        <v>0.375209391117096</v>
       </c>
       <c r="C35" s="1">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>34852</v>
       </c>
       <c r="E35" s="1">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3513,19 +3554,19 @@
         <v>43</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3357199132442474</v>
+        <v>0.3417085409164429</v>
       </c>
       <c r="C36" s="1">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="F36" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -3539,19 +3580,19 @@
         <v>44</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3220170736312866</v>
+        <v>0.3283081948757172</v>
       </c>
       <c r="C37" s="1">
+        <v>196</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
         <v>188</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
-        <v>148</v>
-      </c>
       <c r="F37" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -3562,25 +3603,25 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3134527802467346</v>
+        <v>0.3149078786373138</v>
       </c>
       <c r="C38" s="1">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D38" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G38" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -3588,25 +3629,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3048884868621826</v>
+        <v>0.3065326511859894</v>
       </c>
       <c r="C39" s="1">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3614,25 +3655,25 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3014627695083618</v>
+        <v>0.2981574535369873</v>
       </c>
       <c r="C40" s="1">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -3640,45 +3681,45 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B41" s="2">
-        <v>0.287759929895401</v>
+        <v>0.2948073744773865</v>
       </c>
       <c r="C41" s="1">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D41" s="1">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2672056555747986</v>
+        <v>0.2814070284366608</v>
       </c>
       <c r="C42" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E42" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3687,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3695,16 +3736,16 @@
         <v>47</v>
       </c>
       <c r="B43" s="2">
-        <v>0.260354220867157</v>
+        <v>0.2613065242767334</v>
       </c>
       <c r="C43" s="1">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3721,16 +3762,16 @@
         <v>48</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2535027861595154</v>
+        <v>0.2546063661575317</v>
       </c>
       <c r="C44" s="1">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3747,16 +3788,16 @@
         <v>49</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2363742291927338</v>
+        <v>0.2479061931371689</v>
       </c>
       <c r="C45" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3773,7 +3814,7 @@
         <v>50</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2363742291927338</v>
+        <v>0.2311557829380035</v>
       </c>
       <c r="C46" s="1">
         <v>138</v>
@@ -3799,16 +3840,16 @@
         <v>51</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2295227944850922</v>
+        <v>0.2311557829380035</v>
       </c>
       <c r="C47" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3825,16 +3866,16 @@
         <v>52</v>
       </c>
       <c r="B48" s="2">
-        <v>0.219245657324791</v>
+        <v>0.2244556099176407</v>
       </c>
       <c r="C48" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3851,7 +3892,7 @@
         <v>53</v>
       </c>
       <c r="B49" s="2">
-        <v>0.219245657324791</v>
+        <v>0.214405357837677</v>
       </c>
       <c r="C49" s="1">
         <v>128</v>
@@ -3877,16 +3918,16 @@
         <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2123942375183106</v>
+        <v>0.214405357837677</v>
       </c>
       <c r="C50" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3903,16 +3944,16 @@
         <v>55</v>
       </c>
       <c r="B51" s="2">
-        <v>0.205542802810669</v>
+        <v>0.2077051997184753</v>
       </c>
       <c r="C51" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3929,16 +3970,16 @@
         <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1918399482965469</v>
+        <v>0.2010050266981125</v>
       </c>
       <c r="C52" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3952,25 +3993,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1849885284900665</v>
+        <v>0.187604695558548</v>
       </c>
       <c r="C53" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -3978,19 +4019,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1781370937824249</v>
+        <v>0.1809045225381851</v>
       </c>
       <c r="C54" s="1">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D54" s="1">
         <v>4</v>
       </c>
       <c r="E54" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -4004,16 +4045,16 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1712856739759445</v>
+        <v>0.1742043495178223</v>
       </c>
       <c r="C55" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E55" s="1">
         <v>100</v>
@@ -4022,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -4030,25 +4071,25 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1575828194618225</v>
+        <v>0.1675041913986206</v>
       </c>
       <c r="C56" s="1">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -4056,25 +4097,25 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1541571021080017</v>
+        <v>0.1608040183782578</v>
       </c>
       <c r="C57" s="1">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E57" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -4085,16 +4126,16 @@
         <v>59</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1507313847541809</v>
+        <v>0.1507537662982941</v>
       </c>
       <c r="C58" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -4111,7 +4152,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1507313847541809</v>
+        <v>0.1474036872386932</v>
       </c>
       <c r="C59" s="1">
         <v>88</v>
@@ -4137,16 +4178,16 @@
         <v>61</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1404542475938797</v>
+        <v>0.1474036872386932</v>
       </c>
       <c r="C60" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -4163,16 +4204,16 @@
         <v>62</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1336028277873993</v>
+        <v>0.1373534351587296</v>
       </c>
       <c r="C61" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4189,7 +4230,7 @@
         <v>63</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1336028277873993</v>
+        <v>0.1306532621383667</v>
       </c>
       <c r="C62" s="1">
         <v>78</v>
@@ -4215,16 +4256,16 @@
         <v>64</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1267513930797577</v>
+        <v>0.1306532621383667</v>
       </c>
       <c r="C63" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -4241,19 +4282,19 @@
         <v>65</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1233256831765175</v>
+        <v>0.1239530965685844</v>
       </c>
       <c r="C64" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F64" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -4267,19 +4308,19 @@
         <v>66</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1164742559194565</v>
+        <v>0.1206030175089836</v>
       </c>
       <c r="C65" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -4293,16 +4334,16 @@
         <v>67</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1096228286623955</v>
+        <v>0.1139028444886208</v>
       </c>
       <c r="C66" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -4316,25 +4357,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="B67" s="2">
-        <v>0.09934569150209427</v>
+        <v>0.1072026789188385</v>
       </c>
       <c r="C67" s="1">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -4342,25 +4383,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B68" s="2">
-        <v>0.08906854689121246</v>
+        <v>0.09715242683887482</v>
       </c>
       <c r="C68" s="1">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E68" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -4371,7 +4412,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.08906854689121246</v>
+        <v>0.08710217475891113</v>
       </c>
       <c r="C69" s="1">
         <v>52</v>
@@ -4397,16 +4438,16 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.08221711963415146</v>
+        <v>0.08710217475891113</v>
       </c>
       <c r="C70" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4423,7 +4464,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.08221711963415146</v>
+        <v>0.08040200918912888</v>
       </c>
       <c r="C71" s="1">
         <v>48</v>
@@ -4449,7 +4490,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.08221711963415146</v>
+        <v>0.08040200918912888</v>
       </c>
       <c r="C72" s="1">
         <v>48</v>
@@ -4472,25 +4513,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>0.08221711963415146</v>
+        <v>0.08040200918912888</v>
       </c>
       <c r="C73" s="1">
         <v>48</v>
       </c>
       <c r="D73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F73" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4498,25 +4539,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="B74" s="2">
-        <v>0.07536569237709045</v>
+        <v>0.08040200918912888</v>
       </c>
       <c r="C74" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D74" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E74" s="1">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -4527,7 +4568,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07536569237709045</v>
+        <v>0.07370184361934662</v>
       </c>
       <c r="C75" s="1">
         <v>44</v>
@@ -4553,16 +4594,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.06851426512002945</v>
+        <v>0.07370184361934662</v>
       </c>
       <c r="C76" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4579,16 +4620,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.06508855521678925</v>
+        <v>0.06700167804956436</v>
       </c>
       <c r="C77" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4605,16 +4646,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="2">
-        <v>0.06166284158825874</v>
+        <v>0.06365159153938294</v>
       </c>
       <c r="C78" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4631,7 +4672,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2">
-        <v>0.06166284158825874</v>
+        <v>0.06030150875449181</v>
       </c>
       <c r="C79" s="1">
         <v>36</v>
@@ -4657,16 +4698,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="2">
-        <v>0.05823712795972824</v>
+        <v>0.06030150875449181</v>
       </c>
       <c r="C80" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4683,16 +4724,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="2">
-        <v>0.04795998707413673</v>
+        <v>0.05695142224431038</v>
       </c>
       <c r="C81" s="1">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4709,16 +4750,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>0.04453427344560623</v>
+        <v>0.04690117388963699</v>
       </c>
       <c r="C82" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4735,16 +4776,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="2">
-        <v>0.04110855981707573</v>
+        <v>0.04355108737945557</v>
       </c>
       <c r="C83" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4761,16 +4802,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="2">
-        <v>0.03425713256001473</v>
+        <v>0.04020100459456444</v>
       </c>
       <c r="C84" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4787,16 +4828,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>0.03083142079412937</v>
+        <v>0.03350083902478218</v>
       </c>
       <c r="C85" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -4813,16 +4854,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.02740570716559887</v>
+        <v>0.0301507543772459</v>
       </c>
       <c r="C86" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4839,7 +4880,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.02740570716559887</v>
+        <v>0.02680066972970963</v>
       </c>
       <c r="C87" s="1">
         <v>16</v>
@@ -4865,7 +4906,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.02740570716559887</v>
+        <v>0.02680066972970963</v>
       </c>
       <c r="C88" s="1">
         <v>16</v>
@@ -4891,16 +4932,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.02397999353706837</v>
+        <v>0.02680066972970963</v>
       </c>
       <c r="C89" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -4917,16 +4958,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.02055427990853787</v>
+        <v>0.0234505869448185</v>
       </c>
       <c r="C90" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -4943,7 +4984,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.02055427990853787</v>
+        <v>0.02010050229728222</v>
       </c>
       <c r="C91" s="1">
         <v>12</v>
@@ -4969,16 +5010,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.01712856628000736</v>
+        <v>0.02010050229728222</v>
       </c>
       <c r="C92" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -4995,7 +5036,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.01712856628000736</v>
+        <v>0.01675041951239109</v>
       </c>
       <c r="C93" s="1">
         <v>10</v>
@@ -5021,7 +5062,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.01712856628000736</v>
+        <v>0.01675041951239109</v>
       </c>
       <c r="C94" s="1">
         <v>10</v>
@@ -5047,7 +5088,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.01712856628000736</v>
+        <v>0.01675041951239109</v>
       </c>
       <c r="C95" s="1">
         <v>10</v>
@@ -5073,7 +5114,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.01712856628000736</v>
+        <v>0.01675041951239109</v>
       </c>
       <c r="C96" s="1">
         <v>10</v>
@@ -5099,16 +5140,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01370285358279944</v>
+        <v>0.01675041951239109</v>
       </c>
       <c r="C97" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5122,16 +5163,16 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01370285358279944</v>
+        <v>0.01340033486485481</v>
       </c>
       <c r="C98" s="1">
         <v>8</v>
       </c>
       <c r="D98" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1">
         <v>8</v>
@@ -5143,21 +5184,21 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01370285358279944</v>
+        <v>0.01340033486485481</v>
       </c>
       <c r="C99" s="1">
         <v>8</v>
       </c>
       <c r="D99" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E99" s="1">
         <v>8</v>
@@ -5169,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -5177,7 +5218,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01370285358279944</v>
+        <v>0.01340033486485481</v>
       </c>
       <c r="C100" s="1">
         <v>8</v>
@@ -5203,16 +5244,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01340033486485481</v>
       </c>
       <c r="C101" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -5229,7 +5270,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C102" s="1">
         <v>6</v>
@@ -5255,7 +5296,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C103" s="1">
         <v>6</v>
@@ -5281,7 +5322,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C104" s="1">
         <v>6</v>
@@ -5307,7 +5348,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C105" s="1">
         <v>6</v>
@@ -5333,7 +5374,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C106" s="1">
         <v>6</v>
@@ -5359,7 +5400,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C107" s="1">
         <v>6</v>
@@ -5385,7 +5426,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C108" s="1">
         <v>6</v>
@@ -5411,7 +5452,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C109" s="1">
         <v>6</v>
@@ -5437,7 +5478,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C110" s="1">
         <v>6</v>
@@ -5463,7 +5504,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C111" s="1">
         <v>6</v>
@@ -5489,7 +5530,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C112" s="1">
         <v>6</v>
@@ -5515,7 +5556,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C113" s="1">
         <v>6</v>
@@ -5541,7 +5582,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C114" s="1">
         <v>6</v>
@@ -5567,7 +5608,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C115" s="1">
         <v>6</v>
@@ -5593,7 +5634,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5619,7 +5660,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5645,7 +5686,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5671,7 +5712,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5697,7 +5738,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5723,7 +5764,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5749,7 +5790,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.01027713995426893</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5775,16 +5816,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.006851426791399717</v>
+        <v>0.01005025114864111</v>
       </c>
       <c r="C123" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -5801,7 +5842,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.006851426791399717</v>
+        <v>0.006700167432427406</v>
       </c>
       <c r="C124" s="1">
         <v>4</v>
@@ -5827,7 +5868,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.006851426791399717</v>
+        <v>0.006700167432427406</v>
       </c>
       <c r="C125" s="1">
         <v>4</v>
@@ -5853,16 +5894,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.006700167432427406</v>
       </c>
       <c r="C126" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -5879,7 +5920,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.003350083716213703</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -5905,7 +5946,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.003350083716213703</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -5931,7 +5972,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.003350083716213703</v>
       </c>
       <c r="C129" s="1">
         <v>2</v>
@@ -5957,7 +5998,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.003350083716213703</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -5983,7 +6024,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.003350083716213703</v>
       </c>
       <c r="C131" s="1">
         <v>2</v>
@@ -6009,7 +6050,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.003425713395699859</v>
+        <v>0.003350083716213703</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -6031,34 +6072,60 @@
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" t="s">
-        <v>132</v>
-      </c>
-      <c r="B133">
+      <c r="A133" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0.003350083716213703</v>
+      </c>
+      <c r="C133" s="1">
+        <v>2</v>
+      </c>
+      <c r="D133" s="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1">
+        <v>2</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C133">
+      <c r="C134">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D133">
+      <c r="D134">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E133">
+      <c r="E134">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F133">
+      <c r="F134">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G133">
+      <c r="G134">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H133">
+      <c r="H134">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -842,16 +842,16 @@
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>lludivv7m.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>malloc.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>can_task.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>lludivv7m.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>stm32f4xx_ll_fsmc.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>malloc.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>sys.o</c:v>
@@ -1160,397 +1160,397 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="132"/>
                 <c:pt idx="0">
-                  <c:v>22.19765472412109</c:v>
+                  <c:v>22.20732688903809</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.35510921478272</c:v>
+                  <c:v>13.36092758178711</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.690117359161377</c:v>
+                  <c:v>6.693032264709473</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.469011783599854</c:v>
+                  <c:v>4.470958709716797</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.278057098388672</c:v>
+                  <c:v>4.279921054840088</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.725293159484863</c:v>
+                  <c:v>3.726916313171387</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.445561170578003</c:v>
+                  <c:v>3.447062253952026</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.242881059646606</c:v>
+                  <c:v>3.244293928146362</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.04857611656189</c:v>
+                  <c:v>3.049904584884644</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.777219533920288</c:v>
+                  <c:v>2.778429508209229</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.636515855789185</c:v>
+                  <c:v>2.637664556503296</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.966499209403992</c:v>
+                  <c:v>1.967355966567993</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.845896124839783</c:v>
+                  <c:v>1.846700429916382</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.765494108200073</c:v>
+                  <c:v>1.766263365745544</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.638190984725952</c:v>
+                  <c:v>1.638904690742493</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.487437129020691</c:v>
+                  <c:v>1.488085269927979</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.474036812782288</c:v>
+                  <c:v>1.474679112434387</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.343383550643921</c:v>
+                  <c:v>1.343968868255615</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.190954804420471</c:v>
+                  <c:v>1.191473722457886</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.095477342605591</c:v>
+                  <c:v>1.095954656600952</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8844221234321594</c:v>
+                  <c:v>0.8848074674606323</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8525963425636292</c:v>
+                  <c:v>0.8529677987098694</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8241205811500549</c:v>
+                  <c:v>0.8244796991348267</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7839195728302002</c:v>
+                  <c:v>0.784261167049408</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6850921511650085</c:v>
+                  <c:v>0.6853906512260437</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6298157572746277</c:v>
+                  <c:v>0.6300901770591736</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5762144327163696</c:v>
+                  <c:v>0.5764654874801636</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5695142149925232</c:v>
+                  <c:v>0.5697623491287231</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5293132066726685</c:v>
+                  <c:v>0.5295438766479492</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4053601324558258</c:v>
+                  <c:v>0.3988336622714996</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.3986599743366242</c:v>
+                  <c:v>0.3887790441513062</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3886097073554993</c:v>
+                  <c:v>0.3753728568553925</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.375209391117096</c:v>
+                  <c:v>0.3619666993618012</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3417085409164429</c:v>
+                  <c:v>0.3418574333190918</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3283081948757172</c:v>
+                  <c:v>0.3284512460231781</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3149078786373138</c:v>
+                  <c:v>0.3150450885295868</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3065326511859894</c:v>
+                  <c:v>0.306666225194931</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2981574535369873</c:v>
+                  <c:v>0.2982873618602753</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2948073744773865</c:v>
+                  <c:v>0.2949358224868774</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2814070284366608</c:v>
+                  <c:v>0.2815296351909638</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2613065242767334</c:v>
+                  <c:v>0.2614203989505768</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2546063661575317</c:v>
+                  <c:v>0.2547172904014587</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2479061931371689</c:v>
+                  <c:v>0.2480142116546631</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2311557829380035</c:v>
+                  <c:v>0.2312564998865128</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2311557829380035</c:v>
+                  <c:v>0.2312564998865128</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2244556099176407</c:v>
+                  <c:v>0.2245534062385559</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.214405357837677</c:v>
+                  <c:v>0.2144987732172012</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.214405357837677</c:v>
+                  <c:v>0.2144987732172012</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2077051997184753</c:v>
+                  <c:v>0.2077956944704056</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2010050266981125</c:v>
+                  <c:v>0.2010926008224487</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.187604695558548</c:v>
+                  <c:v>0.1876864284276962</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1809045225381851</c:v>
+                  <c:v>0.1809833496809006</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1742043495178223</c:v>
+                  <c:v>0.1742802560329437</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1675041913986206</c:v>
+                  <c:v>0.1675771623849869</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1608040183782578</c:v>
+                  <c:v>0.1608740836381912</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1507537662982941</c:v>
+                  <c:v>0.1508194506168366</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1474036872386932</c:v>
+                  <c:v>0.1474679112434387</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1474036872386932</c:v>
+                  <c:v>0.1474679112434387</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1373534351587296</c:v>
+                  <c:v>0.1374132782220841</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1306532621383667</c:v>
+                  <c:v>0.1307101994752884</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1306532621383667</c:v>
+                  <c:v>0.1307101994752884</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1239530965685844</c:v>
+                  <c:v>0.1240071058273315</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1206030175089836</c:v>
+                  <c:v>0.1206555590033531</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1139028444886208</c:v>
+                  <c:v>0.1139524728059769</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1072026789188385</c:v>
+                  <c:v>0.1072493866086006</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.09715242683887482</c:v>
+                  <c:v>0.09719476103782654</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.08710217475891113</c:v>
+                  <c:v>0.08714012801647186</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.08710217475891113</c:v>
+                  <c:v>0.08714012801647186</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.08040200918912888</c:v>
+                  <c:v>0.08043704181909561</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.08040200918912888</c:v>
+                  <c:v>0.08043704181909561</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.08040200918912888</c:v>
+                  <c:v>0.08043704181909561</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.08040200918912888</c:v>
+                  <c:v>0.08043704181909561</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07370184361934662</c:v>
+                  <c:v>0.07373395562171936</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.07370184361934662</c:v>
+                  <c:v>0.07373395562171936</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.06700167804956436</c:v>
+                  <c:v>0.06703086942434311</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.06365159153938294</c:v>
+                  <c:v>0.06367932260036469</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.06030150875449181</c:v>
+                  <c:v>0.06032777950167656</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.06030150875449181</c:v>
+                  <c:v>0.06032777950167656</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.05695142224431038</c:v>
+                  <c:v>0.05697623640298843</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.04690117388963699</c:v>
+                  <c:v>0.04692160710692406</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.04355108737945557</c:v>
+                  <c:v>0.04357006400823593</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.04020100459456444</c:v>
+                  <c:v>0.04021852090954781</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.03350083902478218</c:v>
+                  <c:v>0.03351543471217156</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.0301507543772459</c:v>
+                  <c:v>0.03016388975083828</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.02680066972970963</c:v>
+                  <c:v>0.02681234665215015</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.02680066972970963</c:v>
+                  <c:v>0.02681234665215015</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.02680066972970963</c:v>
+                  <c:v>0.02681234665215015</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.0234505869448185</c:v>
+                  <c:v>0.02346080355346203</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.02010050229728222</c:v>
+                  <c:v>0.0201092604547739</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.02010050229728222</c:v>
+                  <c:v>0.0201092604547739</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.01675041951239109</c:v>
+                  <c:v>0.01675771735608578</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.01675041951239109</c:v>
+                  <c:v>0.01675771735608578</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.01675041951239109</c:v>
+                  <c:v>0.01675771735608578</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01675041951239109</c:v>
+                  <c:v>0.01675771735608578</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01675041951239109</c:v>
+                  <c:v>0.01675771735608578</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01340033486485481</c:v>
+                  <c:v>0.01340617332607508</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01340033486485481</c:v>
+                  <c:v>0.01340617332607508</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01340033486485481</c:v>
+                  <c:v>0.01340617332607508</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01340033486485481</c:v>
+                  <c:v>0.01340617332607508</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.01005025114864111</c:v>
+                  <c:v>0.01005463022738695</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.006700167432427406</c:v>
+                  <c:v>0.006703086663037539</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.006700167432427406</c:v>
+                  <c:v>0.006703086663037539</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.006700167432427406</c:v>
+                  <c:v>0.006703086663037539</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.003350083716213703</c:v>
+                  <c:v>0.003351543331518769</c:v>
                 </c:pt>
                 <c:pt idx="131">
                   <c:v>0</c:v>
@@ -2413,10 +2413,10 @@
         <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="E18" s="1">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2696,7 +2696,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>22.19765472412109</v>
+        <v>22.20732688903809</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2722,7 +2722,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>13.35510921478272</v>
+        <v>13.36092758178711</v>
       </c>
       <c r="C4" s="1">
         <v>7973</v>
@@ -2748,7 +2748,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>6.690117359161377</v>
+        <v>6.693032264709473</v>
       </c>
       <c r="C5" s="1">
         <v>3994</v>
@@ -2774,7 +2774,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>4.469011783599854</v>
+        <v>4.470958709716797</v>
       </c>
       <c r="C6" s="1">
         <v>2668</v>
@@ -2800,7 +2800,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>4.278057098388672</v>
+        <v>4.279921054840088</v>
       </c>
       <c r="C7" s="1">
         <v>2554</v>
@@ -2826,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>3.725293159484863</v>
+        <v>3.726916313171387</v>
       </c>
       <c r="C8" s="1">
         <v>2224</v>
@@ -2852,7 +2852,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="2">
-        <v>3.445561170578003</v>
+        <v>3.447062253952026</v>
       </c>
       <c r="C9" s="1">
         <v>2057</v>
@@ -2878,7 +2878,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="2">
-        <v>3.242881059646606</v>
+        <v>3.244293928146362</v>
       </c>
       <c r="C10" s="1">
         <v>1936</v>
@@ -2904,7 +2904,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="2">
-        <v>3.04857611656189</v>
+        <v>3.049904584884644</v>
       </c>
       <c r="C11" s="1">
         <v>1820</v>
@@ -2930,7 +2930,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="2">
-        <v>2.777219533920288</v>
+        <v>2.778429508209229</v>
       </c>
       <c r="C12" s="1">
         <v>1658</v>
@@ -2956,7 +2956,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>2.636515855789185</v>
+        <v>2.637664556503296</v>
       </c>
       <c r="C13" s="1">
         <v>1574</v>
@@ -2982,7 +2982,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>1.966499209403992</v>
+        <v>1.967355966567993</v>
       </c>
       <c r="C14" s="1">
         <v>1174</v>
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>1.845896124839783</v>
+        <v>1.846700429916382</v>
       </c>
       <c r="C15" s="1">
         <v>1102</v>
@@ -3034,7 +3034,7 @@
         <v>30</v>
       </c>
       <c r="B16" s="2">
-        <v>1.765494108200073</v>
+        <v>1.766263365745544</v>
       </c>
       <c r="C16" s="1">
         <v>1054</v>
@@ -3060,7 +3060,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="2">
-        <v>1.638190984725952</v>
+        <v>1.638904690742493</v>
       </c>
       <c r="C17" s="1">
         <v>978</v>
@@ -3086,7 +3086,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="2">
-        <v>1.487437129020691</v>
+        <v>1.488085269927979</v>
       </c>
       <c r="C18" s="1">
         <v>888</v>
@@ -3112,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>1.474036812782288</v>
+        <v>1.474679112434387</v>
       </c>
       <c r="C19" s="1">
         <v>880</v>
@@ -3138,7 +3138,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="2">
-        <v>1.343383550643921</v>
+        <v>1.343968868255615</v>
       </c>
       <c r="C20" s="1">
         <v>802</v>
@@ -3164,7 +3164,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="2">
-        <v>1.190954804420471</v>
+        <v>1.191473722457886</v>
       </c>
       <c r="C21" s="1">
         <v>711</v>
@@ -3190,7 +3190,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2">
-        <v>1.095477342605591</v>
+        <v>1.095954656600952</v>
       </c>
       <c r="C22" s="1">
         <v>654</v>
@@ -3216,7 +3216,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8844221234321594</v>
+        <v>0.8848074674606323</v>
       </c>
       <c r="C23" s="1">
         <v>528</v>
@@ -3242,7 +3242,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8525963425636292</v>
+        <v>0.8529677987098694</v>
       </c>
       <c r="C24" s="1">
         <v>509</v>
@@ -3268,7 +3268,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8241205811500549</v>
+        <v>0.8244796991348267</v>
       </c>
       <c r="C25" s="1">
         <v>492</v>
@@ -3294,7 +3294,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7839195728302002</v>
+        <v>0.784261167049408</v>
       </c>
       <c r="C26" s="1">
         <v>468</v>
@@ -3320,7 +3320,7 @@
         <v>36</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6850921511650085</v>
+        <v>0.6853906512260437</v>
       </c>
       <c r="C27" s="1">
         <v>409</v>
@@ -3346,7 +3346,7 @@
         <v>37</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6298157572746277</v>
+        <v>0.6300901770591736</v>
       </c>
       <c r="C28" s="1">
         <v>376</v>
@@ -3372,7 +3372,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5762144327163696</v>
+        <v>0.5764654874801636</v>
       </c>
       <c r="C29" s="1">
         <v>344</v>
@@ -3398,7 +3398,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5695142149925232</v>
+        <v>0.5697623491287231</v>
       </c>
       <c r="C30" s="1">
         <v>340</v>
@@ -3424,7 +3424,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5293132066726685</v>
+        <v>0.5295438766479492</v>
       </c>
       <c r="C31" s="1">
         <v>316</v>
@@ -3447,25 +3447,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4053601324558258</v>
+        <v>0.3988336622714996</v>
       </c>
       <c r="C32" s="1">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D32" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -3473,19 +3473,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2">
-        <v>0.3986599743366242</v>
+        <v>0.3887790441513062</v>
       </c>
       <c r="C33" s="1">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -3499,54 +3499,54 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3886097073554993</v>
+        <v>0.3753728568553925</v>
       </c>
       <c r="C34" s="1">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>34852</v>
       </c>
       <c r="E34" s="1">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B35" s="2">
-        <v>0.375209391117096</v>
+        <v>0.3619666993618012</v>
       </c>
       <c r="C35" s="1">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D35" s="1">
-        <v>34852</v>
+        <v>8</v>
       </c>
       <c r="E35" s="1">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="F35" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H35" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3554,7 +3554,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3417085409164429</v>
+        <v>0.3418574333190918</v>
       </c>
       <c r="C36" s="1">
         <v>204</v>
@@ -3580,7 +3580,7 @@
         <v>44</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3283081948757172</v>
+        <v>0.3284512460231781</v>
       </c>
       <c r="C37" s="1">
         <v>196</v>
@@ -3606,7 +3606,7 @@
         <v>45</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3149078786373138</v>
+        <v>0.3150450885295868</v>
       </c>
       <c r="C38" s="1">
         <v>188</v>
@@ -3632,7 +3632,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3065326511859894</v>
+        <v>0.306666225194931</v>
       </c>
       <c r="C39" s="1">
         <v>183</v>
@@ -3658,7 +3658,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2981574535369873</v>
+        <v>0.2982873618602753</v>
       </c>
       <c r="C40" s="1">
         <v>178</v>
@@ -3684,7 +3684,7 @@
         <v>21</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2948073744773865</v>
+        <v>0.2949358224868774</v>
       </c>
       <c r="C41" s="1">
         <v>176</v>
@@ -3710,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2814070284366608</v>
+        <v>0.2815296351909638</v>
       </c>
       <c r="C42" s="1">
         <v>168</v>
@@ -3736,7 +3736,7 @@
         <v>47</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2613065242767334</v>
+        <v>0.2614203989505768</v>
       </c>
       <c r="C43" s="1">
         <v>156</v>
@@ -3762,7 +3762,7 @@
         <v>48</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2546063661575317</v>
+        <v>0.2547172904014587</v>
       </c>
       <c r="C44" s="1">
         <v>152</v>
@@ -3788,7 +3788,7 @@
         <v>49</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2479061931371689</v>
+        <v>0.2480142116546631</v>
       </c>
       <c r="C45" s="1">
         <v>148</v>
@@ -3814,7 +3814,7 @@
         <v>50</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2311557829380035</v>
+        <v>0.2312564998865128</v>
       </c>
       <c r="C46" s="1">
         <v>138</v>
@@ -3840,7 +3840,7 @@
         <v>51</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2311557829380035</v>
+        <v>0.2312564998865128</v>
       </c>
       <c r="C47" s="1">
         <v>138</v>
@@ -3866,7 +3866,7 @@
         <v>52</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2244556099176407</v>
+        <v>0.2245534062385559</v>
       </c>
       <c r="C48" s="1">
         <v>134</v>
@@ -3892,7 +3892,7 @@
         <v>53</v>
       </c>
       <c r="B49" s="2">
-        <v>0.214405357837677</v>
+        <v>0.2144987732172012</v>
       </c>
       <c r="C49" s="1">
         <v>128</v>
@@ -3918,7 +3918,7 @@
         <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>0.214405357837677</v>
+        <v>0.2144987732172012</v>
       </c>
       <c r="C50" s="1">
         <v>128</v>
@@ -3944,7 +3944,7 @@
         <v>55</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2077051997184753</v>
+        <v>0.2077956944704056</v>
       </c>
       <c r="C51" s="1">
         <v>124</v>
@@ -3970,7 +3970,7 @@
         <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2010050266981125</v>
+        <v>0.2010926008224487</v>
       </c>
       <c r="C52" s="1">
         <v>120</v>
@@ -3996,7 +3996,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="2">
-        <v>0.187604695558548</v>
+        <v>0.1876864284276962</v>
       </c>
       <c r="C53" s="1">
         <v>112</v>
@@ -4022,7 +4022,7 @@
         <v>22</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1809045225381851</v>
+        <v>0.1809833496809006</v>
       </c>
       <c r="C54" s="1">
         <v>108</v>
@@ -4048,7 +4048,7 @@
         <v>18</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1742043495178223</v>
+        <v>0.1742802560329437</v>
       </c>
       <c r="C55" s="1">
         <v>104</v>
@@ -4074,7 +4074,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1675041913986206</v>
+        <v>0.1675771623849869</v>
       </c>
       <c r="C56" s="1">
         <v>100</v>
@@ -4100,7 +4100,7 @@
         <v>20</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1608040183782578</v>
+        <v>0.1608740836381912</v>
       </c>
       <c r="C57" s="1">
         <v>96</v>
@@ -4126,7 +4126,7 @@
         <v>59</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1507537662982941</v>
+        <v>0.1508194506168366</v>
       </c>
       <c r="C58" s="1">
         <v>90</v>
@@ -4152,7 +4152,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1474036872386932</v>
+        <v>0.1474679112434387</v>
       </c>
       <c r="C59" s="1">
         <v>88</v>
@@ -4178,7 +4178,7 @@
         <v>61</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1474036872386932</v>
+        <v>0.1474679112434387</v>
       </c>
       <c r="C60" s="1">
         <v>88</v>
@@ -4204,7 +4204,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1373534351587296</v>
+        <v>0.1374132782220841</v>
       </c>
       <c r="C61" s="1">
         <v>82</v>
@@ -4230,7 +4230,7 @@
         <v>63</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1306532621383667</v>
+        <v>0.1307101994752884</v>
       </c>
       <c r="C62" s="1">
         <v>78</v>
@@ -4256,7 +4256,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1306532621383667</v>
+        <v>0.1307101994752884</v>
       </c>
       <c r="C63" s="1">
         <v>78</v>
@@ -4282,7 +4282,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1239530965685844</v>
+        <v>0.1240071058273315</v>
       </c>
       <c r="C64" s="1">
         <v>74</v>
@@ -4308,7 +4308,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1206030175089836</v>
+        <v>0.1206555590033531</v>
       </c>
       <c r="C65" s="1">
         <v>72</v>
@@ -4334,7 +4334,7 @@
         <v>67</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1139028444886208</v>
+        <v>0.1139524728059769</v>
       </c>
       <c r="C66" s="1">
         <v>68</v>
@@ -4360,7 +4360,7 @@
         <v>68</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1072026789188385</v>
+        <v>0.1072493866086006</v>
       </c>
       <c r="C67" s="1">
         <v>64</v>
@@ -4386,7 +4386,7 @@
         <v>19</v>
       </c>
       <c r="B68" s="2">
-        <v>0.09715242683887482</v>
+        <v>0.09719476103782654</v>
       </c>
       <c r="C68" s="1">
         <v>58</v>
@@ -4412,7 +4412,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.08710217475891113</v>
+        <v>0.08714012801647186</v>
       </c>
       <c r="C69" s="1">
         <v>52</v>
@@ -4438,7 +4438,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.08710217475891113</v>
+        <v>0.08714012801647186</v>
       </c>
       <c r="C70" s="1">
         <v>52</v>
@@ -4464,7 +4464,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.08040200918912888</v>
+        <v>0.08043704181909561</v>
       </c>
       <c r="C71" s="1">
         <v>48</v>
@@ -4490,7 +4490,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.08040200918912888</v>
+        <v>0.08043704181909561</v>
       </c>
       <c r="C72" s="1">
         <v>48</v>
@@ -4516,7 +4516,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>0.08040200918912888</v>
+        <v>0.08043704181909561</v>
       </c>
       <c r="C73" s="1">
         <v>48</v>
@@ -4542,7 +4542,7 @@
         <v>17</v>
       </c>
       <c r="B74" s="2">
-        <v>0.08040200918912888</v>
+        <v>0.08043704181909561</v>
       </c>
       <c r="C74" s="1">
         <v>48</v>
@@ -4568,7 +4568,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07370184361934662</v>
+        <v>0.07373395562171936</v>
       </c>
       <c r="C75" s="1">
         <v>44</v>
@@ -4594,7 +4594,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.07370184361934662</v>
+        <v>0.07373395562171936</v>
       </c>
       <c r="C76" s="1">
         <v>44</v>
@@ -4620,7 +4620,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.06700167804956436</v>
+        <v>0.06703086942434311</v>
       </c>
       <c r="C77" s="1">
         <v>40</v>
@@ -4646,7 +4646,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2">
-        <v>0.06365159153938294</v>
+        <v>0.06367932260036469</v>
       </c>
       <c r="C78" s="1">
         <v>38</v>
@@ -4672,7 +4672,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2">
-        <v>0.06030150875449181</v>
+        <v>0.06032777950167656</v>
       </c>
       <c r="C79" s="1">
         <v>36</v>
@@ -4698,7 +4698,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2">
-        <v>0.06030150875449181</v>
+        <v>0.06032777950167656</v>
       </c>
       <c r="C80" s="1">
         <v>36</v>
@@ -4724,7 +4724,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2">
-        <v>0.05695142224431038</v>
+        <v>0.05697623640298843</v>
       </c>
       <c r="C81" s="1">
         <v>34</v>
@@ -4750,7 +4750,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>0.04690117388963699</v>
+        <v>0.04692160710692406</v>
       </c>
       <c r="C82" s="1">
         <v>28</v>
@@ -4776,7 +4776,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2">
-        <v>0.04355108737945557</v>
+        <v>0.04357006400823593</v>
       </c>
       <c r="C83" s="1">
         <v>26</v>
@@ -4802,7 +4802,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2">
-        <v>0.04020100459456444</v>
+        <v>0.04021852090954781</v>
       </c>
       <c r="C84" s="1">
         <v>24</v>
@@ -4828,7 +4828,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>0.03350083902478218</v>
+        <v>0.03351543471217156</v>
       </c>
       <c r="C85" s="1">
         <v>20</v>
@@ -4854,7 +4854,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.0301507543772459</v>
+        <v>0.03016388975083828</v>
       </c>
       <c r="C86" s="1">
         <v>18</v>
@@ -4880,7 +4880,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.02680066972970963</v>
+        <v>0.02681234665215015</v>
       </c>
       <c r="C87" s="1">
         <v>16</v>
@@ -4906,7 +4906,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.02680066972970963</v>
+        <v>0.02681234665215015</v>
       </c>
       <c r="C88" s="1">
         <v>16</v>
@@ -4932,7 +4932,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.02680066972970963</v>
+        <v>0.02681234665215015</v>
       </c>
       <c r="C89" s="1">
         <v>16</v>
@@ -4958,7 +4958,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.0234505869448185</v>
+        <v>0.02346080355346203</v>
       </c>
       <c r="C90" s="1">
         <v>14</v>
@@ -4984,7 +4984,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.02010050229728222</v>
+        <v>0.0201092604547739</v>
       </c>
       <c r="C91" s="1">
         <v>12</v>
@@ -5010,7 +5010,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.02010050229728222</v>
+        <v>0.0201092604547739</v>
       </c>
       <c r="C92" s="1">
         <v>12</v>
@@ -5036,7 +5036,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.01675041951239109</v>
+        <v>0.01675771735608578</v>
       </c>
       <c r="C93" s="1">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.01675041951239109</v>
+        <v>0.01675771735608578</v>
       </c>
       <c r="C94" s="1">
         <v>10</v>
@@ -5088,7 +5088,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.01675041951239109</v>
+        <v>0.01675771735608578</v>
       </c>
       <c r="C95" s="1">
         <v>10</v>
@@ -5114,7 +5114,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.01675041951239109</v>
+        <v>0.01675771735608578</v>
       </c>
       <c r="C96" s="1">
         <v>10</v>
@@ -5140,7 +5140,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01675041951239109</v>
+        <v>0.01675771735608578</v>
       </c>
       <c r="C97" s="1">
         <v>10</v>
@@ -5166,7 +5166,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01340033486485481</v>
+        <v>0.01340617332607508</v>
       </c>
       <c r="C98" s="1">
         <v>8</v>
@@ -5192,7 +5192,7 @@
         <v>8</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01340033486485481</v>
+        <v>0.01340617332607508</v>
       </c>
       <c r="C99" s="1">
         <v>8</v>
@@ -5218,7 +5218,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01340033486485481</v>
+        <v>0.01340617332607508</v>
       </c>
       <c r="C100" s="1">
         <v>8</v>
@@ -5244,7 +5244,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01340033486485481</v>
+        <v>0.01340617332607508</v>
       </c>
       <c r="C101" s="1">
         <v>8</v>
@@ -5270,7 +5270,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C102" s="1">
         <v>6</v>
@@ -5296,7 +5296,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C103" s="1">
         <v>6</v>
@@ -5322,7 +5322,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C104" s="1">
         <v>6</v>
@@ -5348,7 +5348,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C105" s="1">
         <v>6</v>
@@ -5374,7 +5374,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C106" s="1">
         <v>6</v>
@@ -5400,7 +5400,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C107" s="1">
         <v>6</v>
@@ -5426,7 +5426,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C108" s="1">
         <v>6</v>
@@ -5452,7 +5452,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C109" s="1">
         <v>6</v>
@@ -5478,7 +5478,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C110" s="1">
         <v>6</v>
@@ -5504,7 +5504,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C111" s="1">
         <v>6</v>
@@ -5530,7 +5530,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C112" s="1">
         <v>6</v>
@@ -5556,7 +5556,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C113" s="1">
         <v>6</v>
@@ -5582,7 +5582,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C114" s="1">
         <v>6</v>
@@ -5608,7 +5608,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C115" s="1">
         <v>6</v>
@@ -5634,7 +5634,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5660,7 +5660,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5686,7 +5686,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5712,7 +5712,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5738,7 +5738,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5764,7 +5764,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5790,7 +5790,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5816,7 +5816,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.01005025114864111</v>
+        <v>0.01005463022738695</v>
       </c>
       <c r="C123" s="1">
         <v>6</v>
@@ -5842,7 +5842,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.006700167432427406</v>
+        <v>0.006703086663037539</v>
       </c>
       <c r="C124" s="1">
         <v>4</v>
@@ -5868,7 +5868,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.006700167432427406</v>
+        <v>0.006703086663037539</v>
       </c>
       <c r="C125" s="1">
         <v>4</v>
@@ -5894,7 +5894,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.006700167432427406</v>
+        <v>0.006703086663037539</v>
       </c>
       <c r="C126" s="1">
         <v>4</v>
@@ -5920,7 +5920,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -5946,7 +5946,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C129" s="1">
         <v>2</v>
@@ -5998,7 +5998,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -6024,7 +6024,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C131" s="1">
         <v>2</v>
@@ -6050,7 +6050,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -6076,7 +6076,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="2">
-        <v>0.003350083716213703</v>
+        <v>0.003351543331518769</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
   <si>
     <t>atk_f407</t>
   </si>
@@ -74,9 +74,6 @@
     <t>led_task.o</t>
   </si>
   <si>
-    <t>key_task.o</t>
-  </si>
-  <si>
     <t>freertos_start.o</t>
   </si>
   <si>
@@ -104,13 +101,13 @@
     <t>stm32f4xx_hal_rcc.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_dma.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_can.o</t>
   </si>
   <si>
     <t>_printf_fp_dec.o</t>
-  </si>
-  <si>
-    <t>stm32f4xx_hal_dma.o</t>
   </si>
   <si>
     <t>usbd_core.o</t>
@@ -530,9 +527,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$134</c:f>
+              <c:f>ram_percent!$A$3:$A$133</c:f>
               <c:strCache>
-                <c:ptCount val="132"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -588,21 +585,18 @@
                   <c:v>led_task.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>key_task.o</c:v>
+                  <c:v>freertos_start.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>freertos_start.o</c:v>
+                  <c:v>delay.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>delay.o</c:v>
+                  <c:v>ai_task.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>ai_task.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="130">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -610,80 +604,77 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$134</c:f>
+              <c:f>ram_percent!$B$3:$B$133</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="132"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
-                  <c:v>56.00291442871094</c:v>
+                  <c:v>56.0035514831543</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.68391418457031</c:v>
+                  <c:v>39.68436431884766</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.176216125488281</c:v>
+                  <c:v>1.176229476928711</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.165968298912048</c:v>
+                  <c:v>1.165981531143189</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9154673218727112</c:v>
+                  <c:v>0.9154776930809021</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.313126266002655</c:v>
+                  <c:v>0.3165457844734192</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1093095317482948</c:v>
+                  <c:v>0.1093107759952545</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1093095317482948</c:v>
+                  <c:v>0.1093107759952545</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1093095317482948</c:v>
+                  <c:v>0.1093107759952545</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1070322468876839</c:v>
+                  <c:v>0.1070334613323212</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1047549620270729</c:v>
+                  <c:v>0.1047561541199684</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07287301868200302</c:v>
+                  <c:v>0.07287384569644928</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06831845641136169</c:v>
+                  <c:v>0.06831923127174377</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01366369146853685</c:v>
+                  <c:v>0.01366384699940682</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01024776790291071</c:v>
+                  <c:v>0.01024788524955511</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.009109127335250378</c:v>
+                  <c:v>0.00910923071205616</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.004554563667625189</c:v>
+                  <c:v>0.00455461535602808</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.004554563667625189</c:v>
+                  <c:v>0.00455461535602808</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004554563667625189</c:v>
+                  <c:v>0.00455461535602808</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004554563667625189</c:v>
+                  <c:v>0.00455461535602808</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.004554563667625189</c:v>
+                  <c:v>0.00455461535602808</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.004554563667625189</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.001138640916906297</c:v>
-                </c:pt>
-                <c:pt idx="131">
+                  <c:v>0.00113865383900702</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -751,9 +742,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$134</c:f>
+              <c:f>flash_percent!$A$3:$A$133</c:f>
               <c:strCache>
-                <c:ptCount val="132"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
@@ -782,22 +773,22 @@
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>queue.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>stm32f4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>stm32f4xx_hal_can.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>queue.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>_printf_fp_dec.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>usbd_core.o</c:v>
@@ -809,10 +800,10 @@
                   <c:v>_printf_fp_hex.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>fz_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>fz_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
@@ -821,10 +812,10 @@
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>startup_stm32f407xx.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>can.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>__printf_flags_ss_wp.o</c:v>
@@ -851,10 +842,10 @@
                   <c:v>malloc.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>can_task.o</c:v>
+                  <c:v>sys.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>sys.o</c:v>
+                  <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>_printf_wctomb.o</c:v>
@@ -872,37 +863,37 @@
                   <c:v>delay.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>dma.o</c:v>
+                  <c:v>dnaninf.o</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>dnaninf.o</c:v>
+                  <c:v>led.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>led.o</c:v>
+                  <c:v>list.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>list.o</c:v>
+                  <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>rt_memcpy_v6.o</c:v>
+                  <c:v>lludiv10.o</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>lludiv10.o</c:v>
+                  <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>usbd_ioreq.o</c:v>
+                  <c:v>strcmpv7m.o</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>strcmpv7m.o</c:v>
+                  <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>_printf_fp_infnan.o</c:v>
+                  <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>_printf_longlong_dec.o</c:v>
+                  <c:v>_printf_dec.o</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>_printf_dec.o</c:v>
+                  <c:v>can_task.o</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>_printf_oct_int_ll.o</c:v>
@@ -950,204 +941,201 @@
                   <c:v>_wcrtomb.o</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>key_task.o</c:v>
+                  <c:v>vsnprintf.o</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>vsnprintf.o</c:v>
+                  <c:v>__scatter.o</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>__scatter.o</c:v>
+                  <c:v>m_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>m_wm.l</c:v>
+                  <c:v>fpclassify.o</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>fpclassify.o</c:v>
+                  <c:v>_printf_char_common.o</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>_printf_char_common.o</c:v>
+                  <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>system_stm32f4xx.o</c:v>
+                  <c:v>_printf_wchar.o</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>_printf_wchar.o</c:v>
+                  <c:v>_printf_char.o</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>_printf_char.o</c:v>
+                  <c:v>_printf_charcount.o</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>_printf_charcount.o</c:v>
+                  <c:v>dflt_clz.o</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>dflt_clz.o</c:v>
+                  <c:v>_printf_truncate.o</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>_printf_truncate.o</c:v>
+                  <c:v>_printf_char_file.o</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>_printf_char_file.o</c:v>
+                  <c:v>libinit2.o</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>libinit2.o</c:v>
+                  <c:v>__scatter_zi.o</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>__scatter_zi.o</c:v>
+                  <c:v>__scatter_copy.o</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>__scatter_copy.o</c:v>
+                  <c:v>__2printf.o</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>__2printf.o</c:v>
+                  <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>stm32f4xx_it.o</c:v>
+                  <c:v>exit.o</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>exit.o</c:v>
+                  <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>rt_ctype_table.o</c:v>
+                  <c:v>aeabi_memset.o</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>aeabi_memset.o</c:v>
+                  <c:v>_snputc.o</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>_snputc.o</c:v>
+                  <c:v>__printf_wp.o</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>__printf_wp.o</c:v>
+                  <c:v>dretinf.o</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>dretinf.o</c:v>
+                  <c:v>__rtentry2.o</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>__rtentry2.o</c:v>
+                  <c:v>fpinit.o</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>fpinit.o</c:v>
+                  <c:v>rtexit2.o</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>rtexit2.o</c:v>
+                  <c:v>_sputc.o</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>_sputc.o</c:v>
+                  <c:v>_printf_ll.o</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>_printf_ll.o</c:v>
+                  <c:v>_printf_l.o</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>_printf_l.o</c:v>
+                  <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>rt_locale_intlibspace.o</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>libspace.o</c:v>
+                  <c:v>ferror.o</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>ferror.o</c:v>
+                  <c:v>__main.o</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>__main.o</c:v>
+                  <c:v>heapauxi.o</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>heapauxi.o</c:v>
+                  <c:v>_printf_x.o</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>_printf_x.o</c:v>
+                  <c:v>_printf_u.o</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>_printf_u.o</c:v>
+                  <c:v>_printf_s.o</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>_printf_s.o</c:v>
+                  <c:v>_printf_p.o</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>_printf_p.o</c:v>
+                  <c:v>_printf_o.o</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>_printf_o.o</c:v>
+                  <c:v>_printf_n.o</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>_printf_n.o</c:v>
+                  <c:v>_printf_ls.o</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>_printf_ls.o</c:v>
+                  <c:v>_printf_llx.o</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>_printf_llx.o</c:v>
+                  <c:v>_printf_llu.o</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>_printf_llu.o</c:v>
+                  <c:v>_printf_llo.o</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>_printf_llo.o</c:v>
+                  <c:v>_printf_lli.o</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>_printf_lli.o</c:v>
+                  <c:v>_printf_lld.o</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>_printf_lld.o</c:v>
+                  <c:v>_printf_lc.o</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>_printf_lc.o</c:v>
+                  <c:v>_printf_i.o</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>_printf_i.o</c:v>
+                  <c:v>_printf_g.o</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>_printf_g.o</c:v>
+                  <c:v>_printf_f.o</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>_printf_f.o</c:v>
+                  <c:v>_printf_e.o</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>_printf_e.o</c:v>
+                  <c:v>_printf_d.o</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>_printf_d.o</c:v>
+                  <c:v>_printf_c.o</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>_printf_c.o</c:v>
+                  <c:v>_printf_a.o</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>_printf_a.o</c:v>
+                  <c:v>__rtentry4.o</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>__rtentry4.o</c:v>
+                  <c:v>printf2.o</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>printf2.o</c:v>
+                  <c:v>printf1.o</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>printf1.o</c:v>
+                  <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>_printf_percent_end.o</c:v>
+                  <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>use_no_semi_2.o</c:v>
+                  <c:v>use_no_semi.o</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>use_no_semi.o</c:v>
+                  <c:v>rtexit.o</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>rtexit.o</c:v>
+                  <c:v>libshutdown2.o</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>libshutdown2.o</c:v>
+                  <c:v>libshutdown.o</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>libshutdown.o</c:v>
+                  <c:v>libinit.o</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>libinit.o</c:v>
+                  <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="131">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1155,404 +1143,401 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$134</c:f>
+              <c:f>flash_percent!$B$3:$B$133</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="132"/>
+                <c:ptCount val="131"/>
                 <c:pt idx="0">
-                  <c:v>22.20732688903809</c:v>
+                  <c:v>22.31991004943848</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.36092758178711</c:v>
+                  <c:v>13.42866325378418</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.693032264709473</c:v>
+                  <c:v>6.726963520050049</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.470958709716797</c:v>
+                  <c:v>4.493625164031982</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.279921054840088</c:v>
+                  <c:v>4.301618576049805</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.726916313171387</c:v>
+                  <c:v>3.570646524429321</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.447062253952026</c:v>
+                  <c:v>3.464537858963013</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.244293928146362</c:v>
+                  <c:v>3.260741472244263</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.049904584884644</c:v>
+                  <c:v>3.065366506576538</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.778429508209229</c:v>
+                  <c:v>2.651036739349365</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.637664556503296</c:v>
+                  <c:v>2.617351293563843</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.967355966567993</c:v>
+                  <c:v>2.088491439819336</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.846700429916382</c:v>
+                  <c:v>1.977329730987549</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.766263365745544</c:v>
+                  <c:v>1.856062531471252</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.638904690742493</c:v>
+                  <c:v>1.775217652320862</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.488085269927979</c:v>
+                  <c:v>1.49562931060791</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.474679112434387</c:v>
+                  <c:v>1.482155203819275</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.343968868255615</c:v>
+                  <c:v>1.35078239440918</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.191473722457886</c:v>
+                  <c:v>1.101510763168335</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.095954656600952</c:v>
+                  <c:v>0.9465581774711609</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8848074674606323</c:v>
+                  <c:v>0.8892931342124939</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8529677987098694</c:v>
+                  <c:v>0.8572920560836792</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8244796991348267</c:v>
+                  <c:v>0.7882370948791504</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.784261167049408</c:v>
+                  <c:v>0.7006551623344421</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6853906512260437</c:v>
+                  <c:v>0.6888653039932251</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6300901770591736</c:v>
+                  <c:v>0.6332845091819763</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5764654874801636</c:v>
+                  <c:v>0.5793879628181458</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5697623491287231</c:v>
+                  <c:v>0.5726508498191834</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5295438766479492</c:v>
+                  <c:v>0.5322284698486328</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.3988336622714996</c:v>
+                  <c:v>0.4008556008338928</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.3887790441513062</c:v>
+                  <c:v>0.390749990940094</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3753728568553925</c:v>
+                  <c:v>0.3772758543491364</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3619666993618012</c:v>
+                  <c:v>0.3435905277729034</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3418574333190918</c:v>
+                  <c:v>0.3368534445762634</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3284512460231781</c:v>
+                  <c:v>0.3301163911819458</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3150450885295868</c:v>
+                  <c:v>0.3166422545909882</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.306666225194931</c:v>
+                  <c:v>0.3082209229469299</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2982873618602753</c:v>
+                  <c:v>0.2997995615005493</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2949358224868774</c:v>
+                  <c:v>0.2964310348033905</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2815296351909638</c:v>
+                  <c:v>0.2627456784248352</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2614203989505768</c:v>
+                  <c:v>0.2560086250305176</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2547172904014587</c:v>
+                  <c:v>0.2492715567350388</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2480142116546631</c:v>
+                  <c:v>0.2324288785457611</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2312564998865128</c:v>
+                  <c:v>0.2324288785457611</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2312564998865128</c:v>
+                  <c:v>0.2256918102502823</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2245534062385559</c:v>
+                  <c:v>0.2155862152576447</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2144987732172012</c:v>
+                  <c:v>0.2155862152576447</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2144987732172012</c:v>
+                  <c:v>0.2088491469621658</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2077956944704056</c:v>
+                  <c:v>0.2021120637655258</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2010926008224487</c:v>
+                  <c:v>0.195374995470047</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1876864284276962</c:v>
+                  <c:v>0.1886379271745682</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1809833496809006</c:v>
+                  <c:v>0.1819008588790894</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1742802560329437</c:v>
+                  <c:v>0.1751637905836105</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1675771623849869</c:v>
+                  <c:v>0.1684267222881317</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1608740836381912</c:v>
+                  <c:v>0.1549525856971741</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1508194506168366</c:v>
+                  <c:v>0.1515840590000153</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1474679112434387</c:v>
+                  <c:v>0.1482155174016953</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1474679112434387</c:v>
+                  <c:v>0.1482155174016953</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1374132782220841</c:v>
+                  <c:v>0.1381099224090576</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1307101994752884</c:v>
+                  <c:v>0.1313728392124176</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1307101994752884</c:v>
+                  <c:v>0.1313728392124176</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1240071058273315</c:v>
+                  <c:v>0.1246357783675194</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1206555590033531</c:v>
+                  <c:v>0.12126724421978</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1139524728059769</c:v>
+                  <c:v>0.1145301759243012</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1072493866086006</c:v>
+                  <c:v>0.1077931076288223</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.09719476103782654</c:v>
+                  <c:v>0.08758189529180527</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.08714012801647186</c:v>
+                  <c:v>0.08758189529180527</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.08714012801647186</c:v>
+                  <c:v>0.08084482699632645</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.08043704181909561</c:v>
+                  <c:v>0.08084482699632645</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.08043704181909561</c:v>
+                  <c:v>0.08084482699632645</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.08043704181909561</c:v>
+                  <c:v>0.08084482699632645</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.08043704181909561</c:v>
+                  <c:v>0.07410775870084763</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07373395562171936</c:v>
+                  <c:v>0.07410775870084763</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.07373395562171936</c:v>
+                  <c:v>0.06737069040536881</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.06703086942434311</c:v>
+                  <c:v>0.0640021562576294</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.06367932260036469</c:v>
+                  <c:v>0.06063362210988998</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.06032777950167656</c:v>
+                  <c:v>0.06063362210988998</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.06032777950167656</c:v>
+                  <c:v>0.05726508796215057</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.05697623640298843</c:v>
+                  <c:v>0.04715948179364204</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.04692160710692406</c:v>
+                  <c:v>0.04379094764590263</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.04357006400823593</c:v>
+                  <c:v>0.04042241349816322</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.04021852090954781</c:v>
+                  <c:v>0.0336853452026844</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.03351543471217156</c:v>
+                  <c:v>0.03031681105494499</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.03016388975083828</c:v>
+                  <c:v>0.02694827690720558</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.02681234665215015</c:v>
+                  <c:v>0.02694827690720558</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.02681234665215015</c:v>
+                  <c:v>0.02694827690720558</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.02681234665215015</c:v>
+                  <c:v>0.02357974089682102</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.02346080355346203</c:v>
+                  <c:v>0.02021120674908161</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.0201092604547739</c:v>
+                  <c:v>0.02021120674908161</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.0201092604547739</c:v>
+                  <c:v>0.0168426726013422</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.01675771735608578</c:v>
+                  <c:v>0.0168426726013422</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.01675771735608578</c:v>
+                  <c:v>0.0168426726013422</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.01675771735608578</c:v>
+                  <c:v>0.0168426726013422</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01675771735608578</c:v>
+                  <c:v>0.0168426726013422</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01675771735608578</c:v>
+                  <c:v>0.01347413845360279</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01340617332607508</c:v>
+                  <c:v>0.01347413845360279</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01340617332607508</c:v>
+                  <c:v>0.01347413845360279</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01340617332607508</c:v>
+                  <c:v>0.01347413845360279</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01340617332607508</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.01010560337454081</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.01005463022738695</c:v>
+                  <c:v>0.006737069226801395</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.006703086663037539</c:v>
+                  <c:v>0.006737069226801395</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.006703086663037539</c:v>
+                  <c:v>0.006737069226801395</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.006703086663037539</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.003351543331518769</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.003351543331518769</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.003351543331518769</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.003351543331518769</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.003351543331518769</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.003351543331518769</c:v>
+                  <c:v>0.003368534613400698</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.003351543331518769</c:v>
-                </c:pt>
-                <c:pt idx="131">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1657,8 +1642,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H134" totalsRowCount="1">
-  <autoFilter ref="A2:H133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H133" totalsRowCount="1">
+  <autoFilter ref="A2:H132"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1674,8 +1659,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H134" totalsRowCount="1">
-  <autoFilter ref="A2:H133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H133" totalsRowCount="1">
+  <autoFilter ref="A2:H132"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1975,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1988,28 +1973,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
         <v>134</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>135</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>136</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>137</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>138</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>139</v>
-      </c>
-      <c r="H2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2017,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>56.00291442871094</v>
+        <v>56.0035514831543</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2043,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>39.68391418457031</v>
+        <v>39.68436431884766</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -2069,7 +2054,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.176216125488281</v>
+        <v>1.176229476928711</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -2095,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.165968298912048</v>
+        <v>1.165981531143189</v>
       </c>
       <c r="C6" s="1">
         <v>1024</v>
@@ -2121,7 +2106,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.9154673218727112</v>
+        <v>0.9154776930809021</v>
       </c>
       <c r="C7" s="1">
         <v>804</v>
@@ -2147,22 +2132,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.313126266002655</v>
+        <v>0.3165457844734192</v>
       </c>
       <c r="C8" s="1">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D8" s="1">
-        <v>711</v>
+        <v>562</v>
       </c>
       <c r="E8" s="1">
-        <v>704</v>
+        <v>552</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1">
         <v>268</v>
@@ -2173,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1093095317482948</v>
+        <v>0.1093107759952545</v>
       </c>
       <c r="C9" s="1">
         <v>96</v>
@@ -2199,7 +2184,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1093095317482948</v>
+        <v>0.1093107759952545</v>
       </c>
       <c r="C10" s="1">
         <v>96</v>
@@ -2225,16 +2210,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1093095317482948</v>
+        <v>0.1093107759952545</v>
       </c>
       <c r="C11" s="1">
         <v>96</v>
       </c>
       <c r="D11" s="1">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E11" s="1">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2251,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1070322468876839</v>
+        <v>0.1070334613323212</v>
       </c>
       <c r="C12" s="1">
         <v>94</v>
@@ -2277,16 +2262,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1047549620270729</v>
+        <v>0.1047561541199684</v>
       </c>
       <c r="C13" s="1">
         <v>92</v>
       </c>
       <c r="D13" s="1">
-        <v>492</v>
+        <v>416</v>
       </c>
       <c r="E13" s="1">
-        <v>492</v>
+        <v>416</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2303,7 +2288,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.07287301868200302</v>
+        <v>0.07287384569644928</v>
       </c>
       <c r="C14" s="1">
         <v>64</v>
@@ -2329,7 +2314,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06831845641136169</v>
+        <v>0.06831923127174377</v>
       </c>
       <c r="C15" s="1">
         <v>60</v>
@@ -2355,7 +2340,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01366369146853685</v>
+        <v>0.01366384699940682</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
@@ -2381,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01024776790291071</v>
+        <v>0.01024788524955511</v>
       </c>
       <c r="C17" s="1">
         <v>9</v>
@@ -2407,16 +2392,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.009109127335250378</v>
+        <v>0.00910923071205616</v>
       </c>
       <c r="C18" s="1">
         <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>216</v>
+        <v>116</v>
       </c>
       <c r="E18" s="1">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2433,7 +2418,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.004554563667625189</v>
+        <v>0.00455461535602808</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -2459,7 +2444,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.004554563667625189</v>
+        <v>0.00455461535602808</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
@@ -2485,16 +2470,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004554563667625189</v>
+        <v>0.00455461535602808</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="E21" s="1">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2511,16 +2496,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004554563667625189</v>
+        <v>0.00455461535602808</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="E22" s="1">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2537,16 +2522,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.004554563667625189</v>
+        <v>0.00455461535602808</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="E23" s="1">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2563,82 +2548,56 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.004554563667625189</v>
+        <v>0.00113865383900702</v>
       </c>
       <c r="C24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" s="1">
-        <v>108</v>
+        <v>2057</v>
       </c>
       <c r="E24" s="1">
-        <v>104</v>
+        <v>2056</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2">
-        <v>0.001138640916906297</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2057</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2056</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" t="s">
-        <v>133</v>
-      </c>
-      <c r="B134">
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C134">
+      <c r="C133">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D134">
+      <c r="D133">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E134">
+      <c r="E133">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F134">
+      <c r="F133">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G134">
+      <c r="G133">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H134">
+      <c r="H133">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2654,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2667,28 +2626,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" t="s">
         <v>136</v>
       </c>
-      <c r="D2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>137</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>138</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>139</v>
-      </c>
-      <c r="H2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2696,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>22.20732688903809</v>
+        <v>22.31991004943848</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2722,7 +2681,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>13.36092758178711</v>
+        <v>13.42866325378418</v>
       </c>
       <c r="C4" s="1">
         <v>7973</v>
@@ -2748,7 +2707,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>6.693032264709473</v>
+        <v>6.726963520050049</v>
       </c>
       <c r="C5" s="1">
         <v>3994</v>
@@ -2771,10 +2730,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
-        <v>4.470958709716797</v>
+        <v>4.493625164031982</v>
       </c>
       <c r="C6" s="1">
         <v>2668</v>
@@ -2797,10 +2756,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
-        <v>4.279921054840088</v>
+        <v>4.301618576049805</v>
       </c>
       <c r="C7" s="1">
         <v>2554</v>
@@ -2823,19 +2782,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
-        <v>3.726916313171387</v>
+        <v>3.570646524429321</v>
       </c>
       <c r="C8" s="1">
-        <v>2224</v>
+        <v>2120</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2224</v>
+        <v>2120</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2849,10 +2808,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
-        <v>3.447062253952026</v>
+        <v>3.464537858963013</v>
       </c>
       <c r="C9" s="1">
         <v>2057</v>
@@ -2875,10 +2834,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>3.244293928146362</v>
+        <v>3.260741472244263</v>
       </c>
       <c r="C10" s="1">
         <v>1936</v>
@@ -2901,10 +2860,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>3.049904584884644</v>
+        <v>3.065366506576538</v>
       </c>
       <c r="C11" s="1">
         <v>1820</v>
@@ -2927,19 +2886,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>2.778429508209229</v>
+        <v>2.651036739349365</v>
       </c>
       <c r="C12" s="1">
-        <v>1658</v>
+        <v>1574</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1">
-        <v>1658</v>
+        <v>1574</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2948,56 +2907,56 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
-        <v>2.637664556503296</v>
+        <v>2.617351293563843</v>
       </c>
       <c r="C13" s="1">
-        <v>1574</v>
+        <v>1554</v>
       </c>
       <c r="D13" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1574</v>
+        <v>1546</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
-        <v>1.967355966567993</v>
+        <v>2.088491439819336</v>
       </c>
       <c r="C14" s="1">
-        <v>1174</v>
+        <v>1240</v>
       </c>
       <c r="D14" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1162</v>
+        <v>1240</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -3005,74 +2964,74 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>1.846700429916382</v>
+        <v>1.977329730987549</v>
       </c>
       <c r="C15" s="1">
-        <v>1102</v>
+        <v>1174</v>
       </c>
       <c r="D15" s="1">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1">
-        <v>1082</v>
+        <v>1162</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H15" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>1.766263365745544</v>
+        <v>1.856062531471252</v>
       </c>
       <c r="C16" s="1">
-        <v>1054</v>
+        <v>1102</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E16" s="1">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2">
-        <v>1.638904690742493</v>
+        <v>1.775217652320862</v>
       </c>
       <c r="C17" s="1">
-        <v>978</v>
+        <v>1054</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>970</v>
+        <v>1054</v>
       </c>
       <c r="F17" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -3083,10 +3042,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2">
-        <v>1.488085269927979</v>
+        <v>1.49562931060791</v>
       </c>
       <c r="C18" s="1">
         <v>888</v>
@@ -3112,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>1.474679112434387</v>
+        <v>1.482155203819275</v>
       </c>
       <c r="C19" s="1">
         <v>880</v>
@@ -3135,10 +3094,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2">
-        <v>1.343968868255615</v>
+        <v>1.35078239440918</v>
       </c>
       <c r="C20" s="1">
         <v>802</v>
@@ -3161,62 +3120,62 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2">
-        <v>1.191473722457886</v>
+        <v>1.101510763168335</v>
       </c>
       <c r="C21" s="1">
-        <v>711</v>
+        <v>654</v>
       </c>
       <c r="D21" s="1">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>704</v>
+        <v>654</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2">
-        <v>1.095954656600952</v>
+        <v>0.9465581774711609</v>
       </c>
       <c r="C22" s="1">
-        <v>654</v>
+        <v>562</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="E22" s="1">
-        <v>654</v>
+        <v>552</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8848074674606323</v>
+        <v>0.8892931342124939</v>
       </c>
       <c r="C23" s="1">
         <v>528</v>
@@ -3242,7 +3201,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8529677987098694</v>
+        <v>0.8572920560836792</v>
       </c>
       <c r="C24" s="1">
         <v>509</v>
@@ -3265,62 +3224,62 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8244796991348267</v>
+        <v>0.7882370948791504</v>
       </c>
       <c r="C25" s="1">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="D25" s="1">
-        <v>92</v>
+        <v>1024</v>
       </c>
       <c r="E25" s="1">
-        <v>492</v>
+        <v>76</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>92</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B26" s="2">
-        <v>0.784261167049408</v>
+        <v>0.7006551623344421</v>
       </c>
       <c r="C26" s="1">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="D26" s="1">
-        <v>1024</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1">
-        <v>76</v>
+        <v>416</v>
       </c>
       <c r="F26" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>1024</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6853906512260437</v>
+        <v>0.6888653039932251</v>
       </c>
       <c r="C27" s="1">
         <v>409</v>
@@ -3343,10 +3302,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6300901770591736</v>
+        <v>0.6332845091819763</v>
       </c>
       <c r="C28" s="1">
         <v>376</v>
@@ -3369,10 +3328,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5764654874801636</v>
+        <v>0.5793879628181458</v>
       </c>
       <c r="C29" s="1">
         <v>344</v>
@@ -3395,10 +3354,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5697623491287231</v>
+        <v>0.5726508498191834</v>
       </c>
       <c r="C30" s="1">
         <v>340</v>
@@ -3421,10 +3380,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5295438766479492</v>
+        <v>0.5322284698486328</v>
       </c>
       <c r="C31" s="1">
         <v>316</v>
@@ -3447,10 +3406,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2">
-        <v>0.3988336622714996</v>
+        <v>0.4008556008338928</v>
       </c>
       <c r="C32" s="1">
         <v>238</v>
@@ -3473,10 +3432,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="2">
-        <v>0.3887790441513062</v>
+        <v>0.390749990940094</v>
       </c>
       <c r="C33" s="1">
         <v>232</v>
@@ -3502,7 +3461,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3753728568553925</v>
+        <v>0.3772758543491364</v>
       </c>
       <c r="C34" s="1">
         <v>224</v>
@@ -3525,25 +3484,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3619666993618012</v>
+        <v>0.3435905277729034</v>
       </c>
       <c r="C35" s="1">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D35" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -3551,19 +3510,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3418574333190918</v>
+        <v>0.3368534445762634</v>
       </c>
       <c r="C36" s="1">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E36" s="1">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -3572,15 +3531,15 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3284512460231781</v>
+        <v>0.3301163911819458</v>
       </c>
       <c r="C37" s="1">
         <v>196</v>
@@ -3603,10 +3562,10 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3150450885295868</v>
+        <v>0.3166422545909882</v>
       </c>
       <c r="C38" s="1">
         <v>188</v>
@@ -3632,7 +3591,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="2">
-        <v>0.306666225194931</v>
+        <v>0.3082209229469299</v>
       </c>
       <c r="C39" s="1">
         <v>183</v>
@@ -3655,10 +3614,10 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2982873618602753</v>
+        <v>0.2997995615005493</v>
       </c>
       <c r="C40" s="1">
         <v>178</v>
@@ -3681,10 +3640,10 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2949358224868774</v>
+        <v>0.2964310348033905</v>
       </c>
       <c r="C41" s="1">
         <v>176</v>
@@ -3707,19 +3666,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2815296351909638</v>
+        <v>0.2627456784248352</v>
       </c>
       <c r="C42" s="1">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D42" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3728,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3736,16 +3695,16 @@
         <v>47</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2614203989505768</v>
+        <v>0.2560086250305176</v>
       </c>
       <c r="C43" s="1">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3762,16 +3721,16 @@
         <v>48</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2547172904014587</v>
+        <v>0.2492715567350388</v>
       </c>
       <c r="C44" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3788,16 +3747,16 @@
         <v>49</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2480142116546631</v>
+        <v>0.2324288785457611</v>
       </c>
       <c r="C45" s="1">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3814,7 +3773,7 @@
         <v>50</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2312564998865128</v>
+        <v>0.2324288785457611</v>
       </c>
       <c r="C46" s="1">
         <v>138</v>
@@ -3840,16 +3799,16 @@
         <v>51</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2312564998865128</v>
+        <v>0.2256918102502823</v>
       </c>
       <c r="C47" s="1">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3866,16 +3825,16 @@
         <v>52</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2245534062385559</v>
+        <v>0.2155862152576447</v>
       </c>
       <c r="C48" s="1">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3892,7 +3851,7 @@
         <v>53</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2144987732172012</v>
+        <v>0.2155862152576447</v>
       </c>
       <c r="C49" s="1">
         <v>128</v>
@@ -3918,16 +3877,16 @@
         <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2144987732172012</v>
+        <v>0.2088491469621658</v>
       </c>
       <c r="C50" s="1">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3944,16 +3903,16 @@
         <v>55</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2077956944704056</v>
+        <v>0.2021120637655258</v>
       </c>
       <c r="C51" s="1">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3967,25 +3926,25 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2010926008224487</v>
+        <v>0.195374995470047</v>
       </c>
       <c r="C52" s="1">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -3993,10 +3952,10 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1876864284276962</v>
+        <v>0.1886379271745682</v>
       </c>
       <c r="C53" s="1">
         <v>112</v>
@@ -4019,10 +3978,10 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1809833496809006</v>
+        <v>0.1819008588790894</v>
       </c>
       <c r="C54" s="1">
         <v>108</v>
@@ -4048,7 +4007,7 @@
         <v>18</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1742802560329437</v>
+        <v>0.1751637905836105</v>
       </c>
       <c r="C55" s="1">
         <v>104</v>
@@ -4071,10 +4030,10 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1675771623849869</v>
+        <v>0.1684267222881317</v>
       </c>
       <c r="C56" s="1">
         <v>100</v>
@@ -4097,19 +4056,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1608740836381912</v>
+        <v>0.1549525856971741</v>
       </c>
       <c r="C57" s="1">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
       </c>
       <c r="E57" s="1">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4123,10 +4082,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1508194506168366</v>
+        <v>0.1515840590000153</v>
       </c>
       <c r="C58" s="1">
         <v>90</v>
@@ -4149,10 +4108,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1474679112434387</v>
+        <v>0.1482155174016953</v>
       </c>
       <c r="C59" s="1">
         <v>88</v>
@@ -4175,10 +4134,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1474679112434387</v>
+        <v>0.1482155174016953</v>
       </c>
       <c r="C60" s="1">
         <v>88</v>
@@ -4201,10 +4160,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1374132782220841</v>
+        <v>0.1381099224090576</v>
       </c>
       <c r="C61" s="1">
         <v>82</v>
@@ -4227,10 +4186,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1307101994752884</v>
+        <v>0.1313728392124176</v>
       </c>
       <c r="C62" s="1">
         <v>78</v>
@@ -4253,10 +4212,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1307101994752884</v>
+        <v>0.1313728392124176</v>
       </c>
       <c r="C63" s="1">
         <v>78</v>
@@ -4279,10 +4238,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1240071058273315</v>
+        <v>0.1246357783675194</v>
       </c>
       <c r="C64" s="1">
         <v>74</v>
@@ -4305,10 +4264,10 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1206555590033531</v>
+        <v>0.12126724421978</v>
       </c>
       <c r="C65" s="1">
         <v>72</v>
@@ -4331,10 +4290,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1139524728059769</v>
+        <v>0.1145301759243012</v>
       </c>
       <c r="C66" s="1">
         <v>68</v>
@@ -4357,10 +4316,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1072493866086006</v>
+        <v>0.1077931076288223</v>
       </c>
       <c r="C67" s="1">
         <v>64</v>
@@ -4383,25 +4342,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.09719476103782654</v>
+        <v>0.08758189529180527</v>
       </c>
       <c r="C68" s="1">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -4412,7 +4371,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.08714012801647186</v>
+        <v>0.08758189529180527</v>
       </c>
       <c r="C69" s="1">
         <v>52</v>
@@ -4438,16 +4397,16 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.08714012801647186</v>
+        <v>0.08084482699632645</v>
       </c>
       <c r="C70" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4464,7 +4423,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.08043704181909561</v>
+        <v>0.08084482699632645</v>
       </c>
       <c r="C71" s="1">
         <v>48</v>
@@ -4490,7 +4449,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.08043704181909561</v>
+        <v>0.08084482699632645</v>
       </c>
       <c r="C72" s="1">
         <v>48</v>
@@ -4513,25 +4472,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="B73" s="2">
-        <v>0.08043704181909561</v>
+        <v>0.08084482699632645</v>
       </c>
       <c r="C73" s="1">
         <v>48</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4539,25 +4498,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.08043704181909561</v>
+        <v>0.07410775870084763</v>
       </c>
       <c r="C74" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D74" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F74" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -4568,7 +4527,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07373395562171936</v>
+        <v>0.07410775870084763</v>
       </c>
       <c r="C75" s="1">
         <v>44</v>
@@ -4594,16 +4553,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.07373395562171936</v>
+        <v>0.06737069040536881</v>
       </c>
       <c r="C76" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4620,16 +4579,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.06703086942434311</v>
+        <v>0.0640021562576294</v>
       </c>
       <c r="C77" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4646,16 +4605,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="2">
-        <v>0.06367932260036469</v>
+        <v>0.06063362210988998</v>
       </c>
       <c r="C78" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4672,7 +4631,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2">
-        <v>0.06032777950167656</v>
+        <v>0.06063362210988998</v>
       </c>
       <c r="C79" s="1">
         <v>36</v>
@@ -4698,16 +4657,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="2">
-        <v>0.06032777950167656</v>
+        <v>0.05726508796215057</v>
       </c>
       <c r="C80" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4724,16 +4683,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="2">
-        <v>0.05697623640298843</v>
+        <v>0.04715948179364204</v>
       </c>
       <c r="C81" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4750,16 +4709,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>0.04692160710692406</v>
+        <v>0.04379094764590263</v>
       </c>
       <c r="C82" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4776,16 +4735,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="2">
-        <v>0.04357006400823593</v>
+        <v>0.04042241349816322</v>
       </c>
       <c r="C83" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4802,16 +4761,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="2">
-        <v>0.04021852090954781</v>
+        <v>0.0336853452026844</v>
       </c>
       <c r="C84" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4828,16 +4787,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>0.03351543471217156</v>
+        <v>0.03031681105494499</v>
       </c>
       <c r="C85" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -4854,16 +4813,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.03016388975083828</v>
+        <v>0.02694827690720558</v>
       </c>
       <c r="C86" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4880,7 +4839,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.02681234665215015</v>
+        <v>0.02694827690720558</v>
       </c>
       <c r="C87" s="1">
         <v>16</v>
@@ -4906,7 +4865,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.02681234665215015</v>
+        <v>0.02694827690720558</v>
       </c>
       <c r="C88" s="1">
         <v>16</v>
@@ -4932,16 +4891,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.02681234665215015</v>
+        <v>0.02357974089682102</v>
       </c>
       <c r="C89" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -4958,16 +4917,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.02346080355346203</v>
+        <v>0.02021120674908161</v>
       </c>
       <c r="C90" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -4984,7 +4943,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.0201092604547739</v>
+        <v>0.02021120674908161</v>
       </c>
       <c r="C91" s="1">
         <v>12</v>
@@ -5010,16 +4969,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.0201092604547739</v>
+        <v>0.0168426726013422</v>
       </c>
       <c r="C92" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -5036,7 +4995,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.01675771735608578</v>
+        <v>0.0168426726013422</v>
       </c>
       <c r="C93" s="1">
         <v>10</v>
@@ -5062,7 +5021,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.01675771735608578</v>
+        <v>0.0168426726013422</v>
       </c>
       <c r="C94" s="1">
         <v>10</v>
@@ -5088,7 +5047,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.01675771735608578</v>
+        <v>0.0168426726013422</v>
       </c>
       <c r="C95" s="1">
         <v>10</v>
@@ -5114,7 +5073,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.01675771735608578</v>
+        <v>0.0168426726013422</v>
       </c>
       <c r="C96" s="1">
         <v>10</v>
@@ -5140,16 +5099,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01675771735608578</v>
+        <v>0.01347413845360279</v>
       </c>
       <c r="C97" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5163,16 +5122,16 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01340617332607508</v>
+        <v>0.01347413845360279</v>
       </c>
       <c r="C98" s="1">
         <v>8</v>
       </c>
       <c r="D98" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E98" s="1">
         <v>8</v>
@@ -5184,21 +5143,21 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01340617332607508</v>
+        <v>0.01347413845360279</v>
       </c>
       <c r="C99" s="1">
         <v>8</v>
       </c>
       <c r="D99" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E99" s="1">
         <v>8</v>
@@ -5210,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -5218,7 +5177,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01340617332607508</v>
+        <v>0.01347413845360279</v>
       </c>
       <c r="C100" s="1">
         <v>8</v>
@@ -5244,16 +5203,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01340617332607508</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C101" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -5270,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C102" s="1">
         <v>6</v>
@@ -5296,7 +5255,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C103" s="1">
         <v>6</v>
@@ -5322,7 +5281,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C104" s="1">
         <v>6</v>
@@ -5348,7 +5307,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C105" s="1">
         <v>6</v>
@@ -5374,7 +5333,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C106" s="1">
         <v>6</v>
@@ -5400,7 +5359,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C107" s="1">
         <v>6</v>
@@ -5426,7 +5385,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C108" s="1">
         <v>6</v>
@@ -5452,7 +5411,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C109" s="1">
         <v>6</v>
@@ -5478,7 +5437,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C110" s="1">
         <v>6</v>
@@ -5504,7 +5463,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C111" s="1">
         <v>6</v>
@@ -5530,7 +5489,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C112" s="1">
         <v>6</v>
@@ -5556,7 +5515,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C113" s="1">
         <v>6</v>
@@ -5582,7 +5541,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C114" s="1">
         <v>6</v>
@@ -5608,7 +5567,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C115" s="1">
         <v>6</v>
@@ -5634,7 +5593,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5660,7 +5619,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5686,7 +5645,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5712,7 +5671,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5738,7 +5697,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5764,7 +5723,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5790,7 +5749,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.01010560337454081</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5816,16 +5775,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.01005463022738695</v>
+        <v>0.006737069226801395</v>
       </c>
       <c r="C123" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -5842,7 +5801,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.006703086663037539</v>
+        <v>0.006737069226801395</v>
       </c>
       <c r="C124" s="1">
         <v>4</v>
@@ -5868,7 +5827,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.006703086663037539</v>
+        <v>0.006737069226801395</v>
       </c>
       <c r="C125" s="1">
         <v>4</v>
@@ -5894,16 +5853,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.006703086663037539</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C126" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -5920,7 +5879,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.003351543331518769</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C127" s="1">
         <v>2</v>
@@ -5946,7 +5905,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.003351543331518769</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -5972,7 +5931,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.003351543331518769</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C129" s="1">
         <v>2</v>
@@ -5998,7 +5957,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003351543331518769</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -6024,7 +5983,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.003351543331518769</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C131" s="1">
         <v>2</v>
@@ -6050,7 +6009,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.003351543331518769</v>
+        <v>0.003368534613400698</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -6072,60 +6031,34 @@
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B133" s="2">
-        <v>0.003351543331518769</v>
-      </c>
-      <c r="C133" s="1">
-        <v>2</v>
-      </c>
-      <c r="D133" s="1">
-        <v>0</v>
-      </c>
-      <c r="E133" s="1">
-        <v>2</v>
-      </c>
-      <c r="F133" s="1">
-        <v>0</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0</v>
-      </c>
-      <c r="H133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" t="s">
-        <v>133</v>
-      </c>
-      <c r="B134">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C134">
+      <c r="C133">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D134">
+      <c r="D133">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E134">
+      <c r="E133">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F134">
+      <c r="F133">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G134">
+      <c r="G133">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H134">
+      <c r="H133">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="144">
   <si>
     <t>atk_f407</t>
   </si>
@@ -53,6 +53,9 @@
     <t>can.o</t>
   </si>
   <si>
+    <t>dht11.o</t>
+  </si>
+  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>port.o</t>
   </si>
   <si>
+    <t>dht11_task.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal.o</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t>usbd_ctlreq.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_i2c.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_pcd.o</t>
   </si>
   <si>
@@ -191,13 +200,13 @@
     <t>rt_memcpy_w.o</t>
   </si>
   <si>
+    <t>main.o</t>
+  </si>
+  <si>
     <t>dfixu.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_sram.o</t>
-  </si>
-  <si>
-    <t>main.o</t>
   </si>
   <si>
     <t>_printf_str.o</t>
@@ -527,9 +536,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$133</c:f>
+              <c:f>ram_percent!$A$3:$A$136</c:f>
               <c:strCache>
-                <c:ptCount val="131"/>
+                <c:ptCount val="134"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -564,39 +573,45 @@
                   <c:v>can.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>dht11.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
+                  <c:v>dht11_task.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="133">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -604,77 +619,83 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$133</c:f>
+              <c:f>ram_percent!$B$3:$B$136</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="131"/>
+                <c:ptCount val="134"/>
                 <c:pt idx="0">
-                  <c:v>56.0035514831543</c:v>
+                  <c:v>55.93858337402344</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.68436431884766</c:v>
+                  <c:v>39.63832855224609</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.176229476928711</c:v>
+                  <c:v>1.174864888191223</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.165981531143189</c:v>
+                  <c:v>1.164628982543945</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9154776930809021</c:v>
+                  <c:v>0.914415717124939</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3165457844734192</c:v>
+                  <c:v>0.316178560256958</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1093107759952545</c:v>
+                  <c:v>0.1091839671134949</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1093107759952545</c:v>
+                  <c:v>0.1091839671134949</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1093107759952545</c:v>
+                  <c:v>0.1091839671134949</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1070334613323212</c:v>
+                  <c:v>0.1069092974066734</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1047561541199684</c:v>
+                  <c:v>0.1046346351504326</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07287384569644928</c:v>
+                  <c:v>0.1023599654436112</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06831923127174377</c:v>
+                  <c:v>0.07278931140899658</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01366384699940682</c:v>
+                  <c:v>0.0682399794459343</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01024788524955511</c:v>
+                  <c:v>0.01364799588918686</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.00910923071205616</c:v>
+                  <c:v>0.01364799588918686</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00455461535602808</c:v>
+                  <c:v>0.01023599691689014</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00455461535602808</c:v>
+                  <c:v>0.009098663926124573</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00455461535602808</c:v>
+                  <c:v>0.004549331963062286</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.00455461535602808</c:v>
+                  <c:v>0.004549331963062286</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.00455461535602808</c:v>
+                  <c:v>0.004549331963062286</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00113865383900702</c:v>
-                </c:pt>
-                <c:pt idx="130">
+                  <c:v>0.004549331963062286</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.004549331963062286</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.001137332990765572</c:v>
+                </c:pt>
+                <c:pt idx="133">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -742,9 +763,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$133</c:f>
+              <c:f>flash_percent!$A$3:$A$136</c:f>
               <c:strCache>
-                <c:ptCount val="131"/>
+                <c:ptCount val="134"/>
                 <c:pt idx="0">
                   <c:v>lcd.o</c:v>
                 </c:pt>
@@ -755,387 +776,396 @@
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>stm32f4xx_hal_i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>stm32f4xx_hal_pcd.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>stm32f4xx_ll_usb.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>stm32f4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>btod.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>stm32f4xx_hal_can.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>_printf_fp_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>usbd_core.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>_printf_fp_hex.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>fz_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
+                  <c:v>dht11.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>__printf_flags_ss_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>bigflt0.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>stm32f4xx_ll_fsmc.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>malloc.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="36">
                   <c:v>_printf_wctomb.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>_printf_hex_int_ll_ptr.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="38">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>dnaninf.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="42">
                   <c:v>led.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="43">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>strcmpv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>_printf_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="51">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="52">
                   <c:v>_printf_oct_int_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="53">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="54">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="55">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="56">
                   <c:v>freertos_start.o</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>dfixu.o</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>stm32f4xx_hal_sram.o</c:v>
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>dfixu.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>stm32f4xx_hal_sram.o</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>dht11_task.o</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>_printf_str.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="62">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="63">
                   <c:v>_printf_pad.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="64">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="65">
                   <c:v>lc_numeric_c.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="66">
                   <c:v>rt_memclr.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="67">
                   <c:v>_wcrtomb.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="68">
                   <c:v>vsnprintf.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="69">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="70">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="71">
                   <c:v>fpclassify.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="72">
                   <c:v>_printf_char_common.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="73">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="74">
                   <c:v>_printf_wchar.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="75">
                   <c:v>_printf_char.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="76">
                   <c:v>_printf_charcount.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="77">
                   <c:v>dflt_clz.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="78">
                   <c:v>_printf_truncate.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="79">
                   <c:v>_printf_char_file.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="80">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="81">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="82">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="83">
                   <c:v>__2printf.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="84">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="85">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="86">
                   <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="87">
                   <c:v>aeabi_memset.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="88">
                   <c:v>_snputc.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="89">
                   <c:v>__printf_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="90">
                   <c:v>dretinf.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="91">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="92">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="93">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="94">
                   <c:v>_sputc.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="95">
                   <c:v>_printf_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="96">
                   <c:v>_printf_l.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="97">
                   <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="98">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="99">
                   <c:v>ferror.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="100">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="101">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="102">
                   <c:v>_printf_x.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="103">
                   <c:v>_printf_u.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="104">
                   <c:v>_printf_s.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="105">
                   <c:v>_printf_p.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="106">
                   <c:v>_printf_o.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="107">
                   <c:v>_printf_n.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="108">
                   <c:v>_printf_ls.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="109">
                   <c:v>_printf_llx.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="110">
                   <c:v>_printf_llu.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="111">
                   <c:v>_printf_llo.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="112">
                   <c:v>_printf_lli.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="113">
                   <c:v>_printf_lld.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="114">
                   <c:v>_printf_lc.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="115">
                   <c:v>_printf_i.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="116">
                   <c:v>_printf_g.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="117">
                   <c:v>_printf_f.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="118">
                   <c:v>_printf_e.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="119">
                   <c:v>_printf_d.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="120">
                   <c:v>_printf_c.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="121">
                   <c:v>_printf_a.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="122">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="123">
                   <c:v>printf2.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="124">
                   <c:v>printf1.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="125">
                   <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="126">
                   <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="127">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="128">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="129">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="130">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="131">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="132">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="133">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1143,401 +1173,410 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$133</c:f>
+              <c:f>flash_percent!$B$3:$B$136</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="131"/>
+                <c:ptCount val="134"/>
                 <c:pt idx="0">
-                  <c:v>22.31991004943848</c:v>
+                  <c:v>21.13994979858398</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.42866325378418</c:v>
+                  <c:v>12.71874523162842</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.726963520050049</c:v>
+                  <c:v>6.371336936950684</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.493625164031982</c:v>
+                  <c:v>4.466635704040527</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.301618576049805</c:v>
+                  <c:v>4.256065845489502</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.570646524429321</c:v>
+                  <c:v>4.074210166931152</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.464537858963013</c:v>
+                  <c:v>3.381881475448608</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.260741472244263</c:v>
+                  <c:v>3.281382083892822</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.065366506576538</c:v>
+                  <c:v>3.088359594345093</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.651036739349365</c:v>
+                  <c:v>2.903313398361206</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.617351293563843</c:v>
+                  <c:v>2.510887384414673</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.088491439819336</c:v>
+                  <c:v>2.478982925415039</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.977329730987549</c:v>
+                  <c:v>1.978081583976746</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.856062531471252</c:v>
+                  <c:v>1.872796535491943</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.775217652320862</c:v>
+                  <c:v>1.757940292358398</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.49562931060791</c:v>
+                  <c:v>1.681369304656982</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.482155203819275</c:v>
+                  <c:v>1.416561603546143</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.35078239440918</c:v>
+                  <c:v>1.403799772262573</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.101510763168335</c:v>
+                  <c:v>1.279372096061707</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9465581774711609</c:v>
+                  <c:v>1.043278455734253</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8892931342124939</c:v>
+                  <c:v>0.8965176343917847</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8572920560836792</c:v>
+                  <c:v>0.8422799110412598</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.7882370948791504</c:v>
+                  <c:v>0.811970591545105</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7006551623344421</c:v>
+                  <c:v>0.7465662956237793</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6888653039932251</c:v>
+                  <c:v>0.6668049097061157</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6332845091819763</c:v>
+                  <c:v>0.6636144518852234</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5793879628181458</c:v>
+                  <c:v>0.6524478793144226</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5726508498191834</c:v>
+                  <c:v>0.5998053550720215</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5322284698486328</c:v>
+                  <c:v>0.5487580895423889</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4008556008338928</c:v>
+                  <c:v>0.542377233505249</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.390749990940094</c:v>
+                  <c:v>0.504091739654541</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3772758543491364</c:v>
+                  <c:v>0.3796640336513519</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3435905277729034</c:v>
+                  <c:v>0.3700926899909973</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3368534445762634</c:v>
+                  <c:v>0.357330858707428</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3301163911819458</c:v>
+                  <c:v>0.325426310300827</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3166422545909882</c:v>
+                  <c:v>0.3190454244613648</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3082209229469299</c:v>
+                  <c:v>0.3126645088195801</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2997995615005493</c:v>
+                  <c:v>0.2999026775360107</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2964310348033905</c:v>
+                  <c:v>0.2919265627861023</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2627456784248352</c:v>
+                  <c:v>0.2839504182338715</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2560086250305176</c:v>
+                  <c:v>0.2807599604129791</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2492715567350388</c:v>
+                  <c:v>0.2488554269075394</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2324288785457611</c:v>
+                  <c:v>0.2424745112657547</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2324288785457611</c:v>
+                  <c:v>0.2360936105251312</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2256918102502823</c:v>
+                  <c:v>0.2201413363218308</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2155862152576447</c:v>
+                  <c:v>0.2201413363218308</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2155862152576447</c:v>
+                  <c:v>0.2137604355812073</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2088491469621658</c:v>
+                  <c:v>0.2041890621185303</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2021120637655258</c:v>
+                  <c:v>0.2041890621185303</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.195374995470047</c:v>
+                  <c:v>0.1978081613779068</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1886379271745682</c:v>
+                  <c:v>0.1914272457361221</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1819008588790894</c:v>
+                  <c:v>0.1850463449954987</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1751637905836105</c:v>
+                  <c:v>0.178665429353714</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1684267222881317</c:v>
+                  <c:v>0.1722845286130905</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1549525856971741</c:v>
+                  <c:v>0.1659036129713059</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1515840590000153</c:v>
+                  <c:v>0.1595227122306824</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1482155174016953</c:v>
+                  <c:v>0.1531417965888977</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1482155174016953</c:v>
+                  <c:v>0.1467608958482742</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1381099224090576</c:v>
+                  <c:v>0.1435704380273819</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1313728392124176</c:v>
+                  <c:v>0.1403799802064896</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1313728392124176</c:v>
+                  <c:v>0.1403799802064896</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1246357783675194</c:v>
+                  <c:v>0.1308086216449738</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.12126724421978</c:v>
+                  <c:v>0.1244277134537697</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1145301759243012</c:v>
+                  <c:v>0.1244277134537697</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1077931076288223</c:v>
+                  <c:v>0.1180468052625656</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.08758189529180527</c:v>
+                  <c:v>0.1148563474416733</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.08758189529180527</c:v>
+                  <c:v>0.1084754392504692</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.08084482699632645</c:v>
+                  <c:v>0.1020945310592651</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.08084482699632645</c:v>
+                  <c:v>0.08295180648565292</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.08084482699632645</c:v>
+                  <c:v>0.08295180648565292</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.08084482699632645</c:v>
+                  <c:v>0.07657089829444885</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.07410775870084763</c:v>
+                  <c:v>0.07657089829444885</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07410775870084763</c:v>
+                  <c:v>0.07657089829444885</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.06737069040536881</c:v>
+                  <c:v>0.07657089829444885</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.0640021562576294</c:v>
+                  <c:v>0.07018999010324478</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.06063362210988998</c:v>
+                  <c:v>0.07018999010324478</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.06063362210988998</c:v>
+                  <c:v>0.06380908191204071</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.05726508796215057</c:v>
+                  <c:v>0.06061862781643868</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.04715948179364204</c:v>
+                  <c:v>0.05742817372083664</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.04379094764590263</c:v>
+                  <c:v>0.05742817372083664</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.04042241349816322</c:v>
+                  <c:v>0.0542377196252346</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.0336853452026844</c:v>
+                  <c:v>0.0446663573384285</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.03031681105494499</c:v>
+                  <c:v>0.04147590324282646</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.02694827690720558</c:v>
+                  <c:v>0.03828544914722443</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.02694827690720558</c:v>
+                  <c:v>0.03190454095602036</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.02694827690720558</c:v>
+                  <c:v>0.02871408686041832</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.02357974089682102</c:v>
+                  <c:v>0.02552363276481628</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.02021120674908161</c:v>
+                  <c:v>0.02552363276481628</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.02021120674908161</c:v>
+                  <c:v>0.02552363276481628</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.0168426726013422</c:v>
+                  <c:v>0.02233317866921425</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.0168426726013422</c:v>
+                  <c:v>0.01914272457361221</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.0168426726013422</c:v>
+                  <c:v>0.01914272457361221</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.0168426726013422</c:v>
+                  <c:v>0.01595227047801018</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.0168426726013422</c:v>
+                  <c:v>0.01595227047801018</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01347413845360279</c:v>
+                  <c:v>0.01595227047801018</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01347413845360279</c:v>
+                  <c:v>0.01595227047801018</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01347413845360279</c:v>
+                  <c:v>0.01595227047801018</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01347413845360279</c:v>
+                  <c:v>0.01276181638240814</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.01276181638240814</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.01276181638240814</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.01276181638240814</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.01010560337454081</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.006737069226801395</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.006737069226801395</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.006737069226801395</c:v>
+                  <c:v>0.009571362286806107</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.006380908191204071</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.006380908191204071</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.006380908191204071</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.003190454095602036</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.003190454095602036</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.003190454095602036</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.003368534613400698</c:v>
+                  <c:v>0.003190454095602036</c:v>
                 </c:pt>
                 <c:pt idx="130">
+                  <c:v>0.003190454095602036</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.003190454095602036</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.003190454095602036</c:v>
+                </c:pt>
+                <c:pt idx="133">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1642,8 +1681,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H133" totalsRowCount="1">
-  <autoFilter ref="A2:H132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H136" totalsRowCount="1">
+  <autoFilter ref="A2:H135"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1659,8 +1698,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H133" totalsRowCount="1">
-  <autoFilter ref="A2:H132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H136" totalsRowCount="1">
+  <autoFilter ref="A2:H135"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1960,7 +1999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1973,28 +2012,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2002,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>56.0035514831543</v>
+        <v>55.93858337402344</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2028,7 +2067,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>39.68436431884766</v>
+        <v>39.63832855224609</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -2054,7 +2093,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.176229476928711</v>
+        <v>1.174864888191223</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -2080,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.165981531143189</v>
+        <v>1.164628982543945</v>
       </c>
       <c r="C6" s="1">
         <v>1024</v>
@@ -2106,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.9154776930809021</v>
+        <v>0.914415717124939</v>
       </c>
       <c r="C7" s="1">
         <v>804</v>
@@ -2132,7 +2171,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3165457844734192</v>
+        <v>0.316178560256958</v>
       </c>
       <c r="C8" s="1">
         <v>278</v>
@@ -2158,7 +2197,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1093107759952545</v>
+        <v>0.1091839671134949</v>
       </c>
       <c r="C9" s="1">
         <v>96</v>
@@ -2184,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1093107759952545</v>
+        <v>0.1091839671134949</v>
       </c>
       <c r="C10" s="1">
         <v>96</v>
@@ -2210,7 +2249,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1093107759952545</v>
+        <v>0.1091839671134949</v>
       </c>
       <c r="C11" s="1">
         <v>96</v>
@@ -2236,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1070334613323212</v>
+        <v>0.1069092974066734</v>
       </c>
       <c r="C12" s="1">
         <v>94</v>
@@ -2262,7 +2301,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1047561541199684</v>
+        <v>0.1046346351504326</v>
       </c>
       <c r="C13" s="1">
         <v>92</v>
@@ -2288,25 +2327,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.07287384569644928</v>
+        <v>0.1023599654436112</v>
       </c>
       <c r="C14" s="1">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D14" s="1">
-        <v>1574</v>
+        <v>418</v>
       </c>
       <c r="E14" s="1">
-        <v>1574</v>
+        <v>412</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2314,25 +2353,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06831923127174377</v>
+        <v>0.07278931140899658</v>
       </c>
       <c r="C15" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D15" s="1">
-        <v>1102</v>
+        <v>1574</v>
       </c>
       <c r="E15" s="1">
-        <v>1082</v>
+        <v>1574</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2340,25 +2379,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01366384699940682</v>
+        <v>0.0682399794459343</v>
       </c>
       <c r="C16" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1">
-        <v>1174</v>
+        <v>1102</v>
       </c>
       <c r="E16" s="1">
-        <v>1162</v>
+        <v>1082</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2366,22 +2405,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01024788524955511</v>
+        <v>0.01364799588918686</v>
       </c>
       <c r="C17" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>183</v>
+        <v>1174</v>
       </c>
       <c r="E17" s="1">
-        <v>174</v>
+        <v>1162</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -2392,22 +2431,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.00910923071205616</v>
+        <v>0.01364799588918686</v>
       </c>
       <c r="C18" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -2418,22 +2457,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.00455461535602808</v>
+        <v>0.01023599691689014</v>
       </c>
       <c r="C19" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1">
-        <v>48</v>
+        <v>183</v>
       </c>
       <c r="E19" s="1">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F19" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -2444,22 +2483,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.00455461535602808</v>
+        <v>0.009098663926124573</v>
       </c>
       <c r="C20" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E20" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -2470,19 +2509,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.00455461535602808</v>
+        <v>0.004549331963062286</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="E21" s="1">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
@@ -2496,16 +2535,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.00455461535602808</v>
+        <v>0.004549331963062286</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="1">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="E22" s="1">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2522,16 +2561,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.00455461535602808</v>
+        <v>0.004549331963062286</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2548,56 +2587,108 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.00113865383900702</v>
+        <v>0.004549331963062286</v>
       </c>
       <c r="C24" s="1">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1">
+        <v>176</v>
+      </c>
+      <c r="E24" s="1">
+        <v>172</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.004549331963062286</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="1">
+        <v>108</v>
+      </c>
+      <c r="E25" s="1">
+        <v>104</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.001137332990765572</v>
+      </c>
+      <c r="C26" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D26" s="1">
         <v>2057</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E26" s="1">
         <v>2056</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
         <v>1</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" t="s">
-        <v>132</v>
-      </c>
-      <c r="B133">
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C133">
+      <c r="C136">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D133">
+      <c r="D136">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E133">
+      <c r="E136">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F133">
+      <c r="F136">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G133">
+      <c r="G136">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H133">
+      <c r="H136">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2613,7 +2704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2626,28 +2717,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
         <v>140</v>
       </c>
-      <c r="C2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" t="s">
-        <v>137</v>
-      </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2655,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>22.31991004943848</v>
+        <v>21.13994979858398</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2681,7 +2772,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>13.42866325378418</v>
+        <v>12.71874523162842</v>
       </c>
       <c r="C4" s="1">
         <v>7973</v>
@@ -2707,7 +2798,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>6.726963520050049</v>
+        <v>6.371336936950684</v>
       </c>
       <c r="C5" s="1">
         <v>3994</v>
@@ -2730,19 +2821,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2">
-        <v>4.493625164031982</v>
+        <v>4.466635704040527</v>
       </c>
       <c r="C6" s="1">
-        <v>2668</v>
+        <v>2800</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2668</v>
+        <v>2800</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2756,19 +2847,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2">
-        <v>4.301618576049805</v>
+        <v>4.256065845489502</v>
       </c>
       <c r="C7" s="1">
-        <v>2554</v>
+        <v>2668</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>2554</v>
+        <v>2668</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2782,19 +2873,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2">
-        <v>3.570646524429321</v>
+        <v>4.074210166931152</v>
       </c>
       <c r="C8" s="1">
-        <v>2120</v>
+        <v>2554</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2120</v>
+        <v>2554</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2808,25 +2899,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2">
-        <v>3.464537858963013</v>
+        <v>3.381881475448608</v>
       </c>
       <c r="C9" s="1">
-        <v>2057</v>
+        <v>2120</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>2056</v>
+        <v>2120</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2834,25 +2925,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2">
-        <v>3.260741472244263</v>
+        <v>3.281382083892822</v>
       </c>
       <c r="C10" s="1">
-        <v>1936</v>
+        <v>2057</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>1936</v>
+        <v>2056</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -2860,19 +2951,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2">
-        <v>3.065366506576538</v>
+        <v>3.088359594345093</v>
       </c>
       <c r="C11" s="1">
-        <v>1820</v>
+        <v>1936</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>1820</v>
+        <v>1936</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2886,19 +2977,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2">
-        <v>2.651036739349365</v>
+        <v>2.903313398361206</v>
       </c>
       <c r="C12" s="1">
-        <v>1574</v>
+        <v>1820</v>
       </c>
       <c r="D12" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1574</v>
+        <v>1820</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2907,53 +2998,53 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>2.617351293563843</v>
+        <v>2.510887384414673</v>
       </c>
       <c r="C13" s="1">
-        <v>1554</v>
+        <v>1574</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1">
-        <v>1546</v>
+        <v>1574</v>
       </c>
       <c r="F13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2">
-        <v>2.088491439819336</v>
+        <v>2.478982925415039</v>
       </c>
       <c r="C14" s="1">
-        <v>1240</v>
+        <v>1554</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1240</v>
+        <v>1546</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2964,25 +3055,25 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>1.977329730987549</v>
+        <v>1.978081583976746</v>
       </c>
       <c r="C15" s="1">
-        <v>1174</v>
+        <v>1240</v>
       </c>
       <c r="D15" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1162</v>
+        <v>1240</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -2990,71 +3081,71 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>1.856062531471252</v>
+        <v>1.872796535491943</v>
       </c>
       <c r="C16" s="1">
-        <v>1102</v>
+        <v>1174</v>
       </c>
       <c r="D16" s="1">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1">
-        <v>1082</v>
+        <v>1162</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>1.775217652320862</v>
+        <v>1.757940292358398</v>
       </c>
       <c r="C17" s="1">
-        <v>1054</v>
+        <v>1102</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>1.49562931060791</v>
+        <v>1.681369304656982</v>
       </c>
       <c r="C18" s="1">
-        <v>888</v>
+        <v>1054</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>888</v>
+        <v>1054</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -3068,74 +3159,74 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2">
-        <v>1.482155203819275</v>
+        <v>1.416561603546143</v>
       </c>
       <c r="C19" s="1">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D19" s="1">
-        <v>49184</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>848</v>
+        <v>888</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.403799772262573</v>
+      </c>
+      <c r="C20" s="1">
+        <v>880</v>
+      </c>
+      <c r="D20" s="1">
+        <v>49184</v>
+      </c>
+      <c r="E20" s="1">
+        <v>848</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
         <v>32</v>
       </c>
-      <c r="B20" s="2">
-        <v>1.35078239440918</v>
-      </c>
-      <c r="C20" s="1">
-        <v>802</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>764</v>
-      </c>
-      <c r="F20" s="1">
-        <v>38</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2">
-        <v>1.101510763168335</v>
+        <v>1.279372096061707</v>
       </c>
       <c r="C21" s="1">
-        <v>654</v>
+        <v>802</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>654</v>
+        <v>764</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -3146,204 +3237,204 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9465581774711609</v>
+        <v>1.043278455734253</v>
       </c>
       <c r="C22" s="1">
-        <v>562</v>
+        <v>654</v>
       </c>
       <c r="D22" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>552</v>
+        <v>654</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8892931342124939</v>
+        <v>0.8965176343917847</v>
       </c>
       <c r="C23" s="1">
-        <v>528</v>
+        <v>562</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="E23" s="1">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8572920560836792</v>
+        <v>0.8422799110412598</v>
       </c>
       <c r="C24" s="1">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="D24" s="1">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>1032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="2">
-        <v>0.7882370948791504</v>
+        <v>0.811970591545105</v>
       </c>
       <c r="C25" s="1">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="D25" s="1">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="E25" s="1">
-        <v>76</v>
+        <v>508</v>
       </c>
       <c r="F25" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7006551623344421</v>
+        <v>0.7465662956237793</v>
       </c>
       <c r="C26" s="1">
-        <v>416</v>
+        <v>468</v>
       </c>
       <c r="D26" s="1">
-        <v>92</v>
+        <v>1024</v>
       </c>
       <c r="E26" s="1">
-        <v>416</v>
+        <v>76</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>92</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6888653039932251</v>
+        <v>0.6668049097061157</v>
       </c>
       <c r="C27" s="1">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E27" s="1">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="F27" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6332845091819763</v>
+        <v>0.6636144518852234</v>
       </c>
       <c r="C28" s="1">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E28" s="1">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="F28" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5793879628181458</v>
+        <v>0.6524478793144226</v>
       </c>
       <c r="C29" s="1">
-        <v>344</v>
+        <v>409</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -3354,22 +3445,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5726508498191834</v>
+        <v>0.5998053550720215</v>
       </c>
       <c r="C30" s="1">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>340</v>
+        <v>228</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -3380,22 +3471,22 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5322284698486328</v>
+        <v>0.5487580895423889</v>
       </c>
       <c r="C31" s="1">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>44</v>
+        <v>344</v>
       </c>
       <c r="F31" s="1">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -3406,19 +3497,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4008556008338928</v>
+        <v>0.542377233505249</v>
       </c>
       <c r="C32" s="1">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -3432,22 +3523,22 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2">
-        <v>0.390749990940094</v>
+        <v>0.504091739654541</v>
       </c>
       <c r="C33" s="1">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>232</v>
+        <v>44</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -3458,45 +3549,45 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3772758543491364</v>
+        <v>0.3796640336513519</v>
       </c>
       <c r="C34" s="1">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D34" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="F34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3435905277729034</v>
+        <v>0.3700926899909973</v>
       </c>
       <c r="C35" s="1">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -3510,48 +3601,48 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3368534445762634</v>
+        <v>0.357330858707428</v>
       </c>
       <c r="C36" s="1">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="D36" s="1">
-        <v>96</v>
+        <v>34852</v>
       </c>
       <c r="E36" s="1">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H36" s="1">
-        <v>96</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3301163911819458</v>
+        <v>0.325426310300827</v>
       </c>
       <c r="C37" s="1">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="F37" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -3562,51 +3653,51 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3166422545909882</v>
+        <v>0.3190454244613648</v>
       </c>
       <c r="C38" s="1">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E38" s="1">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="F38" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3082209229469299</v>
+        <v>0.3126645088195801</v>
       </c>
       <c r="C39" s="1">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D39" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="F39" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3614,22 +3705,22 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2997995615005493</v>
+        <v>0.2999026775360107</v>
       </c>
       <c r="C40" s="1">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -3640,25 +3731,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2964310348033905</v>
+        <v>0.2919265627861023</v>
       </c>
       <c r="C41" s="1">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D41" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E41" s="1">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3666,19 +3757,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2627456784248352</v>
+        <v>0.2839504182338715</v>
       </c>
       <c r="C42" s="1">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3692,25 +3783,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2560086250305176</v>
+        <v>0.2807599604129791</v>
       </c>
       <c r="C43" s="1">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E43" s="1">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3718,19 +3809,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2492715567350388</v>
+        <v>0.2488554269075394</v>
       </c>
       <c r="C44" s="1">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3744,19 +3835,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2324288785457611</v>
+        <v>0.2424745112657547</v>
       </c>
       <c r="C45" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3770,19 +3861,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2324288785457611</v>
+        <v>0.2360936105251312</v>
       </c>
       <c r="C46" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3796,19 +3887,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2256918102502823</v>
+        <v>0.2201413363218308</v>
       </c>
       <c r="C47" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3822,19 +3913,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2155862152576447</v>
+        <v>0.2201413363218308</v>
       </c>
       <c r="C48" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3848,19 +3939,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2155862152576447</v>
+        <v>0.2137604355812073</v>
       </c>
       <c r="C49" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3874,19 +3965,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2088491469621658</v>
+        <v>0.2041890621185303</v>
       </c>
       <c r="C50" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3900,19 +3991,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2021120637655258</v>
+        <v>0.2041890621185303</v>
       </c>
       <c r="C51" s="1">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3926,25 +4017,25 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="B52" s="2">
-        <v>0.195374995470047</v>
+        <v>0.1978081613779068</v>
       </c>
       <c r="C52" s="1">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D52" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -3952,19 +4043,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1886379271745682</v>
+        <v>0.1914272457361221</v>
       </c>
       <c r="C53" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3978,25 +4069,25 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1819008588790894</v>
+        <v>0.1850463449954987</v>
       </c>
       <c r="C54" s="1">
+        <v>116</v>
+      </c>
+      <c r="D54" s="1">
+        <v>8</v>
+      </c>
+      <c r="E54" s="1">
         <v>108</v>
       </c>
-      <c r="D54" s="1">
-        <v>4</v>
-      </c>
-      <c r="E54" s="1">
-        <v>104</v>
-      </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -4004,25 +4095,25 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1751637905836105</v>
+        <v>0.178665429353714</v>
       </c>
       <c r="C55" s="1">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D55" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -4030,25 +4121,25 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1684267222881317</v>
+        <v>0.1722845286130905</v>
       </c>
       <c r="C56" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E56" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -4056,19 +4147,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1549525856971741</v>
+        <v>0.1659036129713059</v>
       </c>
       <c r="C57" s="1">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
       </c>
       <c r="E57" s="1">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4082,19 +4173,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1515840590000153</v>
+        <v>0.1595227122306824</v>
       </c>
       <c r="C58" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -4108,25 +4199,25 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1482155174016953</v>
+        <v>0.1531417965888977</v>
       </c>
       <c r="C59" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E59" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -4134,19 +4225,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1482155174016953</v>
+        <v>0.1467608958482742</v>
       </c>
       <c r="C60" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -4160,19 +4251,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1381099224090576</v>
+        <v>0.1435704380273819</v>
       </c>
       <c r="C61" s="1">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4186,19 +4277,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1313728392124176</v>
+        <v>0.1403799802064896</v>
       </c>
       <c r="C62" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -4212,25 +4303,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1313728392124176</v>
+        <v>0.1403799802064896</v>
       </c>
       <c r="C63" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -4241,16 +4332,16 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1246357783675194</v>
+        <v>0.1308086216449738</v>
       </c>
       <c r="C64" s="1">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -4267,19 +4358,19 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.12126724421978</v>
+        <v>0.1244277134537697</v>
       </c>
       <c r="C65" s="1">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="F65" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -4293,16 +4384,16 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1145301759243012</v>
+        <v>0.1244277134537697</v>
       </c>
       <c r="C66" s="1">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -4319,16 +4410,16 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1077931076288223</v>
+        <v>0.1180468052625656</v>
       </c>
       <c r="C67" s="1">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -4345,19 +4436,19 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.08758189529180527</v>
+        <v>0.1148563474416733</v>
       </c>
       <c r="C68" s="1">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F68" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -4371,16 +4462,16 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.08758189529180527</v>
+        <v>0.1084754392504692</v>
       </c>
       <c r="C69" s="1">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -4397,16 +4488,16 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.08084482699632645</v>
+        <v>0.1020945310592651</v>
       </c>
       <c r="C70" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4423,16 +4514,16 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.08084482699632645</v>
+        <v>0.08295180648565292</v>
       </c>
       <c r="C71" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4449,16 +4540,16 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.08084482699632645</v>
+        <v>0.08295180648565292</v>
       </c>
       <c r="C72" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -4472,25 +4563,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>0.08084482699632645</v>
+        <v>0.07657089829444885</v>
       </c>
       <c r="C73" s="1">
         <v>48</v>
       </c>
       <c r="D73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F73" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4498,19 +4589,19 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="2">
-        <v>0.07410775870084763</v>
+        <v>0.07657089829444885</v>
       </c>
       <c r="C74" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4524,19 +4615,19 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07410775870084763</v>
+        <v>0.07657089829444885</v>
       </c>
       <c r="C75" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4550,25 +4641,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B76" s="2">
-        <v>0.06737069040536881</v>
+        <v>0.07657089829444885</v>
       </c>
       <c r="C76" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D76" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E76" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -4579,16 +4670,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.0640021562576294</v>
+        <v>0.07018999010324478</v>
       </c>
       <c r="C77" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4605,16 +4696,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="2">
-        <v>0.06063362210988998</v>
+        <v>0.07018999010324478</v>
       </c>
       <c r="C78" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4631,16 +4722,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="2">
-        <v>0.06063362210988998</v>
+        <v>0.06380908191204071</v>
       </c>
       <c r="C79" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4657,16 +4748,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="2">
-        <v>0.05726508796215057</v>
+        <v>0.06061862781643868</v>
       </c>
       <c r="C80" s="1">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4683,16 +4774,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="2">
-        <v>0.04715948179364204</v>
+        <v>0.05742817372083664</v>
       </c>
       <c r="C81" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4709,16 +4800,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>0.04379094764590263</v>
+        <v>0.05742817372083664</v>
       </c>
       <c r="C82" s="1">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4735,16 +4826,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="2">
-        <v>0.04042241349816322</v>
+        <v>0.0542377196252346</v>
       </c>
       <c r="C83" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4761,16 +4852,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="2">
-        <v>0.0336853452026844</v>
+        <v>0.0446663573384285</v>
       </c>
       <c r="C84" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4787,16 +4878,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>0.03031681105494499</v>
+        <v>0.04147590324282646</v>
       </c>
       <c r="C85" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -4813,16 +4904,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.02694827690720558</v>
+        <v>0.03828544914722443</v>
       </c>
       <c r="C86" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4839,16 +4930,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.02694827690720558</v>
+        <v>0.03190454095602036</v>
       </c>
       <c r="C87" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -4865,16 +4956,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.02694827690720558</v>
+        <v>0.02871408686041832</v>
       </c>
       <c r="C88" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -4891,16 +4982,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.02357974089682102</v>
+        <v>0.02552363276481628</v>
       </c>
       <c r="C89" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -4917,16 +5008,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.02021120674908161</v>
+        <v>0.02552363276481628</v>
       </c>
       <c r="C90" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -4943,16 +5034,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.02021120674908161</v>
+        <v>0.02552363276481628</v>
       </c>
       <c r="C91" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -4969,16 +5060,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.0168426726013422</v>
+        <v>0.02233317866921425</v>
       </c>
       <c r="C92" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -4995,16 +5086,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.0168426726013422</v>
+        <v>0.01914272457361221</v>
       </c>
       <c r="C93" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5021,16 +5112,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.0168426726013422</v>
+        <v>0.01914272457361221</v>
       </c>
       <c r="C94" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -5047,7 +5138,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.0168426726013422</v>
+        <v>0.01595227047801018</v>
       </c>
       <c r="C95" s="1">
         <v>10</v>
@@ -5073,7 +5164,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.0168426726013422</v>
+        <v>0.01595227047801018</v>
       </c>
       <c r="C96" s="1">
         <v>10</v>
@@ -5099,16 +5190,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01347413845360279</v>
+        <v>0.01595227047801018</v>
       </c>
       <c r="C97" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5122,19 +5213,19 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01347413845360279</v>
+        <v>0.01595227047801018</v>
       </c>
       <c r="C98" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D98" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5143,24 +5234,24 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01347413845360279</v>
+        <v>0.01595227047801018</v>
       </c>
       <c r="C99" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5174,10 +5265,10 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01347413845360279</v>
+        <v>0.01276181638240814</v>
       </c>
       <c r="C100" s="1">
         <v>8</v>
@@ -5200,19 +5291,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.01276181638240814</v>
       </c>
       <c r="C101" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D101" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E101" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -5221,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -5229,16 +5320,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.01276181638240814</v>
       </c>
       <c r="C102" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5255,16 +5346,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.01276181638240814</v>
       </c>
       <c r="C103" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5281,7 +5372,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C104" s="1">
         <v>6</v>
@@ -5307,7 +5398,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C105" s="1">
         <v>6</v>
@@ -5333,7 +5424,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C106" s="1">
         <v>6</v>
@@ -5359,7 +5450,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C107" s="1">
         <v>6</v>
@@ -5385,7 +5476,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C108" s="1">
         <v>6</v>
@@ -5411,7 +5502,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C109" s="1">
         <v>6</v>
@@ -5437,7 +5528,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C110" s="1">
         <v>6</v>
@@ -5463,7 +5554,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C111" s="1">
         <v>6</v>
@@ -5489,7 +5580,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C112" s="1">
         <v>6</v>
@@ -5515,7 +5606,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C113" s="1">
         <v>6</v>
@@ -5541,7 +5632,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C114" s="1">
         <v>6</v>
@@ -5567,7 +5658,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C115" s="1">
         <v>6</v>
@@ -5593,7 +5684,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5619,7 +5710,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5645,7 +5736,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5671,7 +5762,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5697,7 +5788,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5723,7 +5814,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5749,7 +5840,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.01010560337454081</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5775,16 +5866,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.006737069226801395</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C123" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -5801,16 +5892,16 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.006737069226801395</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C124" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -5827,16 +5918,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.006737069226801395</v>
+        <v>0.009571362286806107</v>
       </c>
       <c r="C125" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
       </c>
       <c r="E125" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -5853,16 +5944,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.006380908191204071</v>
       </c>
       <c r="C126" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -5879,16 +5970,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.006380908191204071</v>
       </c>
       <c r="C127" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -5905,16 +5996,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.006380908191204071</v>
       </c>
       <c r="C128" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -5931,7 +6022,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.003190454095602036</v>
       </c>
       <c r="C129" s="1">
         <v>2</v>
@@ -5957,7 +6048,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.003190454095602036</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -5983,7 +6074,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.003190454095602036</v>
       </c>
       <c r="C131" s="1">
         <v>2</v>
@@ -6009,7 +6100,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.003368534613400698</v>
+        <v>0.003190454095602036</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -6031,34 +6122,112 @@
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" t="s">
+      <c r="A133" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0.003190454095602036</v>
+      </c>
+      <c r="C133" s="1">
+        <v>2</v>
+      </c>
+      <c r="D133" s="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1">
+        <v>2</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B133">
+      <c r="B134" s="2">
+        <v>0.003190454095602036</v>
+      </c>
+      <c r="C134" s="1">
+        <v>2</v>
+      </c>
+      <c r="D134" s="1">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1">
+        <v>2</v>
+      </c>
+      <c r="F134" s="1">
+        <v>0</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2">
+        <v>0.003190454095602036</v>
+      </c>
+      <c r="C135" s="1">
+        <v>2</v>
+      </c>
+      <c r="D135" s="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1">
+        <v>2</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C133">
+      <c r="C136">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D133">
+      <c r="D136">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E133">
+      <c r="E136">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F133">
+      <c r="F136">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G133">
+      <c r="G136">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H133">
+      <c r="H136">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -62,10 +62,10 @@
     <t>timers.o</t>
   </si>
   <si>
+    <t>dht11_task.o</t>
+  </si>
+  <si>
     <t>port.o</t>
-  </si>
-  <si>
-    <t>dht11_task.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal.o</t>
@@ -582,10 +582,10 @@
                   <c:v>timers.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>dht11_task.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>dht11_task.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>stm32f4xx_hal.o</c:v>
@@ -624,76 +624,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="134"/>
                 <c:pt idx="0">
-                  <c:v>55.93858337402344</c:v>
+                  <c:v>55.93095016479492</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.63832855224609</c:v>
+                  <c:v>39.63291931152344</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.174864888191223</c:v>
+                  <c:v>1.174704670906067</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.164628982543945</c:v>
+                  <c:v>1.164470076560974</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.914415717124939</c:v>
+                  <c:v>0.9142909049987793</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.316178560256958</c:v>
+                  <c:v>0.3161354064941406</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1091839671134949</c:v>
+                  <c:v>0.109169065952301</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1091839671134949</c:v>
+                  <c:v>0.109169065952301</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1091839671134949</c:v>
+                  <c:v>0.109169065952301</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1069092974066734</c:v>
+                  <c:v>0.1068947091698647</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1046346351504326</c:v>
+                  <c:v>0.1046203523874283</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1023599654436112</c:v>
+                  <c:v>0.1023459956049919</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.07278931140899658</c:v>
+                  <c:v>0.07277937978506088</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0682399794459343</c:v>
+                  <c:v>0.06823066622018814</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01364799588918686</c:v>
+                  <c:v>0.02729226648807526</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01364799588918686</c:v>
+                  <c:v>0.01364613324403763</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01023599691689014</c:v>
+                  <c:v>0.01023459993302822</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.009098663926124573</c:v>
+                  <c:v>0.00909742247313261</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004549331963062286</c:v>
+                  <c:v>0.004548711236566305</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004549331963062286</c:v>
+                  <c:v>0.004548711236566305</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.004549331963062286</c:v>
+                  <c:v>0.004548711236566305</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.004549331963062286</c:v>
+                  <c:v>0.004548711236566305</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.004549331963062286</c:v>
+                  <c:v>0.004548711236566305</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.001137332990765572</c:v>
+                  <c:v>0.001137177809141576</c:v>
                 </c:pt>
                 <c:pt idx="133">
                   <c:v>0</c:v>
@@ -905,49 +905,49 @@
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
                 <c:pt idx="46">
+                  <c:v>dht11_task.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>strcmpv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>_printf_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>_printf_oct_int_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>dfixu.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>stm32f4xx_hal_sram.o</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>dht11_task.o</c:v>
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>_printf_str.o</c:v>
@@ -1178,403 +1178,403 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="134"/>
                 <c:pt idx="0">
-                  <c:v>21.13994979858398</c:v>
+                  <c:v>21.11569595336914</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.71874523162842</c:v>
+                  <c:v>12.7041540145874</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.371336936950684</c:v>
+                  <c:v>6.364027500152588</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.466635704040527</c:v>
+                  <c:v>4.461511611938477</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.256065845489502</c:v>
+                  <c:v>4.251183032989502</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.074210166931152</c:v>
+                  <c:v>4.069535732269287</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.381881475448608</c:v>
+                  <c:v>3.37800145149231</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.281382083892822</c:v>
+                  <c:v>3.277617454528809</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.088359594345093</c:v>
+                  <c:v>3.084816455841065</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.903313398361206</c:v>
+                  <c:v>2.899982452392578</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.510887384414673</c:v>
+                  <c:v>2.508006811141968</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.478982925415039</c:v>
+                  <c:v>2.476138830184937</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.978081583976746</c:v>
+                  <c:v>1.975812196731567</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.872796535491943</c:v>
+                  <c:v>1.87064802646637</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.757940292358398</c:v>
+                  <c:v>1.755923509597778</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.681369304656982</c:v>
+                  <c:v>1.679440379142761</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.416561603546143</c:v>
+                  <c:v>1.414936542510986</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.403799772262573</c:v>
+                  <c:v>1.402189373970032</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.279372096061707</c:v>
+                  <c:v>1.277904391288757</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.043278455734253</c:v>
+                  <c:v>1.042081594467163</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8965176343917847</c:v>
+                  <c:v>0.8954890966415405</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8422799110412598</c:v>
+                  <c:v>0.8413136005401611</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.811970591545105</c:v>
+                  <c:v>0.8110390305519104</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7465662956237793</c:v>
+                  <c:v>0.7457097768783569</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6668049097061157</c:v>
+                  <c:v>0.7042814493179321</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6636144518852234</c:v>
+                  <c:v>0.6628531217575073</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6524478793144226</c:v>
+                  <c:v>0.6516993641853333</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5998053550720215</c:v>
+                  <c:v>0.5991172790527344</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5487580895423889</c:v>
+                  <c:v>0.5481285452842712</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.542377233505249</c:v>
+                  <c:v>0.541754961013794</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.504091739654541</c:v>
+                  <c:v>0.5035134553909302</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3796640336513519</c:v>
+                  <c:v>0.3792284727096558</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3700926899909973</c:v>
+                  <c:v>0.3696680963039398</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.357330858707428</c:v>
+                  <c:v>0.3569209277629852</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.325426310300827</c:v>
+                  <c:v>0.3250529766082764</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3190454244613648</c:v>
+                  <c:v>0.3186793923377991</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3126645088195801</c:v>
+                  <c:v>0.3123058080673218</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2999026775360107</c:v>
+                  <c:v>0.2995586395263672</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2919265627861023</c:v>
+                  <c:v>0.2915916442871094</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2839504182338715</c:v>
+                  <c:v>0.2836246490478516</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2807599604129791</c:v>
+                  <c:v>0.2804378569126129</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2488554269075394</c:v>
+                  <c:v>0.2485699206590653</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2424745112657547</c:v>
+                  <c:v>0.242196336388588</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2360936105251312</c:v>
+                  <c:v>0.2358227521181107</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2201413363218308</c:v>
+                  <c:v>0.2198887765407562</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2201413363218308</c:v>
+                  <c:v>0.2198887765407562</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2137604355812073</c:v>
+                  <c:v>0.2167019844055176</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2041890621185303</c:v>
+                  <c:v>0.2135151922702789</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2041890621185303</c:v>
+                  <c:v>0.203954815864563</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1978081613779068</c:v>
+                  <c:v>0.203954815864563</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1914272457361221</c:v>
+                  <c:v>0.1975812166929245</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1850463449954987</c:v>
+                  <c:v>0.1912076324224472</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.178665429353714</c:v>
+                  <c:v>0.1848340481519699</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1722845286130905</c:v>
+                  <c:v>0.1784604638814926</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1659036129713059</c:v>
+                  <c:v>0.1720868647098541</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1595227122306824</c:v>
+                  <c:v>0.1657132804393768</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1531417965888977</c:v>
+                  <c:v>0.1593396961688995</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1467608958482742</c:v>
+                  <c:v>0.1529661118984222</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1435704380273819</c:v>
+                  <c:v>0.146592527627945</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1403799802064896</c:v>
+                  <c:v>0.1434057205915451</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1403799802064896</c:v>
+                  <c:v>0.1402189284563065</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1308086216449738</c:v>
+                  <c:v>0.1306585520505905</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1244277134537697</c:v>
+                  <c:v>0.1242849603295326</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1244277134537697</c:v>
+                  <c:v>0.1242849603295326</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1180468052625656</c:v>
+                  <c:v>0.1179113760590553</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.1148563474416733</c:v>
+                  <c:v>0.1147245839238167</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.1084754392504692</c:v>
+                  <c:v>0.1083509922027588</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.1020945310592651</c:v>
+                  <c:v>0.1019774079322815</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.08295180648565292</c:v>
+                  <c:v>0.08285664021968842</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.08295180648565292</c:v>
+                  <c:v>0.08285664021968842</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.07657089829444885</c:v>
+                  <c:v>0.07648305594921112</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.07657089829444885</c:v>
+                  <c:v>0.07648305594921112</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07657089829444885</c:v>
+                  <c:v>0.07648305594921112</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.07657089829444885</c:v>
+                  <c:v>0.07648305594921112</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.07018999010324478</c:v>
+                  <c:v>0.07010946422815323</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.07018999010324478</c:v>
+                  <c:v>0.07010946422815323</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.06380908191204071</c:v>
+                  <c:v>0.06373587995767593</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.06061862781643868</c:v>
+                  <c:v>0.06054908409714699</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.05742817372083664</c:v>
+                  <c:v>0.05736229196190834</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.05742817372083664</c:v>
+                  <c:v>0.05736229196190834</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.0542377196252346</c:v>
+                  <c:v>0.0541754961013794</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.0446663573384285</c:v>
+                  <c:v>0.04461511597037315</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.04147590324282646</c:v>
+                  <c:v>0.04142832010984421</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.03828544914722443</c:v>
+                  <c:v>0.03824152797460556</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.03190454095602036</c:v>
+                  <c:v>0.03186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.02871408686041832</c:v>
+                  <c:v>0.02868114598095417</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.02552363276481628</c:v>
+                  <c:v>0.02549435198307037</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.02552363276481628</c:v>
+                  <c:v>0.02549435198307037</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.02552363276481628</c:v>
+                  <c:v>0.02549435198307037</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.02233317866921425</c:v>
+                  <c:v>0.02230755798518658</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.01914272457361221</c:v>
+                  <c:v>0.01912076398730278</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.01914272457361221</c:v>
+                  <c:v>0.01912076398730278</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.01595227047801018</c:v>
+                  <c:v>0.01593396998941898</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01595227047801018</c:v>
+                  <c:v>0.01593396998941898</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01595227047801018</c:v>
+                  <c:v>0.01593396998941898</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01595227047801018</c:v>
+                  <c:v>0.01593396998941898</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01595227047801018</c:v>
+                  <c:v>0.01593396998941898</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01276181638240814</c:v>
+                  <c:v>0.01274717599153519</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01276181638240814</c:v>
+                  <c:v>0.01274717599153519</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01276181638240814</c:v>
+                  <c:v>0.01274717599153519</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01276181638240814</c:v>
+                  <c:v>0.01274717599153519</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.009571362286806107</c:v>
+                  <c:v>0.00956038199365139</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.006380908191204071</c:v>
+                  <c:v>0.006373587995767593</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.006380908191204071</c:v>
+                  <c:v>0.006373587995767593</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.006380908191204071</c:v>
+                  <c:v>0.006373587995767593</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.003190454095602036</c:v>
+                  <c:v>0.003186793997883797</c:v>
                 </c:pt>
                 <c:pt idx="133">
                   <c:v>0</c:v>
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>55.93858337402344</v>
+        <v>55.93095016479492</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2067,7 +2067,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>39.63832855224609</v>
+        <v>39.63291931152344</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -2093,7 +2093,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.174864888191223</v>
+        <v>1.174704670906067</v>
       </c>
       <c r="C5" s="1">
         <v>1033</v>
@@ -2119,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.164628982543945</v>
+        <v>1.164470076560974</v>
       </c>
       <c r="C6" s="1">
         <v>1024</v>
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.914415717124939</v>
+        <v>0.9142909049987793</v>
       </c>
       <c r="C7" s="1">
         <v>804</v>
@@ -2171,7 +2171,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.316178560256958</v>
+        <v>0.3161354064941406</v>
       </c>
       <c r="C8" s="1">
         <v>278</v>
@@ -2197,7 +2197,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1091839671134949</v>
+        <v>0.109169065952301</v>
       </c>
       <c r="C9" s="1">
         <v>96</v>
@@ -2223,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1091839671134949</v>
+        <v>0.109169065952301</v>
       </c>
       <c r="C10" s="1">
         <v>96</v>
@@ -2249,7 +2249,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1091839671134949</v>
+        <v>0.109169065952301</v>
       </c>
       <c r="C11" s="1">
         <v>96</v>
@@ -2275,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1069092974066734</v>
+        <v>0.1068947091698647</v>
       </c>
       <c r="C12" s="1">
         <v>94</v>
@@ -2301,7 +2301,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1046346351504326</v>
+        <v>0.1046203523874283</v>
       </c>
       <c r="C13" s="1">
         <v>92</v>
@@ -2327,16 +2327,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1023599654436112</v>
+        <v>0.1023459956049919</v>
       </c>
       <c r="C14" s="1">
         <v>90</v>
       </c>
       <c r="D14" s="1">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="E14" s="1">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.07278931140899658</v>
+        <v>0.07277937978506088</v>
       </c>
       <c r="C15" s="1">
         <v>64</v>
@@ -2379,7 +2379,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0682399794459343</v>
+        <v>0.06823066622018814</v>
       </c>
       <c r="C16" s="1">
         <v>60</v>
@@ -2405,25 +2405,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01364799588918686</v>
+        <v>0.02729226648807526</v>
       </c>
       <c r="C17" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1">
-        <v>1174</v>
+        <v>136</v>
       </c>
       <c r="E17" s="1">
-        <v>1162</v>
+        <v>128</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2431,16 +2431,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01364799588918686</v>
+        <v>0.01364613324403763</v>
       </c>
       <c r="C18" s="1">
         <v>12</v>
       </c>
       <c r="D18" s="1">
-        <v>88</v>
+        <v>1174</v>
       </c>
       <c r="E18" s="1">
-        <v>76</v>
+        <v>1162</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.01023599691689014</v>
+        <v>0.01023459993302822</v>
       </c>
       <c r="C19" s="1">
         <v>9</v>
@@ -2483,7 +2483,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.009098663926124573</v>
+        <v>0.00909742247313261</v>
       </c>
       <c r="C20" s="1">
         <v>8</v>
@@ -2509,7 +2509,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004549331963062286</v>
+        <v>0.004548711236566305</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -2535,7 +2535,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004549331963062286</v>
+        <v>0.004548711236566305</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
@@ -2561,7 +2561,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.004549331963062286</v>
+        <v>0.004548711236566305</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
@@ -2587,7 +2587,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.004549331963062286</v>
+        <v>0.004548711236566305</v>
       </c>
       <c r="C24" s="1">
         <v>4</v>
@@ -2613,7 +2613,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.004549331963062286</v>
+        <v>0.004548711236566305</v>
       </c>
       <c r="C25" s="1">
         <v>4</v>
@@ -2639,7 +2639,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.001137332990765572</v>
+        <v>0.001137177809141576</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>21.13994979858398</v>
+        <v>21.11569595336914</v>
       </c>
       <c r="C3" s="1">
         <v>13252</v>
@@ -2772,7 +2772,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>12.71874523162842</v>
+        <v>12.7041540145874</v>
       </c>
       <c r="C4" s="1">
         <v>7973</v>
@@ -2798,7 +2798,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>6.371336936950684</v>
+        <v>6.364027500152588</v>
       </c>
       <c r="C5" s="1">
         <v>3994</v>
@@ -2824,7 +2824,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2">
-        <v>4.466635704040527</v>
+        <v>4.461511611938477</v>
       </c>
       <c r="C6" s="1">
         <v>2800</v>
@@ -2850,7 +2850,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="2">
-        <v>4.256065845489502</v>
+        <v>4.251183032989502</v>
       </c>
       <c r="C7" s="1">
         <v>2668</v>
@@ -2876,7 +2876,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="2">
-        <v>4.074210166931152</v>
+        <v>4.069535732269287</v>
       </c>
       <c r="C8" s="1">
         <v>2554</v>
@@ -2902,7 +2902,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="2">
-        <v>3.381881475448608</v>
+        <v>3.37800145149231</v>
       </c>
       <c r="C9" s="1">
         <v>2120</v>
@@ -2928,7 +2928,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="2">
-        <v>3.281382083892822</v>
+        <v>3.277617454528809</v>
       </c>
       <c r="C10" s="1">
         <v>2057</v>
@@ -2954,7 +2954,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="2">
-        <v>3.088359594345093</v>
+        <v>3.084816455841065</v>
       </c>
       <c r="C11" s="1">
         <v>1936</v>
@@ -2980,7 +2980,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="2">
-        <v>2.903313398361206</v>
+        <v>2.899982452392578</v>
       </c>
       <c r="C12" s="1">
         <v>1820</v>
@@ -3006,7 +3006,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>2.510887384414673</v>
+        <v>2.508006811141968</v>
       </c>
       <c r="C13" s="1">
         <v>1574</v>
@@ -3032,7 +3032,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="2">
-        <v>2.478982925415039</v>
+        <v>2.476138830184937</v>
       </c>
       <c r="C14" s="1">
         <v>1554</v>
@@ -3058,7 +3058,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>1.978081583976746</v>
+        <v>1.975812196731567</v>
       </c>
       <c r="C15" s="1">
         <v>1240</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>1.872796535491943</v>
+        <v>1.87064802646637</v>
       </c>
       <c r="C16" s="1">
         <v>1174</v>
@@ -3110,7 +3110,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>1.757940292358398</v>
+        <v>1.755923509597778</v>
       </c>
       <c r="C17" s="1">
         <v>1102</v>
@@ -3136,7 +3136,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>1.681369304656982</v>
+        <v>1.679440379142761</v>
       </c>
       <c r="C18" s="1">
         <v>1054</v>
@@ -3162,7 +3162,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2">
-        <v>1.416561603546143</v>
+        <v>1.414936542510986</v>
       </c>
       <c r="C19" s="1">
         <v>888</v>
@@ -3188,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>1.403799772262573</v>
+        <v>1.402189373970032</v>
       </c>
       <c r="C20" s="1">
         <v>880</v>
@@ -3214,7 +3214,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="2">
-        <v>1.279372096061707</v>
+        <v>1.277904391288757</v>
       </c>
       <c r="C21" s="1">
         <v>802</v>
@@ -3240,7 +3240,7 @@
         <v>36</v>
       </c>
       <c r="B22" s="2">
-        <v>1.043278455734253</v>
+        <v>1.042081594467163</v>
       </c>
       <c r="C22" s="1">
         <v>654</v>
@@ -3266,7 +3266,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8965176343917847</v>
+        <v>0.8954890966415405</v>
       </c>
       <c r="C23" s="1">
         <v>562</v>
@@ -3292,7 +3292,7 @@
         <v>37</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8422799110412598</v>
+        <v>0.8413136005401611</v>
       </c>
       <c r="C24" s="1">
         <v>528</v>
@@ -3318,7 +3318,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2">
-        <v>0.811970591545105</v>
+        <v>0.8110390305519104</v>
       </c>
       <c r="C25" s="1">
         <v>509</v>
@@ -3344,7 +3344,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7465662956237793</v>
+        <v>0.7457097768783569</v>
       </c>
       <c r="C26" s="1">
         <v>468</v>
@@ -3370,16 +3370,16 @@
         <v>12</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6668049097061157</v>
+        <v>0.7042814493179321</v>
       </c>
       <c r="C27" s="1">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="D27" s="1">
         <v>90</v>
       </c>
       <c r="E27" s="1">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6636144518852234</v>
+        <v>0.6628531217575073</v>
       </c>
       <c r="C28" s="1">
         <v>416</v>
@@ -3422,7 +3422,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6524478793144226</v>
+        <v>0.6516993641853333</v>
       </c>
       <c r="C29" s="1">
         <v>409</v>
@@ -3448,7 +3448,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5998053550720215</v>
+        <v>0.5991172790527344</v>
       </c>
       <c r="C30" s="1">
         <v>376</v>
@@ -3474,7 +3474,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5487580895423889</v>
+        <v>0.5481285452842712</v>
       </c>
       <c r="C31" s="1">
         <v>344</v>
@@ -3500,7 +3500,7 @@
         <v>41</v>
       </c>
       <c r="B32" s="2">
-        <v>0.542377233505249</v>
+        <v>0.541754961013794</v>
       </c>
       <c r="C32" s="1">
         <v>340</v>
@@ -3526,7 +3526,7 @@
         <v>42</v>
       </c>
       <c r="B33" s="2">
-        <v>0.504091739654541</v>
+        <v>0.5035134553909302</v>
       </c>
       <c r="C33" s="1">
         <v>316</v>
@@ -3552,7 +3552,7 @@
         <v>43</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3796640336513519</v>
+        <v>0.3792284727096558</v>
       </c>
       <c r="C34" s="1">
         <v>238</v>
@@ -3578,7 +3578,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3700926899909973</v>
+        <v>0.3696680963039398</v>
       </c>
       <c r="C35" s="1">
         <v>232</v>
@@ -3604,7 +3604,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="2">
-        <v>0.357330858707428</v>
+        <v>0.3569209277629852</v>
       </c>
       <c r="C36" s="1">
         <v>224</v>
@@ -3630,7 +3630,7 @@
         <v>45</v>
       </c>
       <c r="B37" s="2">
-        <v>0.325426310300827</v>
+        <v>0.3250529766082764</v>
       </c>
       <c r="C37" s="1">
         <v>204</v>
@@ -3656,7 +3656,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3190454244613648</v>
+        <v>0.3186793923377991</v>
       </c>
       <c r="C38" s="1">
         <v>200</v>
@@ -3682,7 +3682,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3126645088195801</v>
+        <v>0.3123058080673218</v>
       </c>
       <c r="C39" s="1">
         <v>196</v>
@@ -3708,7 +3708,7 @@
         <v>47</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2999026775360107</v>
+        <v>0.2995586395263672</v>
       </c>
       <c r="C40" s="1">
         <v>188</v>
@@ -3734,7 +3734,7 @@
         <v>17</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2919265627861023</v>
+        <v>0.2915916442871094</v>
       </c>
       <c r="C41" s="1">
         <v>183</v>
@@ -3760,7 +3760,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2839504182338715</v>
+        <v>0.2836246490478516</v>
       </c>
       <c r="C42" s="1">
         <v>178</v>
@@ -3786,7 +3786,7 @@
         <v>22</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2807599604129791</v>
+        <v>0.2804378569126129</v>
       </c>
       <c r="C43" s="1">
         <v>176</v>
@@ -3812,7 +3812,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2488554269075394</v>
+        <v>0.2485699206590653</v>
       </c>
       <c r="C44" s="1">
         <v>156</v>
@@ -3838,7 +3838,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2424745112657547</v>
+        <v>0.242196336388588</v>
       </c>
       <c r="C45" s="1">
         <v>152</v>
@@ -3864,7 +3864,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2360936105251312</v>
+        <v>0.2358227521181107</v>
       </c>
       <c r="C46" s="1">
         <v>148</v>
@@ -3890,7 +3890,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2201413363218308</v>
+        <v>0.2198887765407562</v>
       </c>
       <c r="C47" s="1">
         <v>138</v>
@@ -3916,7 +3916,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2201413363218308</v>
+        <v>0.2198887765407562</v>
       </c>
       <c r="C48" s="1">
         <v>138</v>
@@ -3939,45 +3939,45 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2137604355812073</v>
+        <v>0.2167019844055176</v>
       </c>
       <c r="C49" s="1">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E49" s="1">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2041890621185303</v>
+        <v>0.2135151922702789</v>
       </c>
       <c r="C50" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3991,10 +3991,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2041890621185303</v>
+        <v>0.203954815864563</v>
       </c>
       <c r="C51" s="1">
         <v>128</v>
@@ -4017,19 +4017,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1978081613779068</v>
+        <v>0.203954815864563</v>
       </c>
       <c r="C52" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -4043,19 +4043,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1914272457361221</v>
+        <v>0.1975812166929245</v>
       </c>
       <c r="C53" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -4069,25 +4069,25 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1850463449954987</v>
+        <v>0.1912076324224472</v>
       </c>
       <c r="C54" s="1">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D54" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -4095,25 +4095,25 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="B55" s="2">
-        <v>0.178665429353714</v>
+        <v>0.1848340481519699</v>
       </c>
       <c r="C55" s="1">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E55" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -4121,25 +4121,25 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1722845286130905</v>
+        <v>0.1784604638814926</v>
       </c>
       <c r="C56" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -4147,19 +4147,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1659036129713059</v>
+        <v>0.1720868647098541</v>
       </c>
       <c r="C57" s="1">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
       </c>
       <c r="E57" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4173,16 +4173,16 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1595227122306824</v>
+        <v>0.1657132804393768</v>
       </c>
       <c r="C58" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E58" s="1">
         <v>100</v>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -4199,25 +4199,25 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1531417965888977</v>
+        <v>0.1593396961688995</v>
       </c>
       <c r="C59" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -4225,16 +4225,16 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1467608958482742</v>
+        <v>0.1529661118984222</v>
       </c>
       <c r="C60" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E60" s="1">
         <v>92</v>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -4251,19 +4251,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1435704380273819</v>
+        <v>0.146592527627945</v>
       </c>
       <c r="C61" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4277,19 +4277,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1403799802064896</v>
+        <v>0.1434057205915451</v>
       </c>
       <c r="C62" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -4303,25 +4303,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1403799802064896</v>
+        <v>0.1402189284563065</v>
       </c>
       <c r="C63" s="1">
         <v>88</v>
       </c>
       <c r="D63" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1308086216449738</v>
+        <v>0.1306585520505905</v>
       </c>
       <c r="C64" s="1">
         <v>82</v>
@@ -4358,7 +4358,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1244277134537697</v>
+        <v>0.1242849603295326</v>
       </c>
       <c r="C65" s="1">
         <v>78</v>
@@ -4384,7 +4384,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1244277134537697</v>
+        <v>0.1242849603295326</v>
       </c>
       <c r="C66" s="1">
         <v>78</v>
@@ -4410,7 +4410,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1180468052625656</v>
+        <v>0.1179113760590553</v>
       </c>
       <c r="C67" s="1">
         <v>74</v>
@@ -4436,7 +4436,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.1148563474416733</v>
+        <v>0.1147245839238167</v>
       </c>
       <c r="C68" s="1">
         <v>72</v>
@@ -4462,7 +4462,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.1084754392504692</v>
+        <v>0.1083509922027588</v>
       </c>
       <c r="C69" s="1">
         <v>68</v>
@@ -4488,7 +4488,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.1020945310592651</v>
+        <v>0.1019774079322815</v>
       </c>
       <c r="C70" s="1">
         <v>64</v>
@@ -4514,7 +4514,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.08295180648565292</v>
+        <v>0.08285664021968842</v>
       </c>
       <c r="C71" s="1">
         <v>52</v>
@@ -4540,7 +4540,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.08295180648565292</v>
+        <v>0.08285664021968842</v>
       </c>
       <c r="C72" s="1">
         <v>52</v>
@@ -4566,7 +4566,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>0.07657089829444885</v>
+        <v>0.07648305594921112</v>
       </c>
       <c r="C73" s="1">
         <v>48</v>
@@ -4592,7 +4592,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="2">
-        <v>0.07657089829444885</v>
+        <v>0.07648305594921112</v>
       </c>
       <c r="C74" s="1">
         <v>48</v>
@@ -4618,7 +4618,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07657089829444885</v>
+        <v>0.07648305594921112</v>
       </c>
       <c r="C75" s="1">
         <v>48</v>
@@ -4644,7 +4644,7 @@
         <v>19</v>
       </c>
       <c r="B76" s="2">
-        <v>0.07657089829444885</v>
+        <v>0.07648305594921112</v>
       </c>
       <c r="C76" s="1">
         <v>48</v>
@@ -4670,7 +4670,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.07018999010324478</v>
+        <v>0.07010946422815323</v>
       </c>
       <c r="C77" s="1">
         <v>44</v>
@@ -4696,7 +4696,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2">
-        <v>0.07018999010324478</v>
+        <v>0.07010946422815323</v>
       </c>
       <c r="C78" s="1">
         <v>44</v>
@@ -4722,7 +4722,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2">
-        <v>0.06380908191204071</v>
+        <v>0.06373587995767593</v>
       </c>
       <c r="C79" s="1">
         <v>40</v>
@@ -4748,7 +4748,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2">
-        <v>0.06061862781643868</v>
+        <v>0.06054908409714699</v>
       </c>
       <c r="C80" s="1">
         <v>38</v>
@@ -4774,7 +4774,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2">
-        <v>0.05742817372083664</v>
+        <v>0.05736229196190834</v>
       </c>
       <c r="C81" s="1">
         <v>36</v>
@@ -4800,7 +4800,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>0.05742817372083664</v>
+        <v>0.05736229196190834</v>
       </c>
       <c r="C82" s="1">
         <v>36</v>
@@ -4826,7 +4826,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2">
-        <v>0.0542377196252346</v>
+        <v>0.0541754961013794</v>
       </c>
       <c r="C83" s="1">
         <v>34</v>
@@ -4852,7 +4852,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2">
-        <v>0.0446663573384285</v>
+        <v>0.04461511597037315</v>
       </c>
       <c r="C84" s="1">
         <v>28</v>
@@ -4878,7 +4878,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>0.04147590324282646</v>
+        <v>0.04142832010984421</v>
       </c>
       <c r="C85" s="1">
         <v>26</v>
@@ -4904,7 +4904,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.03828544914722443</v>
+        <v>0.03824152797460556</v>
       </c>
       <c r="C86" s="1">
         <v>24</v>
@@ -4930,7 +4930,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.03190454095602036</v>
+        <v>0.03186793997883797</v>
       </c>
       <c r="C87" s="1">
         <v>20</v>
@@ -4956,7 +4956,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.02871408686041832</v>
+        <v>0.02868114598095417</v>
       </c>
       <c r="C88" s="1">
         <v>18</v>
@@ -4982,7 +4982,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.02552363276481628</v>
+        <v>0.02549435198307037</v>
       </c>
       <c r="C89" s="1">
         <v>16</v>
@@ -5008,7 +5008,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.02552363276481628</v>
+        <v>0.02549435198307037</v>
       </c>
       <c r="C90" s="1">
         <v>16</v>
@@ -5034,7 +5034,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.02552363276481628</v>
+        <v>0.02549435198307037</v>
       </c>
       <c r="C91" s="1">
         <v>16</v>
@@ -5060,7 +5060,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.02233317866921425</v>
+        <v>0.02230755798518658</v>
       </c>
       <c r="C92" s="1">
         <v>14</v>
@@ -5086,7 +5086,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.01914272457361221</v>
+        <v>0.01912076398730278</v>
       </c>
       <c r="C93" s="1">
         <v>12</v>
@@ -5112,7 +5112,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.01914272457361221</v>
+        <v>0.01912076398730278</v>
       </c>
       <c r="C94" s="1">
         <v>12</v>
@@ -5138,7 +5138,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.01595227047801018</v>
+        <v>0.01593396998941898</v>
       </c>
       <c r="C95" s="1">
         <v>10</v>
@@ -5164,7 +5164,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.01595227047801018</v>
+        <v>0.01593396998941898</v>
       </c>
       <c r="C96" s="1">
         <v>10</v>
@@ -5190,7 +5190,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01595227047801018</v>
+        <v>0.01593396998941898</v>
       </c>
       <c r="C97" s="1">
         <v>10</v>
@@ -5216,7 +5216,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01595227047801018</v>
+        <v>0.01593396998941898</v>
       </c>
       <c r="C98" s="1">
         <v>10</v>
@@ -5242,7 +5242,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01595227047801018</v>
+        <v>0.01593396998941898</v>
       </c>
       <c r="C99" s="1">
         <v>10</v>
@@ -5268,7 +5268,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01276181638240814</v>
+        <v>0.01274717599153519</v>
       </c>
       <c r="C100" s="1">
         <v>8</v>
@@ -5294,7 +5294,7 @@
         <v>8</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01276181638240814</v>
+        <v>0.01274717599153519</v>
       </c>
       <c r="C101" s="1">
         <v>8</v>
@@ -5320,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01276181638240814</v>
+        <v>0.01274717599153519</v>
       </c>
       <c r="C102" s="1">
         <v>8</v>
@@ -5346,7 +5346,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01276181638240814</v>
+        <v>0.01274717599153519</v>
       </c>
       <c r="C103" s="1">
         <v>8</v>
@@ -5372,7 +5372,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C104" s="1">
         <v>6</v>
@@ -5398,7 +5398,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C105" s="1">
         <v>6</v>
@@ -5424,7 +5424,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C106" s="1">
         <v>6</v>
@@ -5450,7 +5450,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C107" s="1">
         <v>6</v>
@@ -5476,7 +5476,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C108" s="1">
         <v>6</v>
@@ -5502,7 +5502,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C109" s="1">
         <v>6</v>
@@ -5528,7 +5528,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C110" s="1">
         <v>6</v>
@@ -5554,7 +5554,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C111" s="1">
         <v>6</v>
@@ -5580,7 +5580,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C112" s="1">
         <v>6</v>
@@ -5606,7 +5606,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C113" s="1">
         <v>6</v>
@@ -5632,7 +5632,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C114" s="1">
         <v>6</v>
@@ -5658,7 +5658,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C115" s="1">
         <v>6</v>
@@ -5684,7 +5684,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5710,7 +5710,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5736,7 +5736,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5762,7 +5762,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5788,7 +5788,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5814,7 +5814,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5840,7 +5840,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5866,7 +5866,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C123" s="1">
         <v>6</v>
@@ -5892,7 +5892,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C124" s="1">
         <v>6</v>
@@ -5918,7 +5918,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.009571362286806107</v>
+        <v>0.00956038199365139</v>
       </c>
       <c r="C125" s="1">
         <v>6</v>
@@ -5944,7 +5944,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.006380908191204071</v>
+        <v>0.006373587995767593</v>
       </c>
       <c r="C126" s="1">
         <v>4</v>
@@ -5970,7 +5970,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.006380908191204071</v>
+        <v>0.006373587995767593</v>
       </c>
       <c r="C127" s="1">
         <v>4</v>
@@ -5996,7 +5996,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.006380908191204071</v>
+        <v>0.006373587995767593</v>
       </c>
       <c r="C128" s="1">
         <v>4</v>
@@ -6022,7 +6022,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C129" s="1">
         <v>2</v>
@@ -6048,7 +6048,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -6074,7 +6074,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C131" s="1">
         <v>2</v>
@@ -6100,7 +6100,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -6126,7 +6126,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>
@@ -6152,7 +6152,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C134" s="1">
         <v>2</v>
@@ -6178,7 +6178,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="2">
-        <v>0.003190454095602036</v>
+        <v>0.003186793997883797</v>
       </c>
       <c r="C135" s="1">
         <v>2</v>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="155">
   <si>
     <t>atk_f407</t>
   </si>
@@ -26,6 +26,9 @@
     <t>malloc.o</t>
   </si>
   <si>
+    <t>norflash.o</t>
+  </si>
+  <si>
     <t>usbd_conf.o</t>
   </si>
   <si>
@@ -35,6 +38,12 @@
     <t>tasks.o</t>
   </si>
   <si>
+    <t>error_log_task.o</t>
+  </si>
+  <si>
+    <t>fattester.o</t>
+  </si>
+  <si>
     <t>usart.o</t>
   </si>
   <si>
@@ -65,9 +74,15 @@
     <t>dht11_task.o</t>
   </si>
   <si>
+    <t>exfuns.o</t>
+  </si>
+  <si>
     <t>port.o</t>
   </si>
   <si>
+    <t>ff.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal.o</t>
   </si>
   <si>
@@ -113,9 +128,15 @@
     <t>stm32f4xx_hal_dma.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_spi.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_can.o</t>
   </si>
   <si>
+    <t>ffunicode.o</t>
+  </si>
+  <si>
     <t>_printf_fp_dec.o</t>
   </si>
   <si>
@@ -143,6 +164,9 @@
     <t>dmul.o</t>
   </si>
   <si>
+    <t>diskio.o</t>
+  </si>
+  <si>
     <t>lc_ctype_c.o</t>
   </si>
   <si>
@@ -206,6 +230,9 @@
     <t>dfixu.o</t>
   </si>
   <si>
+    <t>memcmp.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_sram.o</t>
   </si>
   <si>
@@ -266,6 +293,9 @@
     <t>libinit2.o</t>
   </si>
   <si>
+    <t>ffsystem.o</t>
+  </si>
+  <si>
     <t>__scatter_zi.o</t>
   </si>
   <si>
@@ -273,6 +303,9 @@
   </si>
   <si>
     <t>__2printf.o</t>
+  </si>
+  <si>
+    <t>strchr.o</t>
   </si>
   <si>
     <t>stm32f4xx_it.o</t>
@@ -536,9 +569,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$136</c:f>
+              <c:f>ram_percent!$A$3:$A$147</c:f>
               <c:strCache>
-                <c:ptCount val="134"/>
+                <c:ptCount val="145"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -546,72 +579,87 @@
                   <c:v>malloc.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>norflash.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>error_log_task.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>fattester.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>c_w.l</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>lcd.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
                   <c:v>dht11.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>dht11_task.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
+                  <c:v>exfuns.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
+                  <c:v>ff.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="22">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="23">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="24">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="25">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="26">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="27">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="28">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="144">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -619,83 +667,98 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$136</c:f>
+              <c:f>ram_percent!$B$3:$B$147</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="134"/>
+                <c:ptCount val="145"/>
                 <c:pt idx="0">
-                  <c:v>55.93095016479492</c:v>
+                  <c:v>52.80369186401367</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.63291931152344</c:v>
+                  <c:v>37.41693115234375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.174704670906067</c:v>
+                  <c:v>4.494068622589111</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.164470076560974</c:v>
+                  <c:v>1.109023571014404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9142909049987793</c:v>
+                  <c:v>1.099361181259155</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3161354064941406</c:v>
+                  <c:v>0.863170325756073</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.109169065952301</c:v>
+                  <c:v>0.6570401191711426</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.109169065952301</c:v>
+                  <c:v>0.4122604429721832</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.109169065952301</c:v>
+                  <c:v>0.2984593808650971</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1068947091698647</c:v>
+                  <c:v>0.1030651107430458</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1046203523874283</c:v>
+                  <c:v>0.1030651107430458</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1023459956049919</c:v>
+                  <c:v>0.1030651107430458</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.07277937978506088</c:v>
+                  <c:v>0.1009179204702377</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.06823066622018814</c:v>
+                  <c:v>0.09877073019742966</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.02729226648807526</c:v>
+                  <c:v>0.09662354737520218</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01364613324403763</c:v>
+                  <c:v>0.06871007382869721</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01023459993302822</c:v>
+                  <c:v>0.06441569328308106</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00909742247313261</c:v>
+                  <c:v>0.02576627768576145</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.004548711236566305</c:v>
+                  <c:v>0.0171775184571743</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.004548711236566305</c:v>
+                  <c:v>0.01288313884288073</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.004548711236566305</c:v>
+                  <c:v>0.01073594950139523</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.004548711236566305</c:v>
+                  <c:v>0.009662354364991188</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.004548711236566305</c:v>
+                  <c:v>0.008588759228587151</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.001137177809141576</c:v>
-                </c:pt>
-                <c:pt idx="133">
+                  <c:v>0.004294379614293575</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.004294379614293575</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.004294379614293575</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.004294379614293575</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.004294379614293575</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.001073594903573394</c:v>
+                </c:pt>
+                <c:pt idx="144">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -763,409 +826,442 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$136</c:f>
+              <c:f>flash_percent!$A$3:$A$147</c:f>
               <c:strCache>
-                <c:ptCount val="134"/>
+                <c:ptCount val="145"/>
                 <c:pt idx="0">
+                  <c:v>ff.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>lcd.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>c_w.l</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>stm32f4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>stm32f4xx_hal_pcd.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>stm32f4xx_ll_usb.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>stm32f4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>btod.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>norflash.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>stm32f4xx_hal_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>stm32f4xx_hal_can.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
+                  <c:v>ffunicode.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="18">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>_printf_fp_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>usbd_core.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>_printf_fp_hex.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>fz_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
+                  <c:v>malloc.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="26">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="27">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="28">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="29">
                   <c:v>dht11.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="30">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="31">
                   <c:v>__printf_flags_ss_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="32">
                   <c:v>bigflt0.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="33">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="34">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="35">
+                  <c:v>diskio.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="37">
+                  <c:v>error_log_task.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="39">
                   <c:v>stm32f4xx_ll_fsmc.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
-                  <c:v>malloc.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="40">
+                  <c:v>exfuns.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="42">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="43">
                   <c:v>_printf_wctomb.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="44">
                   <c:v>_printf_hex_int_ll_ptr.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="45">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="46">
                   <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="47">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="48">
                   <c:v>dnaninf.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="49">
                   <c:v>led.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="50">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="51">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="52">
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="53">
                   <c:v>dht11_task.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="54">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="55">
                   <c:v>strcmpv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="56">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="57">
                   <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="58">
                   <c:v>_printf_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="59">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="60">
                   <c:v>_printf_oct_int_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="61">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="62">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="63">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="64">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="65">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="66">
+                  <c:v>fattester.o</c:v>
+                </c:pt>
+                <c:pt idx="67">
                   <c:v>dfixu.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="68">
+                  <c:v>memcmp.o</c:v>
+                </c:pt>
+                <c:pt idx="69">
                   <c:v>stm32f4xx_hal_sram.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="70">
                   <c:v>_printf_str.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="71">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="72">
                   <c:v>_printf_pad.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="73">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="74">
                   <c:v>lc_numeric_c.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="75">
                   <c:v>rt_memclr.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="76">
                   <c:v>_wcrtomb.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="77">
                   <c:v>vsnprintf.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="78">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="79">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="80">
                   <c:v>fpclassify.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="81">
                   <c:v>_printf_char_common.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="82">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="83">
                   <c:v>_printf_wchar.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="84">
                   <c:v>_printf_char.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="85">
                   <c:v>_printf_charcount.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="86">
                   <c:v>dflt_clz.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="87">
                   <c:v>_printf_truncate.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="88">
                   <c:v>_printf_char_file.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="89">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="90">
+                  <c:v>ffsystem.o</c:v>
+                </c:pt>
+                <c:pt idx="91">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="92">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="93">
                   <c:v>__2printf.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="94">
+                  <c:v>strchr.o</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="96">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="97">
                   <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="98">
                   <c:v>aeabi_memset.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="99">
                   <c:v>_snputc.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="100">
                   <c:v>__printf_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="101">
                   <c:v>dretinf.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="102">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="103">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="104">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="105">
                   <c:v>_sputc.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="106">
                   <c:v>_printf_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="107">
                   <c:v>_printf_l.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="108">
                   <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="109">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="110">
                   <c:v>ferror.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="111">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="112">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="113">
                   <c:v>_printf_x.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="114">
                   <c:v>_printf_u.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="115">
                   <c:v>_printf_s.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="116">
                   <c:v>_printf_p.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="117">
                   <c:v>_printf_o.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="118">
                   <c:v>_printf_n.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="119">
                   <c:v>_printf_ls.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="120">
                   <c:v>_printf_llx.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="121">
                   <c:v>_printf_llu.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="122">
                   <c:v>_printf_llo.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="123">
                   <c:v>_printf_lli.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="124">
                   <c:v>_printf_lld.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="125">
                   <c:v>_printf_lc.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="126">
                   <c:v>_printf_i.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="127">
                   <c:v>_printf_g.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="128">
                   <c:v>_printf_f.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="129">
                   <c:v>_printf_e.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="130">
                   <c:v>_printf_d.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="131">
                   <c:v>_printf_c.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="132">
                   <c:v>_printf_a.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="133">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="134">
                   <c:v>printf2.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="135">
                   <c:v>printf1.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="136">
                   <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="137">
                   <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="138">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="139">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="140">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="141">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="142">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="143">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="144">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1173,410 +1269,443 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$136</c:f>
+              <c:f>flash_percent!$B$3:$B$147</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="134"/>
+                <c:ptCount val="145"/>
                 <c:pt idx="0">
-                  <c:v>21.11569595336914</c:v>
+                  <c:v>19.23008728027344</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.7041540145874</c:v>
+                  <c:v>15.68228340148926</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.364027500152588</c:v>
+                  <c:v>9.562973976135254</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.461511611938477</c:v>
+                  <c:v>4.726459503173828</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.251183032989502</c:v>
+                  <c:v>3.313491821289063</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.069535732269287</c:v>
+                  <c:v>3.157284259796143</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.37800145149231</c:v>
+                  <c:v>3.022377967834473</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.277617454528809</c:v>
+                  <c:v>2.508786678314209</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.084816455841065</c:v>
+                  <c:v>2.43423318862915</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.899982452392578</c:v>
+                  <c:v>2.291042804718018</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.508006811141968</c:v>
+                  <c:v>2.153769731521606</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.476138830184937</c:v>
+                  <c:v>1.862655758857727</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.975812196731567</c:v>
+                  <c:v>1.838987946510315</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.87064802646637</c:v>
+                  <c:v>1.75141716003418</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.755923509597778</c:v>
+                  <c:v>1.500538468360901</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.679440379142761</c:v>
+                  <c:v>1.467403531074524</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.414936542510986</c:v>
+                  <c:v>1.450836062431335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.402189373970032</c:v>
+                  <c:v>1.389299750328064</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.277904391288757</c:v>
+                  <c:v>1.30409574508667</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.042081594467163</c:v>
+                  <c:v>1.247292995452881</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8954890966415405</c:v>
+                  <c:v>1.05085027217865</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8413136005401611</c:v>
+                  <c:v>1.041383147239685</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8110390305519104</c:v>
+                  <c:v>0.9490787386894226</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7457097768783569</c:v>
+                  <c:v>0.7739370465278626</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.7042814493179321</c:v>
+                  <c:v>0.6816325783729553</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6628531217575073</c:v>
+                  <c:v>0.6650651693344116</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6516993641853333</c:v>
+                  <c:v>0.624829888343811</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5991172790527344</c:v>
+                  <c:v>0.6023454666137695</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5481285452842712</c:v>
+                  <c:v>0.5538265109062195</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.541754961013794</c:v>
+                  <c:v>0.5230583548545837</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5035134553909302</c:v>
+                  <c:v>0.4922902286052704</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3792284727096558</c:v>
+                  <c:v>0.4840064942836762</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3696680963039398</c:v>
+                  <c:v>0.4449546039104462</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3569209277629852</c:v>
+                  <c:v>0.4070861339569092</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.3250529766082764</c:v>
+                  <c:v>0.4023525714874268</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3186793923377991</c:v>
+                  <c:v>0.3976190090179443</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3123058080673218</c:v>
+                  <c:v>0.3739512264728546</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.2995586395263672</c:v>
+                  <c:v>0.3195152878761292</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2915916442871094</c:v>
+                  <c:v>0.2816468179225922</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2836246490478516</c:v>
+                  <c:v>0.2745464742183685</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2804378569126129</c:v>
+                  <c:v>0.2485118806362152</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2485699206590653</c:v>
+                  <c:v>0.2414115518331528</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.242196336388588</c:v>
+                  <c:v>0.2366779893636704</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2358227521181107</c:v>
+                  <c:v>0.2319444268941879</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2198887765407562</c:v>
+                  <c:v>0.2224773019552231</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2198887765407562</c:v>
+                  <c:v>0.2165603637695313</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2167019844055176</c:v>
+                  <c:v>0.2106434106826782</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2135151922702789</c:v>
+                  <c:v>0.208276629447937</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.203954815864563</c:v>
+                  <c:v>0.1846088320016861</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.203954815864563</c:v>
+                  <c:v>0.1798752695322037</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1975812166929245</c:v>
+                  <c:v>0.1751417070627213</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1912076324224472</c:v>
+                  <c:v>0.1633078157901764</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1848340481519699</c:v>
+                  <c:v>0.1633078157901764</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1784604638814926</c:v>
+                  <c:v>0.1609410345554352</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1720868647098541</c:v>
+                  <c:v>0.158574253320694</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1657132804393768</c:v>
+                  <c:v>0.1514739096164703</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1593396961688995</c:v>
+                  <c:v>0.1514739096164703</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1529661118984222</c:v>
+                  <c:v>0.1467403471469879</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.146592527627945</c:v>
+                  <c:v>0.1420067995786667</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1434057205915451</c:v>
+                  <c:v>0.1372732371091843</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1402189284563065</c:v>
+                  <c:v>0.1325396746397018</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1306585520505905</c:v>
+                  <c:v>0.1278061121702194</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1242849603295326</c:v>
+                  <c:v>0.1230725571513176</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1242849603295326</c:v>
+                  <c:v>0.1183389946818352</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1179113760590553</c:v>
+                  <c:v>0.1183389946818352</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.1147245839238167</c:v>
+                  <c:v>0.1136054322123528</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.1083509922027588</c:v>
+                  <c:v>0.1136054322123528</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.1019774079322815</c:v>
+                  <c:v>0.1065050959587097</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.08285664021968842</c:v>
+                  <c:v>0.1041383147239685</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.08285664021968842</c:v>
+                  <c:v>0.1041383147239685</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.07648305594921112</c:v>
+                  <c:v>0.09703797847032547</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.07648305594921112</c:v>
+                  <c:v>0.09230441600084305</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07648305594921112</c:v>
+                  <c:v>0.09230441600084305</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.07648305594921112</c:v>
+                  <c:v>0.08757085353136063</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.07010946422815323</c:v>
+                  <c:v>0.08520407229661942</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.07010946422815323</c:v>
+                  <c:v>0.08047051727771759</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.06373587995767593</c:v>
+                  <c:v>0.07573695480823517</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.06054908409714699</c:v>
+                  <c:v>0.0615362785756588</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.05736229196190834</c:v>
+                  <c:v>0.0615362785756588</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.05736229196190834</c:v>
+                  <c:v>0.05680271610617638</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.0541754961013794</c:v>
+                  <c:v>0.05680271610617638</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.04461511597037315</c:v>
+                  <c:v>0.05680271610617638</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.04142832010984421</c:v>
+                  <c:v>0.05680271610617638</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.03824152797460556</c:v>
+                  <c:v>0.05206915736198425</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.03186793997883797</c:v>
+                  <c:v>0.05206915736198425</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.02868114598095417</c:v>
+                  <c:v>0.04733559861779213</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.02549435198307037</c:v>
+                  <c:v>0.04496881738305092</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.02549435198307037</c:v>
+                  <c:v>0.04260203614830971</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.02549435198307037</c:v>
+                  <c:v>0.04260203614830971</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.02230755798518658</c:v>
+                  <c:v>0.0402352586388588</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.01912076398730278</c:v>
+                  <c:v>0.03786847740411758</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.01912076398730278</c:v>
+                  <c:v>0.03313491865992546</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.01593396998941898</c:v>
+                  <c:v>0.0307681392878294</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01593396998941898</c:v>
+                  <c:v>0.02840135805308819</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.01593396998941898</c:v>
+                  <c:v>0.02366779930889607</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.01593396998941898</c:v>
+                  <c:v>0.02366779930889607</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.01593396998941898</c:v>
+                  <c:v>0.02130101807415485</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01274717599153519</c:v>
+                  <c:v>0.01893423870205879</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01274717599153519</c:v>
+                  <c:v>0.01893423870205879</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01274717599153519</c:v>
+                  <c:v>0.01893423870205879</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01274717599153519</c:v>
+                  <c:v>0.01656745932996273</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01420067902654409</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01420067902654409</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01183389965444803</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01183389965444803</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01183389965444803</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01183389965444803</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.01183389965444803</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.009467119351029396</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.009467119351029396</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.009467119351029396</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.009467119351029396</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.00956038199365139</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.006373587995767593</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.006373587995767593</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.006373587995767593</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.003186793997883797</c:v>
+                  <c:v>0.007100339513272047</c:v>
                 </c:pt>
                 <c:pt idx="133">
+                  <c:v>0.007100339513272047</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.004733559675514698</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.004733559675514698</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.004733559675514698</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.002366779837757349</c:v>
+                </c:pt>
+                <c:pt idx="144">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1681,8 +1810,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H136" totalsRowCount="1">
-  <autoFilter ref="A2:H135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H147" totalsRowCount="1">
+  <autoFilter ref="A2:H146"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1698,8 +1827,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H136" totalsRowCount="1">
-  <autoFilter ref="A2:H135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H147" totalsRowCount="1">
+  <autoFilter ref="A2:H146"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1999,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2012,28 +2141,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2041,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>55.93095016479492</v>
+        <v>52.80369186401367</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2067,16 +2196,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>39.63291931152344</v>
+        <v>37.41693115234375</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
       </c>
       <c r="D4" s="1">
-        <v>224</v>
+        <v>576</v>
       </c>
       <c r="E4" s="1">
-        <v>152</v>
+        <v>504</v>
       </c>
       <c r="F4" s="1">
         <v>36</v>
@@ -2093,25 +2222,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.174704670906067</v>
+        <v>4.494068622589111</v>
       </c>
       <c r="C5" s="1">
-        <v>1033</v>
+        <v>4186</v>
       </c>
       <c r="D5" s="1">
-        <v>509</v>
+        <v>1480</v>
       </c>
       <c r="E5" s="1">
-        <v>508</v>
+        <v>1478</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>1032</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2119,25 +2248,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.164470076560974</v>
+        <v>1.109023571014404</v>
       </c>
       <c r="C6" s="1">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="D6" s="1">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="E6" s="1">
-        <v>76</v>
+        <v>508</v>
       </c>
       <c r="F6" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2145,25 +2274,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.9142909049987793</v>
+        <v>1.099361181259155</v>
       </c>
       <c r="C7" s="1">
-        <v>804</v>
+        <v>1024</v>
       </c>
       <c r="D7" s="1">
-        <v>3994</v>
+        <v>468</v>
       </c>
       <c r="E7" s="1">
-        <v>3930</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G7" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>740</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2171,25 +2300,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3161354064941406</v>
+        <v>0.863170325756073</v>
       </c>
       <c r="C8" s="1">
-        <v>278</v>
+        <v>804</v>
       </c>
       <c r="D8" s="1">
-        <v>562</v>
+        <v>3994</v>
       </c>
       <c r="E8" s="1">
-        <v>552</v>
+        <v>3930</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="H8" s="1">
-        <v>268</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2197,25 +2326,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.109169065952301</v>
+        <v>0.6570401191711426</v>
       </c>
       <c r="C9" s="1">
-        <v>96</v>
+        <v>612</v>
       </c>
       <c r="D9" s="1">
-        <v>7973</v>
+        <v>270</v>
       </c>
       <c r="E9" s="1">
-        <v>7422</v>
+        <v>208</v>
       </c>
       <c r="F9" s="1">
-        <v>551</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H9" s="1">
-        <v>96</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2223,16 +2352,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.109169065952301</v>
+        <v>0.4122604429721832</v>
       </c>
       <c r="C10" s="1">
+        <v>384</v>
+      </c>
+      <c r="D10" s="1">
         <v>96</v>
       </c>
-      <c r="D10" s="1">
-        <v>8</v>
-      </c>
       <c r="E10" s="1">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -2241,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>96</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2249,25 +2378,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.109169065952301</v>
+        <v>0.2984593808650971</v>
       </c>
       <c r="C11" s="1">
-        <v>96</v>
+        <v>278</v>
       </c>
       <c r="D11" s="1">
-        <v>200</v>
+        <v>562</v>
       </c>
       <c r="E11" s="1">
-        <v>200</v>
+        <v>552</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>96</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2275,25 +2404,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1068947091698647</v>
+        <v>0.1030651107430458</v>
       </c>
       <c r="C12" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1">
-        <v>13252</v>
+        <v>8081</v>
       </c>
       <c r="E12" s="1">
-        <v>13252</v>
+        <v>7530</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2301,16 +2430,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1046203523874283</v>
+        <v>0.1030651107430458</v>
       </c>
       <c r="C13" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1">
-        <v>416</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1">
-        <v>416</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2319,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2327,25 +2456,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1023459956049919</v>
+        <v>0.1030651107430458</v>
       </c>
       <c r="C14" s="1">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D14" s="1">
-        <v>442</v>
+        <v>200</v>
       </c>
       <c r="E14" s="1">
-        <v>436</v>
+        <v>200</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2353,16 +2482,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.07277937978506088</v>
+        <v>0.1009179204702377</v>
       </c>
       <c r="C15" s="1">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1">
-        <v>1574</v>
+        <v>13252</v>
       </c>
       <c r="E15" s="1">
-        <v>1574</v>
+        <v>13252</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2371,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2379,25 +2508,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.06823066622018814</v>
+        <v>0.09877073019742966</v>
       </c>
       <c r="C16" s="1">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1">
-        <v>1102</v>
+        <v>416</v>
       </c>
       <c r="E16" s="1">
-        <v>1082</v>
+        <v>416</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>40</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2405,25 +2534,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.02729226648807526</v>
+        <v>0.09662354737520218</v>
       </c>
       <c r="C17" s="1">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D17" s="1">
-        <v>136</v>
+        <v>442</v>
       </c>
       <c r="E17" s="1">
-        <v>128</v>
+        <v>436</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H17" s="1">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2431,25 +2560,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01364613324403763</v>
+        <v>0.06871007382869721</v>
       </c>
       <c r="C18" s="1">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="D18" s="1">
-        <v>1174</v>
+        <v>1574</v>
       </c>
       <c r="E18" s="1">
-        <v>1162</v>
+        <v>1574</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2457,25 +2586,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.01023459993302822</v>
+        <v>0.06441569328308106</v>
       </c>
       <c r="C19" s="1">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1">
-        <v>183</v>
+        <v>1102</v>
       </c>
       <c r="E19" s="1">
-        <v>174</v>
+        <v>1082</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2483,16 +2612,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.00909742247313261</v>
+        <v>0.02576627768576145</v>
       </c>
       <c r="C20" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D20" s="1">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="E20" s="1">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2501,7 +2630,7 @@
         <v>8</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2509,22 +2638,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.004548711236566305</v>
+        <v>0.0171775184571743</v>
       </c>
       <c r="C21" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="E21" s="1">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="F21" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -2535,22 +2664,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.004548711236566305</v>
+        <v>0.01288313884288073</v>
       </c>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1">
-        <v>104</v>
+        <v>1174</v>
       </c>
       <c r="E22" s="1">
-        <v>100</v>
+        <v>1162</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2561,22 +2690,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.004548711236566305</v>
+        <v>0.01073594950139523</v>
       </c>
       <c r="C23" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1">
-        <v>96</v>
+        <v>16250</v>
       </c>
       <c r="E23" s="1">
-        <v>92</v>
+        <v>16036</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="G23" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2587,22 +2716,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.004548711236566305</v>
+        <v>0.009662354364991188</v>
       </c>
       <c r="C24" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24" s="1">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E24" s="1">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -2613,22 +2742,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.004548711236566305</v>
+        <v>0.008588759228587151</v>
       </c>
       <c r="C25" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1">
+        <v>116</v>
+      </c>
+      <c r="E25" s="1">
         <v>108</v>
       </c>
-      <c r="E25" s="1">
-        <v>104</v>
-      </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2639,56 +2768,186 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.001137177809141576</v>
+        <v>0.004294379614293575</v>
       </c>
       <c r="C26" s="1">
+        <v>4</v>
+      </c>
+      <c r="D26" s="1">
+        <v>48</v>
+      </c>
+      <c r="E26" s="1">
+        <v>20</v>
+      </c>
+      <c r="F26" s="1">
+        <v>24</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.004294379614293575</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="1">
+        <v>104</v>
+      </c>
+      <c r="E27" s="1">
+        <v>100</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.004294379614293575</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1">
+        <v>96</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.004294379614293575</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4</v>
+      </c>
+      <c r="D29" s="1">
+        <v>176</v>
+      </c>
+      <c r="E29" s="1">
+        <v>172</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.004294379614293575</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4</v>
+      </c>
+      <c r="D30" s="1">
+        <v>108</v>
+      </c>
+      <c r="E30" s="1">
+        <v>104</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.001073594903573394</v>
+      </c>
+      <c r="C31" s="1">
         <v>1</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D31" s="1">
         <v>2057</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E31" s="1">
         <v>2056</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
         <v>1</v>
       </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" t="s">
-        <v>135</v>
-      </c>
-      <c r="B136">
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C136">
+      <c r="C147">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D136">
+      <c r="D147">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E136">
+      <c r="E147">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F136">
+      <c r="F147">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G136">
+      <c r="G147">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H136">
+      <c r="H147">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2704,7 +2963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2717,149 +2976,149 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2">
+        <v>19.23008728027344</v>
+      </c>
+      <c r="C3" s="1">
+        <v>16250</v>
+      </c>
+      <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="B3" s="2">
-        <v>21.11569595336914</v>
-      </c>
-      <c r="C3" s="1">
-        <v>13252</v>
-      </c>
-      <c r="D3" s="1">
-        <v>94</v>
-      </c>
       <c r="E3" s="1">
-        <v>13252</v>
+        <v>16036</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1">
-        <v>94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>12.7041540145874</v>
+        <v>15.68228340148926</v>
       </c>
       <c r="C4" s="1">
-        <v>7973</v>
+        <v>13252</v>
       </c>
       <c r="D4" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" s="1">
-        <v>7422</v>
+        <v>13252</v>
       </c>
       <c r="F4" s="1">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>6.364027500152588</v>
+        <v>9.562973976135254</v>
       </c>
       <c r="C5" s="1">
-        <v>3994</v>
+        <v>8081</v>
       </c>
       <c r="D5" s="1">
-        <v>804</v>
+        <v>96</v>
       </c>
       <c r="E5" s="1">
-        <v>3930</v>
+        <v>7530</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G5" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>740</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>4.461511611938477</v>
+        <v>4.726459503173828</v>
       </c>
       <c r="C6" s="1">
-        <v>2800</v>
+        <v>3994</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="E6" s="1">
-        <v>2800</v>
+        <v>3930</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2">
-        <v>4.251183032989502</v>
+        <v>3.313491821289063</v>
       </c>
       <c r="C7" s="1">
-        <v>2668</v>
+        <v>2800</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>2668</v>
+        <v>2800</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2873,19 +3132,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2">
-        <v>4.069535732269287</v>
+        <v>3.157284259796143</v>
       </c>
       <c r="C8" s="1">
-        <v>2554</v>
+        <v>2668</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2554</v>
+        <v>2668</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2899,19 +3158,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2">
-        <v>3.37800145149231</v>
+        <v>3.022377967834473</v>
       </c>
       <c r="C9" s="1">
-        <v>2120</v>
+        <v>2554</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>2120</v>
+        <v>2554</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2925,25 +3184,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2">
-        <v>3.277617454528809</v>
+        <v>2.508786678314209</v>
       </c>
       <c r="C10" s="1">
-        <v>2057</v>
+        <v>2120</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>2056</v>
+        <v>2120</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -2954,22 +3213,22 @@
         <v>29</v>
       </c>
       <c r="B11" s="2">
-        <v>3.084816455841065</v>
+        <v>2.43423318862915</v>
       </c>
       <c r="C11" s="1">
-        <v>1936</v>
+        <v>2057</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>1936</v>
+        <v>2056</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -2977,19 +3236,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2">
-        <v>2.899982452392578</v>
+        <v>2.291042804718018</v>
       </c>
       <c r="C12" s="1">
-        <v>1820</v>
+        <v>1936</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1820</v>
+        <v>1936</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -3003,19 +3262,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2">
-        <v>2.508006811141968</v>
+        <v>2.153769731521606</v>
       </c>
       <c r="C13" s="1">
-        <v>1574</v>
+        <v>1820</v>
       </c>
       <c r="D13" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1574</v>
+        <v>1820</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -3024,53 +3283,53 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>2.476138830184937</v>
+        <v>1.862655758857727</v>
       </c>
       <c r="C14" s="1">
-        <v>1554</v>
+        <v>1574</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1">
-        <v>1546</v>
+        <v>1574</v>
       </c>
       <c r="F14" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2">
-        <v>1.975812196731567</v>
+        <v>1.838987946510315</v>
       </c>
       <c r="C15" s="1">
-        <v>1240</v>
+        <v>1554</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1240</v>
+        <v>1546</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -3081,71 +3340,71 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>1.87064802646637</v>
+        <v>1.75141716003418</v>
       </c>
       <c r="C16" s="1">
-        <v>1174</v>
+        <v>1480</v>
       </c>
       <c r="D16" s="1">
-        <v>12</v>
+        <v>4186</v>
       </c>
       <c r="E16" s="1">
-        <v>1162</v>
+        <v>1478</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2">
-        <v>1.755923509597778</v>
+        <v>1.500538468360901</v>
       </c>
       <c r="C17" s="1">
-        <v>1102</v>
+        <v>1268</v>
       </c>
       <c r="D17" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>1082</v>
+        <v>1268</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
-        <v>1.679440379142761</v>
+        <v>1.467403531074524</v>
       </c>
       <c r="C18" s="1">
-        <v>1054</v>
+        <v>1240</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>1054</v>
+        <v>1240</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -3159,22 +3418,22 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2">
-        <v>1.414936542510986</v>
+        <v>1.450836062431335</v>
       </c>
       <c r="C19" s="1">
-        <v>888</v>
+        <v>1226</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>888</v>
+        <v>284</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>942</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3185,71 +3444,71 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>1.402189373970032</v>
+        <v>1.389299750328064</v>
       </c>
       <c r="C20" s="1">
-        <v>880</v>
+        <v>1174</v>
       </c>
       <c r="D20" s="1">
-        <v>49184</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1">
-        <v>848</v>
+        <v>1162</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H20" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1.277904391288757</v>
+        <v>1.30409574508667</v>
       </c>
       <c r="C21" s="1">
-        <v>802</v>
+        <v>1102</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E21" s="1">
-        <v>764</v>
+        <v>1082</v>
       </c>
       <c r="F21" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2">
-        <v>1.042081594467163</v>
+        <v>1.247292995452881</v>
       </c>
       <c r="C22" s="1">
-        <v>654</v>
+        <v>1054</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>654</v>
+        <v>1054</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3263,178 +3522,178 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8954890966415405</v>
+        <v>1.05085027217865</v>
       </c>
       <c r="C23" s="1">
-        <v>562</v>
+        <v>888</v>
       </c>
       <c r="D23" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>552</v>
+        <v>888</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8413136005401611</v>
+        <v>1.041383147239685</v>
       </c>
       <c r="C24" s="1">
-        <v>528</v>
+        <v>880</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>49184</v>
       </c>
       <c r="E24" s="1">
-        <v>528</v>
+        <v>848</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8110390305519104</v>
+        <v>0.9490787386894226</v>
       </c>
       <c r="C25" s="1">
-        <v>509</v>
+        <v>802</v>
       </c>
       <c r="D25" s="1">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>508</v>
+        <v>764</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>1032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7457097768783569</v>
+        <v>0.7739370465278626</v>
       </c>
       <c r="C26" s="1">
-        <v>468</v>
+        <v>654</v>
       </c>
       <c r="D26" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>76</v>
+        <v>654</v>
       </c>
       <c r="F26" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2">
-        <v>0.7042814493179321</v>
+        <v>0.6816325783729553</v>
       </c>
       <c r="C27" s="1">
-        <v>442</v>
+        <v>576</v>
       </c>
       <c r="D27" s="1">
-        <v>90</v>
+        <v>34852</v>
       </c>
       <c r="E27" s="1">
-        <v>436</v>
+        <v>504</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G27" s="1">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H27" s="1">
-        <v>84</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6628531217575073</v>
+        <v>0.6650651693344116</v>
       </c>
       <c r="C28" s="1">
-        <v>416</v>
+        <v>562</v>
       </c>
       <c r="D28" s="1">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="E28" s="1">
-        <v>416</v>
+        <v>552</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H28" s="1">
-        <v>92</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6516993641853333</v>
+        <v>0.624829888343811</v>
       </c>
       <c r="C29" s="1">
-        <v>409</v>
+        <v>528</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>392</v>
+        <v>528</v>
       </c>
       <c r="F29" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -3445,126 +3704,126 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5991172790527344</v>
+        <v>0.6023454666137695</v>
       </c>
       <c r="C30" s="1">
-        <v>376</v>
+        <v>509</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="E30" s="1">
-        <v>228</v>
+        <v>508</v>
       </c>
       <c r="F30" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5481285452842712</v>
+        <v>0.5538265109062195</v>
       </c>
       <c r="C31" s="1">
-        <v>344</v>
+        <v>468</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E31" s="1">
-        <v>344</v>
+        <v>76</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2">
-        <v>0.541754961013794</v>
+        <v>0.5230583548545837</v>
       </c>
       <c r="C32" s="1">
-        <v>340</v>
+        <v>442</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E32" s="1">
-        <v>340</v>
+        <v>436</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5035134553909302</v>
+        <v>0.4922902286052704</v>
       </c>
       <c r="C33" s="1">
-        <v>316</v>
+        <v>416</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E33" s="1">
-        <v>44</v>
+        <v>416</v>
       </c>
       <c r="F33" s="1">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3792284727096558</v>
+        <v>0.4840064942836762</v>
       </c>
       <c r="C34" s="1">
-        <v>238</v>
+        <v>409</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>238</v>
+        <v>392</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -3575,22 +3834,22 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3696680963039398</v>
+        <v>0.4449546039104462</v>
       </c>
       <c r="C35" s="1">
-        <v>232</v>
+        <v>376</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -3601,45 +3860,45 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3569209277629852</v>
+        <v>0.4070861339569092</v>
       </c>
       <c r="C36" s="1">
-        <v>224</v>
+        <v>344</v>
       </c>
       <c r="D36" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>152</v>
+        <v>344</v>
       </c>
       <c r="F36" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B37" s="2">
-        <v>0.3250529766082764</v>
+        <v>0.4023525714874268</v>
       </c>
       <c r="C37" s="1">
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3653,19 +3912,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3186793923377991</v>
+        <v>0.3976190090179443</v>
       </c>
       <c r="C38" s="1">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="D38" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -3674,27 +3933,27 @@
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3123058080673218</v>
+        <v>0.3739512264728546</v>
       </c>
       <c r="C39" s="1">
-        <v>196</v>
+        <v>316</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="F39" s="1">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -3705,51 +3964,51 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B40" s="2">
-        <v>0.2995586395263672</v>
+        <v>0.3195152878761292</v>
       </c>
       <c r="C40" s="1">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="E40" s="1">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="F40" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2915916442871094</v>
+        <v>0.2816468179225922</v>
       </c>
       <c r="C41" s="1">
-        <v>183</v>
+        <v>238</v>
       </c>
       <c r="D41" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3757,19 +4016,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2836246490478516</v>
+        <v>0.2745464742183685</v>
       </c>
       <c r="C42" s="1">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3783,25 +4042,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2804378569126129</v>
+        <v>0.2485118806362152</v>
       </c>
       <c r="C43" s="1">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="D43" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E43" s="1">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3809,19 +4068,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2485699206590653</v>
+        <v>0.2414115518331528</v>
       </c>
       <c r="C44" s="1">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3835,19 +4094,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B45" s="2">
-        <v>0.242196336388588</v>
+        <v>0.2366779893636704</v>
       </c>
       <c r="C45" s="1">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E45" s="1">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3856,27 +4115,27 @@
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2358227521181107</v>
+        <v>0.2319444268941879</v>
       </c>
       <c r="C46" s="1">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="F46" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
@@ -3887,22 +4146,22 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2198887765407562</v>
+        <v>0.2224773019552231</v>
       </c>
       <c r="C47" s="1">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
@@ -3913,25 +4172,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2198887765407562</v>
+        <v>0.2165603637695313</v>
       </c>
       <c r="C48" s="1">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E48" s="1">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -3939,51 +4198,51 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2167019844055176</v>
+        <v>0.2106434106826782</v>
       </c>
       <c r="C49" s="1">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="D49" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2135151922702789</v>
+        <v>0.208276629447937</v>
       </c>
       <c r="C50" s="1">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E50" s="1">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -3991,19 +4250,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2">
-        <v>0.203954815864563</v>
+        <v>0.1846088320016861</v>
       </c>
       <c r="C51" s="1">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -4017,19 +4276,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2">
-        <v>0.203954815864563</v>
+        <v>0.1798752695322037</v>
       </c>
       <c r="C52" s="1">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -4043,19 +4302,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1975812166929245</v>
+        <v>0.1751417070627213</v>
       </c>
       <c r="C53" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -4069,19 +4328,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1912076324224472</v>
+        <v>0.1633078157901764</v>
       </c>
       <c r="C54" s="1">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -4095,25 +4354,25 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1848340481519699</v>
+        <v>0.1633078157901764</v>
       </c>
       <c r="C55" s="1">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="D55" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -4121,51 +4380,51 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1784604638814926</v>
+        <v>0.1609410345554352</v>
       </c>
       <c r="C56" s="1">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E56" s="1">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1720868647098541</v>
+        <v>0.158574253320694</v>
       </c>
       <c r="C57" s="1">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="D57" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -4173,25 +4432,25 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1657132804393768</v>
+        <v>0.1514739096164703</v>
       </c>
       <c r="C58" s="1">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -4199,19 +4458,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1593396961688995</v>
+        <v>0.1514739096164703</v>
       </c>
       <c r="C59" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -4225,25 +4484,25 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1529661118984222</v>
+        <v>0.1467403471469879</v>
       </c>
       <c r="C60" s="1">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D60" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -4251,19 +4510,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B61" s="2">
-        <v>0.146592527627945</v>
+        <v>0.1420067995786667</v>
       </c>
       <c r="C61" s="1">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4277,25 +4536,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1434057205915451</v>
+        <v>0.1372732371091843</v>
       </c>
       <c r="C62" s="1">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="D62" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E62" s="1">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -4303,19 +4562,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1402189284563065</v>
+        <v>0.1325396746397018</v>
       </c>
       <c r="C63" s="1">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -4329,25 +4588,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1306585520505905</v>
+        <v>0.1278061121702194</v>
       </c>
       <c r="C64" s="1">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D64" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E64" s="1">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -4355,25 +4614,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1242849603295326</v>
+        <v>0.1230725571513176</v>
       </c>
       <c r="C65" s="1">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -4381,19 +4640,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1242849603295326</v>
+        <v>0.1183389946818352</v>
       </c>
       <c r="C66" s="1">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -4407,25 +4666,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1179113760590553</v>
+        <v>0.1183389946818352</v>
       </c>
       <c r="C67" s="1">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E67" s="1">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -4433,22 +4692,22 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B68" s="2">
-        <v>0.1147245839238167</v>
+        <v>0.1136054322123528</v>
       </c>
       <c r="C68" s="1">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="F68" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -4459,19 +4718,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="B69" s="2">
-        <v>0.1083509922027588</v>
+        <v>0.1136054322123528</v>
       </c>
       <c r="C69" s="1">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="E69" s="1">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -4480,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -4488,16 +4747,16 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.1019774079322815</v>
+        <v>0.1065050959587097</v>
       </c>
       <c r="C70" s="1">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4514,16 +4773,16 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.08285664021968842</v>
+        <v>0.1041383147239685</v>
       </c>
       <c r="C71" s="1">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4540,16 +4799,16 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.08285664021968842</v>
+        <v>0.1041383147239685</v>
       </c>
       <c r="C72" s="1">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -4566,16 +4825,16 @@
         <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>0.07648305594921112</v>
+        <v>0.09703797847032547</v>
       </c>
       <c r="C73" s="1">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4592,16 +4851,16 @@
         <v>74</v>
       </c>
       <c r="B74" s="2">
-        <v>0.07648305594921112</v>
+        <v>0.09230441600084305</v>
       </c>
       <c r="C74" s="1">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4618,16 +4877,16 @@
         <v>75</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07648305594921112</v>
+        <v>0.09230441600084305</v>
       </c>
       <c r="C75" s="1">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4641,25 +4900,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B76" s="2">
-        <v>0.07648305594921112</v>
+        <v>0.08757085353136063</v>
       </c>
       <c r="C76" s="1">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D76" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="F76" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -4667,13 +4926,13 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" s="2">
-        <v>0.07010946422815323</v>
+        <v>0.08520407229661942</v>
       </c>
       <c r="C77" s="1">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
@@ -4682,7 +4941,7 @@
         <v>44</v>
       </c>
       <c r="F77" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -4693,19 +4952,19 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" s="2">
-        <v>0.07010946422815323</v>
+        <v>0.08047051727771759</v>
       </c>
       <c r="C78" s="1">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4719,19 +4978,19 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="2">
-        <v>0.06373587995767593</v>
+        <v>0.07573695480823517</v>
       </c>
       <c r="C79" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4745,19 +5004,19 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="2">
-        <v>0.06054908409714699</v>
+        <v>0.0615362785756588</v>
       </c>
       <c r="C80" s="1">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4771,19 +5030,19 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2">
-        <v>0.05736229196190834</v>
+        <v>0.0615362785756588</v>
       </c>
       <c r="C81" s="1">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4797,19 +5056,19 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="2">
-        <v>0.05736229196190834</v>
+        <v>0.05680271610617638</v>
       </c>
       <c r="C82" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -4823,19 +5082,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="2">
-        <v>0.0541754961013794</v>
+        <v>0.05680271610617638</v>
       </c>
       <c r="C83" s="1">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -4849,19 +5108,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="2">
-        <v>0.04461511597037315</v>
+        <v>0.05680271610617638</v>
       </c>
       <c r="C84" s="1">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4875,25 +5134,25 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="B85" s="2">
-        <v>0.04142832010984421</v>
+        <v>0.05680271610617638</v>
       </c>
       <c r="C85" s="1">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D85" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E85" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -4904,16 +5163,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>0.03824152797460556</v>
+        <v>0.05206915736198425</v>
       </c>
       <c r="C86" s="1">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -4930,16 +5189,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>0.03186793997883797</v>
+        <v>0.05206915736198425</v>
       </c>
       <c r="C87" s="1">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -4956,16 +5215,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="2">
-        <v>0.02868114598095417</v>
+        <v>0.04733559861779213</v>
       </c>
       <c r="C88" s="1">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -4982,16 +5241,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.02549435198307037</v>
+        <v>0.04496881738305092</v>
       </c>
       <c r="C89" s="1">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5008,16 +5267,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.02549435198307037</v>
+        <v>0.04260203614830971</v>
       </c>
       <c r="C90" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5034,16 +5293,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.02549435198307037</v>
+        <v>0.04260203614830971</v>
       </c>
       <c r="C91" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5060,16 +5319,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.02230755798518658</v>
+        <v>0.0402352586388588</v>
       </c>
       <c r="C92" s="1">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -5086,16 +5345,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.01912076398730278</v>
+        <v>0.03786847740411758</v>
       </c>
       <c r="C93" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5112,16 +5371,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.01912076398730278</v>
+        <v>0.03313491865992546</v>
       </c>
       <c r="C94" s="1">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -5138,16 +5397,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.01593396998941898</v>
+        <v>0.0307681392878294</v>
       </c>
       <c r="C95" s="1">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -5164,16 +5423,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.01593396998941898</v>
+        <v>0.02840135805308819</v>
       </c>
       <c r="C96" s="1">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5190,16 +5449,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.01593396998941898</v>
+        <v>0.02366779930889607</v>
       </c>
       <c r="C97" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5216,16 +5475,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.01593396998941898</v>
+        <v>0.02366779930889607</v>
       </c>
       <c r="C98" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5242,16 +5501,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="2">
-        <v>0.01593396998941898</v>
+        <v>0.02130101807415485</v>
       </c>
       <c r="C99" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5268,16 +5527,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01274717599153519</v>
+        <v>0.01893423870205879</v>
       </c>
       <c r="C100" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5291,19 +5550,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01274717599153519</v>
+        <v>0.01893423870205879</v>
       </c>
       <c r="C101" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D101" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -5312,24 +5571,24 @@
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01274717599153519</v>
+        <v>0.01893423870205879</v>
       </c>
       <c r="C102" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5343,19 +5602,19 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01274717599153519</v>
+        <v>0.01656745932996273</v>
       </c>
       <c r="C103" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5369,19 +5628,19 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B104" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01420067902654409</v>
       </c>
       <c r="C104" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -5395,19 +5654,19 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B105" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01420067902654409</v>
       </c>
       <c r="C105" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -5421,19 +5680,19 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B106" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01183389965444803</v>
       </c>
       <c r="C106" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -5447,19 +5706,19 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01183389965444803</v>
       </c>
       <c r="C107" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -5473,19 +5732,19 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B108" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01183389965444803</v>
       </c>
       <c r="C108" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -5499,19 +5758,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B109" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01183389965444803</v>
       </c>
       <c r="C109" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -5525,19 +5784,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.01183389965444803</v>
       </c>
       <c r="C110" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -5551,19 +5810,19 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.009467119351029396</v>
       </c>
       <c r="C111" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -5577,19 +5836,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="B112" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.009467119351029396</v>
       </c>
       <c r="C112" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D112" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E112" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -5598,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -5606,16 +5865,16 @@
         <v>111</v>
       </c>
       <c r="B113" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.009467119351029396</v>
       </c>
       <c r="C113" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -5632,16 +5891,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.009467119351029396</v>
       </c>
       <c r="C114" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -5658,7 +5917,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C115" s="1">
         <v>6</v>
@@ -5684,7 +5943,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C116" s="1">
         <v>6</v>
@@ -5710,7 +5969,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C117" s="1">
         <v>6</v>
@@ -5736,7 +5995,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -5762,7 +6021,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -5788,7 +6047,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -5814,7 +6073,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -5840,7 +6099,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -5866,7 +6125,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C123" s="1">
         <v>6</v>
@@ -5892,7 +6151,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C124" s="1">
         <v>6</v>
@@ -5918,7 +6177,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.00956038199365139</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C125" s="1">
         <v>6</v>
@@ -5944,16 +6203,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.006373587995767593</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C126" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -5970,16 +6229,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.006373587995767593</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C127" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -5996,16 +6255,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.006373587995767593</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C128" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -6022,16 +6281,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C129" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -6048,16 +6307,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C130" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -6074,16 +6333,16 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C131" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -6100,16 +6359,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C132" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -6126,16 +6385,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C133" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -6152,16 +6411,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C134" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
       </c>
       <c r="E134" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -6178,56 +6437,342 @@
         <v>133</v>
       </c>
       <c r="B135" s="2">
-        <v>0.003186793997883797</v>
+        <v>0.007100339513272047</v>
       </c>
       <c r="C135" s="1">
+        <v>6</v>
+      </c>
+      <c r="D135" s="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1">
+        <v>6</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2">
+        <v>0.007100339513272047</v>
+      </c>
+      <c r="C136" s="1">
+        <v>6</v>
+      </c>
+      <c r="D136" s="1">
+        <v>0</v>
+      </c>
+      <c r="E136" s="1">
+        <v>6</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2">
+        <v>0.004733559675514698</v>
+      </c>
+      <c r="C137" s="1">
+        <v>4</v>
+      </c>
+      <c r="D137" s="1">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1">
+        <v>4</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.004733559675514698</v>
+      </c>
+      <c r="C138" s="1">
+        <v>4</v>
+      </c>
+      <c r="D138" s="1">
+        <v>0</v>
+      </c>
+      <c r="E138" s="1">
+        <v>4</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2">
+        <v>0.004733559675514698</v>
+      </c>
+      <c r="C139" s="1">
+        <v>4</v>
+      </c>
+      <c r="D139" s="1">
+        <v>0</v>
+      </c>
+      <c r="E139" s="1">
+        <v>4</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C140" s="1">
         <v>2</v>
       </c>
-      <c r="D135" s="1">
-        <v>0</v>
-      </c>
-      <c r="E135" s="1">
+      <c r="D140" s="1">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1">
         <v>2</v>
       </c>
-      <c r="F135" s="1">
-        <v>0</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0</v>
-      </c>
-      <c r="H135" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" t="s">
-        <v>135</v>
-      </c>
-      <c r="B136">
+      <c r="F140" s="1">
+        <v>0</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C141" s="1">
+        <v>2</v>
+      </c>
+      <c r="D141" s="1">
+        <v>0</v>
+      </c>
+      <c r="E141" s="1">
+        <v>2</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C142" s="1">
+        <v>2</v>
+      </c>
+      <c r="D142" s="1">
+        <v>0</v>
+      </c>
+      <c r="E142" s="1">
+        <v>2</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C143" s="1">
+        <v>2</v>
+      </c>
+      <c r="D143" s="1">
+        <v>0</v>
+      </c>
+      <c r="E143" s="1">
+        <v>2</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C144" s="1">
+        <v>2</v>
+      </c>
+      <c r="D144" s="1">
+        <v>0</v>
+      </c>
+      <c r="E144" s="1">
+        <v>2</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C145" s="1">
+        <v>2</v>
+      </c>
+      <c r="D145" s="1">
+        <v>0</v>
+      </c>
+      <c r="E145" s="1">
+        <v>2</v>
+      </c>
+      <c r="F145" s="1">
+        <v>0</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2">
+        <v>0.002366779837757349</v>
+      </c>
+      <c r="C146" s="1">
+        <v>2</v>
+      </c>
+      <c r="D146" s="1">
+        <v>0</v>
+      </c>
+      <c r="E146" s="1">
+        <v>2</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C136">
+      <c r="C147">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D136">
+      <c r="D147">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E136">
+      <c r="E147">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F136">
+      <c r="F147">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G136">
+      <c r="G147">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H136">
+      <c r="H147">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="158">
   <si>
     <t>atk_f407</t>
   </si>
@@ -47,6 +47,9 @@
     <t>usart.o</t>
   </si>
   <si>
+    <t>sdio_sdcard.o</t>
+  </si>
+  <si>
     <t>c_w.l</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t>usbd_ctlreq.o</t>
   </si>
   <si>
+    <t>stm32f4xx_hal_sd.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_i2c.o</t>
   </si>
   <si>
@@ -119,6 +125,9 @@
     <t>stm32f4xx_hal_uart.o</t>
   </si>
   <si>
+    <t>stm32f4xx_ll_sdmmc.o</t>
+  </si>
+  <si>
     <t>btod.o</t>
   </si>
   <si>
@@ -152,6 +161,9 @@
     <t>stm32f4xx_hal_gpio.o</t>
   </si>
   <si>
+    <t>diskio.o</t>
+  </si>
+  <si>
     <t>__printf_flags_ss_wp.o</t>
   </si>
   <si>
@@ -162,9 +174,6 @@
   </si>
   <si>
     <t>dmul.o</t>
-  </si>
-  <si>
-    <t>diskio.o</t>
   </si>
   <si>
     <t>lc_ctype_c.o</t>
@@ -569,9 +578,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$147</c:f>
+              <c:f>ram_percent!$A$3:$A$150</c:f>
               <c:strCache>
-                <c:ptCount val="145"/>
+                <c:ptCount val="148"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -600,66 +609,69 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>sdio_sdcard.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>c_w.l</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>lcd.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>dht11.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>dht11_task.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>exfuns.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>ff.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="147">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -667,98 +679,101 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$147</c:f>
+              <c:f>ram_percent!$B$3:$B$150</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="145"/>
+                <c:ptCount val="148"/>
                 <c:pt idx="0">
-                  <c:v>52.80369186401367</c:v>
+                  <c:v>52.70410919189453</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.41693115234375</c:v>
+                  <c:v>37.34636306762695</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.494068622589111</c:v>
+                  <c:v>4.485592842102051</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.109023571014404</c:v>
+                  <c:v>1.106932044029236</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.099361181259155</c:v>
+                  <c:v>1.097287893295288</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.863170325756073</c:v>
+                  <c:v>0.8615424036979675</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6570401191711426</c:v>
+                  <c:v>0.6686598062515259</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4122604429721832</c:v>
+                  <c:v>0.411482959985733</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2984593808650971</c:v>
+                  <c:v>0.2978965044021606</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1030651107430458</c:v>
+                  <c:v>0.1757375150918961</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1030651107430458</c:v>
+                  <c:v>0.1028707399964333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1030651107430458</c:v>
+                  <c:v>0.1028707399964333</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1009179204702377</c:v>
+                  <c:v>0.1028707399964333</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.09877073019742966</c:v>
+                  <c:v>0.1007275953888893</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.09662354737520218</c:v>
+                  <c:v>0.09858445823192596</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.06871007382869721</c:v>
+                  <c:v>0.09644131362438202</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.06441569328308106</c:v>
+                  <c:v>0.06858049333095551</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.02576627768576145</c:v>
+                  <c:v>0.06429421156644821</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0171775184571743</c:v>
+                  <c:v>0.02571768499910832</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.01288313884288073</c:v>
+                  <c:v>0.01714512333273888</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.01073594950139523</c:v>
+                  <c:v>0.01285884249955416</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.009662354364991188</c:v>
+                  <c:v>0.01071570161730051</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.008588759228587151</c:v>
+                  <c:v>0.009644131176173687</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.004294379614293575</c:v>
+                  <c:v>0.008572561666369438</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.004294379614293575</c:v>
+                  <c:v>0.004286280833184719</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.004294379614293575</c:v>
+                  <c:v>0.004286280833184719</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.004294379614293575</c:v>
+                  <c:v>0.004286280833184719</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.004294379614293575</c:v>
+                  <c:v>0.004286280833184719</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.001073594903573394</c:v>
-                </c:pt>
-                <c:pt idx="144">
+                  <c:v>0.004286280833184719</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.00107157020829618</c:v>
+                </c:pt>
+                <c:pt idx="147">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -826,9 +841,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$147</c:f>
+              <c:f>flash_percent!$A$3:$A$150</c:f>
               <c:strCache>
-                <c:ptCount val="145"/>
+                <c:ptCount val="148"/>
                 <c:pt idx="0">
                   <c:v>ff.o</c:v>
                 </c:pt>
@@ -842,426 +857,435 @@
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>stm32f4xx_hal_sd.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>stm32f4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>stm32f4xx_hal_pcd.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>stm32f4xx_ll_usb.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>stm32f4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
+                  <c:v>stm32f4xx_ll_sdmmc.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>btod.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>norflash.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>stm32f4xx_hal_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>stm32f4xx_hal_can.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>ffunicode.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>_printf_fp_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>usbd_core.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>_printf_fp_hex.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>fz_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
+                  <c:v>sdio_sdcard.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>malloc.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="30">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="31">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="32">
                   <c:v>dht11.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="33">
+                  <c:v>diskio.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="35">
                   <c:v>__printf_flags_ss_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>bigflt0.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
-                  <c:v>diskio.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="39">
+                  <c:v>error_log_task.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
-                  <c:v>error_log_task.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="41">
+                  <c:v>exfuns.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="43">
                   <c:v>stm32f4xx_ll_fsmc.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
-                  <c:v>exfuns.o</c:v>
-                </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="44">
+                  <c:v>stm32f4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="46">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="47">
                   <c:v>_printf_wctomb.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="48">
                   <c:v>_printf_hex_int_ll_ptr.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
-                  <c:v>stm32f4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="49">
                   <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="50">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="51">
                   <c:v>dnaninf.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="52">
                   <c:v>led.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="53">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="54">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="55">
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="56">
                   <c:v>dht11_task.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="57">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="58">
                   <c:v>strcmpv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="59">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="60">
                   <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="61">
                   <c:v>_printf_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="62">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="63">
                   <c:v>_printf_oct_int_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="64">
                   <c:v>ai_task.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="65">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="66">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="67">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="68">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="69">
                   <c:v>fattester.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="70">
                   <c:v>dfixu.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="71">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="72">
                   <c:v>stm32f4xx_hal_sram.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="73">
                   <c:v>_printf_str.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="74">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="75">
                   <c:v>_printf_pad.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="76">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="77">
                   <c:v>lc_numeric_c.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="78">
                   <c:v>rt_memclr.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="79">
                   <c:v>_wcrtomb.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="80">
                   <c:v>vsnprintf.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="81">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="82">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="83">
                   <c:v>fpclassify.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="84">
                   <c:v>_printf_char_common.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="85">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="86">
                   <c:v>_printf_wchar.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="87">
                   <c:v>_printf_char.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="88">
                   <c:v>_printf_charcount.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="89">
                   <c:v>dflt_clz.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="90">
                   <c:v>_printf_truncate.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="91">
                   <c:v>_printf_char_file.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="92">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="93">
                   <c:v>ffsystem.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="94">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="95">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="96">
                   <c:v>__2printf.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="97">
                   <c:v>strchr.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="98">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="99">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="100">
                   <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="101">
                   <c:v>aeabi_memset.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="102">
                   <c:v>_snputc.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="103">
                   <c:v>__printf_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="104">
                   <c:v>dretinf.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="105">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="106">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="107">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="108">
                   <c:v>_sputc.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="109">
                   <c:v>_printf_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="110">
                   <c:v>_printf_l.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="111">
                   <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="112">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="113">
                   <c:v>ferror.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="114">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="115">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="116">
                   <c:v>_printf_x.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="117">
                   <c:v>_printf_u.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="118">
                   <c:v>_printf_s.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="119">
                   <c:v>_printf_p.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="120">
                   <c:v>_printf_o.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="121">
                   <c:v>_printf_n.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="122">
                   <c:v>_printf_ls.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="123">
                   <c:v>_printf_llx.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="124">
                   <c:v>_printf_llu.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="125">
                   <c:v>_printf_llo.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="126">
                   <c:v>_printf_lli.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="127">
                   <c:v>_printf_lld.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="128">
                   <c:v>_printf_lc.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="129">
                   <c:v>_printf_i.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="130">
                   <c:v>_printf_g.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="131">
                   <c:v>_printf_f.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="132">
                   <c:v>_printf_e.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="133">
                   <c:v>_printf_d.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="134">
                   <c:v>_printf_c.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="135">
                   <c:v>_printf_a.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="136">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="137">
                   <c:v>printf2.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="138">
                   <c:v>printf1.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="139">
                   <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="140">
                   <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="141">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="142">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="143">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="144">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="145">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="146">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="147">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1269,443 +1293,452 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$147</c:f>
+              <c:f>flash_percent!$B$3:$B$150</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="145"/>
+                <c:ptCount val="148"/>
                 <c:pt idx="0">
-                  <c:v>19.23008728027344</c:v>
+                  <c:v>17.91522026062012</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.68228340148926</c:v>
+                  <c:v>14.60999965667725</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.562973976135254</c:v>
+                  <c:v>8.909100532531738</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.726459503173828</c:v>
+                  <c:v>4.403285503387451</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.313491821289063</c:v>
+                  <c:v>3.556584596633911</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.157284259796143</c:v>
+                  <c:v>3.086930274963379</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.022377967834473</c:v>
+                  <c:v>2.941403388977051</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.508786678314209</c:v>
+                  <c:v>2.815721273422241</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.43423318862915</c:v>
+                  <c:v>2.337247133255005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.291042804718018</c:v>
+                  <c:v>2.32622241973877</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.153769731521606</c:v>
+                  <c:v>2.267791271209717</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.862655758857727</c:v>
+                  <c:v>2.134391784667969</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.838987946510315</c:v>
+                  <c:v>2.006504535675049</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.75141716003418</c:v>
+                  <c:v>1.73529577255249</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.500538468360901</c:v>
+                  <c:v>1.71324622631073</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.467403531074524</c:v>
+                  <c:v>1.631663084030151</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.450836062431335</c:v>
+                  <c:v>1.397938370704651</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.389299750328064</c:v>
+                  <c:v>1.367069125175476</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.30409574508667</c:v>
+                  <c:v>1.351634383201599</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.247292995452881</c:v>
+                  <c:v>1.294305682182312</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.05085027217865</c:v>
+                  <c:v>1.214927554130554</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.041383147239685</c:v>
+                  <c:v>1.162008762359619</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9490787386894226</c:v>
+                  <c:v>0.9789978265762329</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7739370465278626</c:v>
+                  <c:v>0.9701780676841736</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6816325783729553</c:v>
+                  <c:v>0.8841850161552429</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.6650651693344116</c:v>
+                  <c:v>0.7210186719894409</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.624829888343811</c:v>
+                  <c:v>0.6923543214797974</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6023454666137695</c:v>
+                  <c:v>0.6350256204605103</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5538265109062195</c:v>
+                  <c:v>0.6195909976959229</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5230583548545837</c:v>
+                  <c:v>0.5821068286895752</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4922902286052704</c:v>
+                  <c:v>0.5611597895622253</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4840064942836762</c:v>
+                  <c:v>0.515958309173584</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4449546039104462</c:v>
+                  <c:v>0.4872939884662628</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4070861339569092</c:v>
+                  <c:v>0.4740642607212067</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4023525714874268</c:v>
+                  <c:v>0.4586296379566193</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.3976190090179443</c:v>
+                  <c:v>0.4509122967720032</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3739512264728546</c:v>
+                  <c:v>0.4145306348800659</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3195152878761292</c:v>
+                  <c:v>0.3792514204978943</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.2816468179225922</c:v>
+                  <c:v>0.3748415112495422</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.2745464742183685</c:v>
+                  <c:v>0.3549969792366028</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.2485118806362152</c:v>
+                  <c:v>0.3483821153640747</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2414115518331528</c:v>
+                  <c:v>0.2888484597206116</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2366779893636704</c:v>
+                  <c:v>0.262389063835144</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2319444268941879</c:v>
+                  <c:v>0.255774199962616</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2224773019552231</c:v>
+                  <c:v>0.2458519339561462</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2165603637695313</c:v>
+                  <c:v>0.2249049097299576</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2106434106826782</c:v>
+                  <c:v>0.2204950153827667</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.208276629447937</c:v>
+                  <c:v>0.2160851061344147</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1846088320016861</c:v>
+                  <c:v>0.207265317440033</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1798752695322037</c:v>
+                  <c:v>0.196240559220314</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1751417070627213</c:v>
+                  <c:v>0.194035604596138</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1633078157901764</c:v>
+                  <c:v>0.1719861030578613</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1633078157901764</c:v>
+                  <c:v>0.1675762087106705</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1609410345554352</c:v>
+                  <c:v>0.1631663143634796</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.158574253320694</c:v>
+                  <c:v>0.1521415561437607</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1514739096164703</c:v>
+                  <c:v>0.1521415561437607</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1514739096164703</c:v>
+                  <c:v>0.1499366015195847</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1467403471469879</c:v>
+                  <c:v>0.1477316617965698</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1420067995786667</c:v>
+                  <c:v>0.1411168128252029</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1372732371091843</c:v>
+                  <c:v>0.1411168128252029</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1325396746397018</c:v>
+                  <c:v>0.1367069035768509</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1278061121702194</c:v>
+                  <c:v>0.13229700922966</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1230725571513176</c:v>
+                  <c:v>0.127887099981308</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1183389946818352</c:v>
+                  <c:v>0.1234772056341171</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1183389946818352</c:v>
+                  <c:v>0.1190673038363457</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.1136054322123528</c:v>
+                  <c:v>0.1146574094891548</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.1136054322123528</c:v>
+                  <c:v>0.1102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.1065050959587097</c:v>
+                  <c:v>0.1102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.1041383147239685</c:v>
+                  <c:v>0.1058376058936119</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.1041383147239685</c:v>
+                  <c:v>0.1058376058936119</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.09703797847032547</c:v>
+                  <c:v>0.09922275692224503</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.09230441600084305</c:v>
+                  <c:v>0.097017802298069</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.09230441600084305</c:v>
+                  <c:v>0.097017802298069</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.08757085353136063</c:v>
+                  <c:v>0.09040295332670212</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.08520407229661942</c:v>
+                  <c:v>0.08599305152893066</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.08047051727771759</c:v>
+                  <c:v>0.08599305152893066</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.07573695480823517</c:v>
+                  <c:v>0.08158315718173981</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.0615362785756588</c:v>
+                  <c:v>0.07937820255756378</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.0615362785756588</c:v>
+                  <c:v>0.07496830075979233</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.05680271610617638</c:v>
+                  <c:v>0.07055840641260147</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.05680271610617638</c:v>
+                  <c:v>0.05732870474457741</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.05680271610617638</c:v>
+                  <c:v>0.05732870474457741</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.05680271610617638</c:v>
+                  <c:v>0.05291880294680595</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.05206915736198425</c:v>
+                  <c:v>0.05291880294680595</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.05206915736198425</c:v>
+                  <c:v>0.05291880294680595</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.04733559861779213</c:v>
+                  <c:v>0.05291880294680595</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.04496881738305092</c:v>
+                  <c:v>0.0485089011490345</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.04260203614830971</c:v>
+                  <c:v>0.0485089011490345</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.04260203614830971</c:v>
+                  <c:v>0.04409900307655335</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.0402352586388588</c:v>
+                  <c:v>0.04189405217766762</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.03786847740411758</c:v>
+                  <c:v>0.03968910127878189</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.03313491865992546</c:v>
+                  <c:v>0.03968910127878189</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.0307681392878294</c:v>
+                  <c:v>0.03748415037989616</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.02840135805308819</c:v>
+                  <c:v>0.03527920320630074</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.02366779930889607</c:v>
+                  <c:v>0.03086930140852928</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.02366779930889607</c:v>
+                  <c:v>0.0286643523722887</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.02130101807415485</c:v>
+                  <c:v>0.02645940147340298</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.01893423870205879</c:v>
+                  <c:v>0.02204950153827667</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.01893423870205879</c:v>
+                  <c:v>0.02204950153827667</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01893423870205879</c:v>
+                  <c:v>0.01984455063939095</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01656745932996273</c:v>
+                  <c:v>0.01763960160315037</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01420067902654409</c:v>
+                  <c:v>0.01763960160315037</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.01420067902654409</c:v>
+                  <c:v>0.01763960160315037</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.01183389965444803</c:v>
+                  <c:v>0.01543465070426464</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.01183389965444803</c:v>
+                  <c:v>0.01322970073670149</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.01183389965444803</c:v>
+                  <c:v>0.01322970073670149</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.01183389965444803</c:v>
+                  <c:v>0.01102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.01183389965444803</c:v>
+                  <c:v>0.01102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.009467119351029396</c:v>
+                  <c:v>0.01102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.009467119351029396</c:v>
+                  <c:v>0.01102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.009467119351029396</c:v>
+                  <c:v>0.01102475076913834</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.009467119351029396</c:v>
+                  <c:v>0.008819800801575184</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.008819800801575184</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.008819800801575184</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.008819800801575184</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.007100339513272047</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.004733559675514698</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.004733559675514698</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.004733559675514698</c:v>
+                  <c:v>0.006614850368350744</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.004409900400787592</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.004409900400787592</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.004409900400787592</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.002204950200393796</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.002204950200393796</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.002204950200393796</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.002366779837757349</c:v>
+                  <c:v>0.002204950200393796</c:v>
                 </c:pt>
                 <c:pt idx="144">
+                  <c:v>0.002204950200393796</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.002204950200393796</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.002204950200393796</c:v>
+                </c:pt>
+                <c:pt idx="147">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1810,8 +1843,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H147" totalsRowCount="1">
-  <autoFilter ref="A2:H146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H150" totalsRowCount="1">
+  <autoFilter ref="A2:H149"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1827,8 +1860,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H147" totalsRowCount="1">
-  <autoFilter ref="A2:H146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H150" totalsRowCount="1">
+  <autoFilter ref="A2:H149"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2128,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2141,28 +2174,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2170,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>52.80369186401367</v>
+        <v>52.70410919189453</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2196,7 +2229,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>37.41693115234375</v>
+        <v>37.34636306762695</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -2222,7 +2255,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>4.494068622589111</v>
+        <v>4.485592842102051</v>
       </c>
       <c r="C5" s="1">
         <v>4186</v>
@@ -2248,7 +2281,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.109023571014404</v>
+        <v>1.106932044029236</v>
       </c>
       <c r="C6" s="1">
         <v>1033</v>
@@ -2274,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.099361181259155</v>
+        <v>1.097287893295288</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -2300,7 +2333,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.863170325756073</v>
+        <v>0.8615424036979675</v>
       </c>
       <c r="C8" s="1">
         <v>804</v>
@@ -2326,22 +2359,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.6570401191711426</v>
+        <v>0.6686598062515259</v>
       </c>
       <c r="C9" s="1">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="D9" s="1">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="E9" s="1">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="F9" s="1">
         <v>50</v>
       </c>
       <c r="G9" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1">
         <v>600</v>
@@ -2352,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.4122604429721832</v>
+        <v>0.411482959985733</v>
       </c>
       <c r="C10" s="1">
         <v>384</v>
@@ -2378,7 +2411,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2984593808650971</v>
+        <v>0.2978965044021606</v>
       </c>
       <c r="C11" s="1">
         <v>278</v>
@@ -2404,25 +2437,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1030651107430458</v>
+        <v>0.1757375150918961</v>
       </c>
       <c r="C12" s="1">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="D12" s="1">
-        <v>8081</v>
+        <v>628</v>
       </c>
       <c r="E12" s="1">
-        <v>7530</v>
+        <v>628</v>
       </c>
       <c r="F12" s="1">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>96</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2430,19 +2463,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1030651107430458</v>
+        <v>0.1028707399964333</v>
       </c>
       <c r="C13" s="1">
         <v>96</v>
       </c>
       <c r="D13" s="1">
-        <v>8</v>
+        <v>8081</v>
       </c>
       <c r="E13" s="1">
-        <v>8</v>
+        <v>7530</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2456,16 +2489,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1030651107430458</v>
+        <v>0.1028707399964333</v>
       </c>
       <c r="C14" s="1">
         <v>96</v>
       </c>
       <c r="D14" s="1">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2482,16 +2515,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.1009179204702377</v>
+        <v>0.1028707399964333</v>
       </c>
       <c r="C15" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="1">
-        <v>13252</v>
+        <v>200</v>
       </c>
       <c r="E15" s="1">
-        <v>13252</v>
+        <v>200</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2500,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2508,16 +2541,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.09877073019742966</v>
+        <v>0.1007275953888893</v>
       </c>
       <c r="C16" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D16" s="1">
-        <v>416</v>
+        <v>13252</v>
       </c>
       <c r="E16" s="1">
-        <v>416</v>
+        <v>13252</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2526,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2534,25 +2567,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.09662354737520218</v>
+        <v>0.09858445823192596</v>
       </c>
       <c r="C17" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D17" s="1">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="E17" s="1">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2560,25 +2593,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.06871007382869721</v>
+        <v>0.09644131362438202</v>
       </c>
       <c r="C18" s="1">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D18" s="1">
-        <v>1574</v>
+        <v>442</v>
       </c>
       <c r="E18" s="1">
-        <v>1574</v>
+        <v>436</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H18" s="1">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2586,25 +2619,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.06441569328308106</v>
+        <v>0.06858049333095551</v>
       </c>
       <c r="C19" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D19" s="1">
-        <v>1102</v>
+        <v>1574</v>
       </c>
       <c r="E19" s="1">
-        <v>1082</v>
+        <v>1574</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2612,25 +2645,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.02576627768576145</v>
+        <v>0.06429421156644821</v>
       </c>
       <c r="C20" s="1">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1">
-        <v>136</v>
+        <v>1102</v>
       </c>
       <c r="E20" s="1">
-        <v>128</v>
+        <v>1082</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2638,25 +2671,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0171775184571743</v>
+        <v>0.02571768499910832</v>
       </c>
       <c r="C21" s="1">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1">
+        <v>136</v>
+      </c>
+      <c r="E21" s="1">
+        <v>128</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>8</v>
+      </c>
+      <c r="H21" s="1">
         <v>16</v>
-      </c>
-      <c r="D21" s="1">
-        <v>210</v>
-      </c>
-      <c r="E21" s="1">
-        <v>194</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>16</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2664,22 +2697,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.01288313884288073</v>
+        <v>0.01714512333273888</v>
       </c>
       <c r="C22" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1">
-        <v>1174</v>
+        <v>262</v>
       </c>
       <c r="E22" s="1">
-        <v>1162</v>
+        <v>246</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2690,22 +2723,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.01073594950139523</v>
+        <v>0.01285884249955416</v>
       </c>
       <c r="C23" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1">
-        <v>16250</v>
+        <v>1174</v>
       </c>
       <c r="E23" s="1">
-        <v>16036</v>
+        <v>1162</v>
       </c>
       <c r="F23" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2716,22 +2749,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.009662354364991188</v>
+        <v>0.01071570161730051</v>
       </c>
       <c r="C24" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1">
-        <v>183</v>
+        <v>16250</v>
       </c>
       <c r="E24" s="1">
-        <v>174</v>
+        <v>16036</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="G24" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -2742,22 +2775,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.008588759228587151</v>
+        <v>0.009644131176173687</v>
       </c>
       <c r="C25" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="1">
-        <v>116</v>
+        <v>223</v>
       </c>
       <c r="E25" s="1">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2768,22 +2801,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.004294379614293575</v>
+        <v>0.008572561666369438</v>
       </c>
       <c r="C26" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="E26" s="1">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="F26" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -2794,19 +2827,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.004294379614293575</v>
+        <v>0.004286280833184719</v>
       </c>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="1">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="E27" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G27" s="1">
         <v>4</v>
@@ -2820,16 +2853,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.004294379614293575</v>
+        <v>0.004286280833184719</v>
       </c>
       <c r="C28" s="1">
         <v>4</v>
       </c>
       <c r="D28" s="1">
+        <v>104</v>
+      </c>
+      <c r="E28" s="1">
         <v>100</v>
-      </c>
-      <c r="E28" s="1">
-        <v>96</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2846,16 +2879,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.004294379614293575</v>
+        <v>0.004286280833184719</v>
       </c>
       <c r="C29" s="1">
         <v>4</v>
       </c>
       <c r="D29" s="1">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2872,16 +2905,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.004294379614293575</v>
+        <v>0.004286280833184719</v>
       </c>
       <c r="C30" s="1">
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="E30" s="1">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2898,56 +2931,82 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.001073594903573394</v>
+        <v>0.004286280833184719</v>
       </c>
       <c r="C31" s="1">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1">
+        <v>108</v>
+      </c>
+      <c r="E31" s="1">
+        <v>104</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.00107157020829618</v>
+      </c>
+      <c r="C32" s="1">
         <v>1</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>2057</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E32" s="1">
         <v>2056</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1">
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
         <v>1</v>
       </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
-      <c r="A147" t="s">
-        <v>146</v>
-      </c>
-      <c r="B147">
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C147">
+      <c r="C150">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D147">
+      <c r="D150">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E147">
+      <c r="E150">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F147">
+      <c r="F150">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G147">
+      <c r="G150">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H147">
+      <c r="H150">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2963,7 +3022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2976,36 +3035,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" t="s">
         <v>154</v>
       </c>
-      <c r="C2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" t="s">
-        <v>151</v>
-      </c>
       <c r="G2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2">
-        <v>19.23008728027344</v>
+        <v>17.91522026062012</v>
       </c>
       <c r="C3" s="1">
         <v>16250</v>
@@ -3028,10 +3087,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>15.68228340148926</v>
+        <v>14.60999965667725</v>
       </c>
       <c r="C4" s="1">
         <v>13252</v>
@@ -3054,10 +3113,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
-        <v>9.562973976135254</v>
+        <v>8.909100532531738</v>
       </c>
       <c r="C5" s="1">
         <v>8081</v>
@@ -3083,7 +3142,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>4.726459503173828</v>
+        <v>4.403285503387451</v>
       </c>
       <c r="C6" s="1">
         <v>3994</v>
@@ -3106,19 +3165,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2">
-        <v>3.313491821289063</v>
+        <v>3.556584596633911</v>
       </c>
       <c r="C7" s="1">
-        <v>2800</v>
+        <v>3226</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>2800</v>
+        <v>3226</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -3132,19 +3191,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2">
-        <v>3.157284259796143</v>
+        <v>3.086930274963379</v>
       </c>
       <c r="C8" s="1">
-        <v>2668</v>
+        <v>2800</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2668</v>
+        <v>2800</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -3158,19 +3217,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2">
-        <v>3.022377967834473</v>
+        <v>2.941403388977051</v>
       </c>
       <c r="C9" s="1">
-        <v>2554</v>
+        <v>2668</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>2554</v>
+        <v>2668</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -3184,19 +3243,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2">
-        <v>2.508786678314209</v>
+        <v>2.815721273422241</v>
       </c>
       <c r="C10" s="1">
-        <v>2120</v>
+        <v>2554</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>2120</v>
+        <v>2554</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -3210,25 +3269,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2">
-        <v>2.43423318862915</v>
+        <v>2.337247133255005</v>
       </c>
       <c r="C11" s="1">
-        <v>2057</v>
+        <v>2120</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>2056</v>
+        <v>2120</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -3236,19 +3295,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2">
-        <v>2.291042804718018</v>
+        <v>2.32622241973877</v>
       </c>
       <c r="C12" s="1">
-        <v>1936</v>
+        <v>2110</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1936</v>
+        <v>2110</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -3262,25 +3321,25 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2">
-        <v>2.153769731521606</v>
+        <v>2.267791271209717</v>
       </c>
       <c r="C13" s="1">
-        <v>1820</v>
+        <v>2057</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>1820</v>
+        <v>2056</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -3288,19 +3347,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2">
-        <v>1.862655758857727</v>
+        <v>2.134391784667969</v>
       </c>
       <c r="C14" s="1">
-        <v>1574</v>
+        <v>1936</v>
       </c>
       <c r="D14" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1574</v>
+        <v>1936</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -3309,27 +3368,27 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2">
-        <v>1.838987946510315</v>
+        <v>2.006504535675049</v>
       </c>
       <c r="C15" s="1">
-        <v>1554</v>
+        <v>1820</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1546</v>
+        <v>1820</v>
       </c>
       <c r="F15" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -3340,48 +3399,48 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2">
-        <v>1.75141716003418</v>
+        <v>1.73529577255249</v>
       </c>
       <c r="C16" s="1">
-        <v>1480</v>
+        <v>1574</v>
       </c>
       <c r="D16" s="1">
-        <v>4186</v>
+        <v>64</v>
       </c>
       <c r="E16" s="1">
-        <v>1478</v>
+        <v>1574</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>4184</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2">
-        <v>1.500538468360901</v>
+        <v>1.71324622631073</v>
       </c>
       <c r="C17" s="1">
-        <v>1268</v>
+        <v>1554</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>1268</v>
+        <v>1546</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -3392,48 +3451,48 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="B18" s="2">
-        <v>1.467403531074524</v>
+        <v>1.631663084030151</v>
       </c>
       <c r="C18" s="1">
-        <v>1240</v>
+        <v>1480</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>4186</v>
       </c>
       <c r="E18" s="1">
-        <v>1240</v>
+        <v>1478</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
-        <v>1.450836062431335</v>
+        <v>1.397938370704651</v>
       </c>
       <c r="C19" s="1">
-        <v>1226</v>
+        <v>1268</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>284</v>
+        <v>1268</v>
       </c>
       <c r="F19" s="1">
-        <v>942</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3444,25 +3503,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2">
-        <v>1.389299750328064</v>
+        <v>1.367069125175476</v>
       </c>
       <c r="C20" s="1">
-        <v>1174</v>
+        <v>1240</v>
       </c>
       <c r="D20" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>1162</v>
+        <v>1240</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -3470,51 +3529,51 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2">
-        <v>1.30409574508667</v>
+        <v>1.351634383201599</v>
       </c>
       <c r="C21" s="1">
-        <v>1102</v>
+        <v>1226</v>
       </c>
       <c r="D21" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>1082</v>
+        <v>284</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>942</v>
       </c>
       <c r="G21" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>1.247292995452881</v>
+        <v>1.294305682182312</v>
       </c>
       <c r="C22" s="1">
-        <v>1054</v>
+        <v>1174</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1">
-        <v>1054</v>
+        <v>1162</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -3522,74 +3581,74 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
-        <v>1.05085027217865</v>
+        <v>1.214927554130554</v>
       </c>
       <c r="C23" s="1">
-        <v>888</v>
+        <v>1102</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E23" s="1">
-        <v>888</v>
+        <v>1082</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2">
-        <v>1.041383147239685</v>
+        <v>1.162008762359619</v>
       </c>
       <c r="C24" s="1">
-        <v>880</v>
+        <v>1054</v>
       </c>
       <c r="D24" s="1">
-        <v>49184</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>848</v>
+        <v>1054</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>49152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9490787386894226</v>
+        <v>0.9789978265762329</v>
       </c>
       <c r="C25" s="1">
-        <v>802</v>
+        <v>888</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>764</v>
+        <v>888</v>
       </c>
       <c r="F25" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -3600,97 +3659,97 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7739370465278626</v>
+        <v>0.9701780676841736</v>
       </c>
       <c r="C26" s="1">
-        <v>654</v>
+        <v>880</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>49184</v>
       </c>
       <c r="E26" s="1">
-        <v>654</v>
+        <v>848</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>49152</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6816325783729553</v>
+        <v>0.8841850161552429</v>
       </c>
       <c r="C27" s="1">
-        <v>576</v>
+        <v>802</v>
       </c>
       <c r="D27" s="1">
-        <v>34852</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>504</v>
+        <v>764</v>
       </c>
       <c r="F27" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G27" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>34816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2">
-        <v>0.6650651693344116</v>
+        <v>0.7210186719894409</v>
       </c>
       <c r="C28" s="1">
-        <v>562</v>
+        <v>654</v>
       </c>
       <c r="D28" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>552</v>
+        <v>654</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B29" s="2">
-        <v>0.624829888343811</v>
+        <v>0.6923543214797974</v>
       </c>
       <c r="C29" s="1">
-        <v>528</v>
+        <v>628</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="E29" s="1">
-        <v>528</v>
+        <v>628</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -3699,180 +3758,180 @@
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6023454666137695</v>
+        <v>0.6350256204605103</v>
       </c>
       <c r="C30" s="1">
-        <v>509</v>
+        <v>576</v>
       </c>
       <c r="D30" s="1">
-        <v>1033</v>
+        <v>34852</v>
       </c>
       <c r="E30" s="1">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G30" s="1">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H30" s="1">
-        <v>1032</v>
+        <v>34816</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5538265109062195</v>
+        <v>0.6195909976959229</v>
       </c>
       <c r="C31" s="1">
-        <v>468</v>
+        <v>562</v>
       </c>
       <c r="D31" s="1">
-        <v>1024</v>
+        <v>278</v>
       </c>
       <c r="E31" s="1">
-        <v>76</v>
+        <v>552</v>
       </c>
       <c r="F31" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H31" s="1">
-        <v>1024</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5230583548545837</v>
+        <v>0.5821068286895752</v>
       </c>
       <c r="C32" s="1">
-        <v>442</v>
+        <v>528</v>
       </c>
       <c r="D32" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>436</v>
+        <v>528</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4922902286052704</v>
+        <v>0.5611597895622253</v>
       </c>
       <c r="C33" s="1">
-        <v>416</v>
+        <v>509</v>
       </c>
       <c r="D33" s="1">
-        <v>92</v>
+        <v>1033</v>
       </c>
       <c r="E33" s="1">
-        <v>416</v>
+        <v>508</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1">
-        <v>92</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4840064942836762</v>
+        <v>0.515958309173584</v>
       </c>
       <c r="C34" s="1">
-        <v>409</v>
+        <v>468</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E34" s="1">
+        <v>76</v>
+      </c>
+      <c r="F34" s="1">
         <v>392</v>
       </c>
-      <c r="F34" s="1">
-        <v>17</v>
-      </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4449546039104462</v>
+        <v>0.4872939884662628</v>
       </c>
       <c r="C35" s="1">
-        <v>376</v>
+        <v>442</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E35" s="1">
-        <v>228</v>
+        <v>436</v>
       </c>
       <c r="F35" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4070861339569092</v>
+        <v>0.4740642607212067</v>
       </c>
       <c r="C36" s="1">
-        <v>344</v>
+        <v>430</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>344</v>
+        <v>430</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -3886,19 +3945,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4023525714874268</v>
+        <v>0.4586296379566193</v>
       </c>
       <c r="C37" s="1">
-        <v>340</v>
+        <v>416</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E37" s="1">
-        <v>340</v>
+        <v>416</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3907,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3915,19 +3974,19 @@
         <v>49</v>
       </c>
       <c r="B38" s="2">
-        <v>0.3976190090179443</v>
+        <v>0.4509122967720032</v>
       </c>
       <c r="C38" s="1">
-        <v>336</v>
+        <v>409</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
@@ -3941,19 +4000,19 @@
         <v>50</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3739512264728546</v>
+        <v>0.4145306348800659</v>
       </c>
       <c r="C39" s="1">
-        <v>316</v>
+        <v>376</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="F39" s="1">
-        <v>272</v>
+        <v>148</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -3964,45 +4023,45 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3195152878761292</v>
+        <v>0.3792514204978943</v>
       </c>
       <c r="C40" s="1">
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="D40" s="1">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>208</v>
+        <v>344</v>
       </c>
       <c r="F40" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="2">
-        <v>0.2816468179225922</v>
+        <v>0.3748415112495422</v>
       </c>
       <c r="C41" s="1">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -4016,51 +4075,51 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B42" s="2">
-        <v>0.2745464742183685</v>
+        <v>0.3549969792366028</v>
       </c>
       <c r="C42" s="1">
-        <v>232</v>
+        <v>322</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="E42" s="1">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B43" s="2">
-        <v>0.2485118806362152</v>
+        <v>0.3483821153640747</v>
       </c>
       <c r="C43" s="1">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="D43" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G43" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -4068,25 +4127,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2414115518331528</v>
+        <v>0.2888484597206116</v>
       </c>
       <c r="C44" s="1">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E44" s="1">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4094,19 +4153,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2366779893636704</v>
+        <v>0.262389063835144</v>
       </c>
       <c r="C45" s="1">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="D45" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -4115,27 +4174,27 @@
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2319444268941879</v>
+        <v>0.255774199962616</v>
       </c>
       <c r="C46" s="1">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="F46" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
@@ -4146,25 +4205,25 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2224773019552231</v>
+        <v>0.2458519339561462</v>
       </c>
       <c r="C47" s="1">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E47" s="1">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="F47" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -4172,25 +4231,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2165603637695313</v>
+        <v>0.2249049097299576</v>
       </c>
       <c r="C48" s="1">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="D48" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -4198,19 +4257,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2106434106826782</v>
+        <v>0.2204950153827667</v>
       </c>
       <c r="C49" s="1">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E49" s="1">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -4219,30 +4278,30 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2">
-        <v>0.208276629447937</v>
+        <v>0.2160851061344147</v>
       </c>
       <c r="C50" s="1">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="F50" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -4250,22 +4309,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1846088320016861</v>
+        <v>0.207265317440033</v>
       </c>
       <c r="C51" s="1">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -4276,19 +4335,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1798752695322037</v>
+        <v>0.196240559220314</v>
       </c>
       <c r="C52" s="1">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -4302,25 +4361,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1751417070627213</v>
+        <v>0.194035604596138</v>
       </c>
       <c r="C53" s="1">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -4331,16 +4390,16 @@
         <v>60</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1633078157901764</v>
+        <v>0.1719861030578613</v>
       </c>
       <c r="C54" s="1">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -4357,16 +4416,16 @@
         <v>61</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1633078157901764</v>
+        <v>0.1675762087106705</v>
       </c>
       <c r="C55" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -4380,45 +4439,45 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1609410345554352</v>
+        <v>0.1631663143634796</v>
       </c>
       <c r="C56" s="1">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D56" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57" s="2">
-        <v>0.158574253320694</v>
+        <v>0.1521415561437607</v>
       </c>
       <c r="C57" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4432,19 +4491,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1514739096164703</v>
+        <v>0.1521415561437607</v>
       </c>
       <c r="C58" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -4458,16 +4517,16 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1514739096164703</v>
+        <v>0.1499366015195847</v>
       </c>
       <c r="C59" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E59" s="1">
         <v>128</v>
@@ -4476,10 +4535,10 @@
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -4487,16 +4546,16 @@
         <v>65</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1467403471469879</v>
+        <v>0.1477316617965698</v>
       </c>
       <c r="C60" s="1">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -4513,16 +4572,16 @@
         <v>66</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1420067995786667</v>
+        <v>0.1411168128252029</v>
       </c>
       <c r="C61" s="1">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4536,25 +4595,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1372732371091843</v>
+        <v>0.1411168128252029</v>
       </c>
       <c r="C62" s="1">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D62" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -4562,19 +4621,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1325396746397018</v>
+        <v>0.1367069035768509</v>
       </c>
       <c r="C63" s="1">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -4588,25 +4647,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1278061121702194</v>
+        <v>0.13229700922966</v>
       </c>
       <c r="C64" s="1">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -4614,25 +4673,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B65" s="2">
-        <v>0.1230725571513176</v>
+        <v>0.127887099981308</v>
       </c>
       <c r="C65" s="1">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D65" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E65" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -4640,19 +4699,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1183389946818352</v>
+        <v>0.1234772056341171</v>
       </c>
       <c r="C66" s="1">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -4666,19 +4725,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1183389946818352</v>
+        <v>0.1190673038363457</v>
       </c>
       <c r="C67" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="1">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -4692,25 +4751,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B68" s="2">
-        <v>0.1136054322123528</v>
+        <v>0.1146574094891548</v>
       </c>
       <c r="C68" s="1">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E68" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -4718,19 +4777,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="B69" s="2">
-        <v>0.1136054322123528</v>
+        <v>0.1102475076913834</v>
       </c>
       <c r="C69" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D69" s="1">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -4739,30 +4798,30 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="B70" s="2">
-        <v>0.1065050959587097</v>
+        <v>0.1102475076913834</v>
       </c>
       <c r="C70" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -4770,19 +4829,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" s="2">
-        <v>0.1041383147239685</v>
+        <v>0.1058376058936119</v>
       </c>
       <c r="C71" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4796,19 +4855,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="B72" s="2">
-        <v>0.1041383147239685</v>
+        <v>0.1058376058936119</v>
       </c>
       <c r="C72" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="E72" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -4817,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -4825,16 +4884,16 @@
         <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>0.09703797847032547</v>
+        <v>0.09922275692224503</v>
       </c>
       <c r="C73" s="1">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4851,16 +4910,16 @@
         <v>74</v>
       </c>
       <c r="B74" s="2">
-        <v>0.09230441600084305</v>
+        <v>0.097017802298069</v>
       </c>
       <c r="C74" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4877,16 +4936,16 @@
         <v>75</v>
       </c>
       <c r="B75" s="2">
-        <v>0.09230441600084305</v>
+        <v>0.097017802298069</v>
       </c>
       <c r="C75" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4903,16 +4962,16 @@
         <v>76</v>
       </c>
       <c r="B76" s="2">
-        <v>0.08757085353136063</v>
+        <v>0.09040295332670212</v>
       </c>
       <c r="C76" s="1">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4929,19 +4988,19 @@
         <v>77</v>
       </c>
       <c r="B77" s="2">
-        <v>0.08520407229661942</v>
+        <v>0.08599305152893066</v>
       </c>
       <c r="C77" s="1">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="F77" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -4955,16 +5014,16 @@
         <v>78</v>
       </c>
       <c r="B78" s="2">
-        <v>0.08047051727771759</v>
+        <v>0.08599305152893066</v>
       </c>
       <c r="C78" s="1">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4981,16 +5040,16 @@
         <v>79</v>
       </c>
       <c r="B79" s="2">
-        <v>0.07573695480823517</v>
+        <v>0.08158315718173981</v>
       </c>
       <c r="C79" s="1">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -5007,19 +5066,19 @@
         <v>80</v>
       </c>
       <c r="B80" s="2">
-        <v>0.0615362785756588</v>
+        <v>0.07937820255756378</v>
       </c>
       <c r="C80" s="1">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F80" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
@@ -5033,16 +5092,16 @@
         <v>81</v>
       </c>
       <c r="B81" s="2">
-        <v>0.0615362785756588</v>
+        <v>0.07496830075979233</v>
       </c>
       <c r="C81" s="1">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -5059,16 +5118,16 @@
         <v>82</v>
       </c>
       <c r="B82" s="2">
-        <v>0.05680271610617638</v>
+        <v>0.07055840641260147</v>
       </c>
       <c r="C82" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -5085,16 +5144,16 @@
         <v>83</v>
       </c>
       <c r="B83" s="2">
-        <v>0.05680271610617638</v>
+        <v>0.05732870474457741</v>
       </c>
       <c r="C83" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -5111,16 +5170,16 @@
         <v>84</v>
       </c>
       <c r="B84" s="2">
-        <v>0.05680271610617638</v>
+        <v>0.05732870474457741</v>
       </c>
       <c r="C84" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -5134,25 +5193,25 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="B85" s="2">
-        <v>0.05680271610617638</v>
+        <v>0.05291880294680595</v>
       </c>
       <c r="C85" s="1">
         <v>48</v>
       </c>
       <c r="D85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F85" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -5160,19 +5219,19 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="2">
-        <v>0.05206915736198425</v>
+        <v>0.05291880294680595</v>
       </c>
       <c r="C86" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -5186,19 +5245,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="2">
-        <v>0.05206915736198425</v>
+        <v>0.05291880294680595</v>
       </c>
       <c r="C87" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5212,25 +5271,25 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="B88" s="2">
-        <v>0.04733559861779213</v>
+        <v>0.05291880294680595</v>
       </c>
       <c r="C88" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D88" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E88" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -5241,16 +5300,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="2">
-        <v>0.04496881738305092</v>
+        <v>0.0485089011490345</v>
       </c>
       <c r="C89" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5267,16 +5326,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.04260203614830971</v>
+        <v>0.0485089011490345</v>
       </c>
       <c r="C90" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5293,16 +5352,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.04260203614830971</v>
+        <v>0.04409900307655335</v>
       </c>
       <c r="C91" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5319,16 +5378,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.0402352586388588</v>
+        <v>0.04189405217766762</v>
       </c>
       <c r="C92" s="1">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -5345,16 +5404,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.03786847740411758</v>
+        <v>0.03968910127878189</v>
       </c>
       <c r="C93" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5371,16 +5430,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.03313491865992546</v>
+        <v>0.03968910127878189</v>
       </c>
       <c r="C94" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -5397,16 +5456,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.0307681392878294</v>
+        <v>0.03748415037989616</v>
       </c>
       <c r="C95" s="1">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -5423,16 +5482,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.02840135805308819</v>
+        <v>0.03527920320630074</v>
       </c>
       <c r="C96" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5449,16 +5508,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.02366779930889607</v>
+        <v>0.03086930140852928</v>
       </c>
       <c r="C97" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5475,16 +5534,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.02366779930889607</v>
+        <v>0.0286643523722887</v>
       </c>
       <c r="C98" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5501,16 +5560,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="2">
-        <v>0.02130101807415485</v>
+        <v>0.02645940147340298</v>
       </c>
       <c r="C99" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5527,16 +5586,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="2">
-        <v>0.01893423870205879</v>
+        <v>0.02204950153827667</v>
       </c>
       <c r="C100" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5553,16 +5612,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01893423870205879</v>
+        <v>0.02204950153827667</v>
       </c>
       <c r="C101" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -5579,16 +5638,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01893423870205879</v>
+        <v>0.01984455063939095</v>
       </c>
       <c r="C102" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5605,16 +5664,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01656745932996273</v>
+        <v>0.01763960160315037</v>
       </c>
       <c r="C103" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5631,16 +5690,16 @@
         <v>103</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01420067902654409</v>
+        <v>0.01763960160315037</v>
       </c>
       <c r="C104" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -5657,16 +5716,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="2">
-        <v>0.01420067902654409</v>
+        <v>0.01763960160315037</v>
       </c>
       <c r="C105" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -5683,16 +5742,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="2">
-        <v>0.01183389965444803</v>
+        <v>0.01543465070426464</v>
       </c>
       <c r="C106" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -5709,16 +5768,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="2">
-        <v>0.01183389965444803</v>
+        <v>0.01322970073670149</v>
       </c>
       <c r="C107" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -5735,16 +5794,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="2">
-        <v>0.01183389965444803</v>
+        <v>0.01322970073670149</v>
       </c>
       <c r="C108" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -5761,7 +5820,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="2">
-        <v>0.01183389965444803</v>
+        <v>0.01102475076913834</v>
       </c>
       <c r="C109" s="1">
         <v>10</v>
@@ -5787,7 +5846,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2">
-        <v>0.01183389965444803</v>
+        <v>0.01102475076913834</v>
       </c>
       <c r="C110" s="1">
         <v>10</v>
@@ -5813,16 +5872,16 @@
         <v>110</v>
       </c>
       <c r="B111" s="2">
-        <v>0.009467119351029396</v>
+        <v>0.01102475076913834</v>
       </c>
       <c r="C111" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -5836,19 +5895,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2">
-        <v>0.009467119351029396</v>
+        <v>0.01102475076913834</v>
       </c>
       <c r="C112" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D112" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -5857,24 +5916,24 @@
         <v>0</v>
       </c>
       <c r="H112" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2">
-        <v>0.009467119351029396</v>
+        <v>0.01102475076913834</v>
       </c>
       <c r="C113" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -5888,10 +5947,10 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2">
-        <v>0.009467119351029396</v>
+        <v>0.008819800801575184</v>
       </c>
       <c r="C114" s="1">
         <v>8</v>
@@ -5914,19 +5973,19 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="B115" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.008819800801575184</v>
       </c>
       <c r="C115" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D115" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E115" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -5935,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -5943,16 +6002,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.008819800801575184</v>
       </c>
       <c r="C116" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -5969,16 +6028,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.008819800801575184</v>
       </c>
       <c r="C117" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -5995,7 +6054,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C118" s="1">
         <v>6</v>
@@ -6021,7 +6080,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -6047,7 +6106,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -6073,7 +6132,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -6099,7 +6158,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -6125,7 +6184,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C123" s="1">
         <v>6</v>
@@ -6151,7 +6210,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C124" s="1">
         <v>6</v>
@@ -6177,7 +6236,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C125" s="1">
         <v>6</v>
@@ -6203,7 +6262,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C126" s="1">
         <v>6</v>
@@ -6229,7 +6288,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C127" s="1">
         <v>6</v>
@@ -6255,7 +6314,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C128" s="1">
         <v>6</v>
@@ -6281,7 +6340,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C129" s="1">
         <v>6</v>
@@ -6307,7 +6366,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C130" s="1">
         <v>6</v>
@@ -6333,7 +6392,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C131" s="1">
         <v>6</v>
@@ -6359,7 +6418,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C132" s="1">
         <v>6</v>
@@ -6385,7 +6444,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C133" s="1">
         <v>6</v>
@@ -6411,7 +6470,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C134" s="1">
         <v>6</v>
@@ -6437,7 +6496,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C135" s="1">
         <v>6</v>
@@ -6463,7 +6522,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="2">
-        <v>0.007100339513272047</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C136" s="1">
         <v>6</v>
@@ -6489,16 +6548,16 @@
         <v>135</v>
       </c>
       <c r="B137" s="2">
-        <v>0.004733559675514698</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C137" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D137" s="1">
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -6515,16 +6574,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="2">
-        <v>0.004733559675514698</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C138" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6541,16 +6600,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="2">
-        <v>0.004733559675514698</v>
+        <v>0.006614850368350744</v>
       </c>
       <c r="C139" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D139" s="1">
         <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -6567,16 +6626,16 @@
         <v>138</v>
       </c>
       <c r="B140" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.004409900400787592</v>
       </c>
       <c r="C140" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -6593,16 +6652,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.004409900400787592</v>
       </c>
       <c r="C141" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -6619,16 +6678,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.004409900400787592</v>
       </c>
       <c r="C142" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -6645,7 +6704,7 @@
         <v>141</v>
       </c>
       <c r="B143" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.002204950200393796</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -6671,7 +6730,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.002204950200393796</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -6697,7 +6756,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.002204950200393796</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -6723,7 +6782,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="2">
-        <v>0.002366779837757349</v>
+        <v>0.002204950200393796</v>
       </c>
       <c r="C146" s="1">
         <v>2</v>
@@ -6745,34 +6804,112 @@
       </c>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" t="s">
+      <c r="A147" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2">
+        <v>0.002204950200393796</v>
+      </c>
+      <c r="C147" s="1">
+        <v>2</v>
+      </c>
+      <c r="D147" s="1">
+        <v>0</v>
+      </c>
+      <c r="E147" s="1">
+        <v>2</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B147">
+      <c r="B148" s="2">
+        <v>0.002204950200393796</v>
+      </c>
+      <c r="C148" s="1">
+        <v>2</v>
+      </c>
+      <c r="D148" s="1">
+        <v>0</v>
+      </c>
+      <c r="E148" s="1">
+        <v>2</v>
+      </c>
+      <c r="F148" s="1">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2">
+        <v>0.002204950200393796</v>
+      </c>
+      <c r="C149" s="1">
+        <v>2</v>
+      </c>
+      <c r="D149" s="1">
+        <v>0</v>
+      </c>
+      <c r="E149" s="1">
+        <v>2</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C147">
+      <c r="C150">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D147">
+      <c r="D150">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E147">
+      <c r="E150">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F147">
+      <c r="F150">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G147">
+      <c r="G150">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H147">
+      <c r="H150">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
+++ b/EXAMPLE/Projects/MDK-ARM/atk_f407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="159">
   <si>
     <t>atk_f407</t>
   </si>
@@ -26,6 +26,9 @@
     <t>malloc.o</t>
   </si>
   <si>
+    <t>ai_task.o</t>
+  </si>
+  <si>
     <t>norflash.o</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
     <t>dht11.o</t>
   </si>
   <si>
+    <t>sram.o</t>
+  </si>
+  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -102,9 +108,6 @@
   </si>
   <si>
     <t>delay.o</t>
-  </si>
-  <si>
-    <t>ai_task.o</t>
   </si>
   <si>
     <t>usbd_ctlreq.o</t>
@@ -578,9 +581,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$150</c:f>
+              <c:f>ram_percent!$A$3:$A$151</c:f>
               <c:strCache>
-                <c:ptCount val="148"/>
+                <c:ptCount val="149"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -588,90 +591,93 @@
                   <c:v>malloc.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>ai_task.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>norflash.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>error_log_task.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>fattester.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>sdio_sdcard.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>c_w.l</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>lcd.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>dht11.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
+                  <c:v>sram.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>dht11_task.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>exfuns.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>ff.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>freertos_start.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
-                  <c:v>ai_task.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>usbd_ctlreq.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="148">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -679,101 +685,104 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$150</c:f>
+              <c:f>ram_percent!$B$3:$B$151</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="148"/>
+                <c:ptCount val="149"/>
                 <c:pt idx="0">
-                  <c:v>52.70410919189453</c:v>
+                  <c:v>48.41278457641602</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.34636306762695</c:v>
+                  <c:v>34.30551147460938</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.485592842102051</c:v>
+                  <c:v>8.067484855651856</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.106932044029236</c:v>
+                  <c:v>4.120362758636475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.097287893295288</c:v>
+                  <c:v>1.016802310943604</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8615424036979675</c:v>
+                  <c:v>1.007943511009216</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6686598062515259</c:v>
+                  <c:v>0.7913931012153626</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.411482959985733</c:v>
+                  <c:v>0.6142155528068543</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2978965044021606</c:v>
+                  <c:v>0.3779788017272949</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1757375150918961</c:v>
+                  <c:v>0.273640900850296</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1028707399964333</c:v>
+                  <c:v>0.1614284515380859</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1028707399964333</c:v>
+                  <c:v>0.09449470043182373</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1028707399964333</c:v>
+                  <c:v>0.09449470043182373</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1007275953888893</c:v>
+                  <c:v>0.09449470043182373</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.09858445823192596</c:v>
+                  <c:v>0.09252606332302094</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.09644131362438202</c:v>
+                  <c:v>0.09055741876363754</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.06858049333095551</c:v>
+                  <c:v>0.08858878165483475</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.06429421156644821</c:v>
+                  <c:v>0.07874558120965958</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.02571768499910832</c:v>
+                  <c:v>0.06299646943807602</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.01714512333273888</c:v>
+                  <c:v>0.05905918776988983</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.01285884249955416</c:v>
+                  <c:v>0.02362367510795593</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.01071570161730051</c:v>
+                  <c:v>0.01574911735951901</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.009644131176173687</c:v>
+                  <c:v>0.01181183755397797</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.008572561666369438</c:v>
+                  <c:v>0.009843197651207447</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.004286280833184719</c:v>
+                  <c:v>0.008858878165483475</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.004286280833184719</c:v>
+                  <c:v>0.007874558679759502</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.004286280833184719</c:v>
+                  <c:v>0.003937279339879751</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.004286280833184719</c:v>
+                  <c:v>0.003937279339879751</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.004286280833184719</c:v>
+                  <c:v>0.003937279339879751</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.00107157020829618</c:v>
-                </c:pt>
-                <c:pt idx="147">
+                  <c:v>0.003937279339879751</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0009843198349699378</c:v>
+                </c:pt>
+                <c:pt idx="148">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -841,9 +850,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$150</c:f>
+              <c:f>flash_percent!$A$3:$A$151</c:f>
               <c:strCache>
-                <c:ptCount val="148"/>
+                <c:ptCount val="149"/>
                 <c:pt idx="0">
                   <c:v>ff.o</c:v>
                 </c:pt>
@@ -935,357 +944,360 @@
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>sram.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>usbd_conf.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>startup_stm32f407xx.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>dht11.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>diskio.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>can.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>__printf_flags_ss_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>bigflt0.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>error_log_task.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>lc_ctype_c.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>exfuns.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>stm32f4xx_ll_fsmc.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>sys.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>_printf_wctomb.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>_printf_hex_int_ll_ptr.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>delay.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>dnaninf.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>led.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>lludiv10.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>dht11_task.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>usbd_ioreq.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>strcmpv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>_printf_fp_infnan.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>_printf_longlong_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>_printf_dec.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
+                  <c:v>ai_task.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>can_task.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="65">
                   <c:v>_printf_oct_int_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
-                  <c:v>ai_task.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>led_task.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>rt_memcpy_w.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>freertos_start.o</c:v>
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="69">
+                  <c:v>freertos_start.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>fattester.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>dfixu.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>stm32f4xx_hal_sram.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>_printf_str.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>_printf_pad.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>lc_numeric_c.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>rt_memclr.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>_wcrtomb.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>vsnprintf.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>fpclassify.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>_printf_char_common.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>_printf_wchar.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>_printf_char.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>_printf_charcount.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>dflt_clz.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>_printf_truncate.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>_printf_char_file.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>ffsystem.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>__2printf.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>strchr.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="101">
                   <c:v>rt_ctype_table.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="102">
                   <c:v>aeabi_memset.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="103">
                   <c:v>_snputc.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="104">
                   <c:v>__printf_wp.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="105">
                   <c:v>dretinf.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="106">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="107">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="108">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="109">
                   <c:v>_sputc.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="110">
                   <c:v>_printf_ll.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="111">
                   <c:v>_printf_l.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="112">
                   <c:v>rt_locale_intlibspace.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="113">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="114">
                   <c:v>ferror.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="115">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="116">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="117">
                   <c:v>_printf_x.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="118">
                   <c:v>_printf_u.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="119">
                   <c:v>_printf_s.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="120">
                   <c:v>_printf_p.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="121">
                   <c:v>_printf_o.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="122">
                   <c:v>_printf_n.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="123">
                   <c:v>_printf_ls.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="124">
                   <c:v>_printf_llx.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="125">
                   <c:v>_printf_llu.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="126">
                   <c:v>_printf_llo.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="127">
                   <c:v>_printf_lli.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="128">
                   <c:v>_printf_lld.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="129">
                   <c:v>_printf_lc.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="130">
                   <c:v>_printf_i.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="131">
                   <c:v>_printf_g.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="132">
                   <c:v>_printf_f.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="133">
                   <c:v>_printf_e.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="134">
                   <c:v>_printf_d.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="135">
                   <c:v>_printf_c.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="136">
                   <c:v>_printf_a.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="137">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="138">
                   <c:v>printf2.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="139">
                   <c:v>printf1.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="140">
                   <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="141">
                   <c:v>use_no_semi_2.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="142">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="143">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="144">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="145">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="146">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="147">
                   <c:v>stm32f4xx_hal_pcd_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="148">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1293,452 +1305,455 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$150</c:f>
+              <c:f>flash_percent!$B$3:$B$151</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="148"/>
+                <c:ptCount val="149"/>
                 <c:pt idx="0">
-                  <c:v>17.91522026062012</c:v>
+                  <c:v>17.81153678894043</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.60999965667725</c:v>
+                  <c:v>14.52544593811035</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.909100532531738</c:v>
+                  <c:v>8.857540130615234</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.403285503387451</c:v>
+                  <c:v>4.377801895141602</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.556584596633911</c:v>
+                  <c:v>3.536001205444336</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.086930274963379</c:v>
+                  <c:v>3.069064855575562</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.941403388977051</c:v>
+                  <c:v>2.924380540847778</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.815721273422241</c:v>
+                  <c:v>2.799425601959229</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.337247133255005</c:v>
+                  <c:v>2.323720693588257</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.32622241973877</c:v>
+                  <c:v>2.312759637832642</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.267791271209717</c:v>
+                  <c:v>2.254666566848755</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.134391784667969</c:v>
+                  <c:v>2.122039079666138</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.006504535675049</c:v>
+                  <c:v>1.994892239570618</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.73529577255249</c:v>
+                  <c:v>1.725252866744995</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.71324622631073</c:v>
+                  <c:v>1.703330993652344</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.631663084030151</c:v>
+                  <c:v>1.622220039367676</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.397938370704651</c:v>
+                  <c:v>1.389847993850708</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.367069125175476</c:v>
+                  <c:v>1.35915732383728</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.351634383201599</c:v>
+                  <c:v>1.343811988830566</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.294305682182312</c:v>
+                  <c:v>1.286815047264099</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.214927554130554</c:v>
+                  <c:v>1.207896232604981</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.162008762359619</c:v>
+                  <c:v>1.155283689498901</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9789978265762329</c:v>
+                  <c:v>0.9733320474624634</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.9701780676841736</c:v>
+                  <c:v>0.964563250541687</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8841850161552429</c:v>
+                  <c:v>0.8790678977966309</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7210186719894409</c:v>
+                  <c:v>0.7168458700180054</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6923543214797974</c:v>
+                  <c:v>0.6883473992347717</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6350256204605103</c:v>
+                  <c:v>0.6313505172729492</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.6195909976959229</c:v>
+                  <c:v>0.6160051822662354</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5821068286895752</c:v>
+                  <c:v>0.5787379741668701</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5611597895622253</c:v>
+                  <c:v>0.5612004399299622</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.515958309173584</c:v>
+                  <c:v>0.5579121708869934</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4872939884662628</c:v>
+                  <c:v>0.5129722952842712</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4740642607212067</c:v>
+                  <c:v>0.4844738245010376</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4586296379566193</c:v>
+                  <c:v>0.4713206887245178</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4509122967720032</c:v>
+                  <c:v>0.455975353717804</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4145306348800659</c:v>
+                  <c:v>0.448302686214447</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3792514204978943</c:v>
+                  <c:v>0.4121315777301788</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3748415112495422</c:v>
+                  <c:v>0.3770565390586853</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3549969792366028</c:v>
+                  <c:v>0.3726721704006195</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3483821153640747</c:v>
+                  <c:v>0.3529424667358398</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2888484597206116</c:v>
+                  <c:v>0.34636589884758</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.262389063835144</c:v>
+                  <c:v>0.287176787853241</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.255774199962616</c:v>
+                  <c:v>0.2608705163002014</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2458519339561462</c:v>
+                  <c:v>0.2542939484119415</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2249049097299576</c:v>
+                  <c:v>0.2444290965795517</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2204950153827667</c:v>
+                  <c:v>0.2236033082008362</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2160851061344147</c:v>
+                  <c:v>0.2192189246416092</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.207265317440033</c:v>
+                  <c:v>0.2148345410823822</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.196240559220314</c:v>
+                  <c:v>0.2060657888650894</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.194035604596138</c:v>
+                  <c:v>0.1951048374176025</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1719861030578613</c:v>
+                  <c:v>0.1929126530885696</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1675762087106705</c:v>
+                  <c:v>0.1709907650947571</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1631663143634796</c:v>
+                  <c:v>0.1666063815355301</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1521415561437607</c:v>
+                  <c:v>0.1622219979763031</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1521415561437607</c:v>
+                  <c:v>0.1512610614299774</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1499366015195847</c:v>
+                  <c:v>0.1512610614299774</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1477316617965698</c:v>
+                  <c:v>0.1490688621997833</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1411168128252029</c:v>
+                  <c:v>0.1468766778707504</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1411168128252029</c:v>
+                  <c:v>0.1403001099824905</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1367069035768509</c:v>
+                  <c:v>0.1403001099824905</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.13229700922966</c:v>
+                  <c:v>0.1359157264232636</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.127887099981308</c:v>
+                  <c:v>0.1315313577651978</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1234772056341171</c:v>
+                  <c:v>0.1315313577651978</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1190673038363457</c:v>
+                  <c:v>0.1271469742059708</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.1146574094891548</c:v>
+                  <c:v>0.1227625980973244</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.1102475076913834</c:v>
+                  <c:v>0.113993838429451</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.1102475076913834</c:v>
+                  <c:v>0.1096094623208046</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.1058376058936119</c:v>
+                  <c:v>0.1096094623208046</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.1058376058936119</c:v>
+                  <c:v>0.1096094623208046</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.09922275692224503</c:v>
+                  <c:v>0.1052250862121582</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.097017802298069</c:v>
+                  <c:v>0.09864851832389832</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.097017802298069</c:v>
+                  <c:v>0.09645632654428482</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.09040295332670212</c:v>
+                  <c:v>0.09645632654428482</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.08599305152893066</c:v>
+                  <c:v>0.08987975865602493</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.08599305152893066</c:v>
+                  <c:v>0.08549538254737854</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.08158315718173981</c:v>
+                  <c:v>0.08549538254737854</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.07937820255756378</c:v>
+                  <c:v>0.08111099898815155</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.07496830075979233</c:v>
+                  <c:v>0.07891881465911865</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.07055840641260147</c:v>
+                  <c:v>0.07453443109989166</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.05732870474457741</c:v>
+                  <c:v>0.07015005499124527</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.05732870474457741</c:v>
+                  <c:v>0.05699691921472549</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.05291880294680595</c:v>
+                  <c:v>0.05699691921472549</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.05291880294680595</c:v>
+                  <c:v>0.0526125431060791</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.05291880294680595</c:v>
+                  <c:v>0.0526125431060791</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.05291880294680595</c:v>
+                  <c:v>0.0526125431060791</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.0485089011490345</c:v>
+                  <c:v>0.0526125431060791</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.0485089011490345</c:v>
+                  <c:v>0.04822816327214241</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.04409900307655335</c:v>
+                  <c:v>0.04822816327214241</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.04189405217766762</c:v>
+                  <c:v>0.04384378343820572</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.03968910127878189</c:v>
+                  <c:v>0.04165159538388252</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.03968910127878189</c:v>
+                  <c:v>0.03945940732955933</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.03748415037989616</c:v>
+                  <c:v>0.03945940732955933</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.03527920320630074</c:v>
+                  <c:v>0.03726721554994583</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.03086930140852928</c:v>
+                  <c:v>0.03507502749562264</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.0286643523722887</c:v>
+                  <c:v>0.03069064952433109</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.02645940147340298</c:v>
+                  <c:v>0.02849845960736275</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.02204950153827667</c:v>
+                  <c:v>0.02630627155303955</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.02204950153827667</c:v>
+                  <c:v>0.02192189171910286</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.01984455063939095</c:v>
+                  <c:v>0.02192189171910286</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.01763960160315037</c:v>
+                  <c:v>0.01972970366477966</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.01763960160315037</c:v>
+                  <c:v>0.01753751374781132</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.01763960160315037</c:v>
+                  <c:v>0.01753751374781132</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.01543465070426464</c:v>
+                  <c:v>0.01753751374781132</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.01322970073670149</c:v>
+                  <c:v>0.01534532476216555</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.01322970073670149</c:v>
+                  <c:v>0.01315313577651978</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.01102475076913834</c:v>
+                  <c:v>0.01315313577651978</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.01102475076913834</c:v>
+                  <c:v>0.01096094585955143</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.01102475076913834</c:v>
+                  <c:v>0.01096094585955143</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.01102475076913834</c:v>
+                  <c:v>0.01096094585955143</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.01102475076913834</c:v>
+                  <c:v>0.01096094585955143</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.008819800801575184</c:v>
+                  <c:v>0.01096094585955143</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.008819800801575184</c:v>
+                  <c:v>0.008768756873905659</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.008819800801575184</c:v>
+                  <c:v>0.008768756873905659</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.008819800801575184</c:v>
+                  <c:v>0.008768756873905659</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.008768756873905659</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.006614850368350744</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.004409900400787592</c:v>
+                  <c:v>0.006576567888259888</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.004409900400787592</c:v>
+                  <c:v>0.004384378436952829</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.004409900400787592</c:v>
+                  <c:v>0.004384378436952829</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.004384378436952829</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.002192189218476415</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.002192189218476415</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.002192189218476415</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.002192189218476415</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.002192189218476415</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.002204950200393796</c:v>
+                  <c:v>0.002192189218476415</c:v>
                 </c:pt>
                 <c:pt idx="147">
+                  <c:v>0.002192189218476415</c:v>
+                </c:pt>
+                <c:pt idx="148">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1843,8 +1858,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H150" totalsRowCount="1">
-  <autoFilter ref="A2:H149"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H151" totalsRowCount="1">
+  <autoFilter ref="A2:H150"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1860,8 +1875,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H150" totalsRowCount="1">
-  <autoFilter ref="A2:H149"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H151" totalsRowCount="1">
+  <autoFilter ref="A2:H150"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2161,7 +2176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2174,28 +2189,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2203,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>52.70410919189453</v>
+        <v>48.41278457641602</v>
       </c>
       <c r="C3" s="1">
         <v>49184</v>
@@ -2229,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>37.34636306762695</v>
+        <v>34.30551147460938</v>
       </c>
       <c r="C4" s="1">
         <v>34852</v>
@@ -2255,25 +2270,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>4.485592842102051</v>
+        <v>8.067484855651856</v>
       </c>
       <c r="C5" s="1">
-        <v>4186</v>
+        <v>8196</v>
       </c>
       <c r="D5" s="1">
-        <v>1480</v>
+        <v>120</v>
       </c>
       <c r="E5" s="1">
-        <v>1478</v>
+        <v>116</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1">
-        <v>4184</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2281,25 +2296,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.106932044029236</v>
+        <v>4.120362758636475</v>
       </c>
       <c r="C6" s="1">
-        <v>1033</v>
+        <v>4186</v>
       </c>
       <c r="D6" s="1">
-        <v>509</v>
+        <v>1480</v>
       </c>
       <c r="E6" s="1">
-        <v>508</v>
+        <v>1478</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>1032</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2307,25 +2322,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.097287893295288</v>
+        <v>1.016802310943604</v>
       </c>
       <c r="C7" s="1">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="D7" s="1">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="E7" s="1">
-        <v>76</v>
+        <v>508</v>
       </c>
       <c r="F7" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2333,25 +2348,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.8615424036979675</v>
+        <v>1.007943511009216</v>
       </c>
       <c r="C8" s="1">
-        <v>804</v>
+        <v>1024</v>
       </c>
       <c r="D8" s="1">
-        <v>3994</v>
+        <v>468</v>
       </c>
       <c r="E8" s="1">
-        <v>3930</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G8" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>740</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2359,25 +2374,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.6686598062515259</v>
+        <v>0.7913931012153626</v>
       </c>
       <c r="C9" s="1">
-        <v>624</v>
+        <v>804</v>
       </c>
       <c r="D9" s="1">
-        <v>322</v>
+        <v>3994</v>
       </c>
       <c r="E9" s="1">
-        <v>248</v>
+        <v>3930</v>
       </c>
       <c r="F9" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="H9" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2385,25 +2400,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.411482959985733</v>
+        <v>0.6142155528068543</v>
       </c>
       <c r="C10" s="1">
-        <v>384</v>
+        <v>624</v>
       </c>
       <c r="D10" s="1">
-        <v>96</v>
+        <v>322</v>
       </c>
       <c r="E10" s="1">
-        <v>96</v>
+        <v>248</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1">
-        <v>384</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2411,25 +2426,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2978965044021606</v>
+        <v>0.3779788017272949</v>
       </c>
       <c r="C11" s="1">
-        <v>278</v>
+        <v>384</v>
       </c>
       <c r="D11" s="1">
-        <v>562</v>
+        <v>96</v>
       </c>
       <c r="E11" s="1">
-        <v>552</v>
+        <v>96</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>268</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2437,25 +2452,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1757375150918961</v>
+        <v>0.273640900850296</v>
       </c>
       <c r="C12" s="1">
-        <v>164</v>
+        <v>278</v>
       </c>
       <c r="D12" s="1">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="E12" s="1">
-        <v>628</v>
+        <v>552</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1">
-        <v>164</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2463,25 +2478,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1028707399964333</v>
+        <v>0.1614284515380859</v>
       </c>
       <c r="C13" s="1">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="D13" s="1">
-        <v>8081</v>
+        <v>628</v>
       </c>
       <c r="E13" s="1">
-        <v>7530</v>
+        <v>628</v>
       </c>
       <c r="F13" s="1">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>96</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2489,19 +2504,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1028707399964333</v>
+        <v>0.09449470043182373</v>
       </c>
       <c r="C14" s="1">
         <v>96</v>
       </c>
       <c r="D14" s="1">
-        <v>8</v>
+        <v>8081</v>
       </c>
       <c r="E14" s="1">
-        <v>8</v>
+        <v>7530</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2515,16 +2530,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.1028707399964333</v>
+        <v>0.09449470043182373</v>
       </c>
       <c r="C15" s="1">
         <v>96</v>
       </c>
       <c r="D15" s="1">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2541,16 +2556,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1007275953888893</v>
+        <v>0.09449470043182373</v>
       </c>
       <c r="C16" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1">
-        <v>13252</v>
+        <v>200</v>
       </c>
       <c r="E16" s="1">
-        <v>13252</v>
+        <v>200</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2559,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2567,16 +2582,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.09858445823192596</v>
+        <v>0.09252606332302094</v>
       </c>
       <c r="C17" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1">
-        <v>416</v>
+        <v>13252</v>
       </c>
       <c r="E17" s="1">
-        <v>416</v>
+        <v>13252</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2585,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2593,25 +2608,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.09644131362438202</v>
+        <v>0.09055741876363754</v>
       </c>
       <c r="C18" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D18" s="1">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="E18" s="1">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2619,25 +2634,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.06858049333095551</v>
+        <v>0.08858878165483475</v>
       </c>
       <c r="C19" s="1">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1">
-        <v>1574</v>
+        <v>442</v>
       </c>
       <c r="E19" s="1">
-        <v>1574</v>
+        <v>436</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H19" s="1">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2645,25 +2660,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.06429421156644821</v>
+        <v>0.07874558120965958</v>
       </c>
       <c r="C20" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D20" s="1">
-        <v>1102</v>
+        <v>512</v>
       </c>
       <c r="E20" s="1">
-        <v>1082</v>
+        <v>512</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2671,25 +2686,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.02571768499910832</v>
+        <v>0.06299646943807602</v>
       </c>
       <c r="C21" s="1">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D21" s="1">
-        <v>136</v>
+        <v>1574</v>
       </c>
       <c r="E21" s="1">
-        <v>128</v>
+        <v>1574</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2697,25 +2712,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.01714512333273888</v>
+        <v>0.05905918776988983</v>
       </c>
       <c r="C22" s="1">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1">
-        <v>262</v>
+        <v>1102</v>
       </c>
       <c r="E22" s="1">
-        <v>246</v>
+        <v>1082</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2723,25 +2738,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.01285884249955416</v>
+        <v>0.02362367510795593</v>
       </c>
       <c r="C23" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D23" s="1">
-        <v>1174</v>
+        <v>136</v>
       </c>
       <c r="E23" s="1">
-        <v>1162</v>
+        <v>128</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2749,22 +2764,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.01071570161730051</v>
+        <v>0.01574911735951901</v>
       </c>
       <c r="C24" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1">
-        <v>16250</v>
+        <v>262</v>
       </c>
       <c r="E24" s="1">
-        <v>16036</v>
+        <v>246</v>
       </c>
       <c r="F24" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -2775,22 +2790,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.009644131176173687</v>
+        <v>0.01181183755397797</v>
       </c>
       <c r="C25" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1">
-        <v>223</v>
+        <v>1174</v>
       </c>
       <c r="E25" s="1">
-        <v>214</v>
+        <v>1162</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2801,22 +2816,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.008572561666369438</v>
+        <v>0.009843197651207447</v>
       </c>
       <c r="C26" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1">
-        <v>116</v>
+        <v>16250</v>
       </c>
       <c r="E26" s="1">
-        <v>108</v>
+        <v>16036</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="G26" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -2827,22 +2842,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.004286280833184719</v>
+        <v>0.008858878165483475</v>
       </c>
       <c r="C27" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" s="1">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="E27" s="1">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="F27" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2853,22 +2868,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.004286280833184719</v>
+        <v>0.007874558679759502</v>
       </c>
       <c r="C28" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E28" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -2879,19 +2894,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.004286280833184719</v>
+        <v>0.003937279339879751</v>
       </c>
       <c r="C29" s="1">
         <v>4</v>
       </c>
       <c r="D29" s="1">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E29" s="1">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G29" s="1">
         <v>4</v>
@@ -2905,16 +2920,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.004286280833184719</v>
+        <v>0.003937279339879751</v>
       </c>
       <c r="C30" s="1">
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="E30" s="1">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2931,16 +2946,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.004286280833184719</v>
+        <v>0.003937279339879751</v>
       </c>
       <c r="C31" s="1">
         <v>4</v>
       </c>
       <c r="D31" s="1">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E31" s="1">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2957,56 +2972,82 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.00107157020829618</v>
+        <v>0.003937279339879751</v>
       </c>
       <c r="C32" s="1">
+        <v>4</v>
+      </c>
+      <c r="D32" s="1">
+        <v>176</v>
+      </c>
+      <c r="E32" s="1">
+        <v>172</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.0009843198349699378</v>
+      </c>
+      <c r="C33" s="1">
         <v>1</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>2057</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E33" s="1">
         <v>2056</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>1</v>
       </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
-      <c r="A150" t="s">
-        <v>149</v>
-      </c>
-      <c r="B150">
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+      <c r="B151">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C150">
+      <c r="C151">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D150">
+      <c r="D151">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E150">
+      <c r="E151">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F150">
+      <c r="F151">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G150">
+      <c r="G151">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H150">
+      <c r="H151">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -3022,7 +3063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -3035,36 +3076,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" t="s">
         <v>157</v>
-      </c>
-      <c r="C2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2">
-        <v>17.91522026062012</v>
+        <v>17.81153678894043</v>
       </c>
       <c r="C3" s="1">
         <v>16250</v>
@@ -3087,10 +3128,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>14.60999965667725</v>
+        <v>14.52544593811035</v>
       </c>
       <c r="C4" s="1">
         <v>13252</v>
@@ -3113,10 +3154,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
-        <v>8.909100532531738</v>
+        <v>8.857540130615234</v>
       </c>
       <c r="C5" s="1">
         <v>8081</v>
@@ -3139,10 +3180,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
-        <v>4.403285503387451</v>
+        <v>4.377801895141602</v>
       </c>
       <c r="C6" s="1">
         <v>3994</v>
@@ -3165,10 +3206,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2">
-        <v>3.556584596633911</v>
+        <v>3.536001205444336</v>
       </c>
       <c r="C7" s="1">
         <v>3226</v>
@@ -3191,10 +3232,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2">
-        <v>3.086930274963379</v>
+        <v>3.069064855575562</v>
       </c>
       <c r="C8" s="1">
         <v>2800</v>
@@ -3217,10 +3258,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2">
-        <v>2.941403388977051</v>
+        <v>2.924380540847778</v>
       </c>
       <c r="C9" s="1">
         <v>2668</v>
@@ -3243,10 +3284,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2">
-        <v>2.815721273422241</v>
+        <v>2.799425601959229</v>
       </c>
       <c r="C10" s="1">
         <v>2554</v>
@@ -3269,10 +3310,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2">
-        <v>2.337247133255005</v>
+        <v>2.323720693588257</v>
       </c>
       <c r="C11" s="1">
         <v>2120</v>
@@ -3295,10 +3336,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2">
-        <v>2.32622241973877</v>
+        <v>2.312759637832642</v>
       </c>
       <c r="C12" s="1">
         <v>2110</v>
@@ -3321,10 +3362,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2">
-        <v>2.267791271209717</v>
+        <v>2.254666566848755</v>
       </c>
       <c r="C13" s="1">
         <v>2057</v>
@@ -3347,10 +3388,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2">
-        <v>2.134391784667969</v>
+        <v>2.122039079666138</v>
       </c>
       <c r="C14" s="1">
         <v>1936</v>
@@ -3373,10 +3414,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2">
-        <v>2.006504535675049</v>
+        <v>1.994892239570618</v>
       </c>
       <c r="C15" s="1">
         <v>1820</v>
@@ -3399,10 +3440,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2">
-        <v>1.73529577255249</v>
+        <v>1.725252866744995</v>
       </c>
       <c r="C16" s="1">
         <v>1574</v>
@@ -3425,10 +3466,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2">
-        <v>1.71324622631073</v>
+        <v>1.703330993652344</v>
       </c>
       <c r="C17" s="1">
         <v>1554</v>
@@ -3451,10 +3492,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>1.631663084030151</v>
+        <v>1.622220039367676</v>
       </c>
       <c r="C18" s="1">
         <v>1480</v>
@@ -3477,10 +3518,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>1.397938370704651</v>
+        <v>1.389847993850708</v>
       </c>
       <c r="C19" s="1">
         <v>1268</v>
@@ -3503,10 +3544,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2">
-        <v>1.367069125175476</v>
+        <v>1.35915732383728</v>
       </c>
       <c r="C20" s="1">
         <v>1240</v>
@@ -3529,10 +3570,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>1.351634383201599</v>
+        <v>1.343811988830566</v>
       </c>
       <c r="C21" s="1">
         <v>1226</v>
@@ -3555,10 +3596,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2">
-        <v>1.294305682182312</v>
+        <v>1.286815047264099</v>
       </c>
       <c r="C22" s="1">
         <v>1174</v>
@@ -3581,10 +3622,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2">
-        <v>1.214927554130554</v>
+        <v>1.207896232604981</v>
       </c>
       <c r="C23" s="1">
         <v>1102</v>
@@ -3607,10 +3648,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2">
-        <v>1.162008762359619</v>
+        <v>1.155283689498901</v>
       </c>
       <c r="C24" s="1">
         <v>1054</v>
@@ -3633,10 +3674,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9789978265762329</v>
+        <v>0.9733320474624634</v>
       </c>
       <c r="C25" s="1">
         <v>888</v>
@@ -3662,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>0.9701780676841736</v>
+        <v>0.964563250541687</v>
       </c>
       <c r="C26" s="1">
         <v>880</v>
@@ -3685,10 +3726,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" s="2">
-        <v>0.8841850161552429</v>
+        <v>0.8790678977966309</v>
       </c>
       <c r="C27" s="1">
         <v>802</v>
@@ -3711,10 +3752,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7210186719894409</v>
+        <v>0.7168458700180054</v>
       </c>
       <c r="C28" s="1">
         <v>654</v>
@@ -3737,10 +3778,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6923543214797974</v>
+        <v>0.6883473992347717</v>
       </c>
       <c r="C29" s="1">
         <v>628</v>
@@ -3766,7 +3807,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6350256204605103</v>
+        <v>0.6313505172729492</v>
       </c>
       <c r="C30" s="1">
         <v>576</v>
@@ -3789,10 +3830,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2">
-        <v>0.6195909976959229</v>
+        <v>0.6160051822662354</v>
       </c>
       <c r="C31" s="1">
         <v>562</v>
@@ -3815,10 +3856,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5821068286895752</v>
+        <v>0.5787379741668701</v>
       </c>
       <c r="C32" s="1">
         <v>528</v>
@@ -3841,28 +3882,28 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5611597895622253</v>
+        <v>0.5612004399299622</v>
       </c>
       <c r="C33" s="1">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D33" s="1">
-        <v>1033</v>
+        <v>80</v>
       </c>
       <c r="E33" s="1">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>1032</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3870,94 +3911,94 @@
         <v>5</v>
       </c>
       <c r="B34" s="2">
-        <v>0.515958309173584</v>
+        <v>0.5579121708869934</v>
       </c>
       <c r="C34" s="1">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="D34" s="1">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="E34" s="1">
-        <v>76</v>
+        <v>508</v>
       </c>
       <c r="F34" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4872939884662628</v>
+        <v>0.5129722952842712</v>
       </c>
       <c r="C35" s="1">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="D35" s="1">
-        <v>90</v>
+        <v>1024</v>
       </c>
       <c r="E35" s="1">
-        <v>436</v>
+        <v>76</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G35" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>84</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4740642607212067</v>
+        <v>0.4844738245010376</v>
       </c>
       <c r="C36" s="1">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E36" s="1">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4586296379566193</v>
+        <v>0.4713206887245178</v>
       </c>
       <c r="C37" s="1">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D37" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3966,33 +4007,33 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4509122967720032</v>
+        <v>0.455975353717804</v>
       </c>
       <c r="C38" s="1">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E38" s="1">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="F38" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4000,19 +4041,19 @@
         <v>50</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4145306348800659</v>
+        <v>0.448302686214447</v>
       </c>
       <c r="C39" s="1">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>228</v>
+        <v>392</v>
       </c>
       <c r="F39" s="1">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -4026,19 +4067,19 @@
         <v>51</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3792514204978943</v>
+        <v>0.4121315777301788</v>
       </c>
       <c r="C40" s="1">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -4052,16 +4093,16 @@
         <v>52</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3748415112495422</v>
+        <v>0.3770565390586853</v>
       </c>
       <c r="C41" s="1">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -4075,77 +4116,77 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3549969792366028</v>
+        <v>0.3726721704006195</v>
       </c>
       <c r="C42" s="1">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D42" s="1">
-        <v>624</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="F42" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3483821153640747</v>
+        <v>0.3529424667358398</v>
       </c>
       <c r="C43" s="1">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="E43" s="1">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="F43" s="1">
-        <v>272</v>
+        <v>50</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2888484597206116</v>
+        <v>0.34636589884758</v>
       </c>
       <c r="C44" s="1">
-        <v>262</v>
+        <v>316</v>
       </c>
       <c r="D44" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>246</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G44" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4153,25 +4194,25 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B45" s="2">
-        <v>0.262389063835144</v>
+        <v>0.287176787853241</v>
       </c>
       <c r="C45" s="1">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E45" s="1">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -4182,16 +4223,16 @@
         <v>55</v>
       </c>
       <c r="B46" s="2">
-        <v>0.255774199962616</v>
+        <v>0.2608705163002014</v>
       </c>
       <c r="C46" s="1">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -4205,25 +4246,25 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2458519339561462</v>
+        <v>0.2542939484119415</v>
       </c>
       <c r="C47" s="1">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D47" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -4231,25 +4272,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2249049097299576</v>
+        <v>0.2444290965795517</v>
       </c>
       <c r="C48" s="1">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E48" s="1">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -4257,19 +4298,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2204950153827667</v>
+        <v>0.2236033082008362</v>
       </c>
       <c r="C49" s="1">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D49" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -4278,33 +4319,33 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2160851061344147</v>
+        <v>0.2192189246416092</v>
       </c>
       <c r="C50" s="1">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E50" s="1">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F50" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -4312,19 +4353,19 @@
         <v>58</v>
       </c>
       <c r="B51" s="2">
-        <v>0.207265317440033</v>
+        <v>0.2148345410823822</v>
       </c>
       <c r="C51" s="1">
+        <v>196</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
         <v>188</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
-        <v>148</v>
-      </c>
       <c r="F51" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -4338,19 +4379,19 @@
         <v>59</v>
       </c>
       <c r="B52" s="2">
-        <v>0.196240559220314</v>
+        <v>0.2060657888650894</v>
       </c>
       <c r="C52" s="1">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="F52" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -4361,25 +4402,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="B53" s="2">
-        <v>0.194035604596138</v>
+        <v>0.1951048374176025</v>
       </c>
       <c r="C53" s="1">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -4387,25 +4428,25 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1719861030578613</v>
+        <v>0.1929126530885696</v>
       </c>
       <c r="C54" s="1">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -4416,16 +4457,16 @@
         <v>61</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1675762087106705</v>
+        <v>0.1709907650947571</v>
       </c>
       <c r="C55" s="1">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -4442,16 +4483,16 @@
         <v>62</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1631663143634796</v>
+        <v>0.1666063815355301</v>
       </c>
       <c r="C56" s="1">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -4468,16 +4509,16 @@
         <v>63</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1521415561437607</v>
+        <v>0.1622219979763031</v>
       </c>
       <c r="C57" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4494,7 +4535,7 @@
         <v>64</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1521415561437607</v>
+        <v>0.1512610614299774</v>
       </c>
       <c r="C58" s="1">
         <v>138</v>
@@ -4517,54 +4558,54 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1499366015195847</v>
+        <v>0.1512610614299774</v>
       </c>
       <c r="C59" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D59" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1477316617965698</v>
+        <v>0.1490688621997833</v>
       </c>
       <c r="C60" s="1">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E60" s="1">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -4572,16 +4613,16 @@
         <v>66</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1411168128252029</v>
+        <v>0.1468766778707504</v>
       </c>
       <c r="C61" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4598,7 +4639,7 @@
         <v>67</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1411168128252029</v>
+        <v>0.1403001099824905</v>
       </c>
       <c r="C62" s="1">
         <v>128</v>
@@ -4624,16 +4665,16 @@
         <v>68</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1367069035768509</v>
+        <v>0.1403001099824905</v>
       </c>
       <c r="C63" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -4650,16 +4691,16 @@
         <v>69</v>
       </c>
       <c r="B64" s="2">
-        <v>0.13229700922966</v>
+        <v>0.1359157264232636</v>
       </c>
       <c r="C64" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -4673,25 +4714,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B65" s="2">
-        <v>0.127887099981308</v>
+        <v>0.1315313577651978</v>
       </c>
       <c r="C65" s="1">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D65" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -4699,51 +4740,51 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="B66" s="2">
-        <v>0.1234772056341171</v>
+        <v>0.1315313577651978</v>
       </c>
       <c r="C66" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D66" s="1">
-        <v>0</v>
+        <v>8196</v>
       </c>
       <c r="E66" s="1">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B67" s="2">
-        <v>0.1190673038363457</v>
+        <v>0.1271469742059708</v>
       </c>
       <c r="C67" s="1">
+        <v>116</v>
+      </c>
+      <c r="D67" s="1">
+        <v>8</v>
+      </c>
+      <c r="E67" s="1">
         <v>108</v>
       </c>
-      <c r="D67" s="1">
-        <v>4</v>
-      </c>
-      <c r="E67" s="1">
-        <v>104</v>
-      </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -4751,25 +4792,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B68" s="2">
-        <v>0.1146574094891548</v>
+        <v>0.1227625980973244</v>
       </c>
       <c r="C68" s="1">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -4777,16 +4818,16 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B69" s="2">
-        <v>0.1102475076913834</v>
+        <v>0.113993838429451</v>
       </c>
       <c r="C69" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E69" s="1">
         <v>100</v>
@@ -4795,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -4803,25 +4844,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B70" s="2">
-        <v>0.1102475076913834</v>
+        <v>0.1096094623208046</v>
       </c>
       <c r="C70" s="1">
         <v>100</v>
       </c>
       <c r="D70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -4829,19 +4870,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71" s="2">
-        <v>0.1058376058936119</v>
+        <v>0.1096094623208046</v>
       </c>
       <c r="C71" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4855,16 +4896,16 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B72" s="2">
-        <v>0.1058376058936119</v>
+        <v>0.1096094623208046</v>
       </c>
       <c r="C72" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D72" s="1">
-        <v>384</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
         <v>96</v>
@@ -4873,27 +4914,27 @@
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H72" s="1">
-        <v>384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="B73" s="2">
-        <v>0.09922275692224503</v>
+        <v>0.1052250862121582</v>
       </c>
       <c r="C73" s="1">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="E73" s="1">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4902,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -4910,16 +4951,16 @@
         <v>74</v>
       </c>
       <c r="B74" s="2">
-        <v>0.097017802298069</v>
+        <v>0.09864851832389832</v>
       </c>
       <c r="C74" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4936,7 +4977,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="2">
-        <v>0.097017802298069</v>
+        <v>0.09645632654428482</v>
       </c>
       <c r="C75" s="1">
         <v>88</v>
@@ -4962,16 +5003,16 @@
         <v>76</v>
       </c>
       <c r="B76" s="2">
-        <v>0.09040295332670212</v>
+        <v>0.09645632654428482</v>
       </c>
       <c r="C76" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4988,16 +5029,16 @@
         <v>77</v>
       </c>
       <c r="B77" s="2">
-        <v>0.08599305152893066</v>
+        <v>0.08987975865602493</v>
       </c>
       <c r="C77" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -5014,7 +5055,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="2">
-        <v>0.08599305152893066</v>
+        <v>0.08549538254737854</v>
       </c>
       <c r="C78" s="1">
         <v>78</v>
@@ -5040,16 +5081,16 @@
         <v>79</v>
       </c>
       <c r="B79" s="2">
-        <v>0.08158315718173981</v>
+        <v>0.08549538254737854</v>
       </c>
       <c r="C79" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -5066,19 +5107,19 @@
         <v>80</v>
       </c>
       <c r="B80" s="2">
-        <v>0.07937820255756378</v>
+        <v>0.08111099898815155</v>
       </c>
       <c r="C80" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F80" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
@@ -5092,19 +5133,19 @@
         <v>81</v>
       </c>
       <c r="B81" s="2">
-        <v>0.07496830075979233</v>
+        <v>0.07891881465911865</v>
       </c>
       <c r="C81" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
@@ -5118,16 +5159,16 @@
         <v>82</v>
       </c>
       <c r="B82" s="2">
-        <v>0.07055840641260147</v>
+        <v>0.07453443109989166</v>
       </c>
       <c r="C82" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -5144,16 +5185,16 @@
         <v>83</v>
       </c>
       <c r="B83" s="2">
-        <v>0.05732870474457741</v>
+        <v>0.07015005499124527</v>
       </c>
       <c r="C83" s="1">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -5170,7 +5211,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="2">
-        <v>0.05732870474457741</v>
+        <v>0.05699691921472549</v>
       </c>
       <c r="C84" s="1">
         <v>52</v>
@@ -5196,16 +5237,16 @@
         <v>85</v>
       </c>
       <c r="B85" s="2">
-        <v>0.05291880294680595</v>
+        <v>0.05699691921472549</v>
       </c>
       <c r="C85" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -5222,7 +5263,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="2">
-        <v>0.05291880294680595</v>
+        <v>0.0526125431060791</v>
       </c>
       <c r="C86" s="1">
         <v>48</v>
@@ -5248,7 +5289,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="2">
-        <v>0.05291880294680595</v>
+        <v>0.0526125431060791</v>
       </c>
       <c r="C87" s="1">
         <v>48</v>
@@ -5271,25 +5312,25 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="B88" s="2">
-        <v>0.05291880294680595</v>
+        <v>0.0526125431060791</v>
       </c>
       <c r="C88" s="1">
         <v>48</v>
       </c>
       <c r="D88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F88" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -5297,25 +5338,25 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B89" s="2">
-        <v>0.0485089011490345</v>
+        <v>0.0526125431060791</v>
       </c>
       <c r="C89" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D89" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" s="1">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -5326,7 +5367,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2">
-        <v>0.0485089011490345</v>
+        <v>0.04822816327214241</v>
       </c>
       <c r="C90" s="1">
         <v>44</v>
@@ -5352,16 +5393,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>0.04409900307655335</v>
+        <v>0.04822816327214241</v>
       </c>
       <c r="C91" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5378,16 +5419,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2">
-        <v>0.04189405217766762</v>
+        <v>0.04384378343820572</v>
       </c>
       <c r="C92" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -5404,16 +5445,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>0.03968910127878189</v>
+        <v>0.04165159538388252</v>
       </c>
       <c r="C93" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5430,7 +5471,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>0.03968910127878189</v>
+        <v>0.03945940732955933</v>
       </c>
       <c r="C94" s="1">
         <v>36</v>
@@ -5456,16 +5497,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>0.03748415037989616</v>
+        <v>0.03945940732955933</v>
       </c>
       <c r="C95" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -5482,16 +5523,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>0.03527920320630074</v>
+        <v>0.03726721554994583</v>
       </c>
       <c r="C96" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5508,16 +5549,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>0.03086930140852928</v>
+        <v>0.03507502749562264</v>
       </c>
       <c r="C97" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5534,16 +5575,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>0.0286643523722887</v>
+        <v>0.03069064952433109</v>
       </c>
       <c r="C98" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5560,16 +5601,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="2">
-        <v>0.02645940147340298</v>
+        <v>0.02849845960736275</v>
       </c>
       <c r="C99" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5586,16 +5627,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="2">
-        <v>0.02204950153827667</v>
+        <v>0.02630627155303955</v>
       </c>
       <c r="C100" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5612,7 +5653,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="2">
-        <v>0.02204950153827667</v>
+        <v>0.02192189171910286</v>
       </c>
       <c r="C101" s="1">
         <v>20</v>
@@ -5638,16 +5679,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="2">
-        <v>0.01984455063939095</v>
+        <v>0.02192189171910286</v>
       </c>
       <c r="C102" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5664,16 +5705,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="2">
-        <v>0.01763960160315037</v>
+        <v>0.01972970366477966</v>
       </c>
       <c r="C103" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5690,7 +5731,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2">
-        <v>0.01763960160315037</v>
+        <v>0.01753751374781132</v>
       </c>
       <c r="C104" s="1">
         <v>16</v>
@@ -5716,7 +5757,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="2">
-        <v>0.01763960160315037</v>
+        <v>0.01753751374781132</v>
       </c>
       <c r="C105" s="1">
         <v>16</v>
@@ -5742,16 +5783,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="2">
-        <v>0.01543465070426464</v>
+        <v>0.01753751374781132</v>
       </c>
       <c r="C106" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -5768,16 +5809,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="2">
-        <v>0.01322970073670149</v>
+        <v>0.01534532476216555</v>
       </c>
       <c r="C107" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -5794,7 +5835,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2">
-        <v>0.01322970073670149</v>
+        <v>0.01315313577651978</v>
       </c>
       <c r="C108" s="1">
         <v>12</v>
@@ -5820,16 +5861,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="2">
-        <v>0.01102475076913834</v>
+        <v>0.01315313577651978</v>
       </c>
       <c r="C109" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -5846,7 +5887,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2">
-        <v>0.01102475076913834</v>
+        <v>0.01096094585955143</v>
       </c>
       <c r="C110" s="1">
         <v>10</v>
@@ -5872,7 +5913,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2">
-        <v>0.01102475076913834</v>
+        <v>0.01096094585955143</v>
       </c>
       <c r="C111" s="1">
         <v>10</v>
@@ -5898,7 +5939,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2">
-        <v>0.01102475076913834</v>
+        <v>0.01096094585955143</v>
       </c>
       <c r="C112" s="1">
         <v>10</v>
@@ -5924,7 +5965,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2">
-        <v>0.01102475076913834</v>
+        <v>0.01096094585955143</v>
       </c>
       <c r="C113" s="1">
         <v>10</v>
@@ -5950,16 +5991,16 @@
         <v>113</v>
       </c>
       <c r="B114" s="2">
-        <v>0.008819800801575184</v>
+        <v>0.01096094585955143</v>
       </c>
       <c r="C114" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -5973,16 +6014,16 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2">
-        <v>0.008819800801575184</v>
+        <v>0.008768756873905659</v>
       </c>
       <c r="C115" s="1">
         <v>8</v>
       </c>
       <c r="D115" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E115" s="1">
         <v>8</v>
@@ -5994,21 +6035,21 @@
         <v>0</v>
       </c>
       <c r="H115" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="B116" s="2">
-        <v>0.008819800801575184</v>
+        <v>0.008768756873905659</v>
       </c>
       <c r="C116" s="1">
         <v>8</v>
       </c>
       <c r="D116" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E116" s="1">
         <v>8</v>
@@ -6020,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6028,7 +6069,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2">
-        <v>0.008819800801575184</v>
+        <v>0.008768756873905659</v>
       </c>
       <c r="C117" s="1">
         <v>8</v>
@@ -6054,16 +6095,16 @@
         <v>116</v>
       </c>
       <c r="B118" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.008768756873905659</v>
       </c>
       <c r="C118" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
       </c>
       <c r="E118" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
@@ -6080,7 +6121,7 @@
         <v>117</v>
       </c>
       <c r="B119" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C119" s="1">
         <v>6</v>
@@ -6106,7 +6147,7 @@
         <v>118</v>
       </c>
       <c r="B120" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C120" s="1">
         <v>6</v>
@@ -6132,7 +6173,7 @@
         <v>119</v>
       </c>
       <c r="B121" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
@@ -6158,7 +6199,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -6184,7 +6225,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C123" s="1">
         <v>6</v>
@@ -6210,7 +6251,7 @@
         <v>122</v>
       </c>
       <c r="B124" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C124" s="1">
         <v>6</v>
@@ -6236,7 +6277,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C125" s="1">
         <v>6</v>
@@ -6262,7 +6303,7 @@
         <v>124</v>
       </c>
       <c r="B126" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C126" s="1">
         <v>6</v>
@@ -6288,7 +6329,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C127" s="1">
         <v>6</v>
@@ -6314,7 +6355,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C128" s="1">
         <v>6</v>
@@ -6340,7 +6381,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C129" s="1">
         <v>6</v>
@@ -6366,7 +6407,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C130" s="1">
         <v>6</v>
@@ -6392,7 +6433,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C131" s="1">
         <v>6</v>
@@ -6418,7 +6459,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C132" s="1">
         <v>6</v>
@@ -6444,7 +6485,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C133" s="1">
         <v>6</v>
@@ -6470,7 +6511,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C134" s="1">
         <v>6</v>
@@ -6496,7 +6537,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C135" s="1">
         <v>6</v>
@@ -6522,7 +6563,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C136" s="1">
         <v>6</v>
@@ -6548,7 +6589,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C137" s="1">
         <v>6</v>
@@ -6574,7 +6615,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C138" s="1">
         <v>6</v>
@@ -6600,7 +6641,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="2">
-        <v>0.006614850368350744</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C139" s="1">
         <v>6</v>
@@ -6626,16 +6667,16 @@
         <v>138</v>
       </c>
       <c r="B140" s="2">
-        <v>0.004409900400787592</v>
+        <v>0.006576567888259888</v>
       </c>
       <c r="C140" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -6652,7 +6693,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="2">
-        <v>0.004409900400787592</v>
+        <v>0.004384378436952829</v>
       </c>
       <c r="C141" s="1">
         <v>4</v>
@@ -6678,7 +6719,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="2">
-        <v>0.004409900400787592</v>
+        <v>0.004384378436952829</v>
       </c>
       <c r="C142" s="1">
         <v>4</v>
@@ -6704,16 +6745,16 @@
         <v>141</v>
       </c>
       <c r="B143" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.004384378436952829</v>
       </c>
       <c r="C143" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -6730,7 +6771,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.002192189218476415</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -6756,7 +6797,7 @@
         <v>143</v>
       </c>
       <c r="B145" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.002192189218476415</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -6782,7 +6823,7 @@
         <v>144</v>
       </c>
       <c r="B146" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.002192189218476415</v>
       </c>
       <c r="C146" s="1">
         <v>2</v>
@@ -6808,7 +6849,7 @@
         <v>145</v>
       </c>
       <c r="B147" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.002192189218476415</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -6834,7 +6875,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.002192189218476415</v>
       </c>
       <c r="C148" s="1">
         <v>2</v>
@@ -6860,7 +6901,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="2">
-        <v>0.002204950200393796</v>
+        <v>0.002192189218476415</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
@@ -6882,34 +6923,60 @@
       </c>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" t="s">
-        <v>149</v>
-      </c>
-      <c r="B150">
+      <c r="A150" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2">
+        <v>0.002192189218476415</v>
+      </c>
+      <c r="C150" s="1">
+        <v>2</v>
+      </c>
+      <c r="D150" s="1">
+        <v>0</v>
+      </c>
+      <c r="E150" s="1">
+        <v>2</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+      <c r="B151">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C150">
+      <c r="C151">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D150">
+      <c r="D151">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E150">
+      <c r="E151">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F150">
+      <c r="F151">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G150">
+      <c r="G151">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H150">
+      <c r="H151">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
